--- a/01-artefactos-de-gestao/01.06-avaliacao-interna-do-grupo/m1-grelha-rotacao-papeis-v01.xlsx
+++ b/01-artefactos-de-gestao/01.06-avaliacao-interna-do-grupo/m1-grelha-rotacao-papeis-v01.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ipppt.sharepoint.com/teams/LEI-GrupodeLDS-UTPORTO/Documentos Partilhados/projeto/01-artefactos-de-gestao/01.06-avaliacao-interna-do-grupo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F569A737-370C-4B47-9829-76A920C9C4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="203" documentId="13_ncr:1_{F569A737-370C-4B47-9829-76A920C9C4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1092F603-B15E-487F-AFA0-DDDB335DCADC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="804" windowWidth="19584" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grelha de Rotação de Papéis" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="287">
   <si>
     <t>GRELHA DE ROTAÇÃO DE PAPÉIS</t>
   </si>
@@ -835,13 +835,85 @@
   </si>
   <si>
     <t>Ivan Cristiano Silva Mendes</t>
+  </si>
+  <si>
+    <t>/projeto/01-artefactos-de-gestao/01.04-backlog-de-projeto/m1-s01-sprint-backlog-v01.xlsx</t>
+  </si>
+  <si>
+    <t>/projeto/01-artefactos-de-gestao/01.04-backlog-de-projeto/m1-s01-sprint-backlog-v01.pdf</t>
+  </si>
+  <si>
+    <t>I001</t>
+  </si>
+  <si>
+    <t>I002</t>
+  </si>
+  <si>
+    <t>I003</t>
+  </si>
+  <si>
+    <t>I004</t>
+  </si>
+  <si>
+    <t>I005</t>
+  </si>
+  <si>
+    <t>I006</t>
+  </si>
+  <si>
+    <t>I007</t>
+  </si>
+  <si>
+    <t>I008</t>
+  </si>
+  <si>
+    <t>I009</t>
+  </si>
+  <si>
+    <t>I010</t>
+  </si>
+  <si>
+    <t>Elaborar Proposta de Sistema</t>
+  </si>
+  <si>
+    <t>Elaborar Declaraçao de Âmbito</t>
+  </si>
+  <si>
+    <t>Preparar CCA</t>
+  </si>
+  <si>
+    <t>Elaborar Regulamento Interno</t>
+  </si>
+  <si>
+    <t>Elaborar Plano de Qualidade</t>
+  </si>
+  <si>
+    <t>Elaborar Definition of Ready</t>
+  </si>
+  <si>
+    <t>Elaborar Definition of Done</t>
+  </si>
+  <si>
+    <t>Preparar Grelha de Rotação de Papéis</t>
+  </si>
+  <si>
+    <t>Obter e arquivar homologação PS/DA/CCA</t>
+  </si>
+  <si>
+    <t>Definir Critérios de Qualidade dos Requisitos</t>
+  </si>
+  <si>
+    <t>/projeto/01-artefactos-de-gestao/01.06-avaliacao-interna-do-grupo/m1-s01-mapa-pontuacao-individual-v01.xlsx</t>
+  </si>
+  <si>
+    <t>/projeto/01-artefactos-de-gestao/01.06-avaliacao-interna-do-grupo/m1-s01-mapa-pontuacao-individual-v01.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -850,41 +922,48 @@
       <sz val="9"/>
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF17365D"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -905,6 +984,16 @@
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1156,7 +1245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1212,6 +1301,9 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1233,17 +1325,11 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1277,6 +1363,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1372,7 +1467,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="AtribuicoesIniciaisTable" displayName="AtribuicoesIniciaisTable" ref="A53:K65" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="AtribuicoesIniciaisTable" displayName="AtribuicoesIniciaisTable" ref="A53:K74" totalsRowShown="0">
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Sequência" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Milestone de Entrega" dataDxfId="8"/>
@@ -1391,7 +1486,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TransferenciasRotacaoTable" displayName="TransferenciasRotacaoTable" ref="A158:H159" totalsRowShown="0" headerRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TransferenciasRotacaoTable" displayName="TransferenciasRotacaoTable" ref="A167:H168" totalsRowShown="0" headerRowBorderDxfId="7">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Milestone de Entrega"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Sprint" dataDxfId="6"/>
@@ -1608,64 +1703,65 @@
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="25.3984375" customWidth="1"/>
-    <col min="2" max="9" width="18" customWidth="1"/>
+    <col min="2" max="2" width="23.69921875" customWidth="1"/>
+    <col min="3" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" s="19" t="s">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="20" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="38.1" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="23" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1681,31 +1777,31 @@
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:9" ht="21.9" customHeight="1">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="25" t="s">
+      <c r="I4" s="26" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1713,61 +1809,61 @@
       <c r="A5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="37">
         <v>4</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="40"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="39"/>
     </row>
     <row r="6" spans="1:9" ht="22.8">
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="28"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="42"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="28"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="42"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="40" t="s">
         <v>262</v>
       </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="28"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="42"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1"/>
@@ -1781,31 +1877,31 @@
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:9" ht="21.9" customHeight="1">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="24" t="s">
+      <c r="H10" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="25" t="s">
+      <c r="I10" s="26" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1844,28 +1940,28 @@
         <v>André Filipe Moreira Mesquita</v>
       </c>
       <c r="B12" s="10">
-        <f>IF(A12="","",COUNTIF('Registo da Rotação'!$F$54:$F$153,A12))</f>
-        <v>0</v>
+        <f>IF(A12="","",COUNTIF('Registo da Rotação'!$F$54:$F$162,A12))</f>
+        <v>2</v>
       </c>
       <c r="C12" s="10">
-        <f>IF(A12="","",COUNTIFS('Registo da Rotação'!$F$54:$F$153,A12,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,A12,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(A12="","",COUNTIFS('Registo da Rotação'!$F$54:$F$162,A12,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,A12,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>2</v>
       </c>
       <c r="D12" s="10">
-        <f>IF(A12="","",COUNTIF('Registo da Rotação'!$G$54:$G$153,A12))</f>
-        <v>0</v>
+        <f>IF(A12="","",COUNTIF('Registo da Rotação'!$G$54:$G$162,A12))</f>
+        <v>3</v>
       </c>
       <c r="E12" s="10">
-        <f>IF(A12="","",COUNTIFS('Registo da Rotação'!$G$54:$G$153,A12,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,A12,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(A12="","",COUNTIFS('Registo da Rotação'!$G$54:$G$162,A12,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,A12,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>3</v>
       </c>
       <c r="F12" s="10">
-        <f>IF(A12="","",COUNTIF('Registo da Rotação'!$H$54:$H$153,A12))</f>
-        <v>0</v>
+        <f>IF(A12="","",COUNTIF('Registo da Rotação'!$H$54:$H$162,A12))</f>
+        <v>1</v>
       </c>
       <c r="G12" s="10">
-        <f>IF(A12="","",COUNTIFS('Registo da Rotação'!$H$54:$H$153,A12,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,A12,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(A12="","",COUNTIFS('Registo da Rotação'!$H$54:$H$162,A12,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,A12,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>1</v>
       </c>
       <c r="H12" s="10">
         <f>IF(A12="","",COUNTIF('Registo da Rotação'!$F$6:$F$25,A12))</f>
@@ -1882,36 +1978,36 @@
         <v>Gonçalo Dinis Magalhães Teixeira</v>
       </c>
       <c r="B13" s="10">
-        <f>IF(A13="","",COUNTIF('Registo da Rotação'!$F$54:$F$153,A13))</f>
-        <v>0</v>
+        <f>IF(A13="","",COUNTIF('Registo da Rotação'!$F$54:$F$162,A13))</f>
+        <v>2</v>
       </c>
       <c r="C13" s="10">
-        <f>IF(A13="","",COUNTIFS('Registo da Rotação'!$F$54:$F$153,A13,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,A13,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(A13="","",COUNTIFS('Registo da Rotação'!$F$54:$F$162,A13,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,A13,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>2</v>
       </c>
       <c r="D13" s="10">
-        <f>IF(A13="","",COUNTIF('Registo da Rotação'!$G$54:$G$153,A13))</f>
+        <f>IF(A13="","",COUNTIF('Registo da Rotação'!$G$54:$G$162,A13))</f>
         <v>0</v>
       </c>
       <c r="E13" s="10">
-        <f>IF(A13="","",COUNTIFS('Registo da Rotação'!$G$54:$G$153,A13,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,A13,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(A13="","",COUNTIFS('Registo da Rotação'!$G$54:$G$162,A13,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,A13,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="F13" s="10">
-        <f>IF(A13="","",COUNTIF('Registo da Rotação'!$H$54:$H$153,A13))</f>
-        <v>0</v>
+        <f>IF(A13="","",COUNTIF('Registo da Rotação'!$H$54:$H$162,A13))</f>
+        <v>2</v>
       </c>
       <c r="G13" s="10">
-        <f>IF(A13="","",COUNTIFS('Registo da Rotação'!$H$54:$H$153,A13,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,A13,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(A13="","",COUNTIFS('Registo da Rotação'!$H$54:$H$162,A13,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,A13,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>2</v>
       </c>
       <c r="H13" s="10">
         <f>IF(A13="","",COUNTIF('Registo da Rotação'!$F$6:$F$25,A13))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="10">
         <f>IF(A13="","",COUNTIFS('Registo da Rotação'!$F$6:$F$25,A13,'Registo da Rotação'!$G$6:$G$25,"Sim"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1920,28 +2016,28 @@
         <v>Gonçalo Magalhães Ribeiro</v>
       </c>
       <c r="B14" s="10">
-        <f>IF(A14="","",COUNTIF('Registo da Rotação'!$F$54:$F$153,A14))</f>
-        <v>0</v>
+        <f>IF(A14="","",COUNTIF('Registo da Rotação'!$F$54:$F$162,A14))</f>
+        <v>2</v>
       </c>
       <c r="C14" s="10">
-        <f>IF(A14="","",COUNTIFS('Registo da Rotação'!$F$54:$F$153,A14,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,A14,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(A14="","",COUNTIFS('Registo da Rotação'!$F$54:$F$162,A14,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,A14,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>2</v>
       </c>
       <c r="D14" s="10">
-        <f>IF(A14="","",COUNTIF('Registo da Rotação'!$G$54:$G$153,A14))</f>
-        <v>0</v>
+        <f>IF(A14="","",COUNTIF('Registo da Rotação'!$G$54:$G$162,A14))</f>
+        <v>2</v>
       </c>
       <c r="E14" s="10">
-        <f>IF(A14="","",COUNTIFS('Registo da Rotação'!$G$54:$G$153,A14,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,A14,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(A14="","",COUNTIFS('Registo da Rotação'!$G$54:$G$162,A14,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,A14,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>2</v>
       </c>
       <c r="F14" s="10">
-        <f>IF(A14="","",COUNTIF('Registo da Rotação'!$H$54:$H$153,A14))</f>
-        <v>0</v>
+        <f>IF(A14="","",COUNTIF('Registo da Rotação'!$H$54:$H$162,A14))</f>
+        <v>2</v>
       </c>
       <c r="G14" s="10">
-        <f>IF(A14="","",COUNTIFS('Registo da Rotação'!$H$54:$H$153,A14,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,A14,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(A14="","",COUNTIFS('Registo da Rotação'!$H$54:$H$162,A14,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,A14,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>2</v>
       </c>
       <c r="H14" s="10">
         <f>IF(A14="","",COUNTIF('Registo da Rotação'!$F$6:$F$25,A14))</f>
@@ -1958,28 +2054,28 @@
         <v>Ivan Cristiano Silva Mendes</v>
       </c>
       <c r="B15" s="10">
-        <f>IF(A15="","",COUNTIF('Registo da Rotação'!$F$54:$F$153,A15))</f>
-        <v>0</v>
+        <f>IF(A15="","",COUNTIF('Registo da Rotação'!$F$54:$F$162,A15))</f>
+        <v>4</v>
       </c>
       <c r="C15" s="10">
-        <f>IF(A15="","",COUNTIFS('Registo da Rotação'!$F$54:$F$153,A15,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,A15,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(A15="","",COUNTIFS('Registo da Rotação'!$F$54:$F$162,A15,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,A15,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>4</v>
       </c>
       <c r="D15" s="10">
-        <f>IF(A15="","",COUNTIF('Registo da Rotação'!$G$54:$G$153,A15))</f>
-        <v>0</v>
+        <f>IF(A15="","",COUNTIF('Registo da Rotação'!$G$54:$G$162,A15))</f>
+        <v>5</v>
       </c>
       <c r="E15" s="10">
-        <f>IF(A15="","",COUNTIFS('Registo da Rotação'!$G$54:$G$153,A15,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,A15,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(A15="","",COUNTIFS('Registo da Rotação'!$G$54:$G$162,A15,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,A15,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>5</v>
       </c>
       <c r="F15" s="10">
-        <f>IF(A15="","",COUNTIF('Registo da Rotação'!$H$54:$H$153,A15))</f>
-        <v>0</v>
+        <f>IF(A15="","",COUNTIF('Registo da Rotação'!$H$54:$H$162,A15))</f>
+        <v>5</v>
       </c>
       <c r="G15" s="10">
-        <f>IF(A15="","",COUNTIFS('Registo da Rotação'!$H$54:$H$153,A15,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,A15,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(A15="","",COUNTIFS('Registo da Rotação'!$H$54:$H$162,A15,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,A15,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>5</v>
       </c>
       <c r="H15" s="10">
         <f>IF(A15="","",COUNTIF('Registo da Rotação'!$F$6:$F$25,A15))</f>
@@ -2002,19 +2098,19 @@
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="1:9" ht="21.9" customHeight="1">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="26" t="s">
         <v>19</v>
       </c>
       <c r="F17" s="1"/>
@@ -2049,19 +2145,19 @@
       </c>
       <c r="B19" s="6">
         <f>MIN(C12:C15)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C19" s="6">
         <f>MAX(C12:C15)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D19" s="6">
         <f>C19-B19</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19" s="6" t="str">
         <f>IF(D19=0,"Distribuição igual",IF(D19=1,"Distribuição aproximada","Analisar distribuição"))</f>
-        <v>Distribuição igual</v>
+        <v>Analisar distribuição</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -2078,15 +2174,15 @@
       </c>
       <c r="C20" s="6">
         <f>MAX(E12:E15)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" s="6">
         <f>C20-B20</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E20" s="6" t="str">
         <f>IF(D20=0,"Distribuição igual",IF(D20=1,"Distribuição aproximada","Analisar distribuição"))</f>
-        <v>Distribuição igual</v>
+        <v>Analisar distribuição</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -2099,19 +2195,19 @@
       </c>
       <c r="B21" s="6">
         <f>MIN(G12:G15)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="6">
         <f>MAX(G12:G15)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D21" s="6">
         <f>C21-B21</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E21" s="6" t="str">
         <f>IF(D21=0,"Distribuição igual",IF(D21=1,"Distribuição aproximada","Analisar distribuição"))</f>
-        <v>Distribuição igual</v>
+        <v>Analisar distribuição</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -2128,15 +2224,15 @@
       </c>
       <c r="C22" s="6">
         <f>MAX(I12:I15)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="6">
         <f>C22-B22</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="6" t="str">
         <f>IF(D22=0,"Distribuição igual",IF(D22=1,"Distribuição aproximada","Analisar distribuição"))</f>
-        <v>Distribuição igual</v>
+        <v>Distribuição aproximada</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -2155,25 +2251,25 @@
       <c r="I23" s="1"/>
     </row>
     <row r="24" spans="1:9" ht="21.9" customHeight="1">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="24" t="s">
+      <c r="F24" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="25" t="s">
+      <c r="G24" s="26" t="s">
         <v>29</v>
       </c>
       <c r="H24" s="1"/>
@@ -2214,24 +2310,24 @@
         <v>André Filipe Moreira Mesquita</v>
       </c>
       <c r="C26" s="10">
-        <f>IF(B26="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A26,'Registo da Rotação'!$F$54:$F$153,B26,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A26,'Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,B26,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(B26="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A26,'Registo da Rotação'!$F$54:$F$162,B26,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A26,'Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,B26,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>2</v>
       </c>
       <c r="D26" s="10">
-        <f>IF(B26="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A26,'Registo da Rotação'!$G$54:$G$153,B26,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A26,'Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,B26,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(B26="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A26,'Registo da Rotação'!$G$54:$G$162,B26,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A26,'Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,B26,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>3</v>
       </c>
       <c r="E26" s="10">
-        <f>IF(B26="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A26,'Registo da Rotação'!$H$54:$H$153,B26,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A26,'Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,B26,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(B26="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A26,'Registo da Rotação'!$H$54:$H$162,B26,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A26,'Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,B26,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>1</v>
       </c>
       <c r="F26" s="10">
         <f>IF(B26="","",COUNTIFS('Registo da Rotação'!$A$6:$A$25,A26,'Registo da Rotação'!$F$6:$F$25,B26,'Registo da Rotação'!$G$6:$G$25,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="G26" s="6" t="str">
-        <f>IF(B26="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A26,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A26,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$153,A26)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C26&gt;0,D26&gt;0,E26&gt;0),"Cumprida","Por cumprir")))))</f>
-        <v>Sem sprints concluídos</v>
+        <f>IF(B26="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A26,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A26,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$162,A26)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C26&gt;0,D26&gt;0,E26&gt;0),"Cumprida","Por cumprir")))))</f>
+        <v>Cumprida</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -2246,24 +2342,24 @@
         <v>Gonçalo Dinis Magalhães Teixeira</v>
       </c>
       <c r="C27" s="10">
-        <f>IF(B27="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A27,'Registo da Rotação'!$F$54:$F$153,B27,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A27,'Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,B27,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(B27="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A27,'Registo da Rotação'!$F$54:$F$162,B27,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A27,'Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,B27,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>2</v>
       </c>
       <c r="D27" s="10">
-        <f>IF(B27="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A27,'Registo da Rotação'!$G$54:$G$153,B27,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A27,'Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,B27,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B27="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A27,'Registo da Rotação'!$G$54:$G$162,B27,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A27,'Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,B27,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="E27" s="10">
-        <f>IF(B27="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A27,'Registo da Rotação'!$H$54:$H$153,B27,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A27,'Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,B27,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(B27="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A27,'Registo da Rotação'!$H$54:$H$162,B27,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A27,'Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,B27,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>2</v>
       </c>
       <c r="F27" s="10">
         <f>IF(B27="","",COUNTIFS('Registo da Rotação'!$A$6:$A$25,A27,'Registo da Rotação'!$F$6:$F$25,B27,'Registo da Rotação'!$G$6:$G$25,"Sim"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="6" t="str">
-        <f>IF(B27="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A27,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A27,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$153,A27)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C27&gt;0,D27&gt;0,E27&gt;0),"Cumprida","Por cumprir")))))</f>
-        <v>Sem sprints concluídos</v>
+        <f>IF(B27="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A27,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A27,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$162,A27)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C27&gt;0,D27&gt;0,E27&gt;0),"Cumprida","Por cumprir")))))</f>
+        <v>Por cumprir</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -2278,24 +2374,24 @@
         <v>Gonçalo Magalhães Ribeiro</v>
       </c>
       <c r="C28" s="10">
-        <f>IF(B28="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A28,'Registo da Rotação'!$F$54:$F$153,B28,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A28,'Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,B28,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(B28="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A28,'Registo da Rotação'!$F$54:$F$162,B28,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A28,'Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,B28,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>2</v>
       </c>
       <c r="D28" s="10">
-        <f>IF(B28="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A28,'Registo da Rotação'!$G$54:$G$153,B28,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A28,'Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,B28,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(B28="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A28,'Registo da Rotação'!$G$54:$G$162,B28,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A28,'Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,B28,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>2</v>
       </c>
       <c r="E28" s="10">
-        <f>IF(B28="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A28,'Registo da Rotação'!$H$54:$H$153,B28,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A28,'Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,B28,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(B28="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A28,'Registo da Rotação'!$H$54:$H$162,B28,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A28,'Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,B28,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>2</v>
       </c>
       <c r="F28" s="10">
         <f>IF(B28="","",COUNTIFS('Registo da Rotação'!$A$6:$A$25,A28,'Registo da Rotação'!$F$6:$F$25,B28,'Registo da Rotação'!$G$6:$G$25,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="G28" s="6" t="str">
-        <f>IF(B28="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A28,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A28,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$153,A28)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C28&gt;0,D28&gt;0,E28&gt;0),"Cumprida","Por cumprir")))))</f>
-        <v>Sem sprints concluídos</v>
+        <f>IF(B28="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A28,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A28,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$162,A28)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C28&gt;0,D28&gt;0,E28&gt;0),"Cumprida","Por cumprir")))))</f>
+        <v>Cumprida</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -2310,24 +2406,24 @@
         <v>Ivan Cristiano Silva Mendes</v>
       </c>
       <c r="C29" s="10">
-        <f>IF(B29="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A29,'Registo da Rotação'!$F$54:$F$153,B29,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A29,'Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,B29,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(B29="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A29,'Registo da Rotação'!$F$54:$F$162,B29,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A29,'Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,B29,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>4</v>
       </c>
       <c r="D29" s="10">
-        <f>IF(B29="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A29,'Registo da Rotação'!$G$54:$G$153,B29,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A29,'Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,B29,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(B29="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A29,'Registo da Rotação'!$G$54:$G$162,B29,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A29,'Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,B29,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>5</v>
       </c>
       <c r="E29" s="10">
-        <f>IF(B29="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A29,'Registo da Rotação'!$H$54:$H$153,B29,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A29,'Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,B29,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
-        <v>0</v>
+        <f>IF(B29="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A29,'Registo da Rotação'!$H$54:$H$162,B29,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A29,'Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,B29,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
+        <v>5</v>
       </c>
       <c r="F29" s="10">
         <f>IF(B29="","",COUNTIFS('Registo da Rotação'!$A$6:$A$25,A29,'Registo da Rotação'!$F$6:$F$25,B29,'Registo da Rotação'!$G$6:$G$25,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="G29" s="6" t="str">
-        <f>IF(B29="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A29,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A29,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$153,A29)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C29&gt;0,D29&gt;0,E29&gt;0),"Cumprida","Por cumprir")))))</f>
-        <v>Sem sprints concluídos</v>
+        <f>IF(B29="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A29,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A29,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$162,A29)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C29&gt;0,D29&gt;0,E29&gt;0),"Cumprida","Por cumprir")))))</f>
+        <v>Cumprida</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -2342,15 +2438,15 @@
         <v>André Filipe Moreira Mesquita</v>
       </c>
       <c r="C30" s="10">
-        <f>IF(B30="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A30,'Registo da Rotação'!$F$54:$F$153,B30,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A30,'Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,B30,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B30="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A30,'Registo da Rotação'!$F$54:$F$162,B30,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A30,'Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,B30,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="D30" s="10">
-        <f>IF(B30="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A30,'Registo da Rotação'!$G$54:$G$153,B30,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A30,'Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,B30,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B30="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A30,'Registo da Rotação'!$G$54:$G$162,B30,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A30,'Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,B30,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="E30" s="10">
-        <f>IF(B30="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A30,'Registo da Rotação'!$H$54:$H$153,B30,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A30,'Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,B30,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B30="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A30,'Registo da Rotação'!$H$54:$H$162,B30,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A30,'Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,B30,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="F30" s="10">
@@ -2358,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="6" t="str">
-        <f>IF(B30="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A30,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A30,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$153,A30)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C30&gt;0,D30&gt;0,E30&gt;0),"Cumprida","Por cumprir")))))</f>
+        <f>IF(B30="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A30,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A30,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$162,A30)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C30&gt;0,D30&gt;0,E30&gt;0),"Cumprida","Por cumprir")))))</f>
         <v>Sem sprints concluídos</v>
       </c>
       <c r="H30" s="1"/>
@@ -2374,15 +2470,15 @@
         <v>Gonçalo Dinis Magalhães Teixeira</v>
       </c>
       <c r="C31" s="10">
-        <f>IF(B31="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A31,'Registo da Rotação'!$F$54:$F$153,B31,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A31,'Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,B31,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B31="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A31,'Registo da Rotação'!$F$54:$F$162,B31,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A31,'Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,B31,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="D31" s="10">
-        <f>IF(B31="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A31,'Registo da Rotação'!$G$54:$G$153,B31,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A31,'Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,B31,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B31="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A31,'Registo da Rotação'!$G$54:$G$162,B31,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A31,'Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,B31,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="E31" s="10">
-        <f>IF(B31="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A31,'Registo da Rotação'!$H$54:$H$153,B31,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A31,'Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,B31,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B31="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A31,'Registo da Rotação'!$H$54:$H$162,B31,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A31,'Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,B31,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="F31" s="10">
@@ -2390,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="6" t="str">
-        <f>IF(B31="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A31,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A31,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$153,A31)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C31&gt;0,D31&gt;0,E31&gt;0),"Cumprida","Por cumprir")))))</f>
+        <f>IF(B31="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A31,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A31,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$162,A31)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C31&gt;0,D31&gt;0,E31&gt;0),"Cumprida","Por cumprir")))))</f>
         <v>Sem sprints concluídos</v>
       </c>
       <c r="H31" s="1"/>
@@ -2406,15 +2502,15 @@
         <v>Gonçalo Magalhães Ribeiro</v>
       </c>
       <c r="C32" s="10">
-        <f>IF(B32="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A32,'Registo da Rotação'!$F$54:$F$153,B32,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A32,'Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,B32,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B32="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A32,'Registo da Rotação'!$F$54:$F$162,B32,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A32,'Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,B32,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="D32" s="10">
-        <f>IF(B32="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A32,'Registo da Rotação'!$G$54:$G$153,B32,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A32,'Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,B32,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B32="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A32,'Registo da Rotação'!$G$54:$G$162,B32,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A32,'Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,B32,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="E32" s="10">
-        <f>IF(B32="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A32,'Registo da Rotação'!$H$54:$H$153,B32,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A32,'Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,B32,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B32="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A32,'Registo da Rotação'!$H$54:$H$162,B32,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A32,'Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,B32,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="F32" s="10">
@@ -2422,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="6" t="str">
-        <f>IF(B32="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A32,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A32,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$153,A32)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C32&gt;0,D32&gt;0,E32&gt;0),"Cumprida","Por cumprir")))))</f>
+        <f>IF(B32="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A32,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A32,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$162,A32)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C32&gt;0,D32&gt;0,E32&gt;0),"Cumprida","Por cumprir")))))</f>
         <v>Sem sprints concluídos</v>
       </c>
       <c r="H32" s="1"/>
@@ -2438,15 +2534,15 @@
         <v>Ivan Cristiano Silva Mendes</v>
       </c>
       <c r="C33" s="10">
-        <f>IF(B33="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A33,'Registo da Rotação'!$F$54:$F$153,B33,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A33,'Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,B33,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B33="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A33,'Registo da Rotação'!$F$54:$F$162,B33,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A33,'Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,B33,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="D33" s="10">
-        <f>IF(B33="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A33,'Registo da Rotação'!$G$54:$G$153,B33,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A33,'Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,B33,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B33="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A33,'Registo da Rotação'!$G$54:$G$162,B33,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A33,'Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,B33,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="E33" s="10">
-        <f>IF(B33="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A33,'Registo da Rotação'!$H$54:$H$153,B33,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A33,'Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,B33,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B33="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A33,'Registo da Rotação'!$H$54:$H$162,B33,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A33,'Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,B33,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="F33" s="10">
@@ -2454,7 +2550,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="6" t="str">
-        <f>IF(B33="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A33,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A33,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$153,A33)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C33&gt;0,D33&gt;0,E33&gt;0),"Cumprida","Por cumprir")))))</f>
+        <f>IF(B33="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A33,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A33,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$162,A33)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C33&gt;0,D33&gt;0,E33&gt;0),"Cumprida","Por cumprir")))))</f>
         <v>Sem sprints concluídos</v>
       </c>
       <c r="H33" s="1"/>
@@ -2470,15 +2566,15 @@
         <v>André Filipe Moreira Mesquita</v>
       </c>
       <c r="C34" s="10">
-        <f>IF(B34="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A34,'Registo da Rotação'!$F$54:$F$153,B34,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A34,'Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,B34,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B34="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A34,'Registo da Rotação'!$F$54:$F$162,B34,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A34,'Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,B34,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="D34" s="10">
-        <f>IF(B34="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A34,'Registo da Rotação'!$G$54:$G$153,B34,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A34,'Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,B34,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B34="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A34,'Registo da Rotação'!$G$54:$G$162,B34,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A34,'Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,B34,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="E34" s="10">
-        <f>IF(B34="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A34,'Registo da Rotação'!$H$54:$H$153,B34,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A34,'Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,B34,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B34="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A34,'Registo da Rotação'!$H$54:$H$162,B34,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A34,'Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,B34,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="F34" s="10">
@@ -2486,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="6" t="str">
-        <f>IF(B34="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A34,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A34,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$153,A34)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C34&gt;0,D34&gt;0,E34&gt;0),"Cumprida","Por cumprir")))))</f>
+        <f>IF(B34="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A34,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A34,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$162,A34)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C34&gt;0,D34&gt;0,E34&gt;0),"Cumprida","Por cumprir")))))</f>
         <v>Sem sprints concluídos</v>
       </c>
       <c r="H34" s="1"/>
@@ -2502,15 +2598,15 @@
         <v>Gonçalo Dinis Magalhães Teixeira</v>
       </c>
       <c r="C35" s="10">
-        <f>IF(B35="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A35,'Registo da Rotação'!$F$54:$F$153,B35,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A35,'Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,B35,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B35="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A35,'Registo da Rotação'!$F$54:$F$162,B35,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A35,'Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,B35,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="D35" s="10">
-        <f>IF(B35="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A35,'Registo da Rotação'!$G$54:$G$153,B35,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A35,'Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,B35,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B35="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A35,'Registo da Rotação'!$G$54:$G$162,B35,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A35,'Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,B35,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="E35" s="10">
-        <f>IF(B35="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A35,'Registo da Rotação'!$H$54:$H$153,B35,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A35,'Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,B35,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B35="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A35,'Registo da Rotação'!$H$54:$H$162,B35,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A35,'Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,B35,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="F35" s="10">
@@ -2518,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="6" t="str">
-        <f>IF(B35="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A35,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A35,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$153,A35)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C35&gt;0,D35&gt;0,E35&gt;0),"Cumprida","Por cumprir")))))</f>
+        <f>IF(B35="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A35,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A35,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$162,A35)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C35&gt;0,D35&gt;0,E35&gt;0),"Cumprida","Por cumprir")))))</f>
         <v>Sem sprints concluídos</v>
       </c>
       <c r="H35" s="1"/>
@@ -2534,15 +2630,15 @@
         <v>Gonçalo Magalhães Ribeiro</v>
       </c>
       <c r="C36" s="10">
-        <f>IF(B36="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A36,'Registo da Rotação'!$F$54:$F$153,B36,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A36,'Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,B36,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B36="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A36,'Registo da Rotação'!$F$54:$F$162,B36,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A36,'Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,B36,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="D36" s="10">
-        <f>IF(B36="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A36,'Registo da Rotação'!$G$54:$G$153,B36,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A36,'Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,B36,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B36="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A36,'Registo da Rotação'!$G$54:$G$162,B36,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A36,'Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,B36,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="E36" s="10">
-        <f>IF(B36="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A36,'Registo da Rotação'!$H$54:$H$153,B36,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A36,'Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,B36,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B36="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A36,'Registo da Rotação'!$H$54:$H$162,B36,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A36,'Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,B36,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="F36" s="10">
@@ -2550,7 +2646,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="6" t="str">
-        <f>IF(B36="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A36,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A36,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$153,A36)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C36&gt;0,D36&gt;0,E36&gt;0),"Cumprida","Por cumprir")))))</f>
+        <f>IF(B36="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A36,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A36,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$162,A36)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C36&gt;0,D36&gt;0,E36&gt;0),"Cumprida","Por cumprir")))))</f>
         <v>Sem sprints concluídos</v>
       </c>
       <c r="H36" s="1"/>
@@ -2566,15 +2662,15 @@
         <v>Ivan Cristiano Silva Mendes</v>
       </c>
       <c r="C37" s="10">
-        <f>IF(B37="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A37,'Registo da Rotação'!$F$54:$F$153,B37,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A37,'Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,B37,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B37="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A37,'Registo da Rotação'!$F$54:$F$162,B37,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A37,'Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,B37,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="D37" s="10">
-        <f>IF(B37="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A37,'Registo da Rotação'!$G$54:$G$153,B37,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A37,'Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,B37,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B37="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A37,'Registo da Rotação'!$G$54:$G$162,B37,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A37,'Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,B37,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="E37" s="10">
-        <f>IF(B37="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A37,'Registo da Rotação'!$H$54:$H$153,B37,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A37,'Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,B37,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B37="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A37,'Registo da Rotação'!$H$54:$H$162,B37,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A37,'Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,B37,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="F37" s="10">
@@ -2582,7 +2678,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="6" t="str">
-        <f>IF(B37="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A37,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A37,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$153,A37)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C37&gt;0,D37&gt;0,E37&gt;0),"Cumprida","Por cumprir")))))</f>
+        <f>IF(B37="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A37,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A37,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$162,A37)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C37&gt;0,D37&gt;0,E37&gt;0),"Cumprida","Por cumprir")))))</f>
         <v>Sem sprints concluídos</v>
       </c>
       <c r="H37" s="1"/>
@@ -2598,15 +2694,15 @@
         <v>André Filipe Moreira Mesquita</v>
       </c>
       <c r="C38" s="10">
-        <f>IF(B38="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A38,'Registo da Rotação'!$F$54:$F$153,B38,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A38,'Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,B38,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B38="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A38,'Registo da Rotação'!$F$54:$F$162,B38,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A38,'Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,B38,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="D38" s="10">
-        <f>IF(B38="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A38,'Registo da Rotação'!$G$54:$G$153,B38,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A38,'Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,B38,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B38="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A38,'Registo da Rotação'!$G$54:$G$162,B38,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A38,'Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,B38,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="E38" s="10">
-        <f>IF(B38="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A38,'Registo da Rotação'!$H$54:$H$153,B38,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A38,'Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,B38,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B38="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A38,'Registo da Rotação'!$H$54:$H$162,B38,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A38,'Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,B38,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="F38" s="10">
@@ -2614,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="6" t="str">
-        <f>IF(B38="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A38,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A38,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$153,A38)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C38&gt;0,D38&gt;0,E38&gt;0),"Cumprida","Por cumprir")))))</f>
+        <f>IF(B38="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A38,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A38,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$162,A38)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C38&gt;0,D38&gt;0,E38&gt;0),"Cumprida","Por cumprir")))))</f>
         <v>Sem sprints concluídos</v>
       </c>
       <c r="H38" s="1"/>
@@ -2630,15 +2726,15 @@
         <v>Gonçalo Dinis Magalhães Teixeira</v>
       </c>
       <c r="C39" s="10">
-        <f>IF(B39="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A39,'Registo da Rotação'!$F$54:$F$153,B39,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A39,'Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,B39,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B39="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A39,'Registo da Rotação'!$F$54:$F$162,B39,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A39,'Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,B39,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="D39" s="10">
-        <f>IF(B39="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A39,'Registo da Rotação'!$G$54:$G$153,B39,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A39,'Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,B39,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B39="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A39,'Registo da Rotação'!$G$54:$G$162,B39,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A39,'Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,B39,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="E39" s="10">
-        <f>IF(B39="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A39,'Registo da Rotação'!$H$54:$H$153,B39,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A39,'Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,B39,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B39="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A39,'Registo da Rotação'!$H$54:$H$162,B39,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A39,'Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,B39,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="F39" s="10">
@@ -2646,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="6" t="str">
-        <f>IF(B39="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A39,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A39,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$153,A39)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C39&gt;0,D39&gt;0,E39&gt;0),"Cumprida","Por cumprir")))))</f>
+        <f>IF(B39="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A39,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A39,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$162,A39)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C39&gt;0,D39&gt;0,E39&gt;0),"Cumprida","Por cumprir")))))</f>
         <v>Sem sprints concluídos</v>
       </c>
       <c r="H39" s="1"/>
@@ -2662,15 +2758,15 @@
         <v>Gonçalo Magalhães Ribeiro</v>
       </c>
       <c r="C40" s="10">
-        <f>IF(B40="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A40,'Registo da Rotação'!$F$54:$F$153,B40,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A40,'Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,B40,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B40="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A40,'Registo da Rotação'!$F$54:$F$162,B40,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A40,'Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,B40,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="D40" s="10">
-        <f>IF(B40="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A40,'Registo da Rotação'!$G$54:$G$153,B40,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A40,'Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,B40,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B40="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A40,'Registo da Rotação'!$G$54:$G$162,B40,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A40,'Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,B40,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="E40" s="10">
-        <f>IF(B40="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A40,'Registo da Rotação'!$H$54:$H$153,B40,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A40,'Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,B40,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B40="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A40,'Registo da Rotação'!$H$54:$H$162,B40,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A40,'Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,B40,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="F40" s="10">
@@ -2678,7 +2774,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="6" t="str">
-        <f>IF(B40="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A40,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A40,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$153,A40)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C40&gt;0,D40&gt;0,E40&gt;0),"Cumprida","Por cumprir")))))</f>
+        <f>IF(B40="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A40,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A40,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$162,A40)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C40&gt;0,D40&gt;0,E40&gt;0),"Cumprida","Por cumprir")))))</f>
         <v>Sem sprints concluídos</v>
       </c>
       <c r="H40" s="1"/>
@@ -2694,15 +2790,15 @@
         <v>Ivan Cristiano Silva Mendes</v>
       </c>
       <c r="C41" s="10">
-        <f>IF(B41="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A41,'Registo da Rotação'!$F$54:$F$153,B41,'Registo da Rotação'!$I$54:$I$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A41,'Registo da Rotação'!$D$159:$D$208,"Executor",'Registo da Rotação'!$F$159:$F$208,B41,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B41="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A41,'Registo da Rotação'!$F$54:$F$162,B41,'Registo da Rotação'!$I$54:$I$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A41,'Registo da Rotação'!$D$168:$D$217,"Executor",'Registo da Rotação'!$F$168:$F$217,B41,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="D41" s="10">
-        <f>IF(B41="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A41,'Registo da Rotação'!$G$54:$G$153,B41,'Registo da Rotação'!$J$54:$J$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A41,'Registo da Rotação'!$D$159:$D$208,"Revisor",'Registo da Rotação'!$F$159:$F$208,B41,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B41="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A41,'Registo da Rotação'!$G$54:$G$162,B41,'Registo da Rotação'!$J$54:$J$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A41,'Registo da Rotação'!$D$168:$D$217,"Revisor",'Registo da Rotação'!$F$168:$F$217,B41,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="E41" s="10">
-        <f>IF(B41="","",COUNTIFS('Registo da Rotação'!$B$54:$B$153,A41,'Registo da Rotação'!$H$54:$H$153,B41,'Registo da Rotação'!$K$54:$K$153,"Sim")+COUNTIFS('Registo da Rotação'!$A$159:$A$208,A41,'Registo da Rotação'!$D$159:$D$208,"Auditor",'Registo da Rotação'!$F$159:$F$208,B41,'Registo da Rotação'!$H$159:$H$208,"Sim"))</f>
+        <f>IF(B41="","",COUNTIFS('Registo da Rotação'!$B$54:$B$162,A41,'Registo da Rotação'!$H$54:$H$162,B41,'Registo da Rotação'!$K$54:$K$162,"Sim")+COUNTIFS('Registo da Rotação'!$A$168:$A$217,A41,'Registo da Rotação'!$D$168:$D$217,"Auditor",'Registo da Rotação'!$F$168:$F$217,B41,'Registo da Rotação'!$H$168:$H$217,"Sim"))</f>
         <v>0</v>
       </c>
       <c r="F41" s="10">
@@ -2710,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="6" t="str">
-        <f>IF(B41="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A41,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A41,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$153,A41)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C41&gt;0,D41&gt;0,E41&gt;0),"Cumprida","Por cumprir")))))</f>
+        <f>IF(B41="","",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A41,'Registo da Rotação'!$D$6:$D$25,"Em curso")&gt;0,"Em avaliação",IF(COUNTIFS('Registo da Rotação'!$A$6:$A$25,A41,'Registo da Rotação'!$D$6:$D$25,"Concluído")=0,"Sem sprints concluídos",IF(COUNTIF('Registo da Rotação'!$B$54:$B$162,A41)&lt;$B$5,"Não aplicável — tarefas insuficientes",IF(AND(C41&gt;0,D41&gt;0,E41&gt;0),"Cumprida","Por cumprir")))))</f>
         <v>Sem sprints concluídos</v>
       </c>
       <c r="H41" s="1"/>
@@ -2963,7 +3059,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E78"/>
   </sheetPr>
-  <dimension ref="A1:R210"/>
+  <dimension ref="A1:R219"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2971,124 +3067,126 @@
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
     <col min="7" max="7" width="18.09765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="17" customWidth="1"/>
+    <col min="8" max="8" width="20.296875" customWidth="1"/>
+    <col min="9" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="10.59765625" customWidth="1"/>
     <col min="13" max="13" width="10.09765625" customWidth="1"/>
-    <col min="14" max="14" width="6.8984375" customWidth="1"/>
-    <col min="15" max="18" width="12.59765625" customWidth="1"/>
+    <col min="14" max="14" width="24.796875" customWidth="1"/>
+    <col min="15" max="17" width="12.59765625" customWidth="1"/>
+    <col min="18" max="18" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="26.1" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="N1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="O1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="Q1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="R1" s="20" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="38.1" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="L2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="21" t="s">
+      <c r="N2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="O2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="P2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="Q2" s="21" t="s">
+      <c r="Q2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="R2" s="22" t="s">
+      <c r="R2" s="23" t="s">
         <v>36</v>
       </c>
     </row>
@@ -3113,25 +3211,25 @@
       <c r="R3" s="1"/>
     </row>
     <row r="4" spans="1:18" ht="21.9" customHeight="1">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="26" t="s">
         <v>37</v>
       </c>
       <c r="H4" s="1"/>
@@ -3180,14 +3278,28 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="3"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+    <row r="6" spans="1:18" ht="22.8">
+      <c r="A6" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="14">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -3601,58 +3713,58 @@
       <c r="R26" s="1"/>
     </row>
     <row r="27" spans="1:18" ht="21.9" customHeight="1">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="24" t="s">
+      <c r="D27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="24" t="s">
+      <c r="F27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="G27" s="24" t="s">
+      <c r="G27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="H27" s="24" t="s">
+      <c r="H27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="I27" s="24" t="s">
+      <c r="I27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="J27" s="24" t="s">
+      <c r="J27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="K27" s="24" t="s">
+      <c r="K27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="L27" s="24" t="s">
+      <c r="L27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="M27" s="24" t="s">
+      <c r="M27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="N27" s="24" t="s">
+      <c r="N27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="O27" s="24" t="s">
+      <c r="O27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="P27" s="24" t="s">
+      <c r="P27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="Q27" s="24" t="s">
+      <c r="Q27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="R27" s="25" t="s">
+      <c r="R27" s="26" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3663,113 +3775,123 @@
       <c r="B28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29" t="s">
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29" t="s">
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="L28" s="29"/>
-      <c r="M28" s="29"/>
-      <c r="N28" s="29"/>
-      <c r="O28" s="29" t="s">
+      <c r="L28" s="27"/>
+      <c r="M28" s="27"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="29"/>
+      <c r="P28" s="27"/>
+      <c r="Q28" s="27"/>
+      <c r="R28" s="27"/>
     </row>
     <row r="29" spans="1:18" ht="32.1" customHeight="1">
-      <c r="A29" s="3"/>
+      <c r="A29" s="3" t="s">
+        <v>216</v>
+      </c>
       <c r="B29" s="6"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
+      <c r="C29" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="28" t="s">
+        <v>286</v>
+      </c>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
     </row>
     <row r="30" spans="1:18" ht="32.1" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="6"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="30"/>
-      <c r="O30" s="30"/>
-      <c r="P30" s="30"/>
-      <c r="Q30" s="30"/>
-      <c r="R30" s="30"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="29"/>
     </row>
     <row r="31" spans="1:18" ht="32.1" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="6"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
-      <c r="L31" s="30"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="30"/>
-      <c r="O31" s="30"/>
-      <c r="P31" s="30"/>
-      <c r="Q31" s="30"/>
-      <c r="R31" s="30"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="29"/>
+      <c r="O31" s="29"/>
+      <c r="P31" s="29"/>
+      <c r="Q31" s="29"/>
+      <c r="R31" s="29"/>
     </row>
     <row r="32" spans="1:18" ht="32.1" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="6" t="str">
-        <f t="shared" ref="B29:B48" si="0">IF(A32="","",IFERROR(VLOOKUP(A32,$C$6:$D$25,2,FALSE),"Sprint não registado"))</f>
+        <f t="shared" ref="B32:B48" si="0">IF(A32="","",IFERROR(VLOOKUP(A32,$C$6:$D$25,2,FALSE),"Sprint não registado"))</f>
         <v/>
       </c>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="29"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="29"/>
     </row>
     <row r="33" spans="1:18" ht="32.1" customHeight="1">
       <c r="A33" s="3"/>
@@ -3777,22 +3899,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="30"/>
-      <c r="O33" s="30"/>
-      <c r="P33" s="30"/>
-      <c r="Q33" s="30"/>
-      <c r="R33" s="30"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="29"/>
+      <c r="N33" s="29"/>
+      <c r="O33" s="29"/>
+      <c r="P33" s="29"/>
+      <c r="Q33" s="29"/>
+      <c r="R33" s="29"/>
     </row>
     <row r="34" spans="1:18" ht="32.1" customHeight="1">
       <c r="A34" s="3"/>
@@ -3800,22 +3922,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="30"/>
-      <c r="K34" s="30"/>
-      <c r="L34" s="30"/>
-      <c r="M34" s="30"/>
-      <c r="N34" s="30"/>
-      <c r="O34" s="30"/>
-      <c r="P34" s="30"/>
-      <c r="Q34" s="30"/>
-      <c r="R34" s="30"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="29"/>
+      <c r="N34" s="29"/>
+      <c r="O34" s="29"/>
+      <c r="P34" s="29"/>
+      <c r="Q34" s="29"/>
+      <c r="R34" s="29"/>
     </row>
     <row r="35" spans="1:18" ht="32.1" customHeight="1">
       <c r="A35" s="3"/>
@@ -3823,22 +3945,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="30"/>
-      <c r="K35" s="30"/>
-      <c r="L35" s="30"/>
-      <c r="M35" s="30"/>
-      <c r="N35" s="30"/>
-      <c r="O35" s="30"/>
-      <c r="P35" s="30"/>
-      <c r="Q35" s="30"/>
-      <c r="R35" s="30"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
+      <c r="O35" s="29"/>
+      <c r="P35" s="29"/>
+      <c r="Q35" s="29"/>
+      <c r="R35" s="29"/>
     </row>
     <row r="36" spans="1:18" ht="32.1" customHeight="1">
       <c r="A36" s="3"/>
@@ -3846,22 +3968,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="30"/>
-      <c r="J36" s="30"/>
-      <c r="K36" s="30"/>
-      <c r="L36" s="30"/>
-      <c r="M36" s="30"/>
-      <c r="N36" s="30"/>
-      <c r="O36" s="30"/>
-      <c r="P36" s="30"/>
-      <c r="Q36" s="30"/>
-      <c r="R36" s="30"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="29"/>
+      <c r="N36" s="29"/>
+      <c r="O36" s="29"/>
+      <c r="P36" s="29"/>
+      <c r="Q36" s="29"/>
+      <c r="R36" s="29"/>
     </row>
     <row r="37" spans="1:18" ht="32.1" customHeight="1">
       <c r="A37" s="3"/>
@@ -3869,22 +3991,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="30"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="29"/>
+      <c r="R37" s="29"/>
     </row>
     <row r="38" spans="1:18" ht="32.1" customHeight="1">
       <c r="A38" s="3"/>
@@ -3892,22 +4014,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="30"/>
-      <c r="K38" s="30"/>
-      <c r="L38" s="30"/>
-      <c r="M38" s="30"/>
-      <c r="N38" s="30"/>
-      <c r="O38" s="30"/>
-      <c r="P38" s="30"/>
-      <c r="Q38" s="30"/>
-      <c r="R38" s="30"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="29"/>
+      <c r="N38" s="29"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="29"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="29"/>
     </row>
     <row r="39" spans="1:18" ht="32.1" customHeight="1">
       <c r="A39" s="3"/>
@@ -3915,22 +4037,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="30"/>
-      <c r="L39" s="30"/>
-      <c r="M39" s="30"/>
-      <c r="N39" s="30"/>
-      <c r="O39" s="30"/>
-      <c r="P39" s="30"/>
-      <c r="Q39" s="30"/>
-      <c r="R39" s="30"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="29"/>
+      <c r="N39" s="29"/>
+      <c r="O39" s="29"/>
+      <c r="P39" s="29"/>
+      <c r="Q39" s="29"/>
+      <c r="R39" s="29"/>
     </row>
     <row r="40" spans="1:18" ht="32.1" customHeight="1">
       <c r="A40" s="3"/>
@@ -3938,22 +4060,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="30"/>
-      <c r="O40" s="30"/>
-      <c r="P40" s="30"/>
-      <c r="Q40" s="30"/>
-      <c r="R40" s="30"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="29"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="29"/>
     </row>
     <row r="41" spans="1:18" ht="32.1" customHeight="1">
       <c r="A41" s="3"/>
@@ -3961,22 +4083,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="30"/>
-      <c r="J41" s="30"/>
-      <c r="K41" s="30"/>
-      <c r="L41" s="30"/>
-      <c r="M41" s="30"/>
-      <c r="N41" s="30"/>
-      <c r="O41" s="30"/>
-      <c r="P41" s="30"/>
-      <c r="Q41" s="30"/>
-      <c r="R41" s="30"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="29"/>
+      <c r="L41" s="29"/>
+      <c r="M41" s="29"/>
+      <c r="N41" s="29"/>
+      <c r="O41" s="29"/>
+      <c r="P41" s="29"/>
+      <c r="Q41" s="29"/>
+      <c r="R41" s="29"/>
     </row>
     <row r="42" spans="1:18" ht="32.1" customHeight="1">
       <c r="A42" s="3"/>
@@ -3984,22 +4106,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
-      <c r="K42" s="30"/>
-      <c r="L42" s="30"/>
-      <c r="M42" s="30"/>
-      <c r="N42" s="30"/>
-      <c r="O42" s="30"/>
-      <c r="P42" s="30"/>
-      <c r="Q42" s="30"/>
-      <c r="R42" s="30"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="29"/>
+      <c r="L42" s="29"/>
+      <c r="M42" s="29"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="29"/>
+      <c r="Q42" s="29"/>
+      <c r="R42" s="29"/>
     </row>
     <row r="43" spans="1:18" ht="32.1" customHeight="1">
       <c r="A43" s="3"/>
@@ -4007,22 +4129,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="30"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="30"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="30"/>
-      <c r="R43" s="30"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="29"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
+      <c r="R43" s="29"/>
     </row>
     <row r="44" spans="1:18" ht="32.1" customHeight="1">
       <c r="A44" s="3"/>
@@ -4030,22 +4152,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="30"/>
-      <c r="J44" s="30"/>
-      <c r="K44" s="30"/>
-      <c r="L44" s="30"/>
-      <c r="M44" s="30"/>
-      <c r="N44" s="30"/>
-      <c r="O44" s="30"/>
-      <c r="P44" s="30"/>
-      <c r="Q44" s="30"/>
-      <c r="R44" s="30"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="29"/>
+      <c r="J44" s="29"/>
+      <c r="K44" s="29"/>
+      <c r="L44" s="29"/>
+      <c r="M44" s="29"/>
+      <c r="N44" s="29"/>
+      <c r="O44" s="29"/>
+      <c r="P44" s="29"/>
+      <c r="Q44" s="29"/>
+      <c r="R44" s="29"/>
     </row>
     <row r="45" spans="1:18" ht="32.1" customHeight="1">
       <c r="A45" s="3"/>
@@ -4053,22 +4175,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="30"/>
-      <c r="J45" s="30"/>
-      <c r="K45" s="30"/>
-      <c r="L45" s="30"/>
-      <c r="M45" s="30"/>
-      <c r="N45" s="30"/>
-      <c r="O45" s="30"/>
-      <c r="P45" s="30"/>
-      <c r="Q45" s="30"/>
-      <c r="R45" s="30"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="29"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
+      <c r="L45" s="29"/>
+      <c r="M45" s="29"/>
+      <c r="N45" s="29"/>
+      <c r="O45" s="29"/>
+      <c r="P45" s="29"/>
+      <c r="Q45" s="29"/>
+      <c r="R45" s="29"/>
     </row>
     <row r="46" spans="1:18" ht="32.1" customHeight="1">
       <c r="A46" s="3"/>
@@ -4076,22 +4198,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
-      <c r="P46" s="30"/>
-      <c r="Q46" s="30"/>
-      <c r="R46" s="30"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
     </row>
     <row r="47" spans="1:18" ht="32.1" customHeight="1">
       <c r="A47" s="3"/>
@@ -4099,22 +4221,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="30"/>
-      <c r="K47" s="30"/>
-      <c r="L47" s="30"/>
-      <c r="M47" s="30"/>
-      <c r="N47" s="30"/>
-      <c r="O47" s="30"/>
-      <c r="P47" s="30"/>
-      <c r="Q47" s="30"/>
-      <c r="R47" s="30"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="29"/>
+      <c r="N47" s="29"/>
+      <c r="O47" s="29"/>
+      <c r="P47" s="29"/>
+      <c r="Q47" s="29"/>
+      <c r="R47" s="29"/>
     </row>
     <row r="48" spans="1:18" ht="32.1" customHeight="1">
       <c r="A48" s="3"/>
@@ -4122,22 +4244,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
-      <c r="H48" s="30"/>
-      <c r="I48" s="30"/>
-      <c r="J48" s="30"/>
-      <c r="K48" s="30"/>
-      <c r="L48" s="30"/>
-      <c r="M48" s="30"/>
-      <c r="N48" s="30"/>
-      <c r="O48" s="30"/>
-      <c r="P48" s="30"/>
-      <c r="Q48" s="30"/>
-      <c r="R48" s="30"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
+      <c r="I48" s="29"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="29"/>
+      <c r="L48" s="29"/>
+      <c r="M48" s="29"/>
+      <c r="N48" s="29"/>
+      <c r="O48" s="29"/>
+      <c r="P48" s="29"/>
+      <c r="Q48" s="29"/>
+      <c r="R48" s="29"/>
     </row>
     <row r="49" spans="1:18">
       <c r="A49" s="1"/>
@@ -4180,37 +4302,37 @@
       <c r="R50" s="1"/>
     </row>
     <row r="51" spans="1:18" ht="21.9" customHeight="1">
-      <c r="A51" s="23" t="s">
+      <c r="A51" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="24" t="s">
+      <c r="B51" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="C51" s="24" t="s">
+      <c r="C51" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D51" s="24" t="s">
+      <c r="D51" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="E51" s="24" t="s">
+      <c r="E51" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="F51" s="24" t="s">
+      <c r="F51" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="G51" s="24" t="s">
+      <c r="G51" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="H51" s="24" t="s">
+      <c r="H51" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="I51" s="24" t="s">
+      <c r="I51" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="J51" s="24" t="s">
+      <c r="J51" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="K51" s="25" t="s">
+      <c r="K51" s="26" t="s">
         <v>53</v>
       </c>
       <c r="L51" s="1"/>
@@ -4222,37 +4344,37 @@
       <c r="R51" s="1"/>
     </row>
     <row r="52" spans="1:18" ht="33.9" customHeight="1">
-      <c r="A52" s="37" t="s">
+      <c r="A52" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="21" t="s">
+      <c r="B52" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C52" s="21" t="s">
+      <c r="C52" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D52" s="21" t="s">
+      <c r="D52" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="E52" s="21" t="s">
+      <c r="E52" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="F52" s="21" t="s">
+      <c r="F52" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="G52" s="21" t="s">
+      <c r="G52" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="H52" s="21" t="s">
+      <c r="H52" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="I52" s="21" t="s">
+      <c r="I52" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="J52" s="21" t="s">
+      <c r="J52" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="K52" s="22" t="s">
+      <c r="K52" s="23" t="s">
         <v>54</v>
       </c>
       <c r="L52" s="1"/>
@@ -4306,17 +4428,39 @@
       <c r="R53" s="1"/>
     </row>
     <row r="54" spans="1:18" ht="27.9" customHeight="1">
-      <c r="A54" s="15"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7"/>
+      <c r="A54" s="15">
+        <v>1</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
@@ -4326,17 +4470,39 @@
       <c r="R54" s="1"/>
     </row>
     <row r="55" spans="1:18" ht="27.9" customHeight="1">
-      <c r="A55" s="15"/>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7"/>
+      <c r="A55" s="15">
+        <v>2</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D55" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
@@ -4346,17 +4512,39 @@
       <c r="R55" s="1"/>
     </row>
     <row r="56" spans="1:18" ht="27.9" customHeight="1">
-      <c r="A56" s="15"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
-      <c r="K56" s="7"/>
+      <c r="A56" s="15">
+        <v>3</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D56" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J56" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
@@ -4366,17 +4554,39 @@
       <c r="R56" s="1"/>
     </row>
     <row r="57" spans="1:18" ht="27.9" customHeight="1">
-      <c r="A57" s="15"/>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="7"/>
-      <c r="K57" s="7"/>
+      <c r="A57" s="15">
+        <v>4</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
@@ -4386,17 +4596,39 @@
       <c r="R57" s="1"/>
     </row>
     <row r="58" spans="1:18" ht="27.9" customHeight="1">
-      <c r="A58" s="15"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
-      <c r="K58" s="7"/>
+      <c r="A58" s="15">
+        <v>5</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
@@ -4406,17 +4638,39 @@
       <c r="R58" s="1"/>
     </row>
     <row r="59" spans="1:18" ht="27.9" customHeight="1">
-      <c r="A59" s="15"/>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
-      <c r="J59" s="7"/>
-      <c r="K59" s="7"/>
+      <c r="A59" s="15">
+        <v>6</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="E59" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
@@ -4426,17 +4680,39 @@
       <c r="R59" s="1"/>
     </row>
     <row r="60" spans="1:18" ht="27.9" customHeight="1">
-      <c r="A60" s="15"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7"/>
-      <c r="J60" s="7"/>
-      <c r="K60" s="7"/>
+      <c r="A60" s="15">
+        <v>7</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D60" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="E60" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K60" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
       <c r="N60" s="1"/>
@@ -4446,17 +4722,39 @@
       <c r="R60" s="1"/>
     </row>
     <row r="61" spans="1:18" ht="27.9" customHeight="1">
-      <c r="A61" s="15"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
-      <c r="J61" s="7"/>
-      <c r="K61" s="7"/>
+      <c r="A61" s="15">
+        <v>8</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D61" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="E61" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
@@ -4466,17 +4764,39 @@
       <c r="R61" s="1"/>
     </row>
     <row r="62" spans="1:18" ht="27.9" customHeight="1">
-      <c r="A62" s="15"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="7"/>
-      <c r="K62" s="7"/>
+      <c r="A62" s="15">
+        <v>9</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D62" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="E62" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
       <c r="N62" s="1"/>
@@ -4486,17 +4806,39 @@
       <c r="R62" s="1"/>
     </row>
     <row r="63" spans="1:18" ht="27.9" customHeight="1">
-      <c r="A63" s="15"/>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
-      <c r="G63" s="7"/>
-      <c r="H63" s="7"/>
-      <c r="I63" s="7"/>
-      <c r="J63" s="7"/>
-      <c r="K63" s="7"/>
+      <c r="A63" s="15">
+        <v>10</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D63" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="E63" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
       <c r="N63" s="1"/>
@@ -6306,17 +6648,17 @@
       <c r="R153" s="1"/>
     </row>
     <row r="154" spans="1:18">
-      <c r="A154" s="1"/>
-      <c r="B154" s="1"/>
-      <c r="C154" s="1"/>
-      <c r="D154" s="1"/>
-      <c r="E154" s="1"/>
-      <c r="F154" s="1"/>
-      <c r="G154" s="1"/>
-      <c r="H154" s="1"/>
-      <c r="I154" s="1"/>
-      <c r="J154" s="1"/>
-      <c r="K154" s="1"/>
+      <c r="A154" s="15"/>
+      <c r="B154" s="7"/>
+      <c r="C154" s="7"/>
+      <c r="D154" s="7"/>
+      <c r="E154" s="7"/>
+      <c r="F154" s="7"/>
+      <c r="G154" s="7"/>
+      <c r="H154" s="7"/>
+      <c r="I154" s="7"/>
+      <c r="J154" s="7"/>
+      <c r="K154" s="7"/>
       <c r="L154" s="1"/>
       <c r="M154" s="1"/>
       <c r="N154" s="1"/>
@@ -6326,17 +6668,17 @@
       <c r="R154" s="1"/>
     </row>
     <row r="155" spans="1:18">
-      <c r="A155" s="1"/>
-      <c r="B155" s="1"/>
-      <c r="C155" s="1"/>
-      <c r="D155" s="1"/>
-      <c r="E155" s="1"/>
-      <c r="F155" s="1"/>
-      <c r="G155" s="1"/>
-      <c r="H155" s="1"/>
-      <c r="I155" s="1"/>
-      <c r="J155" s="1"/>
-      <c r="K155" s="1"/>
+      <c r="A155" s="15"/>
+      <c r="B155" s="7"/>
+      <c r="C155" s="7"/>
+      <c r="D155" s="7"/>
+      <c r="E155" s="7"/>
+      <c r="F155" s="7"/>
+      <c r="G155" s="7"/>
+      <c r="H155" s="7"/>
+      <c r="I155" s="7"/>
+      <c r="J155" s="7"/>
+      <c r="K155" s="7"/>
       <c r="L155" s="1"/>
       <c r="M155" s="1"/>
       <c r="N155" s="1"/>
@@ -6346,19 +6688,17 @@
       <c r="R155" s="1"/>
     </row>
     <row r="156" spans="1:18" ht="21.9" customHeight="1">
-      <c r="A156" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="B156" s="32"/>
-      <c r="C156" s="32"/>
-      <c r="D156" s="32"/>
-      <c r="E156" s="32"/>
-      <c r="F156" s="32"/>
-      <c r="G156" s="32"/>
-      <c r="H156" s="33"/>
-      <c r="I156" s="1"/>
-      <c r="J156" s="1"/>
-      <c r="K156" s="1"/>
+      <c r="A156" s="15"/>
+      <c r="B156" s="7"/>
+      <c r="C156" s="7"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="7"/>
+      <c r="F156" s="7"/>
+      <c r="G156" s="7"/>
+      <c r="H156" s="7"/>
+      <c r="I156" s="7"/>
+      <c r="J156" s="7"/>
+      <c r="K156" s="7"/>
       <c r="L156" s="1"/>
       <c r="M156" s="1"/>
       <c r="N156" s="1"/>
@@ -6367,19 +6707,17 @@
       <c r="Q156" s="1"/>
     </row>
     <row r="157" spans="1:18" ht="33.9" customHeight="1">
-      <c r="A157" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="B157" s="35"/>
-      <c r="C157" s="35"/>
-      <c r="D157" s="35"/>
-      <c r="E157" s="35"/>
-      <c r="F157" s="35"/>
-      <c r="G157" s="35"/>
-      <c r="H157" s="36"/>
-      <c r="I157" s="1"/>
-      <c r="J157" s="1"/>
-      <c r="K157" s="1"/>
+      <c r="A157" s="15"/>
+      <c r="B157" s="7"/>
+      <c r="C157" s="7"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7"/>
+      <c r="G157" s="7"/>
+      <c r="H157" s="7"/>
+      <c r="I157" s="7"/>
+      <c r="J157" s="7"/>
+      <c r="K157" s="7"/>
       <c r="L157" s="1"/>
       <c r="M157" s="1"/>
       <c r="N157" s="1"/>
@@ -6388,33 +6726,17 @@
       <c r="Q157" s="1"/>
     </row>
     <row r="158" spans="1:18" ht="39.9" customHeight="1">
-      <c r="A158" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B158" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C158" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D158" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="E158" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="F158" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="G158" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="H158" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="I158" s="1"/>
-      <c r="J158" s="1"/>
-      <c r="K158" s="1"/>
+      <c r="A158" s="15"/>
+      <c r="B158" s="7"/>
+      <c r="C158" s="7"/>
+      <c r="D158" s="7"/>
+      <c r="E158" s="7"/>
+      <c r="F158" s="7"/>
+      <c r="G158" s="7"/>
+      <c r="H158" s="7"/>
+      <c r="I158" s="7"/>
+      <c r="J158" s="7"/>
+      <c r="K158" s="7"/>
       <c r="L158" s="1"/>
       <c r="M158" s="1"/>
       <c r="N158" s="1"/>
@@ -6422,7 +6744,7 @@
       <c r="P158" s="1"/>
     </row>
     <row r="159" spans="1:18" ht="30" customHeight="1">
-      <c r="A159" s="7"/>
+      <c r="A159" s="15"/>
       <c r="B159" s="7"/>
       <c r="C159" s="7"/>
       <c r="D159" s="7"/>
@@ -6430,9 +6752,9 @@
       <c r="F159" s="7"/>
       <c r="G159" s="7"/>
       <c r="H159" s="7"/>
-      <c r="I159" s="1"/>
-      <c r="J159" s="1"/>
-      <c r="K159" s="1"/>
+      <c r="I159" s="7"/>
+      <c r="J159" s="7"/>
+      <c r="K159" s="7"/>
       <c r="L159" s="1"/>
       <c r="M159" s="1"/>
       <c r="N159" s="1"/>
@@ -6441,7 +6763,7 @@
       <c r="Q159" s="1"/>
     </row>
     <row r="160" spans="1:18" ht="30" customHeight="1">
-      <c r="A160" s="7"/>
+      <c r="A160" s="15"/>
       <c r="B160" s="7"/>
       <c r="C160" s="7"/>
       <c r="D160" s="7"/>
@@ -6449,9 +6771,9 @@
       <c r="F160" s="7"/>
       <c r="G160" s="7"/>
       <c r="H160" s="7"/>
-      <c r="I160" s="1"/>
-      <c r="J160" s="1"/>
-      <c r="K160" s="1"/>
+      <c r="I160" s="7"/>
+      <c r="J160" s="7"/>
+      <c r="K160" s="7"/>
       <c r="L160" s="1"/>
       <c r="M160" s="1"/>
       <c r="N160" s="1"/>
@@ -6460,7 +6782,7 @@
       <c r="Q160" s="1"/>
     </row>
     <row r="161" spans="1:18" ht="30" customHeight="1">
-      <c r="A161" s="7"/>
+      <c r="A161" s="15"/>
       <c r="B161" s="7"/>
       <c r="C161" s="7"/>
       <c r="D161" s="7"/>
@@ -6468,9 +6790,9 @@
       <c r="F161" s="7"/>
       <c r="G161" s="7"/>
       <c r="H161" s="7"/>
-      <c r="I161" s="1"/>
-      <c r="J161" s="1"/>
-      <c r="K161" s="1"/>
+      <c r="I161" s="7"/>
+      <c r="J161" s="7"/>
+      <c r="K161" s="7"/>
       <c r="L161" s="1"/>
       <c r="M161" s="1"/>
       <c r="N161" s="1"/>
@@ -6479,7 +6801,7 @@
       <c r="Q161" s="1"/>
     </row>
     <row r="162" spans="1:18" ht="30" customHeight="1">
-      <c r="A162" s="7"/>
+      <c r="A162" s="15"/>
       <c r="B162" s="7"/>
       <c r="C162" s="7"/>
       <c r="D162" s="7"/>
@@ -6487,9 +6809,9 @@
       <c r="F162" s="7"/>
       <c r="G162" s="7"/>
       <c r="H162" s="7"/>
-      <c r="I162" s="1"/>
-      <c r="J162" s="1"/>
-      <c r="K162" s="1"/>
+      <c r="I162" s="7"/>
+      <c r="J162" s="7"/>
+      <c r="K162" s="7"/>
       <c r="L162" s="1"/>
       <c r="M162" s="1"/>
       <c r="N162" s="1"/>
@@ -6498,14 +6820,14 @@
       <c r="Q162" s="1"/>
     </row>
     <row r="163" spans="1:18" ht="30" customHeight="1">
-      <c r="A163" s="7"/>
-      <c r="B163" s="7"/>
-      <c r="C163" s="7"/>
-      <c r="D163" s="7"/>
-      <c r="E163" s="7"/>
-      <c r="F163" s="7"/>
-      <c r="G163" s="7"/>
-      <c r="H163" s="7"/>
+      <c r="A163" s="1"/>
+      <c r="B163" s="1"/>
+      <c r="C163" s="1"/>
+      <c r="D163" s="1"/>
+      <c r="E163" s="1"/>
+      <c r="F163" s="1"/>
+      <c r="G163" s="1"/>
+      <c r="H163" s="1"/>
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
       <c r="K163" s="1"/>
@@ -6517,14 +6839,14 @@
       <c r="Q163" s="1"/>
     </row>
     <row r="164" spans="1:18" ht="30" customHeight="1">
-      <c r="A164" s="7"/>
-      <c r="B164" s="7"/>
-      <c r="C164" s="7"/>
-      <c r="D164" s="7"/>
-      <c r="E164" s="7"/>
-      <c r="F164" s="7"/>
-      <c r="G164" s="7"/>
-      <c r="H164" s="7"/>
+      <c r="A164" s="1"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="1"/>
+      <c r="D164" s="1"/>
+      <c r="E164" s="1"/>
+      <c r="F164" s="1"/>
+      <c r="G164" s="1"/>
+      <c r="H164" s="1"/>
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>
       <c r="K164" s="1"/>
@@ -6536,14 +6858,16 @@
       <c r="Q164" s="1"/>
     </row>
     <row r="165" spans="1:18" ht="30" customHeight="1">
-      <c r="A165" s="7"/>
-      <c r="B165" s="7"/>
-      <c r="C165" s="7"/>
-      <c r="D165" s="7"/>
-      <c r="E165" s="7"/>
-      <c r="F165" s="7"/>
-      <c r="G165" s="7"/>
-      <c r="H165" s="7"/>
+      <c r="A165" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B165" s="31"/>
+      <c r="C165" s="31"/>
+      <c r="D165" s="31"/>
+      <c r="E165" s="31"/>
+      <c r="F165" s="31"/>
+      <c r="G165" s="31"/>
+      <c r="H165" s="32"/>
       <c r="I165" s="1"/>
       <c r="J165" s="1"/>
       <c r="K165" s="1"/>
@@ -6555,14 +6879,16 @@
       <c r="Q165" s="1"/>
     </row>
     <row r="166" spans="1:18" ht="30" customHeight="1">
-      <c r="A166" s="7"/>
-      <c r="B166" s="7"/>
-      <c r="C166" s="7"/>
-      <c r="D166" s="7"/>
-      <c r="E166" s="7"/>
-      <c r="F166" s="7"/>
-      <c r="G166" s="7"/>
-      <c r="H166" s="7"/>
+      <c r="A166" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B166" s="34"/>
+      <c r="C166" s="34"/>
+      <c r="D166" s="34"/>
+      <c r="E166" s="34"/>
+      <c r="F166" s="34"/>
+      <c r="G166" s="34"/>
+      <c r="H166" s="35"/>
       <c r="I166" s="1"/>
       <c r="J166" s="1"/>
       <c r="K166" s="1"/>
@@ -6575,14 +6901,30 @@
       <c r="R166" s="1"/>
     </row>
     <row r="167" spans="1:18" ht="30" customHeight="1">
-      <c r="A167" s="7"/>
-      <c r="B167" s="7"/>
-      <c r="C167" s="7"/>
-      <c r="D167" s="7"/>
-      <c r="E167" s="7"/>
-      <c r="F167" s="7"/>
-      <c r="G167" s="7"/>
-      <c r="H167" s="7"/>
+      <c r="A167" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B167" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C167" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D167" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E167" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="F167" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="G167" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="H167" s="18" t="s">
+        <v>70</v>
+      </c>
       <c r="I167" s="1"/>
       <c r="J167" s="1"/>
       <c r="K167" s="1"/>
@@ -7415,14 +7757,14 @@
       <c r="R208" s="1"/>
     </row>
     <row r="209" spans="1:18">
-      <c r="A209" s="1"/>
-      <c r="B209" s="1"/>
-      <c r="C209" s="1"/>
-      <c r="D209" s="1"/>
-      <c r="E209" s="1"/>
-      <c r="F209" s="1"/>
-      <c r="G209" s="1"/>
-      <c r="H209" s="1"/>
+      <c r="A209" s="7"/>
+      <c r="B209" s="7"/>
+      <c r="C209" s="7"/>
+      <c r="D209" s="7"/>
+      <c r="E209" s="7"/>
+      <c r="F209" s="7"/>
+      <c r="G209" s="7"/>
+      <c r="H209" s="7"/>
       <c r="I209" s="1"/>
       <c r="J209" s="1"/>
       <c r="K209" s="1"/>
@@ -7435,14 +7777,14 @@
       <c r="R209" s="1"/>
     </row>
     <row r="210" spans="1:18">
-      <c r="A210" s="1"/>
-      <c r="B210" s="1"/>
-      <c r="C210" s="1"/>
-      <c r="D210" s="1"/>
-      <c r="E210" s="1"/>
-      <c r="F210" s="1"/>
-      <c r="G210" s="1"/>
-      <c r="H210" s="1"/>
+      <c r="A210" s="7"/>
+      <c r="B210" s="7"/>
+      <c r="C210" s="7"/>
+      <c r="D210" s="7"/>
+      <c r="E210" s="7"/>
+      <c r="F210" s="7"/>
+      <c r="G210" s="7"/>
+      <c r="H210" s="7"/>
       <c r="I210" s="1"/>
       <c r="J210" s="1"/>
       <c r="K210" s="1"/>
@@ -7454,10 +7796,127 @@
       <c r="Q210" s="1"/>
       <c r="R210" s="1"/>
     </row>
+    <row r="211" spans="1:18">
+      <c r="A211" s="7"/>
+      <c r="B211" s="7"/>
+      <c r="C211" s="7"/>
+      <c r="D211" s="7"/>
+      <c r="E211" s="7"/>
+      <c r="F211" s="7"/>
+      <c r="G211" s="7"/>
+      <c r="H211" s="7"/>
+      <c r="I211" s="1"/>
+      <c r="J211" s="1"/>
+      <c r="K211" s="1"/>
+    </row>
+    <row r="212" spans="1:18">
+      <c r="A212" s="7"/>
+      <c r="B212" s="7"/>
+      <c r="C212" s="7"/>
+      <c r="D212" s="7"/>
+      <c r="E212" s="7"/>
+      <c r="F212" s="7"/>
+      <c r="G212" s="7"/>
+      <c r="H212" s="7"/>
+      <c r="I212" s="1"/>
+      <c r="J212" s="1"/>
+      <c r="K212" s="1"/>
+    </row>
+    <row r="213" spans="1:18">
+      <c r="A213" s="7"/>
+      <c r="B213" s="7"/>
+      <c r="C213" s="7"/>
+      <c r="D213" s="7"/>
+      <c r="E213" s="7"/>
+      <c r="F213" s="7"/>
+      <c r="G213" s="7"/>
+      <c r="H213" s="7"/>
+      <c r="I213" s="1"/>
+      <c r="J213" s="1"/>
+      <c r="K213" s="1"/>
+    </row>
+    <row r="214" spans="1:18">
+      <c r="A214" s="7"/>
+      <c r="B214" s="7"/>
+      <c r="C214" s="7"/>
+      <c r="D214" s="7"/>
+      <c r="E214" s="7"/>
+      <c r="F214" s="7"/>
+      <c r="G214" s="7"/>
+      <c r="H214" s="7"/>
+      <c r="I214" s="1"/>
+      <c r="J214" s="1"/>
+      <c r="K214" s="1"/>
+    </row>
+    <row r="215" spans="1:18">
+      <c r="A215" s="7"/>
+      <c r="B215" s="7"/>
+      <c r="C215" s="7"/>
+      <c r="D215" s="7"/>
+      <c r="E215" s="7"/>
+      <c r="F215" s="7"/>
+      <c r="G215" s="7"/>
+      <c r="H215" s="7"/>
+      <c r="I215" s="1"/>
+      <c r="J215" s="1"/>
+      <c r="K215" s="1"/>
+    </row>
+    <row r="216" spans="1:18">
+      <c r="A216" s="7"/>
+      <c r="B216" s="7"/>
+      <c r="C216" s="7"/>
+      <c r="D216" s="7"/>
+      <c r="E216" s="7"/>
+      <c r="F216" s="7"/>
+      <c r="G216" s="7"/>
+      <c r="H216" s="7"/>
+      <c r="I216" s="1"/>
+      <c r="J216" s="1"/>
+      <c r="K216" s="1"/>
+    </row>
+    <row r="217" spans="1:18">
+      <c r="A217" s="7"/>
+      <c r="B217" s="7"/>
+      <c r="C217" s="7"/>
+      <c r="D217" s="7"/>
+      <c r="E217" s="7"/>
+      <c r="F217" s="7"/>
+      <c r="G217" s="7"/>
+      <c r="H217" s="7"/>
+      <c r="I217" s="1"/>
+      <c r="J217" s="1"/>
+      <c r="K217" s="1"/>
+    </row>
+    <row r="218" spans="1:18">
+      <c r="A218" s="1"/>
+      <c r="B218" s="1"/>
+      <c r="C218" s="1"/>
+      <c r="D218" s="1"/>
+      <c r="E218" s="1"/>
+      <c r="F218" s="1"/>
+      <c r="G218" s="1"/>
+      <c r="H218" s="1"/>
+      <c r="I218" s="1"/>
+      <c r="J218" s="1"/>
+      <c r="K218" s="1"/>
+    </row>
+    <row r="219" spans="1:18">
+      <c r="A219" s="1"/>
+      <c r="B219" s="1"/>
+      <c r="C219" s="1"/>
+      <c r="D219" s="1"/>
+      <c r="E219" s="1"/>
+      <c r="F219" s="1"/>
+      <c r="G219" s="1"/>
+      <c r="H219" s="1"/>
+      <c r="I219" s="1"/>
+      <c r="J219" s="1"/>
+      <c r="K219" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="92">
-    <mergeCell ref="A156:H156"/>
-    <mergeCell ref="A157:H157"/>
+    <mergeCell ref="A165:H165"/>
+    <mergeCell ref="A166:H166"/>
     <mergeCell ref="O47:R47"/>
     <mergeCell ref="C48:F48"/>
     <mergeCell ref="G48:J48"/>
@@ -7549,23 +8008,24 @@
     <mergeCell ref="K28:N28"/>
     <mergeCell ref="O28:R28"/>
   </mergeCells>
+  <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="6">
-    <dataValidation type="list" sqref="A6:A25 B54:B153 A159:A208" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="A6:A25 A168:A217 B54:B162" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>MilestonesRotacao</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="C6:C25 A29:A48 C54:C153 B159:B208" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" sqref="C6:C25 A29:A48 B168:B217 C54:C162" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>SprintsRotacao</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="D6:D25" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>SituacoesSprint</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E6:F25 F54:H153 E159:F208" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="list" sqref="E6:F25 E168:F217 F54:H162" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>AlunosRotacao</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G6:G25 I54:K153 H159:H208" xr:uid="{00000000-0002-0000-0100-000004000000}">
+    <dataValidation type="list" sqref="G6:G25 H168:H217 I54:K162" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>Confirmacoes</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D159:D208" xr:uid="{00000000-0002-0000-0100-00000C000000}">
+    <dataValidation type="list" sqref="D168:D217" xr:uid="{00000000-0002-0000-0100-00000C000000}">
       <formula1>PapeisRotacao</formula1>
     </dataValidation>
   </dataValidations>
@@ -7592,30 +8052,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="20" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="33.9" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7645,7 +8105,7 @@
       </c>
       <c r="B5" s="11">
         <f>COUNTIF('Registo da Rotação'!$C$6:$C$25,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>77</v>
@@ -7659,8 +8119,8 @@
         <v>79</v>
       </c>
       <c r="B6" s="11">
-        <f>COUNTIF('Registo da Rotação'!$D$54:$D$153,"&lt;&gt;")</f>
-        <v>0</v>
+        <f>COUNTIF('Registo da Rotação'!$D$54:$D$162,"&lt;&gt;")</f>
+        <v>10</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>77</v>
@@ -7674,7 +8134,7 @@
         <v>81</v>
       </c>
       <c r="B7" s="11">
-        <f>COUNTIF('Registo da Rotação'!$C$159:$C$208,"&lt;&gt;")</f>
+        <f>COUNTIF('Registo da Rotação'!$C$168:$C$217,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -7849,11 +8309,11 @@
       </c>
       <c r="B18" s="11">
         <f>SUM('Listas de apoio'!Q5:Q104)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C18" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>OK</v>
+        <v>Rever</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>99</v>
@@ -7881,11 +8341,11 @@
       </c>
       <c r="B20" s="11">
         <f>SUM('Listas de apoio'!S5:S104)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C20" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>OK</v>
+        <v>Rever</v>
       </c>
       <c r="D20" s="16" t="s">
         <v>245</v>
@@ -7897,11 +8357,11 @@
       </c>
       <c r="B21" s="11">
         <f>SUM('Listas de apoio'!T5:T104)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C21" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>OK</v>
+        <v>Rever</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>247</v>
@@ -8041,11 +8501,11 @@
       </c>
       <c r="B30" s="11">
         <f>COUNTIF('Grelha de Rotação de Papéis'!$G$26:$G$41,"Por cumprir")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>OK</v>
+        <v>Rever</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>118</v>
@@ -8142,30 +8602,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="20" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="36" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="23" t="s">
         <v>122</v>
       </c>
     </row>
@@ -8571,55 +9031,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="26.1" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="N1" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="O1" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="Q1" s="20" t="s">
         <v>189</v>
       </c>
       <c r="R1" s="1"/>
@@ -8641,55 +9101,55 @@
       <c r="AH1" s="1"/>
     </row>
     <row r="2" spans="1:34">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="L2" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="N2" s="21" t="s">
+      <c r="N2" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="O2" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="P2" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="Q2" s="22" t="s">
+      <c r="Q2" s="23" t="s">
         <v>190</v>
       </c>
       <c r="R2" s="1"/>
@@ -8832,7 +9292,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="22.8">
+    <row r="5" spans="1:34">
       <c r="A5" s="3" t="s">
         <v>259</v>
       </c>
@@ -8871,7 +9331,7 @@
       </c>
       <c r="Q5" s="8">
         <f>IF('Registo da Rotação'!A54="",0,IF(OR('Registo da Rotação'!F54='Registo da Rotação'!G54,'Registo da Rotação'!F54='Registo da Rotação'!H54,'Registo da Rotação'!G54='Registo da Rotação'!H54),1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="8">
         <f>IF('Registo da Rotação'!A54="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C54,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I54="Ainda não avaliado",'Registo da Rotação'!J54="Ainda não avaliado",'Registo da Rotação'!K54="Ainda não avaliado")),1,0))</f>
@@ -8884,32 +9344,32 @@
         <v>0</v>
       </c>
       <c r="U5" s="8">
-        <f>IF('Registo da Rotação'!A54="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A54)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C54,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D54)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A54="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A54)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C54,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D54)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V5" s="1"/>
       <c r="W5" s="8">
-        <f>IF('Registo da Rotação'!C159="",0,IF(COUNTA('Registo da Rotação'!A159:H159)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C168="",0,IF(COUNTA('Registo da Rotação'!A168:H168)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X5" s="8">
-        <f>IF('Registo da Rotação'!C159="",0,IF('Registo da Rotação'!E159='Registo da Rotação'!F159,1,0))</f>
+        <f>IF('Registo da Rotação'!C168="",0,IF('Registo da Rotação'!E168='Registo da Rotação'!F168,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>IF('Registo da Rotação'!C159="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B159)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C168="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B168)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z5" s="8">
-        <f>IF('Registo da Rotação'!C159="",0,IF('Registo da Rotação'!D159="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A159,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B159,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C159,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F159)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A159,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B159,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C159,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F159)&gt;0,1,0),IF('Registo da Rotação'!D159="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A159,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B159,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C159,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F159)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A159,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B159,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C159,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F159)&gt;0,1,0),IF('Registo da Rotação'!D159="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A159,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B159,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C159,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F159)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A159,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B159,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C159,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F159)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C168="",0,IF('Registo da Rotação'!D168="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C168,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F168)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C168,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F168)&gt;0,1,0),IF('Registo da Rotação'!D168="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C168,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F168)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C168,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F168)&gt;0,1,0),IF('Registo da Rotação'!D168="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C168,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F168)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C168,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F168)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA5" s="8">
-        <f>IF('Registo da Rotação'!C159="",0,IF('Registo da Rotação'!D159="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A159,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B159,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C159,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E159)=0,1,0),IF('Registo da Rotação'!D159="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A159,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B159,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C159,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E159)=0,1,0),IF('Registo da Rotação'!D159="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A159,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B159,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C159,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E159)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C168="",0,IF('Registo da Rotação'!D168="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C168,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E168)=0,1,0),IF('Registo da Rotação'!D168="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C168,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E168)=0,1,0),IF('Registo da Rotação'!D168="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C168,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E168)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB5" s="8">
-        <f>IF('Registo da Rotação'!C159="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B159,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H159="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C168="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B168,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H168="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC5" s="1"/>
@@ -8973,7 +9433,7 @@
       </c>
       <c r="Q6" s="8">
         <f>IF('Registo da Rotação'!A55="",0,IF(OR('Registo da Rotação'!F55='Registo da Rotação'!G55,'Registo da Rotação'!F55='Registo da Rotação'!H55,'Registo da Rotação'!G55='Registo da Rotação'!H55),1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="8">
         <f>IF('Registo da Rotação'!A55="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C55,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I55="Ainda não avaliado",'Registo da Rotação'!J55="Ainda não avaliado",'Registo da Rotação'!K55="Ainda não avaliado")),1,0))</f>
@@ -8988,32 +9448,32 @@
         <v>0</v>
       </c>
       <c r="U6" s="8">
-        <f>IF('Registo da Rotação'!A55="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A55)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C55,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D55)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A55="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A55)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C55,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D55)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V6" s="1"/>
       <c r="W6" s="8">
-        <f>IF('Registo da Rotação'!C160="",0,IF(COUNTA('Registo da Rotação'!A160:H160)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C169="",0,IF(COUNTA('Registo da Rotação'!A169:H169)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X6" s="8">
-        <f>IF('Registo da Rotação'!C160="",0,IF('Registo da Rotação'!E160='Registo da Rotação'!F160,1,0))</f>
+        <f>IF('Registo da Rotação'!C169="",0,IF('Registo da Rotação'!E169='Registo da Rotação'!F169,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y6" s="8">
-        <f>IF('Registo da Rotação'!C160="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B160)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C169="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B169)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z6" s="8">
-        <f>IF('Registo da Rotação'!C160="",0,IF('Registo da Rotação'!D160="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A160,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B160,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C160,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F160)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A160,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B160,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C160,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F160)&gt;0,1,0),IF('Registo da Rotação'!D160="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A160,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B160,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C160,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F160)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A160,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B160,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C160,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F160)&gt;0,1,0),IF('Registo da Rotação'!D160="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A160,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B160,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C160,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F160)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A160,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B160,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C160,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F160)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C169="",0,IF('Registo da Rotação'!D169="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C169,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F169)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C169,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F169)&gt;0,1,0),IF('Registo da Rotação'!D169="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C169,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F169)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C169,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F169)&gt;0,1,0),IF('Registo da Rotação'!D169="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C169,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F169)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C169,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F169)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA6" s="8">
-        <f>IF('Registo da Rotação'!C160="",0,IF('Registo da Rotação'!D160="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A160,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B160,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C160,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E160)=0,1,0),IF('Registo da Rotação'!D160="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A160,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B160,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C160,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E160)=0,1,0),IF('Registo da Rotação'!D160="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A160,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B160,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C160,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E160)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C169="",0,IF('Registo da Rotação'!D169="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C169,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E169)=0,1,0),IF('Registo da Rotação'!D169="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C169,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E169)=0,1,0),IF('Registo da Rotação'!D169="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C169,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E169)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB6" s="8">
-        <f>IF('Registo da Rotação'!C160="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B160,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H160="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C169="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B169,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H169="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC6" s="1"/>
@@ -9088,32 +9548,32 @@
         <v>0</v>
       </c>
       <c r="U7" s="8">
-        <f>IF('Registo da Rotação'!A56="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A56)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C56,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D56)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A56="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A56)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C56,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D56)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V7" s="1"/>
       <c r="W7" s="8">
-        <f>IF('Registo da Rotação'!C161="",0,IF(COUNTA('Registo da Rotação'!A161:H161)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C170="",0,IF(COUNTA('Registo da Rotação'!A170:H170)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X7" s="8">
-        <f>IF('Registo da Rotação'!C161="",0,IF('Registo da Rotação'!E161='Registo da Rotação'!F161,1,0))</f>
+        <f>IF('Registo da Rotação'!C170="",0,IF('Registo da Rotação'!E170='Registo da Rotação'!F170,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y7" s="8">
-        <f>IF('Registo da Rotação'!C161="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B161)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C170="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B170)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z7" s="8">
-        <f>IF('Registo da Rotação'!C161="",0,IF('Registo da Rotação'!D161="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A161,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B161,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C161,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F161)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A161,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B161,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C161,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F161)&gt;0,1,0),IF('Registo da Rotação'!D161="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A161,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B161,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C161,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F161)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A161,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B161,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C161,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F161)&gt;0,1,0),IF('Registo da Rotação'!D161="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A161,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B161,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C161,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F161)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A161,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B161,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C161,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F161)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C170="",0,IF('Registo da Rotação'!D170="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C170,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F170)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C170,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F170)&gt;0,1,0),IF('Registo da Rotação'!D170="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C170,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F170)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C170,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F170)&gt;0,1,0),IF('Registo da Rotação'!D170="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C170,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F170)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C170,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F170)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA7" s="8">
-        <f>IF('Registo da Rotação'!C161="",0,IF('Registo da Rotação'!D161="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A161,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B161,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C161,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E161)=0,1,0),IF('Registo da Rotação'!D161="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A161,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B161,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C161,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E161)=0,1,0),IF('Registo da Rotação'!D161="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A161,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B161,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C161,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E161)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C170="",0,IF('Registo da Rotação'!D170="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C170,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E170)=0,1,0),IF('Registo da Rotação'!D170="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C170,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E170)=0,1,0),IF('Registo da Rotação'!D170="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C170,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E170)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB7" s="8">
-        <f>IF('Registo da Rotação'!C161="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B161,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H161="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C170="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B170,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H170="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC7" s="1"/>
@@ -9184,32 +9644,32 @@
         <v>0</v>
       </c>
       <c r="U8" s="8">
-        <f>IF('Registo da Rotação'!A57="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A57)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C57,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D57)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A57="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A57)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C57,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D57)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V8" s="1"/>
       <c r="W8" s="8">
-        <f>IF('Registo da Rotação'!C162="",0,IF(COUNTA('Registo da Rotação'!A162:H162)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C171="",0,IF(COUNTA('Registo da Rotação'!A171:H171)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X8" s="8">
-        <f>IF('Registo da Rotação'!C162="",0,IF('Registo da Rotação'!E162='Registo da Rotação'!F162,1,0))</f>
+        <f>IF('Registo da Rotação'!C171="",0,IF('Registo da Rotação'!E171='Registo da Rotação'!F171,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y8" s="8">
-        <f>IF('Registo da Rotação'!C162="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B162)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C171="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B171)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z8" s="8">
-        <f>IF('Registo da Rotação'!C162="",0,IF('Registo da Rotação'!D162="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A162,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B162,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C162,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F162)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A162,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B162,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C162,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F162)&gt;0,1,0),IF('Registo da Rotação'!D162="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A162,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B162,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C162,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F162)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A162,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B162,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C162,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F162)&gt;0,1,0),IF('Registo da Rotação'!D162="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A162,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B162,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C162,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F162)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A162,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B162,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C162,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F162)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C171="",0,IF('Registo da Rotação'!D171="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C171,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F171)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C171,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F171)&gt;0,1,0),IF('Registo da Rotação'!D171="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C171,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F171)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C171,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F171)&gt;0,1,0),IF('Registo da Rotação'!D171="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C171,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F171)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C171,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F171)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA8" s="8">
-        <f>IF('Registo da Rotação'!C162="",0,IF('Registo da Rotação'!D162="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A162,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B162,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C162,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E162)=0,1,0),IF('Registo da Rotação'!D162="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A162,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B162,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C162,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E162)=0,1,0),IF('Registo da Rotação'!D162="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A162,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B162,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C162,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E162)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C171="",0,IF('Registo da Rotação'!D171="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C171,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E171)=0,1,0),IF('Registo da Rotação'!D171="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C171,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E171)=0,1,0),IF('Registo da Rotação'!D171="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C171,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E171)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB8" s="8">
-        <f>IF('Registo da Rotação'!C162="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B162,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H162="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C171="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B171,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H171="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC8" s="1"/>
@@ -9276,32 +9736,32 @@
         <v>0</v>
       </c>
       <c r="U9" s="8">
-        <f>IF('Registo da Rotação'!A58="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A58)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C58,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D58)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A58="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A58)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C58,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D58)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V9" s="1"/>
       <c r="W9" s="8">
-        <f>IF('Registo da Rotação'!C163="",0,IF(COUNTA('Registo da Rotação'!A163:H163)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C172="",0,IF(COUNTA('Registo da Rotação'!A172:H172)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X9" s="8">
-        <f>IF('Registo da Rotação'!C163="",0,IF('Registo da Rotação'!E163='Registo da Rotação'!F163,1,0))</f>
+        <f>IF('Registo da Rotação'!C172="",0,IF('Registo da Rotação'!E172='Registo da Rotação'!F172,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y9" s="8">
-        <f>IF('Registo da Rotação'!C163="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B163)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C172="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B172)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z9" s="8">
-        <f>IF('Registo da Rotação'!C163="",0,IF('Registo da Rotação'!D163="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A163,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B163,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C163,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F163)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A163,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B163,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C163,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F163)&gt;0,1,0),IF('Registo da Rotação'!D163="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A163,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B163,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C163,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F163)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A163,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B163,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C163,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F163)&gt;0,1,0),IF('Registo da Rotação'!D163="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A163,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B163,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C163,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F163)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A163,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B163,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C163,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F163)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C172="",0,IF('Registo da Rotação'!D172="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C172,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F172)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C172,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F172)&gt;0,1,0),IF('Registo da Rotação'!D172="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C172,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F172)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C172,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F172)&gt;0,1,0),IF('Registo da Rotação'!D172="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C172,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F172)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C172,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F172)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA9" s="8">
-        <f>IF('Registo da Rotação'!C163="",0,IF('Registo da Rotação'!D163="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A163,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B163,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C163,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E163)=0,1,0),IF('Registo da Rotação'!D163="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A163,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B163,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C163,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E163)=0,1,0),IF('Registo da Rotação'!D163="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A163,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B163,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C163,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E163)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C172="",0,IF('Registo da Rotação'!D172="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C172,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E172)=0,1,0),IF('Registo da Rotação'!D172="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C172,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E172)=0,1,0),IF('Registo da Rotação'!D172="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C172,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E172)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB9" s="8">
-        <f>IF('Registo da Rotação'!C163="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B163,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H163="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C172="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B172,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H172="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC9" s="1"/>
@@ -9353,7 +9813,7 @@
       </c>
       <c r="Q10" s="8">
         <f>IF('Registo da Rotação'!A59="",0,IF(OR('Registo da Rotação'!F59='Registo da Rotação'!G59,'Registo da Rotação'!F59='Registo da Rotação'!H59,'Registo da Rotação'!G59='Registo da Rotação'!H59),1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="8">
         <f>IF('Registo da Rotação'!A59="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C59,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I59="Ainda não avaliado",'Registo da Rotação'!J59="Ainda não avaliado",'Registo da Rotação'!K59="Ainda não avaliado")),1,0))</f>
@@ -9361,39 +9821,39 @@
       </c>
       <c r="S10" s="8">
         <f>IF('Registo da Rotação'!A59="",0,IF(AND('Registo da Rotação'!G59=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F58='Registo da Rotação'!F59),'Registo da Rotação'!$G$54:'Registo da Rotação'!G58),""),'Registo da Rotação'!H59=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F58='Registo da Rotação'!F59),'Registo da Rotação'!$H$54:'Registo da Rotação'!H58),"")),1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" s="8">
         <f>IF('Registo da Rotação'!A59="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F58='Registo da Rotação'!F59)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G58='Registo da Rotação'!G59)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H58='Registo da Rotação'!H59)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F58)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F59,'Listas de apoio'!$A$5='Registo da Rotação'!G59,'Listas de apoio'!$A$5='Registo da Rotação'!H59),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F58='Registo da Rotação'!F59),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F58)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F58='Registo da Rotação'!F59)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G58='Registo da Rotação'!G59)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H58='Registo da Rotação'!H59)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F58)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G58='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H58='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F59,'Listas de apoio'!$A$6='Registo da Rotação'!G59,'Listas de apoio'!$A$6='Registo da Rotação'!H59),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F58='Registo da Rotação'!F59),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F58)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F58='Registo da Rotação'!F59)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G58='Registo da Rotação'!G59)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H58='Registo da Rotação'!H59)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F58)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G58='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H58='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F59,'Listas de apoio'!$A$7='Registo da Rotação'!G59,'Listas de apoio'!$A$7='Registo da Rotação'!H59),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F58='Registo da Rotação'!F59),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F58)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F58='Registo da Rotação'!F59)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G58='Registo da Rotação'!G59)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H58='Registo da Rotação'!H59)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F58)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G58='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H58='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F59,'Listas de apoio'!$A$8='Registo da Rotação'!G59,'Listas de apoio'!$A$8='Registo da Rotação'!H59),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F58='Registo da Rotação'!F59),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F58)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F58='Registo da Rotação'!F59)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G58='Registo da Rotação'!G59)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H58='Registo da Rotação'!H59)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F58)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G58='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H58='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U10" s="8">
-        <f>IF('Registo da Rotação'!A59="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A59)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C59,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D59)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A59="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A59)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C59,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D59)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V10" s="1"/>
       <c r="W10" s="8">
-        <f>IF('Registo da Rotação'!C164="",0,IF(COUNTA('Registo da Rotação'!A164:H164)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C173="",0,IF(COUNTA('Registo da Rotação'!A173:H173)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X10" s="8">
-        <f>IF('Registo da Rotação'!C164="",0,IF('Registo da Rotação'!E164='Registo da Rotação'!F164,1,0))</f>
+        <f>IF('Registo da Rotação'!C173="",0,IF('Registo da Rotação'!E173='Registo da Rotação'!F173,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y10" s="8">
-        <f>IF('Registo da Rotação'!C164="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B164)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C173="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B173)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z10" s="8">
-        <f>IF('Registo da Rotação'!C164="",0,IF('Registo da Rotação'!D164="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A164,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B164,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C164,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F164)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A164,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B164,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C164,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F164)&gt;0,1,0),IF('Registo da Rotação'!D164="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A164,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B164,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C164,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F164)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A164,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B164,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C164,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F164)&gt;0,1,0),IF('Registo da Rotação'!D164="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A164,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B164,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C164,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F164)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A164,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B164,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C164,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F164)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C173="",0,IF('Registo da Rotação'!D173="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C173,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F173)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C173,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F173)&gt;0,1,0),IF('Registo da Rotação'!D173="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C173,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F173)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C173,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F173)&gt;0,1,0),IF('Registo da Rotação'!D173="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C173,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F173)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C173,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F173)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA10" s="8">
-        <f>IF('Registo da Rotação'!C164="",0,IF('Registo da Rotação'!D164="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A164,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B164,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C164,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E164)=0,1,0),IF('Registo da Rotação'!D164="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A164,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B164,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C164,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E164)=0,1,0),IF('Registo da Rotação'!D164="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A164,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B164,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C164,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E164)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C173="",0,IF('Registo da Rotação'!D173="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C173,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E173)=0,1,0),IF('Registo da Rotação'!D173="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C173,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E173)=0,1,0),IF('Registo da Rotação'!D173="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C173,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E173)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB10" s="8">
-        <f>IF('Registo da Rotação'!C164="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B164,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H164="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C173="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B173,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H173="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC10" s="1"/>
@@ -9445,7 +9905,7 @@
       </c>
       <c r="Q11" s="8">
         <f>IF('Registo da Rotação'!A60="",0,IF(OR('Registo da Rotação'!F60='Registo da Rotação'!G60,'Registo da Rotação'!F60='Registo da Rotação'!H60,'Registo da Rotação'!G60='Registo da Rotação'!H60),1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="8">
         <f>IF('Registo da Rotação'!A60="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C60,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I60="Ainda não avaliado",'Registo da Rotação'!J60="Ainda não avaliado",'Registo da Rotação'!K60="Ainda não avaliado")),1,0))</f>
@@ -9460,32 +9920,32 @@
         <v>0</v>
       </c>
       <c r="U11" s="8">
-        <f>IF('Registo da Rotação'!A60="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A60)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C60,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D60)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A60="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A60)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C60,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D60)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V11" s="1"/>
       <c r="W11" s="8">
-        <f>IF('Registo da Rotação'!C165="",0,IF(COUNTA('Registo da Rotação'!A165:H165)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C174="",0,IF(COUNTA('Registo da Rotação'!A174:H174)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X11" s="8">
-        <f>IF('Registo da Rotação'!C165="",0,IF('Registo da Rotação'!E165='Registo da Rotação'!F165,1,0))</f>
+        <f>IF('Registo da Rotação'!C174="",0,IF('Registo da Rotação'!E174='Registo da Rotação'!F174,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y11" s="8">
-        <f>IF('Registo da Rotação'!C165="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B165)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C174="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B174)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z11" s="8">
-        <f>IF('Registo da Rotação'!C165="",0,IF('Registo da Rotação'!D165="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A165,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B165,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C165,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F165)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A165,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B165,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C165,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F165)&gt;0,1,0),IF('Registo da Rotação'!D165="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A165,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B165,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C165,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F165)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A165,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B165,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C165,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F165)&gt;0,1,0),IF('Registo da Rotação'!D165="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A165,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B165,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C165,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F165)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A165,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B165,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C165,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F165)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C174="",0,IF('Registo da Rotação'!D174="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C174,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F174)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C174,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F174)&gt;0,1,0),IF('Registo da Rotação'!D174="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C174,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F174)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C174,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F174)&gt;0,1,0),IF('Registo da Rotação'!D174="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C174,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F174)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C174,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F174)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA11" s="8">
-        <f>IF('Registo da Rotação'!C165="",0,IF('Registo da Rotação'!D165="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A165,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B165,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C165,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E165)=0,1,0),IF('Registo da Rotação'!D165="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A165,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B165,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C165,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E165)=0,1,0),IF('Registo da Rotação'!D165="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A165,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B165,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C165,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E165)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C174="",0,IF('Registo da Rotação'!D174="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C174,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E174)=0,1,0),IF('Registo da Rotação'!D174="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C174,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E174)=0,1,0),IF('Registo da Rotação'!D174="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C174,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E174)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB11" s="8">
-        <f>IF('Registo da Rotação'!C165="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B165,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H165="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C174="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B174,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H174="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC11" s="1"/>
@@ -9537,7 +9997,7 @@
       </c>
       <c r="Q12" s="8">
         <f>IF('Registo da Rotação'!A61="",0,IF(OR('Registo da Rotação'!F61='Registo da Rotação'!G61,'Registo da Rotação'!F61='Registo da Rotação'!H61,'Registo da Rotação'!G61='Registo da Rotação'!H61),1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="8">
         <f>IF('Registo da Rotação'!A61="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C61,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I61="Ainda não avaliado",'Registo da Rotação'!J61="Ainda não avaliado",'Registo da Rotação'!K61="Ainda não avaliado")),1,0))</f>
@@ -9545,39 +10005,39 @@
       </c>
       <c r="S12" s="8">
         <f>IF('Registo da Rotação'!A61="",0,IF(AND('Registo da Rotação'!G61=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F60='Registo da Rotação'!F61),'Registo da Rotação'!$G$54:'Registo da Rotação'!G60),""),'Registo da Rotação'!H61=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F60='Registo da Rotação'!F61),'Registo da Rotação'!$H$54:'Registo da Rotação'!H60),"")),1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" s="8">
         <f>IF('Registo da Rotação'!A61="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F60='Registo da Rotação'!F61)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G60='Registo da Rotação'!G61)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H60='Registo da Rotação'!H61)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F60)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F61,'Listas de apoio'!$A$5='Registo da Rotação'!G61,'Listas de apoio'!$A$5='Registo da Rotação'!H61),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F60='Registo da Rotação'!F61),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F60)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F60='Registo da Rotação'!F61)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G60='Registo da Rotação'!G61)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H60='Registo da Rotação'!H61)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F60)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G60='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H60='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F61,'Listas de apoio'!$A$6='Registo da Rotação'!G61,'Listas de apoio'!$A$6='Registo da Rotação'!H61),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F60='Registo da Rotação'!F61),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F60)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F60='Registo da Rotação'!F61)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G60='Registo da Rotação'!G61)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H60='Registo da Rotação'!H61)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F60)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G60='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H60='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F61,'Listas de apoio'!$A$7='Registo da Rotação'!G61,'Listas de apoio'!$A$7='Registo da Rotação'!H61),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F60='Registo da Rotação'!F61),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F60)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F60='Registo da Rotação'!F61)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G60='Registo da Rotação'!G61)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H60='Registo da Rotação'!H61)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F60)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G60='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H60='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F61,'Listas de apoio'!$A$8='Registo da Rotação'!G61,'Listas de apoio'!$A$8='Registo da Rotação'!H61),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F60='Registo da Rotação'!F61),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F60)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F60='Registo da Rotação'!F61)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G60='Registo da Rotação'!G61)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H60='Registo da Rotação'!H61)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F60)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G60='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H60='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U12" s="8">
-        <f>IF('Registo da Rotação'!A61="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A61)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C61,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D61)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A61="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A61)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C61,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D61)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V12" s="1"/>
       <c r="W12" s="8">
-        <f>IF('Registo da Rotação'!C166="",0,IF(COUNTA('Registo da Rotação'!A166:H166)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C175="",0,IF(COUNTA('Registo da Rotação'!A175:H175)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X12" s="8">
-        <f>IF('Registo da Rotação'!C166="",0,IF('Registo da Rotação'!E166='Registo da Rotação'!F166,1,0))</f>
+        <f>IF('Registo da Rotação'!C175="",0,IF('Registo da Rotação'!E175='Registo da Rotação'!F175,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y12" s="8">
-        <f>IF('Registo da Rotação'!C166="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B166)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C175="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B175)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z12" s="8">
-        <f>IF('Registo da Rotação'!C166="",0,IF('Registo da Rotação'!D166="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A166,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B166,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C166,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F166)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A166,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B166,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C166,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F166)&gt;0,1,0),IF('Registo da Rotação'!D166="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A166,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B166,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C166,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F166)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A166,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B166,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C166,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F166)&gt;0,1,0),IF('Registo da Rotação'!D166="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A166,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B166,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C166,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F166)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A166,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B166,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C166,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F166)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C175="",0,IF('Registo da Rotação'!D175="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C175,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F175)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C175,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F175)&gt;0,1,0),IF('Registo da Rotação'!D175="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C175,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F175)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C175,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F175)&gt;0,1,0),IF('Registo da Rotação'!D175="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C175,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F175)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C175,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F175)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA12" s="8">
-        <f>IF('Registo da Rotação'!C166="",0,IF('Registo da Rotação'!D166="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A166,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B166,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C166,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E166)=0,1,0),IF('Registo da Rotação'!D166="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A166,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B166,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C166,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E166)=0,1,0),IF('Registo da Rotação'!D166="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A166,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B166,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C166,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E166)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C175="",0,IF('Registo da Rotação'!D175="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C175,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E175)=0,1,0),IF('Registo da Rotação'!D175="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C175,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E175)=0,1,0),IF('Registo da Rotação'!D175="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C175,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E175)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB12" s="8">
-        <f>IF('Registo da Rotação'!C166="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B166,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H166="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C175="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B175,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H175="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC12" s="1"/>
@@ -9644,32 +10104,32 @@
         <v>0</v>
       </c>
       <c r="U13" s="8">
-        <f>IF('Registo da Rotação'!A62="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A62)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C62,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D62)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A62="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A62)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C62,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D62)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V13" s="1"/>
       <c r="W13" s="8">
-        <f>IF('Registo da Rotação'!C167="",0,IF(COUNTA('Registo da Rotação'!A167:H167)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C176="",0,IF(COUNTA('Registo da Rotação'!A176:H176)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X13" s="8">
-        <f>IF('Registo da Rotação'!C167="",0,IF('Registo da Rotação'!E167='Registo da Rotação'!F167,1,0))</f>
+        <f>IF('Registo da Rotação'!C176="",0,IF('Registo da Rotação'!E176='Registo da Rotação'!F176,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y13" s="8">
-        <f>IF('Registo da Rotação'!C167="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B167)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C176="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B176)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z13" s="8">
-        <f>IF('Registo da Rotação'!C167="",0,IF('Registo da Rotação'!D167="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A167,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B167,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C167,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F167)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A167,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B167,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C167,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F167)&gt;0,1,0),IF('Registo da Rotação'!D167="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A167,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B167,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C167,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F167)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A167,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B167,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C167,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F167)&gt;0,1,0),IF('Registo da Rotação'!D167="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A167,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B167,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C167,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F167)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A167,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B167,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C167,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F167)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C176="",0,IF('Registo da Rotação'!D176="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C176,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F176)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C176,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F176)&gt;0,1,0),IF('Registo da Rotação'!D176="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C176,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F176)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C176,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F176)&gt;0,1,0),IF('Registo da Rotação'!D176="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C176,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F176)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C176,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F176)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA13" s="8">
-        <f>IF('Registo da Rotação'!C167="",0,IF('Registo da Rotação'!D167="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A167,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B167,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C167,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E167)=0,1,0),IF('Registo da Rotação'!D167="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A167,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B167,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C167,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E167)=0,1,0),IF('Registo da Rotação'!D167="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A167,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B167,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C167,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E167)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C176="",0,IF('Registo da Rotação'!D176="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C176,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E176)=0,1,0),IF('Registo da Rotação'!D176="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C176,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E176)=0,1,0),IF('Registo da Rotação'!D176="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C176,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E176)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB13" s="8">
-        <f>IF('Registo da Rotação'!C167="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B167,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H167="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C176="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B176,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H176="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC13" s="1"/>
@@ -9733,35 +10193,35 @@
       </c>
       <c r="T14" s="8">
         <f>IF('Registo da Rotação'!A63="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F62='Registo da Rotação'!F63)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G62='Registo da Rotação'!G63)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H62='Registo da Rotação'!H63)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F62)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F63,'Listas de apoio'!$A$5='Registo da Rotação'!G63,'Listas de apoio'!$A$5='Registo da Rotação'!H63),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F62='Registo da Rotação'!F63),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F62)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F62='Registo da Rotação'!F63)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G62='Registo da Rotação'!G63)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H62='Registo da Rotação'!H63)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F62)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G62='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H62='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F63,'Listas de apoio'!$A$6='Registo da Rotação'!G63,'Listas de apoio'!$A$6='Registo da Rotação'!H63),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F62='Registo da Rotação'!F63),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F62)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F62='Registo da Rotação'!F63)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G62='Registo da Rotação'!G63)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H62='Registo da Rotação'!H63)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F62)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G62='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H62='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F63,'Listas de apoio'!$A$7='Registo da Rotação'!G63,'Listas de apoio'!$A$7='Registo da Rotação'!H63),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F62='Registo da Rotação'!F63),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F62)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F62='Registo da Rotação'!F63)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G62='Registo da Rotação'!G63)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H62='Registo da Rotação'!H63)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F62)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G62='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H62='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F63,'Listas de apoio'!$A$8='Registo da Rotação'!G63,'Listas de apoio'!$A$8='Registo da Rotação'!H63),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F62='Registo da Rotação'!F63),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F62)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F62='Registo da Rotação'!F63)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G62='Registo da Rotação'!G63)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H62='Registo da Rotação'!H63)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F62)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G62='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H62='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" s="8">
-        <f>IF('Registo da Rotação'!A63="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A63)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C63,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D63)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A63="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A63)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C63,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D63)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V14" s="1"/>
       <c r="W14" s="8">
-        <f>IF('Registo da Rotação'!C168="",0,IF(COUNTA('Registo da Rotação'!A168:H168)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C177="",0,IF(COUNTA('Registo da Rotação'!A177:H177)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X14" s="8">
-        <f>IF('Registo da Rotação'!C168="",0,IF('Registo da Rotação'!E168='Registo da Rotação'!F168,1,0))</f>
+        <f>IF('Registo da Rotação'!C177="",0,IF('Registo da Rotação'!E177='Registo da Rotação'!F177,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y14" s="8">
-        <f>IF('Registo da Rotação'!C168="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B168)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C177="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B177)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z14" s="8">
-        <f>IF('Registo da Rotação'!C168="",0,IF('Registo da Rotação'!D168="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C168,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F168)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C168,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F168)&gt;0,1,0),IF('Registo da Rotação'!D168="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C168,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F168)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C168,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F168)&gt;0,1,0),IF('Registo da Rotação'!D168="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C168,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F168)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C168,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F168)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C177="",0,IF('Registo da Rotação'!D177="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C177,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F177)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C177,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F177)&gt;0,1,0),IF('Registo da Rotação'!D177="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C177,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F177)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C177,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F177)&gt;0,1,0),IF('Registo da Rotação'!D177="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C177,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F177)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C177,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F177)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA14" s="8">
-        <f>IF('Registo da Rotação'!C168="",0,IF('Registo da Rotação'!D168="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C168,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E168)=0,1,0),IF('Registo da Rotação'!D168="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C168,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E168)=0,1,0),IF('Registo da Rotação'!D168="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A168,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B168,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C168,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E168)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C177="",0,IF('Registo da Rotação'!D177="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C177,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E177)=0,1,0),IF('Registo da Rotação'!D177="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C177,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E177)=0,1,0),IF('Registo da Rotação'!D177="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C177,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E177)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB14" s="8">
-        <f>IF('Registo da Rotação'!C168="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B168,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H168="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C177="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B177,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H177="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC14" s="1"/>
@@ -9828,32 +10288,32 @@
         <v>0</v>
       </c>
       <c r="U15" s="8">
-        <f>IF('Registo da Rotação'!A64="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A64)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C64,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D64)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A64="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A64)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C64,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D64)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V15" s="1"/>
       <c r="W15" s="8">
-        <f>IF('Registo da Rotação'!C169="",0,IF(COUNTA('Registo da Rotação'!A169:H169)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C178="",0,IF(COUNTA('Registo da Rotação'!A178:H178)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X15" s="8">
-        <f>IF('Registo da Rotação'!C169="",0,IF('Registo da Rotação'!E169='Registo da Rotação'!F169,1,0))</f>
+        <f>IF('Registo da Rotação'!C178="",0,IF('Registo da Rotação'!E178='Registo da Rotação'!F178,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y15" s="8">
-        <f>IF('Registo da Rotação'!C169="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B169)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C178="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B178)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z15" s="8">
-        <f>IF('Registo da Rotação'!C169="",0,IF('Registo da Rotação'!D169="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C169,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F169)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C169,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F169)&gt;0,1,0),IF('Registo da Rotação'!D169="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C169,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F169)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C169,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F169)&gt;0,1,0),IF('Registo da Rotação'!D169="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C169,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F169)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C169,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F169)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C178="",0,IF('Registo da Rotação'!D178="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C178,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F178)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C178,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F178)&gt;0,1,0),IF('Registo da Rotação'!D178="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C178,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F178)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C178,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F178)&gt;0,1,0),IF('Registo da Rotação'!D178="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C178,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F178)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C178,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F178)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA15" s="8">
-        <f>IF('Registo da Rotação'!C169="",0,IF('Registo da Rotação'!D169="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C169,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E169)=0,1,0),IF('Registo da Rotação'!D169="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C169,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E169)=0,1,0),IF('Registo da Rotação'!D169="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A169,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B169,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C169,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E169)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C178="",0,IF('Registo da Rotação'!D178="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C178,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E178)=0,1,0),IF('Registo da Rotação'!D178="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C178,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E178)=0,1,0),IF('Registo da Rotação'!D178="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C178,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E178)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB15" s="8">
-        <f>IF('Registo da Rotação'!C169="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B169,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H169="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C178="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B178,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H178="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC15" s="1"/>
@@ -9920,32 +10380,32 @@
         <v>0</v>
       </c>
       <c r="U16" s="8">
-        <f>IF('Registo da Rotação'!A65="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A65)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C65,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D65)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A65="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A65)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C65,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D65)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V16" s="1"/>
       <c r="W16" s="8">
-        <f>IF('Registo da Rotação'!C170="",0,IF(COUNTA('Registo da Rotação'!A170:H170)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C179="",0,IF(COUNTA('Registo da Rotação'!A179:H179)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X16" s="8">
-        <f>IF('Registo da Rotação'!C170="",0,IF('Registo da Rotação'!E170='Registo da Rotação'!F170,1,0))</f>
+        <f>IF('Registo da Rotação'!C179="",0,IF('Registo da Rotação'!E179='Registo da Rotação'!F179,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y16" s="8">
-        <f>IF('Registo da Rotação'!C170="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B170)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C179="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B179)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z16" s="8">
-        <f>IF('Registo da Rotação'!C170="",0,IF('Registo da Rotação'!D170="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C170,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F170)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C170,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F170)&gt;0,1,0),IF('Registo da Rotação'!D170="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C170,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F170)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C170,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F170)&gt;0,1,0),IF('Registo da Rotação'!D170="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C170,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F170)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C170,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F170)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C179="",0,IF('Registo da Rotação'!D179="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C179,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F179)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C179,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F179)&gt;0,1,0),IF('Registo da Rotação'!D179="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C179,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F179)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C179,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F179)&gt;0,1,0),IF('Registo da Rotação'!D179="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C179,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F179)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C179,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F179)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA16" s="8">
-        <f>IF('Registo da Rotação'!C170="",0,IF('Registo da Rotação'!D170="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C170,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E170)=0,1,0),IF('Registo da Rotação'!D170="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C170,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E170)=0,1,0),IF('Registo da Rotação'!D170="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A170,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B170,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C170,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E170)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C179="",0,IF('Registo da Rotação'!D179="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C179,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E179)=0,1,0),IF('Registo da Rotação'!D179="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C179,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E179)=0,1,0),IF('Registo da Rotação'!D179="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C179,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E179)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB16" s="8">
-        <f>IF('Registo da Rotação'!C170="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B170,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H170="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C179="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B179,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H179="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC16" s="1"/>
@@ -9988,56 +10448,56 @@
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="8">
-        <f>IF('Registo da Rotação'!A66="",0,IF(COUNTA('Registo da Rotação'!B66:K66)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A75="",0,IF(COUNTA('Registo da Rotação'!B75:K75)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P17" s="8">
-        <f>IF('Registo da Rotação'!A66="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C66)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A75="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C75)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q17" s="8">
-        <f>IF('Registo da Rotação'!A66="",0,IF(OR('Registo da Rotação'!F66='Registo da Rotação'!G66,'Registo da Rotação'!F66='Registo da Rotação'!H66,'Registo da Rotação'!G66='Registo da Rotação'!H66),1,0))</f>
+        <f>IF('Registo da Rotação'!A75="",0,IF(OR('Registo da Rotação'!F75='Registo da Rotação'!G75,'Registo da Rotação'!F75='Registo da Rotação'!H75,'Registo da Rotação'!G75='Registo da Rotação'!H75),1,0))</f>
         <v>0</v>
       </c>
       <c r="R17" s="8">
-        <f>IF('Registo da Rotação'!A66="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C66,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I66="Ainda não avaliado",'Registo da Rotação'!J66="Ainda não avaliado",'Registo da Rotação'!K66="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A75="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C75,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I75="Ainda não avaliado",'Registo da Rotação'!J75="Ainda não avaliado",'Registo da Rotação'!K75="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S17" s="8">
-        <f>IF('Registo da Rotação'!A66="",0,IF(AND('Registo da Rotação'!G66=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F66),'Registo da Rotação'!$G$54:'Registo da Rotação'!G65),""),'Registo da Rotação'!H66=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F66),'Registo da Rotação'!$H$54:'Registo da Rotação'!H65),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A75="",0,IF(AND('Registo da Rotação'!G75=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F75),'Registo da Rotação'!$G$54:'Registo da Rotação'!G65),""),'Registo da Rotação'!H75=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F75),'Registo da Rotação'!$H$54:'Registo da Rotação'!H65),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T17" s="8">
-        <f>IF('Registo da Rotação'!A66="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F66)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Registo da Rotação'!G66)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Registo da Rotação'!H66)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F66,'Listas de apoio'!$A$5='Registo da Rotação'!G66,'Listas de apoio'!$A$5='Registo da Rotação'!H66),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F66),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F66)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Registo da Rotação'!G66)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Registo da Rotação'!H66)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F66,'Listas de apoio'!$A$6='Registo da Rotação'!G66,'Listas de apoio'!$A$6='Registo da Rotação'!H66),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F66),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F66)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Registo da Rotação'!G66)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Registo da Rotação'!H66)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F66,'Listas de apoio'!$A$7='Registo da Rotação'!G66,'Listas de apoio'!$A$7='Registo da Rotação'!H66),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F66),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F66)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Registo da Rotação'!G66)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Registo da Rotação'!H66)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F66,'Listas de apoio'!$A$8='Registo da Rotação'!G66,'Listas de apoio'!$A$8='Registo da Rotação'!H66),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F66),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F66)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Registo da Rotação'!G66)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Registo da Rotação'!H66)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A75="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F75)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Registo da Rotação'!G75)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Registo da Rotação'!H75)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F75,'Listas de apoio'!$A$5='Registo da Rotação'!G75,'Listas de apoio'!$A$5='Registo da Rotação'!H75),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F75),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F75)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Registo da Rotação'!G75)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Registo da Rotação'!H75)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F75,'Listas de apoio'!$A$6='Registo da Rotação'!G75,'Listas de apoio'!$A$6='Registo da Rotação'!H75),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F75),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F75)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Registo da Rotação'!G75)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Registo da Rotação'!H75)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F75,'Listas de apoio'!$A$7='Registo da Rotação'!G75,'Listas de apoio'!$A$7='Registo da Rotação'!H75),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F75),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F75)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Registo da Rotação'!G75)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Registo da Rotação'!H75)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F75,'Listas de apoio'!$A$8='Registo da Rotação'!G75,'Listas de apoio'!$A$8='Registo da Rotação'!H75),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F75),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F65='Registo da Rotação'!F75)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Registo da Rotação'!G75)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Registo da Rotação'!H75)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F65)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G65='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H65='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U17" s="8">
-        <f>IF('Registo da Rotação'!A66="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A66)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C66,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D66)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A75="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A75)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C75,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D75)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V17" s="1"/>
       <c r="W17" s="8">
-        <f>IF('Registo da Rotação'!C171="",0,IF(COUNTA('Registo da Rotação'!A171:H171)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C180="",0,IF(COUNTA('Registo da Rotação'!A180:H180)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X17" s="8">
-        <f>IF('Registo da Rotação'!C171="",0,IF('Registo da Rotação'!E171='Registo da Rotação'!F171,1,0))</f>
+        <f>IF('Registo da Rotação'!C180="",0,IF('Registo da Rotação'!E180='Registo da Rotação'!F180,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y17" s="8">
-        <f>IF('Registo da Rotação'!C171="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B171)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C180="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B180)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z17" s="8">
-        <f>IF('Registo da Rotação'!C171="",0,IF('Registo da Rotação'!D171="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C171,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F171)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C171,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F171)&gt;0,1,0),IF('Registo da Rotação'!D171="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C171,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F171)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C171,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F171)&gt;0,1,0),IF('Registo da Rotação'!D171="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C171,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F171)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C171,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F171)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C180="",0,IF('Registo da Rotação'!D180="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C180,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F180)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C180,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F180)&gt;0,1,0),IF('Registo da Rotação'!D180="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C180,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F180)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C180,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F180)&gt;0,1,0),IF('Registo da Rotação'!D180="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C180,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F180)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C180,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F180)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA17" s="8">
-        <f>IF('Registo da Rotação'!C171="",0,IF('Registo da Rotação'!D171="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C171,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E171)=0,1,0),IF('Registo da Rotação'!D171="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C171,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E171)=0,1,0),IF('Registo da Rotação'!D171="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A171,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B171,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C171,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E171)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C180="",0,IF('Registo da Rotação'!D180="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C180,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E180)=0,1,0),IF('Registo da Rotação'!D180="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C180,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E180)=0,1,0),IF('Registo da Rotação'!D180="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C180,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E180)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB17" s="8">
-        <f>IF('Registo da Rotação'!C171="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B171,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H171="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C180="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B180,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H180="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC17" s="1"/>
@@ -10080,56 +10540,56 @@
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="8">
-        <f>IF('Registo da Rotação'!A67="",0,IF(COUNTA('Registo da Rotação'!B67:K67)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A76="",0,IF(COUNTA('Registo da Rotação'!B76:K76)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P18" s="8">
-        <f>IF('Registo da Rotação'!A67="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C67)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A76="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C76)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q18" s="8">
-        <f>IF('Registo da Rotação'!A67="",0,IF(OR('Registo da Rotação'!F67='Registo da Rotação'!G67,'Registo da Rotação'!F67='Registo da Rotação'!H67,'Registo da Rotação'!G67='Registo da Rotação'!H67),1,0))</f>
+        <f>IF('Registo da Rotação'!A76="",0,IF(OR('Registo da Rotação'!F76='Registo da Rotação'!G76,'Registo da Rotação'!F76='Registo da Rotação'!H76,'Registo da Rotação'!G76='Registo da Rotação'!H76),1,0))</f>
         <v>0</v>
       </c>
       <c r="R18" s="8">
-        <f>IF('Registo da Rotação'!A67="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C67,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I67="Ainda não avaliado",'Registo da Rotação'!J67="Ainda não avaliado",'Registo da Rotação'!K67="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A76="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C76,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I76="Ainda não avaliado",'Registo da Rotação'!J76="Ainda não avaliado",'Registo da Rotação'!K76="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S18" s="8">
-        <f>IF('Registo da Rotação'!A67="",0,IF(AND('Registo da Rotação'!G67=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F66='Registo da Rotação'!F67),'Registo da Rotação'!$G$54:'Registo da Rotação'!G66),""),'Registo da Rotação'!H67=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F66='Registo da Rotação'!F67),'Registo da Rotação'!$H$54:'Registo da Rotação'!H66),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A76="",0,IF(AND('Registo da Rotação'!G76=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76),'Registo da Rotação'!$G$54:'Registo da Rotação'!G75),""),'Registo da Rotação'!H76=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76),'Registo da Rotação'!$H$54:'Registo da Rotação'!H75),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T18" s="8">
-        <f>IF('Registo da Rotação'!A67="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F66='Registo da Rotação'!F67)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G66='Registo da Rotação'!G67)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H66='Registo da Rotação'!H67)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F66)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F67,'Listas de apoio'!$A$5='Registo da Rotação'!G67,'Listas de apoio'!$A$5='Registo da Rotação'!H67),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F66='Registo da Rotação'!F67),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F66)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F66='Registo da Rotação'!F67)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G66='Registo da Rotação'!G67)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H66='Registo da Rotação'!H67)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F66)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G66='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H66='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F67,'Listas de apoio'!$A$6='Registo da Rotação'!G67,'Listas de apoio'!$A$6='Registo da Rotação'!H67),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F66='Registo da Rotação'!F67),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F66)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F66='Registo da Rotação'!F67)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G66='Registo da Rotação'!G67)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H66='Registo da Rotação'!H67)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F66)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G66='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H66='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F67,'Listas de apoio'!$A$7='Registo da Rotação'!G67,'Listas de apoio'!$A$7='Registo da Rotação'!H67),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F66='Registo da Rotação'!F67),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F66)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F66='Registo da Rotação'!F67)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G66='Registo da Rotação'!G67)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H66='Registo da Rotação'!H67)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F66)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G66='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H66='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F67,'Listas de apoio'!$A$8='Registo da Rotação'!G67,'Listas de apoio'!$A$8='Registo da Rotação'!H67),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F66='Registo da Rotação'!F67),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F66)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F66='Registo da Rotação'!F67)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G66='Registo da Rotação'!G67)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H66='Registo da Rotação'!H67)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F66)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G66='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H66='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A76="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Registo da Rotação'!G76)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Registo da Rotação'!H76)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F76,'Listas de apoio'!$A$5='Registo da Rotação'!G76,'Listas de apoio'!$A$5='Registo da Rotação'!H76),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Registo da Rotação'!G76)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Registo da Rotação'!H76)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F76,'Listas de apoio'!$A$6='Registo da Rotação'!G76,'Listas de apoio'!$A$6='Registo da Rotação'!H76),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Registo da Rotação'!G76)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Registo da Rotação'!H76)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F76,'Listas de apoio'!$A$7='Registo da Rotação'!G76,'Listas de apoio'!$A$7='Registo da Rotação'!H76),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Registo da Rotação'!G76)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Registo da Rotação'!H76)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F76,'Listas de apoio'!$A$8='Registo da Rotação'!G76,'Listas de apoio'!$A$8='Registo da Rotação'!H76),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Registo da Rotação'!G76)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Registo da Rotação'!H76)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U18" s="8">
-        <f>IF('Registo da Rotação'!A67="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A67)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C67,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D67)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A76="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A76)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C76,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D76)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V18" s="1"/>
       <c r="W18" s="8">
-        <f>IF('Registo da Rotação'!C172="",0,IF(COUNTA('Registo da Rotação'!A172:H172)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C181="",0,IF(COUNTA('Registo da Rotação'!A181:H181)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X18" s="8">
-        <f>IF('Registo da Rotação'!C172="",0,IF('Registo da Rotação'!E172='Registo da Rotação'!F172,1,0))</f>
+        <f>IF('Registo da Rotação'!C181="",0,IF('Registo da Rotação'!E181='Registo da Rotação'!F181,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y18" s="8">
-        <f>IF('Registo da Rotação'!C172="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B172)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C181="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B181)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z18" s="8">
-        <f>IF('Registo da Rotação'!C172="",0,IF('Registo da Rotação'!D172="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C172,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F172)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C172,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F172)&gt;0,1,0),IF('Registo da Rotação'!D172="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C172,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F172)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C172,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F172)&gt;0,1,0),IF('Registo da Rotação'!D172="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C172,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F172)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C172,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F172)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C181="",0,IF('Registo da Rotação'!D181="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C181,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F181)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C181,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F181)&gt;0,1,0),IF('Registo da Rotação'!D181="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C181,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F181)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C181,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F181)&gt;0,1,0),IF('Registo da Rotação'!D181="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C181,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F181)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C181,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F181)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA18" s="8">
-        <f>IF('Registo da Rotação'!C172="",0,IF('Registo da Rotação'!D172="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C172,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E172)=0,1,0),IF('Registo da Rotação'!D172="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C172,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E172)=0,1,0),IF('Registo da Rotação'!D172="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A172,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B172,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C172,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E172)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C181="",0,IF('Registo da Rotação'!D181="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C181,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E181)=0,1,0),IF('Registo da Rotação'!D181="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C181,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E181)=0,1,0),IF('Registo da Rotação'!D181="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C181,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E181)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB18" s="8">
-        <f>IF('Registo da Rotação'!C172="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B172,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H172="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C181="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B181,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H181="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC18" s="1"/>
@@ -10172,56 +10632,56 @@
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="8">
-        <f>IF('Registo da Rotação'!A68="",0,IF(COUNTA('Registo da Rotação'!B68:K68)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A77="",0,IF(COUNTA('Registo da Rotação'!B77:K77)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P19" s="8">
-        <f>IF('Registo da Rotação'!A68="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C68)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A77="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C77)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q19" s="8">
-        <f>IF('Registo da Rotação'!A68="",0,IF(OR('Registo da Rotação'!F68='Registo da Rotação'!G68,'Registo da Rotação'!F68='Registo da Rotação'!H68,'Registo da Rotação'!G68='Registo da Rotação'!H68),1,0))</f>
+        <f>IF('Registo da Rotação'!A77="",0,IF(OR('Registo da Rotação'!F77='Registo da Rotação'!G77,'Registo da Rotação'!F77='Registo da Rotação'!H77,'Registo da Rotação'!G77='Registo da Rotação'!H77),1,0))</f>
         <v>0</v>
       </c>
       <c r="R19" s="8">
-        <f>IF('Registo da Rotação'!A68="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C68,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I68="Ainda não avaliado",'Registo da Rotação'!J68="Ainda não avaliado",'Registo da Rotação'!K68="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A77="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C77,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I77="Ainda não avaliado",'Registo da Rotação'!J77="Ainda não avaliado",'Registo da Rotação'!K77="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S19" s="8">
-        <f>IF('Registo da Rotação'!A68="",0,IF(AND('Registo da Rotação'!G68=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F67='Registo da Rotação'!F68),'Registo da Rotação'!$G$54:'Registo da Rotação'!G67),""),'Registo da Rotação'!H68=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F67='Registo da Rotação'!F68),'Registo da Rotação'!$H$54:'Registo da Rotação'!H67),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A77="",0,IF(AND('Registo da Rotação'!G77=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77),'Registo da Rotação'!$G$54:'Registo da Rotação'!G76),""),'Registo da Rotação'!H77=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77),'Registo da Rotação'!$H$54:'Registo da Rotação'!H76),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T19" s="8">
-        <f>IF('Registo da Rotação'!A68="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F67='Registo da Rotação'!F68)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G67='Registo da Rotação'!G68)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H67='Registo da Rotação'!H68)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F67)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F68,'Listas de apoio'!$A$5='Registo da Rotação'!G68,'Listas de apoio'!$A$5='Registo da Rotação'!H68),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F67='Registo da Rotação'!F68),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F67)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F67='Registo da Rotação'!F68)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G67='Registo da Rotação'!G68)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H67='Registo da Rotação'!H68)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F67)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G67='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H67='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F68,'Listas de apoio'!$A$6='Registo da Rotação'!G68,'Listas de apoio'!$A$6='Registo da Rotação'!H68),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F67='Registo da Rotação'!F68),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F67)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F67='Registo da Rotação'!F68)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G67='Registo da Rotação'!G68)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H67='Registo da Rotação'!H68)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F67)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G67='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H67='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F68,'Listas de apoio'!$A$7='Registo da Rotação'!G68,'Listas de apoio'!$A$7='Registo da Rotação'!H68),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F67='Registo da Rotação'!F68),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F67)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F67='Registo da Rotação'!F68)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G67='Registo da Rotação'!G68)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H67='Registo da Rotação'!H68)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F67)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G67='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H67='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F68,'Listas de apoio'!$A$8='Registo da Rotação'!G68,'Listas de apoio'!$A$8='Registo da Rotação'!H68),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F67='Registo da Rotação'!F68),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F67)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F67='Registo da Rotação'!F68)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G67='Registo da Rotação'!G68)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H67='Registo da Rotação'!H68)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F67)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G67='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H67='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A77="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Registo da Rotação'!G77)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Registo da Rotação'!H77)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F77,'Listas de apoio'!$A$5='Registo da Rotação'!G77,'Listas de apoio'!$A$5='Registo da Rotação'!H77),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Registo da Rotação'!G77)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Registo da Rotação'!H77)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F77,'Listas de apoio'!$A$6='Registo da Rotação'!G77,'Listas de apoio'!$A$6='Registo da Rotação'!H77),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Registo da Rotação'!G77)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Registo da Rotação'!H77)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F77,'Listas de apoio'!$A$7='Registo da Rotação'!G77,'Listas de apoio'!$A$7='Registo da Rotação'!H77),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Registo da Rotação'!G77)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Registo da Rotação'!H77)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F77,'Listas de apoio'!$A$8='Registo da Rotação'!G77,'Listas de apoio'!$A$8='Registo da Rotação'!H77),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Registo da Rotação'!G77)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Registo da Rotação'!H77)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U19" s="8">
-        <f>IF('Registo da Rotação'!A68="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A68)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C68,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D68)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A77="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A77)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C77,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D77)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V19" s="1"/>
       <c r="W19" s="8">
-        <f>IF('Registo da Rotação'!C173="",0,IF(COUNTA('Registo da Rotação'!A173:H173)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C182="",0,IF(COUNTA('Registo da Rotação'!A182:H182)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X19" s="8">
-        <f>IF('Registo da Rotação'!C173="",0,IF('Registo da Rotação'!E173='Registo da Rotação'!F173,1,0))</f>
+        <f>IF('Registo da Rotação'!C182="",0,IF('Registo da Rotação'!E182='Registo da Rotação'!F182,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y19" s="8">
-        <f>IF('Registo da Rotação'!C173="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B173)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C182="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B182)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z19" s="8">
-        <f>IF('Registo da Rotação'!C173="",0,IF('Registo da Rotação'!D173="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C173,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F173)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C173,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F173)&gt;0,1,0),IF('Registo da Rotação'!D173="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C173,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F173)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C173,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F173)&gt;0,1,0),IF('Registo da Rotação'!D173="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C173,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F173)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C173,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F173)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C182="",0,IF('Registo da Rotação'!D182="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C182,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F182)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C182,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F182)&gt;0,1,0),IF('Registo da Rotação'!D182="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C182,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F182)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C182,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F182)&gt;0,1,0),IF('Registo da Rotação'!D182="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C182,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F182)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C182,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F182)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA19" s="8">
-        <f>IF('Registo da Rotação'!C173="",0,IF('Registo da Rotação'!D173="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C173,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E173)=0,1,0),IF('Registo da Rotação'!D173="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C173,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E173)=0,1,0),IF('Registo da Rotação'!D173="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A173,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B173,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C173,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E173)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C182="",0,IF('Registo da Rotação'!D182="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C182,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E182)=0,1,0),IF('Registo da Rotação'!D182="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C182,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E182)=0,1,0),IF('Registo da Rotação'!D182="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C182,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E182)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB19" s="8">
-        <f>IF('Registo da Rotação'!C173="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B173,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H173="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C182="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B182,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H182="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC19" s="1"/>
@@ -10264,56 +10724,56 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="8">
-        <f>IF('Registo da Rotação'!A69="",0,IF(COUNTA('Registo da Rotação'!B69:K69)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A78="",0,IF(COUNTA('Registo da Rotação'!B78:K78)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P20" s="8">
-        <f>IF('Registo da Rotação'!A69="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C69)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A78="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C78)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q20" s="8">
-        <f>IF('Registo da Rotação'!A69="",0,IF(OR('Registo da Rotação'!F69='Registo da Rotação'!G69,'Registo da Rotação'!F69='Registo da Rotação'!H69,'Registo da Rotação'!G69='Registo da Rotação'!H69),1,0))</f>
+        <f>IF('Registo da Rotação'!A78="",0,IF(OR('Registo da Rotação'!F78='Registo da Rotação'!G78,'Registo da Rotação'!F78='Registo da Rotação'!H78,'Registo da Rotação'!G78='Registo da Rotação'!H78),1,0))</f>
         <v>0</v>
       </c>
       <c r="R20" s="8">
-        <f>IF('Registo da Rotação'!A69="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C69,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I69="Ainda não avaliado",'Registo da Rotação'!J69="Ainda não avaliado",'Registo da Rotação'!K69="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A78="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C78,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I78="Ainda não avaliado",'Registo da Rotação'!J78="Ainda não avaliado",'Registo da Rotação'!K78="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S20" s="8">
-        <f>IF('Registo da Rotação'!A69="",0,IF(AND('Registo da Rotação'!G69=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F68='Registo da Rotação'!F69),'Registo da Rotação'!$G$54:'Registo da Rotação'!G68),""),'Registo da Rotação'!H69=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F68='Registo da Rotação'!F69),'Registo da Rotação'!$H$54:'Registo da Rotação'!H68),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A78="",0,IF(AND('Registo da Rotação'!G78=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78),'Registo da Rotação'!$G$54:'Registo da Rotação'!G77),""),'Registo da Rotação'!H78=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78),'Registo da Rotação'!$H$54:'Registo da Rotação'!H77),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T20" s="8">
-        <f>IF('Registo da Rotação'!A69="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F68='Registo da Rotação'!F69)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G68='Registo da Rotação'!G69)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H68='Registo da Rotação'!H69)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F68)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F69,'Listas de apoio'!$A$5='Registo da Rotação'!G69,'Listas de apoio'!$A$5='Registo da Rotação'!H69),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F68='Registo da Rotação'!F69),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F68)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F68='Registo da Rotação'!F69)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G68='Registo da Rotação'!G69)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H68='Registo da Rotação'!H69)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F68)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G68='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H68='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F69,'Listas de apoio'!$A$6='Registo da Rotação'!G69,'Listas de apoio'!$A$6='Registo da Rotação'!H69),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F68='Registo da Rotação'!F69),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F68)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F68='Registo da Rotação'!F69)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G68='Registo da Rotação'!G69)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H68='Registo da Rotação'!H69)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F68)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G68='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H68='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F69,'Listas de apoio'!$A$7='Registo da Rotação'!G69,'Listas de apoio'!$A$7='Registo da Rotação'!H69),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F68='Registo da Rotação'!F69),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F68)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F68='Registo da Rotação'!F69)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G68='Registo da Rotação'!G69)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H68='Registo da Rotação'!H69)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F68)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G68='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H68='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F69,'Listas de apoio'!$A$8='Registo da Rotação'!G69,'Listas de apoio'!$A$8='Registo da Rotação'!H69),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F68='Registo da Rotação'!F69),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F68)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F68='Registo da Rotação'!F69)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G68='Registo da Rotação'!G69)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H68='Registo da Rotação'!H69)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F68)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G68='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H68='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A78="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Registo da Rotação'!G78)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Registo da Rotação'!H78)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F78,'Listas de apoio'!$A$5='Registo da Rotação'!G78,'Listas de apoio'!$A$5='Registo da Rotação'!H78),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Registo da Rotação'!G78)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Registo da Rotação'!H78)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F78,'Listas de apoio'!$A$6='Registo da Rotação'!G78,'Listas de apoio'!$A$6='Registo da Rotação'!H78),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Registo da Rotação'!G78)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Registo da Rotação'!H78)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F78,'Listas de apoio'!$A$7='Registo da Rotação'!G78,'Listas de apoio'!$A$7='Registo da Rotação'!H78),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Registo da Rotação'!G78)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Registo da Rotação'!H78)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F78,'Listas de apoio'!$A$8='Registo da Rotação'!G78,'Listas de apoio'!$A$8='Registo da Rotação'!H78),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Registo da Rotação'!G78)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Registo da Rotação'!H78)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U20" s="8">
-        <f>IF('Registo da Rotação'!A69="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A69)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C69,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D69)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A78="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A78)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C78,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D78)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V20" s="1"/>
       <c r="W20" s="8">
-        <f>IF('Registo da Rotação'!C174="",0,IF(COUNTA('Registo da Rotação'!A174:H174)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C183="",0,IF(COUNTA('Registo da Rotação'!A183:H183)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X20" s="8">
-        <f>IF('Registo da Rotação'!C174="",0,IF('Registo da Rotação'!E174='Registo da Rotação'!F174,1,0))</f>
+        <f>IF('Registo da Rotação'!C183="",0,IF('Registo da Rotação'!E183='Registo da Rotação'!F183,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y20" s="8">
-        <f>IF('Registo da Rotação'!C174="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B174)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C183="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B183)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z20" s="8">
-        <f>IF('Registo da Rotação'!C174="",0,IF('Registo da Rotação'!D174="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C174,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F174)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C174,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F174)&gt;0,1,0),IF('Registo da Rotação'!D174="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C174,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F174)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C174,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F174)&gt;0,1,0),IF('Registo da Rotação'!D174="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C174,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F174)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C174,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F174)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C183="",0,IF('Registo da Rotação'!D183="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C183,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F183)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C183,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F183)&gt;0,1,0),IF('Registo da Rotação'!D183="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C183,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F183)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C183,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F183)&gt;0,1,0),IF('Registo da Rotação'!D183="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C183,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F183)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C183,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F183)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA20" s="8">
-        <f>IF('Registo da Rotação'!C174="",0,IF('Registo da Rotação'!D174="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C174,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E174)=0,1,0),IF('Registo da Rotação'!D174="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C174,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E174)=0,1,0),IF('Registo da Rotação'!D174="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A174,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B174,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C174,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E174)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C183="",0,IF('Registo da Rotação'!D183="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C183,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E183)=0,1,0),IF('Registo da Rotação'!D183="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C183,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E183)=0,1,0),IF('Registo da Rotação'!D183="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C183,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E183)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB20" s="8">
-        <f>IF('Registo da Rotação'!C174="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B174,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H174="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C183="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B183,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H183="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC20" s="1"/>
@@ -10356,56 +10816,56 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="8">
-        <f>IF('Registo da Rotação'!A70="",0,IF(COUNTA('Registo da Rotação'!B70:K70)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A79="",0,IF(COUNTA('Registo da Rotação'!B79:K79)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P21" s="8">
-        <f>IF('Registo da Rotação'!A70="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C70)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A79="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C79)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q21" s="8">
-        <f>IF('Registo da Rotação'!A70="",0,IF(OR('Registo da Rotação'!F70='Registo da Rotação'!G70,'Registo da Rotação'!F70='Registo da Rotação'!H70,'Registo da Rotação'!G70='Registo da Rotação'!H70),1,0))</f>
+        <f>IF('Registo da Rotação'!A79="",0,IF(OR('Registo da Rotação'!F79='Registo da Rotação'!G79,'Registo da Rotação'!F79='Registo da Rotação'!H79,'Registo da Rotação'!G79='Registo da Rotação'!H79),1,0))</f>
         <v>0</v>
       </c>
       <c r="R21" s="8">
-        <f>IF('Registo da Rotação'!A70="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C70,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I70="Ainda não avaliado",'Registo da Rotação'!J70="Ainda não avaliado",'Registo da Rotação'!K70="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A79="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C79,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I79="Ainda não avaliado",'Registo da Rotação'!J79="Ainda não avaliado",'Registo da Rotação'!K79="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S21" s="8">
-        <f>IF('Registo da Rotação'!A70="",0,IF(AND('Registo da Rotação'!G70=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F69='Registo da Rotação'!F70),'Registo da Rotação'!$G$54:'Registo da Rotação'!G69),""),'Registo da Rotação'!H70=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F69='Registo da Rotação'!F70),'Registo da Rotação'!$H$54:'Registo da Rotação'!H69),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A79="",0,IF(AND('Registo da Rotação'!G79=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79),'Registo da Rotação'!$G$54:'Registo da Rotação'!G78),""),'Registo da Rotação'!H79=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79),'Registo da Rotação'!$H$54:'Registo da Rotação'!H78),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T21" s="8">
-        <f>IF('Registo da Rotação'!A70="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F69='Registo da Rotação'!F70)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G69='Registo da Rotação'!G70)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H69='Registo da Rotação'!H70)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F69)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F70,'Listas de apoio'!$A$5='Registo da Rotação'!G70,'Listas de apoio'!$A$5='Registo da Rotação'!H70),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F69='Registo da Rotação'!F70),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F69)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F69='Registo da Rotação'!F70)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G69='Registo da Rotação'!G70)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H69='Registo da Rotação'!H70)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F69)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G69='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H69='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F70,'Listas de apoio'!$A$6='Registo da Rotação'!G70,'Listas de apoio'!$A$6='Registo da Rotação'!H70),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F69='Registo da Rotação'!F70),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F69)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F69='Registo da Rotação'!F70)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G69='Registo da Rotação'!G70)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H69='Registo da Rotação'!H70)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F69)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G69='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H69='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F70,'Listas de apoio'!$A$7='Registo da Rotação'!G70,'Listas de apoio'!$A$7='Registo da Rotação'!H70),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F69='Registo da Rotação'!F70),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F69)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F69='Registo da Rotação'!F70)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G69='Registo da Rotação'!G70)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H69='Registo da Rotação'!H70)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F69)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G69='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H69='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F70,'Listas de apoio'!$A$8='Registo da Rotação'!G70,'Listas de apoio'!$A$8='Registo da Rotação'!H70),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F69='Registo da Rotação'!F70),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F69)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F69='Registo da Rotação'!F70)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G69='Registo da Rotação'!G70)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H69='Registo da Rotação'!H70)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F69)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G69='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H69='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A79="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Registo da Rotação'!G79)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Registo da Rotação'!H79)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F79,'Listas de apoio'!$A$5='Registo da Rotação'!G79,'Listas de apoio'!$A$5='Registo da Rotação'!H79),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Registo da Rotação'!G79)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Registo da Rotação'!H79)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F79,'Listas de apoio'!$A$6='Registo da Rotação'!G79,'Listas de apoio'!$A$6='Registo da Rotação'!H79),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Registo da Rotação'!G79)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Registo da Rotação'!H79)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F79,'Listas de apoio'!$A$7='Registo da Rotação'!G79,'Listas de apoio'!$A$7='Registo da Rotação'!H79),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Registo da Rotação'!G79)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Registo da Rotação'!H79)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F79,'Listas de apoio'!$A$8='Registo da Rotação'!G79,'Listas de apoio'!$A$8='Registo da Rotação'!H79),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Registo da Rotação'!G79)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Registo da Rotação'!H79)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U21" s="8">
-        <f>IF('Registo da Rotação'!A70="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A70)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C70,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D70)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A79="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A79)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C79,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D79)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V21" s="1"/>
       <c r="W21" s="8">
-        <f>IF('Registo da Rotação'!C175="",0,IF(COUNTA('Registo da Rotação'!A175:H175)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C184="",0,IF(COUNTA('Registo da Rotação'!A184:H184)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X21" s="8">
-        <f>IF('Registo da Rotação'!C175="",0,IF('Registo da Rotação'!E175='Registo da Rotação'!F175,1,0))</f>
+        <f>IF('Registo da Rotação'!C184="",0,IF('Registo da Rotação'!E184='Registo da Rotação'!F184,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y21" s="8">
-        <f>IF('Registo da Rotação'!C175="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B175)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C184="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B184)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z21" s="8">
-        <f>IF('Registo da Rotação'!C175="",0,IF('Registo da Rotação'!D175="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C175,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F175)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C175,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F175)&gt;0,1,0),IF('Registo da Rotação'!D175="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C175,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F175)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C175,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F175)&gt;0,1,0),IF('Registo da Rotação'!D175="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C175,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F175)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C175,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F175)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C184="",0,IF('Registo da Rotação'!D184="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C184,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F184)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C184,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F184)&gt;0,1,0),IF('Registo da Rotação'!D184="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C184,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F184)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C184,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F184)&gt;0,1,0),IF('Registo da Rotação'!D184="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C184,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F184)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C184,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F184)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA21" s="8">
-        <f>IF('Registo da Rotação'!C175="",0,IF('Registo da Rotação'!D175="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C175,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E175)=0,1,0),IF('Registo da Rotação'!D175="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C175,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E175)=0,1,0),IF('Registo da Rotação'!D175="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A175,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B175,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C175,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E175)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C184="",0,IF('Registo da Rotação'!D184="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C184,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E184)=0,1,0),IF('Registo da Rotação'!D184="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C184,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E184)=0,1,0),IF('Registo da Rotação'!D184="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C184,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E184)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB21" s="8">
-        <f>IF('Registo da Rotação'!C175="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B175,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H175="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C184="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B184,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H184="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC21" s="1"/>
@@ -10448,56 +10908,56 @@
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="8">
-        <f>IF('Registo da Rotação'!A71="",0,IF(COUNTA('Registo da Rotação'!B71:K71)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A80="",0,IF(COUNTA('Registo da Rotação'!B80:K80)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P22" s="8">
-        <f>IF('Registo da Rotação'!A71="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C71)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A80="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C80)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q22" s="8">
-        <f>IF('Registo da Rotação'!A71="",0,IF(OR('Registo da Rotação'!F71='Registo da Rotação'!G71,'Registo da Rotação'!F71='Registo da Rotação'!H71,'Registo da Rotação'!G71='Registo da Rotação'!H71),1,0))</f>
+        <f>IF('Registo da Rotação'!A80="",0,IF(OR('Registo da Rotação'!F80='Registo da Rotação'!G80,'Registo da Rotação'!F80='Registo da Rotação'!H80,'Registo da Rotação'!G80='Registo da Rotação'!H80),1,0))</f>
         <v>0</v>
       </c>
       <c r="R22" s="8">
-        <f>IF('Registo da Rotação'!A71="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C71,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I71="Ainda não avaliado",'Registo da Rotação'!J71="Ainda não avaliado",'Registo da Rotação'!K71="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A80="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C80,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I80="Ainda não avaliado",'Registo da Rotação'!J80="Ainda não avaliado",'Registo da Rotação'!K80="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S22" s="8">
-        <f>IF('Registo da Rotação'!A71="",0,IF(AND('Registo da Rotação'!G71=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F70='Registo da Rotação'!F71),'Registo da Rotação'!$G$54:'Registo da Rotação'!G70),""),'Registo da Rotação'!H71=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F70='Registo da Rotação'!F71),'Registo da Rotação'!$H$54:'Registo da Rotação'!H70),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A80="",0,IF(AND('Registo da Rotação'!G80=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80),'Registo da Rotação'!$G$54:'Registo da Rotação'!G79),""),'Registo da Rotação'!H80=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80),'Registo da Rotação'!$H$54:'Registo da Rotação'!H79),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T22" s="8">
-        <f>IF('Registo da Rotação'!A71="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F70='Registo da Rotação'!F71)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G70='Registo da Rotação'!G71)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H70='Registo da Rotação'!H71)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F70)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F71,'Listas de apoio'!$A$5='Registo da Rotação'!G71,'Listas de apoio'!$A$5='Registo da Rotação'!H71),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F70='Registo da Rotação'!F71),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F70)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F70='Registo da Rotação'!F71)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G70='Registo da Rotação'!G71)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H70='Registo da Rotação'!H71)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F70)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G70='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H70='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F71,'Listas de apoio'!$A$6='Registo da Rotação'!G71,'Listas de apoio'!$A$6='Registo da Rotação'!H71),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F70='Registo da Rotação'!F71),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F70)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F70='Registo da Rotação'!F71)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G70='Registo da Rotação'!G71)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H70='Registo da Rotação'!H71)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F70)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G70='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H70='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F71,'Listas de apoio'!$A$7='Registo da Rotação'!G71,'Listas de apoio'!$A$7='Registo da Rotação'!H71),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F70='Registo da Rotação'!F71),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F70)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F70='Registo da Rotação'!F71)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G70='Registo da Rotação'!G71)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H70='Registo da Rotação'!H71)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F70)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G70='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H70='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F71,'Listas de apoio'!$A$8='Registo da Rotação'!G71,'Listas de apoio'!$A$8='Registo da Rotação'!H71),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F70='Registo da Rotação'!F71),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F70)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F70='Registo da Rotação'!F71)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G70='Registo da Rotação'!G71)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H70='Registo da Rotação'!H71)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F70)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G70='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H70='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A80="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Registo da Rotação'!G80)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Registo da Rotação'!H80)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F80,'Listas de apoio'!$A$5='Registo da Rotação'!G80,'Listas de apoio'!$A$5='Registo da Rotação'!H80),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Registo da Rotação'!G80)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Registo da Rotação'!H80)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F80,'Listas de apoio'!$A$6='Registo da Rotação'!G80,'Listas de apoio'!$A$6='Registo da Rotação'!H80),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Registo da Rotação'!G80)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Registo da Rotação'!H80)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F80,'Listas de apoio'!$A$7='Registo da Rotação'!G80,'Listas de apoio'!$A$7='Registo da Rotação'!H80),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Registo da Rotação'!G80)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Registo da Rotação'!H80)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F80,'Listas de apoio'!$A$8='Registo da Rotação'!G80,'Listas de apoio'!$A$8='Registo da Rotação'!H80),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Registo da Rotação'!G80)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Registo da Rotação'!H80)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U22" s="8">
-        <f>IF('Registo da Rotação'!A71="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A71)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C71,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D71)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A80="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A80)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C80,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D80)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V22" s="1"/>
       <c r="W22" s="8">
-        <f>IF('Registo da Rotação'!C176="",0,IF(COUNTA('Registo da Rotação'!A176:H176)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C185="",0,IF(COUNTA('Registo da Rotação'!A185:H185)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X22" s="8">
-        <f>IF('Registo da Rotação'!C176="",0,IF('Registo da Rotação'!E176='Registo da Rotação'!F176,1,0))</f>
+        <f>IF('Registo da Rotação'!C185="",0,IF('Registo da Rotação'!E185='Registo da Rotação'!F185,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y22" s="8">
-        <f>IF('Registo da Rotação'!C176="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B176)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C185="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B185)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z22" s="8">
-        <f>IF('Registo da Rotação'!C176="",0,IF('Registo da Rotação'!D176="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C176,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F176)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C176,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F176)&gt;0,1,0),IF('Registo da Rotação'!D176="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C176,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F176)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C176,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F176)&gt;0,1,0),IF('Registo da Rotação'!D176="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C176,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F176)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C176,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F176)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C185="",0,IF('Registo da Rotação'!D185="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C185,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F185)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C185,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F185)&gt;0,1,0),IF('Registo da Rotação'!D185="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C185,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F185)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C185,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F185)&gt;0,1,0),IF('Registo da Rotação'!D185="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C185,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F185)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C185,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F185)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA22" s="8">
-        <f>IF('Registo da Rotação'!C176="",0,IF('Registo da Rotação'!D176="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C176,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E176)=0,1,0),IF('Registo da Rotação'!D176="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C176,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E176)=0,1,0),IF('Registo da Rotação'!D176="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A176,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B176,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C176,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E176)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C185="",0,IF('Registo da Rotação'!D185="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C185,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E185)=0,1,0),IF('Registo da Rotação'!D185="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C185,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E185)=0,1,0),IF('Registo da Rotação'!D185="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C185,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E185)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB22" s="8">
-        <f>IF('Registo da Rotação'!C176="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B176,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H176="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C185="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B185,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H185="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC22" s="1"/>
@@ -10540,56 +11000,56 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="8">
-        <f>IF('Registo da Rotação'!A72="",0,IF(COUNTA('Registo da Rotação'!B72:K72)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A81="",0,IF(COUNTA('Registo da Rotação'!B81:K81)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P23" s="8">
-        <f>IF('Registo da Rotação'!A72="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C72)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A81="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C81)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q23" s="8">
-        <f>IF('Registo da Rotação'!A72="",0,IF(OR('Registo da Rotação'!F72='Registo da Rotação'!G72,'Registo da Rotação'!F72='Registo da Rotação'!H72,'Registo da Rotação'!G72='Registo da Rotação'!H72),1,0))</f>
+        <f>IF('Registo da Rotação'!A81="",0,IF(OR('Registo da Rotação'!F81='Registo da Rotação'!G81,'Registo da Rotação'!F81='Registo da Rotação'!H81,'Registo da Rotação'!G81='Registo da Rotação'!H81),1,0))</f>
         <v>0</v>
       </c>
       <c r="R23" s="8">
-        <f>IF('Registo da Rotação'!A72="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C72,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I72="Ainda não avaliado",'Registo da Rotação'!J72="Ainda não avaliado",'Registo da Rotação'!K72="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A81="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C81,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I81="Ainda não avaliado",'Registo da Rotação'!J81="Ainda não avaliado",'Registo da Rotação'!K81="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S23" s="8">
-        <f>IF('Registo da Rotação'!A72="",0,IF(AND('Registo da Rotação'!G72=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F71='Registo da Rotação'!F72),'Registo da Rotação'!$G$54:'Registo da Rotação'!G71),""),'Registo da Rotação'!H72=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F71='Registo da Rotação'!F72),'Registo da Rotação'!$H$54:'Registo da Rotação'!H71),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A81="",0,IF(AND('Registo da Rotação'!G81=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81),'Registo da Rotação'!$G$54:'Registo da Rotação'!G80),""),'Registo da Rotação'!H81=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81),'Registo da Rotação'!$H$54:'Registo da Rotação'!H80),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T23" s="8">
-        <f>IF('Registo da Rotação'!A72="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F71='Registo da Rotação'!F72)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G71='Registo da Rotação'!G72)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H71='Registo da Rotação'!H72)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F71)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F72,'Listas de apoio'!$A$5='Registo da Rotação'!G72,'Listas de apoio'!$A$5='Registo da Rotação'!H72),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F71='Registo da Rotação'!F72),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F71)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F71='Registo da Rotação'!F72)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G71='Registo da Rotação'!G72)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H71='Registo da Rotação'!H72)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F71)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G71='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H71='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F72,'Listas de apoio'!$A$6='Registo da Rotação'!G72,'Listas de apoio'!$A$6='Registo da Rotação'!H72),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F71='Registo da Rotação'!F72),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F71)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F71='Registo da Rotação'!F72)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G71='Registo da Rotação'!G72)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H71='Registo da Rotação'!H72)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F71)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G71='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H71='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F72,'Listas de apoio'!$A$7='Registo da Rotação'!G72,'Listas de apoio'!$A$7='Registo da Rotação'!H72),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F71='Registo da Rotação'!F72),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F71)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F71='Registo da Rotação'!F72)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G71='Registo da Rotação'!G72)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H71='Registo da Rotação'!H72)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F71)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G71='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H71='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F72,'Listas de apoio'!$A$8='Registo da Rotação'!G72,'Listas de apoio'!$A$8='Registo da Rotação'!H72),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F71='Registo da Rotação'!F72),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F71)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F71='Registo da Rotação'!F72)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G71='Registo da Rotação'!G72)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H71='Registo da Rotação'!H72)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F71)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G71='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H71='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A81="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Registo da Rotação'!G81)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Registo da Rotação'!H81)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F81,'Listas de apoio'!$A$5='Registo da Rotação'!G81,'Listas de apoio'!$A$5='Registo da Rotação'!H81),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Registo da Rotação'!G81)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Registo da Rotação'!H81)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F81,'Listas de apoio'!$A$6='Registo da Rotação'!G81,'Listas de apoio'!$A$6='Registo da Rotação'!H81),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Registo da Rotação'!G81)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Registo da Rotação'!H81)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F81,'Listas de apoio'!$A$7='Registo da Rotação'!G81,'Listas de apoio'!$A$7='Registo da Rotação'!H81),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Registo da Rotação'!G81)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Registo da Rotação'!H81)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F81,'Listas de apoio'!$A$8='Registo da Rotação'!G81,'Listas de apoio'!$A$8='Registo da Rotação'!H81),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Registo da Rotação'!G81)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Registo da Rotação'!H81)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U23" s="8">
-        <f>IF('Registo da Rotação'!A72="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A72)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C72,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D72)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A81="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A81)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C81,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D81)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V23" s="1"/>
       <c r="W23" s="8">
-        <f>IF('Registo da Rotação'!C177="",0,IF(COUNTA('Registo da Rotação'!A177:H177)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C186="",0,IF(COUNTA('Registo da Rotação'!A186:H186)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X23" s="8">
-        <f>IF('Registo da Rotação'!C177="",0,IF('Registo da Rotação'!E177='Registo da Rotação'!F177,1,0))</f>
+        <f>IF('Registo da Rotação'!C186="",0,IF('Registo da Rotação'!E186='Registo da Rotação'!F186,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y23" s="8">
-        <f>IF('Registo da Rotação'!C177="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B177)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C186="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B186)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z23" s="8">
-        <f>IF('Registo da Rotação'!C177="",0,IF('Registo da Rotação'!D177="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C177,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F177)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C177,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F177)&gt;0,1,0),IF('Registo da Rotação'!D177="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C177,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F177)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C177,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F177)&gt;0,1,0),IF('Registo da Rotação'!D177="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C177,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F177)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C177,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F177)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C186="",0,IF('Registo da Rotação'!D186="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C186,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F186)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C186,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F186)&gt;0,1,0),IF('Registo da Rotação'!D186="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C186,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F186)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C186,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F186)&gt;0,1,0),IF('Registo da Rotação'!D186="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C186,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F186)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C186,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F186)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA23" s="8">
-        <f>IF('Registo da Rotação'!C177="",0,IF('Registo da Rotação'!D177="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C177,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E177)=0,1,0),IF('Registo da Rotação'!D177="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C177,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E177)=0,1,0),IF('Registo da Rotação'!D177="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A177,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B177,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C177,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E177)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C186="",0,IF('Registo da Rotação'!D186="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C186,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E186)=0,1,0),IF('Registo da Rotação'!D186="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C186,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E186)=0,1,0),IF('Registo da Rotação'!D186="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C186,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E186)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB23" s="8">
-        <f>IF('Registo da Rotação'!C177="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B177,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H177="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C186="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B186,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H186="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC23" s="1"/>
@@ -10631,56 +11091,56 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="8">
-        <f>IF('Registo da Rotação'!A73="",0,IF(COUNTA('Registo da Rotação'!B73:K73)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A82="",0,IF(COUNTA('Registo da Rotação'!B82:K82)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P24" s="8">
-        <f>IF('Registo da Rotação'!A73="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C73)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A82="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C82)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q24" s="8">
-        <f>IF('Registo da Rotação'!A73="",0,IF(OR('Registo da Rotação'!F73='Registo da Rotação'!G73,'Registo da Rotação'!F73='Registo da Rotação'!H73,'Registo da Rotação'!G73='Registo da Rotação'!H73),1,0))</f>
+        <f>IF('Registo da Rotação'!A82="",0,IF(OR('Registo da Rotação'!F82='Registo da Rotação'!G82,'Registo da Rotação'!F82='Registo da Rotação'!H82,'Registo da Rotação'!G82='Registo da Rotação'!H82),1,0))</f>
         <v>0</v>
       </c>
       <c r="R24" s="8">
-        <f>IF('Registo da Rotação'!A73="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C73,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I73="Ainda não avaliado",'Registo da Rotação'!J73="Ainda não avaliado",'Registo da Rotação'!K73="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A82="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C82,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I82="Ainda não avaliado",'Registo da Rotação'!J82="Ainda não avaliado",'Registo da Rotação'!K82="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S24" s="8">
-        <f>IF('Registo da Rotação'!A73="",0,IF(AND('Registo da Rotação'!G73=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F72='Registo da Rotação'!F73),'Registo da Rotação'!$G$54:'Registo da Rotação'!G72),""),'Registo da Rotação'!H73=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F72='Registo da Rotação'!F73),'Registo da Rotação'!$H$54:'Registo da Rotação'!H72),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A82="",0,IF(AND('Registo da Rotação'!G82=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82),'Registo da Rotação'!$G$54:'Registo da Rotação'!G81),""),'Registo da Rotação'!H82=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82),'Registo da Rotação'!$H$54:'Registo da Rotação'!H81),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T24" s="8">
-        <f>IF('Registo da Rotação'!A73="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F72='Registo da Rotação'!F73)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G72='Registo da Rotação'!G73)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H72='Registo da Rotação'!H73)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F72)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F73,'Listas de apoio'!$A$5='Registo da Rotação'!G73,'Listas de apoio'!$A$5='Registo da Rotação'!H73),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F72='Registo da Rotação'!F73),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F72)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F72='Registo da Rotação'!F73)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G72='Registo da Rotação'!G73)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H72='Registo da Rotação'!H73)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F72)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G72='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H72='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F73,'Listas de apoio'!$A$6='Registo da Rotação'!G73,'Listas de apoio'!$A$6='Registo da Rotação'!H73),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F72='Registo da Rotação'!F73),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F72)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F72='Registo da Rotação'!F73)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G72='Registo da Rotação'!G73)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H72='Registo da Rotação'!H73)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F72)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G72='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H72='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F73,'Listas de apoio'!$A$7='Registo da Rotação'!G73,'Listas de apoio'!$A$7='Registo da Rotação'!H73),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F72='Registo da Rotação'!F73),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F72)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F72='Registo da Rotação'!F73)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G72='Registo da Rotação'!G73)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H72='Registo da Rotação'!H73)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F72)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G72='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H72='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F73,'Listas de apoio'!$A$8='Registo da Rotação'!G73,'Listas de apoio'!$A$8='Registo da Rotação'!H73),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F72='Registo da Rotação'!F73),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F72)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F72='Registo da Rotação'!F73)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G72='Registo da Rotação'!G73)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H72='Registo da Rotação'!H73)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F72)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G72='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H72='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A82="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Registo da Rotação'!G82)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Registo da Rotação'!H82)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F82,'Listas de apoio'!$A$5='Registo da Rotação'!G82,'Listas de apoio'!$A$5='Registo da Rotação'!H82),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Registo da Rotação'!G82)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Registo da Rotação'!H82)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F82,'Listas de apoio'!$A$6='Registo da Rotação'!G82,'Listas de apoio'!$A$6='Registo da Rotação'!H82),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Registo da Rotação'!G82)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Registo da Rotação'!H82)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F82,'Listas de apoio'!$A$7='Registo da Rotação'!G82,'Listas de apoio'!$A$7='Registo da Rotação'!H82),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Registo da Rotação'!G82)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Registo da Rotação'!H82)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F82,'Listas de apoio'!$A$8='Registo da Rotação'!G82,'Listas de apoio'!$A$8='Registo da Rotação'!H82),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Registo da Rotação'!G82)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Registo da Rotação'!H82)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U24" s="8">
-        <f>IF('Registo da Rotação'!A73="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A73)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C73,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D73)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A82="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A82)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C82,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D82)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V24" s="1"/>
       <c r="W24" s="8">
-        <f>IF('Registo da Rotação'!C178="",0,IF(COUNTA('Registo da Rotação'!A178:H178)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C187="",0,IF(COUNTA('Registo da Rotação'!A187:H187)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X24" s="8">
-        <f>IF('Registo da Rotação'!C178="",0,IF('Registo da Rotação'!E178='Registo da Rotação'!F178,1,0))</f>
+        <f>IF('Registo da Rotação'!C187="",0,IF('Registo da Rotação'!E187='Registo da Rotação'!F187,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y24" s="8">
-        <f>IF('Registo da Rotação'!C178="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B178)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C187="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B187)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z24" s="8">
-        <f>IF('Registo da Rotação'!C178="",0,IF('Registo da Rotação'!D178="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C178,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F178)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C178,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F178)&gt;0,1,0),IF('Registo da Rotação'!D178="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C178,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F178)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C178,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F178)&gt;0,1,0),IF('Registo da Rotação'!D178="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C178,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F178)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C178,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F178)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C187="",0,IF('Registo da Rotação'!D187="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C187,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F187)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C187,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F187)&gt;0,1,0),IF('Registo da Rotação'!D187="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C187,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F187)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C187,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F187)&gt;0,1,0),IF('Registo da Rotação'!D187="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C187,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F187)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C187,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F187)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA24" s="8">
-        <f>IF('Registo da Rotação'!C178="",0,IF('Registo da Rotação'!D178="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C178,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E178)=0,1,0),IF('Registo da Rotação'!D178="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C178,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E178)=0,1,0),IF('Registo da Rotação'!D178="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A178,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B178,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C178,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E178)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C187="",0,IF('Registo da Rotação'!D187="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C187,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E187)=0,1,0),IF('Registo da Rotação'!D187="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C187,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E187)=0,1,0),IF('Registo da Rotação'!D187="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C187,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E187)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB24" s="8">
-        <f>IF('Registo da Rotação'!C178="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B178,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H178="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C187="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B187,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H187="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC24" s="1"/>
@@ -10720,56 +11180,56 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="8">
-        <f>IF('Registo da Rotação'!A74="",0,IF(COUNTA('Registo da Rotação'!B74:K74)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A83="",0,IF(COUNTA('Registo da Rotação'!B83:K83)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P25" s="8">
-        <f>IF('Registo da Rotação'!A74="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C74)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A83="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C83)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q25" s="8">
-        <f>IF('Registo da Rotação'!A74="",0,IF(OR('Registo da Rotação'!F74='Registo da Rotação'!G74,'Registo da Rotação'!F74='Registo da Rotação'!H74,'Registo da Rotação'!G74='Registo da Rotação'!H74),1,0))</f>
+        <f>IF('Registo da Rotação'!A83="",0,IF(OR('Registo da Rotação'!F83='Registo da Rotação'!G83,'Registo da Rotação'!F83='Registo da Rotação'!H83,'Registo da Rotação'!G83='Registo da Rotação'!H83),1,0))</f>
         <v>0</v>
       </c>
       <c r="R25" s="8">
-        <f>IF('Registo da Rotação'!A74="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C74,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I74="Ainda não avaliado",'Registo da Rotação'!J74="Ainda não avaliado",'Registo da Rotação'!K74="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A83="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C83,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I83="Ainda não avaliado",'Registo da Rotação'!J83="Ainda não avaliado",'Registo da Rotação'!K83="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S25" s="8">
-        <f>IF('Registo da Rotação'!A74="",0,IF(AND('Registo da Rotação'!G74=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F73='Registo da Rotação'!F74),'Registo da Rotação'!$G$54:'Registo da Rotação'!G73),""),'Registo da Rotação'!H74=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F73='Registo da Rotação'!F74),'Registo da Rotação'!$H$54:'Registo da Rotação'!H73),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A83="",0,IF(AND('Registo da Rotação'!G83=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83),'Registo da Rotação'!$G$54:'Registo da Rotação'!G82),""),'Registo da Rotação'!H83=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83),'Registo da Rotação'!$H$54:'Registo da Rotação'!H82),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T25" s="8">
-        <f>IF('Registo da Rotação'!A74="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F73='Registo da Rotação'!F74)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G73='Registo da Rotação'!G74)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H73='Registo da Rotação'!H74)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F73)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F74,'Listas de apoio'!$A$5='Registo da Rotação'!G74,'Listas de apoio'!$A$5='Registo da Rotação'!H74),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F73='Registo da Rotação'!F74),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F73)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F73='Registo da Rotação'!F74)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G73='Registo da Rotação'!G74)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H73='Registo da Rotação'!H74)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F73)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G73='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H73='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F74,'Listas de apoio'!$A$6='Registo da Rotação'!G74,'Listas de apoio'!$A$6='Registo da Rotação'!H74),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F73='Registo da Rotação'!F74),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F73)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F73='Registo da Rotação'!F74)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G73='Registo da Rotação'!G74)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H73='Registo da Rotação'!H74)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F73)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G73='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H73='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F74,'Listas de apoio'!$A$7='Registo da Rotação'!G74,'Listas de apoio'!$A$7='Registo da Rotação'!H74),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F73='Registo da Rotação'!F74),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F73)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F73='Registo da Rotação'!F74)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G73='Registo da Rotação'!G74)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H73='Registo da Rotação'!H74)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F73)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G73='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H73='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F74,'Listas de apoio'!$A$8='Registo da Rotação'!G74,'Listas de apoio'!$A$8='Registo da Rotação'!H74),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F73='Registo da Rotação'!F74),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F73)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F73='Registo da Rotação'!F74)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G73='Registo da Rotação'!G74)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H73='Registo da Rotação'!H74)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F73)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G73='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H73='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A83="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Registo da Rotação'!G83)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Registo da Rotação'!H83)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F83,'Listas de apoio'!$A$5='Registo da Rotação'!G83,'Listas de apoio'!$A$5='Registo da Rotação'!H83),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Registo da Rotação'!G83)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Registo da Rotação'!H83)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F83,'Listas de apoio'!$A$6='Registo da Rotação'!G83,'Listas de apoio'!$A$6='Registo da Rotação'!H83),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Registo da Rotação'!G83)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Registo da Rotação'!H83)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F83,'Listas de apoio'!$A$7='Registo da Rotação'!G83,'Listas de apoio'!$A$7='Registo da Rotação'!H83),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Registo da Rotação'!G83)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Registo da Rotação'!H83)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F83,'Listas de apoio'!$A$8='Registo da Rotação'!G83,'Listas de apoio'!$A$8='Registo da Rotação'!H83),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Registo da Rotação'!G83)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Registo da Rotação'!H83)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U25" s="8">
-        <f>IF('Registo da Rotação'!A74="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A74)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C74,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D74)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A83="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A83)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C83,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D83)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V25" s="1"/>
       <c r="W25" s="8">
-        <f>IF('Registo da Rotação'!C179="",0,IF(COUNTA('Registo da Rotação'!A179:H179)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C188="",0,IF(COUNTA('Registo da Rotação'!A188:H188)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X25" s="8">
-        <f>IF('Registo da Rotação'!C179="",0,IF('Registo da Rotação'!E179='Registo da Rotação'!F179,1,0))</f>
+        <f>IF('Registo da Rotação'!C188="",0,IF('Registo da Rotação'!E188='Registo da Rotação'!F188,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y25" s="8">
-        <f>IF('Registo da Rotação'!C179="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B179)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C188="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B188)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z25" s="8">
-        <f>IF('Registo da Rotação'!C179="",0,IF('Registo da Rotação'!D179="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C179,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F179)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C179,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F179)&gt;0,1,0),IF('Registo da Rotação'!D179="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C179,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F179)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C179,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F179)&gt;0,1,0),IF('Registo da Rotação'!D179="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C179,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F179)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C179,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F179)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C188="",0,IF('Registo da Rotação'!D188="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C188,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F188)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C188,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F188)&gt;0,1,0),IF('Registo da Rotação'!D188="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C188,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F188)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C188,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F188)&gt;0,1,0),IF('Registo da Rotação'!D188="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C188,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F188)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C188,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F188)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA25" s="8">
-        <f>IF('Registo da Rotação'!C179="",0,IF('Registo da Rotação'!D179="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C179,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E179)=0,1,0),IF('Registo da Rotação'!D179="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C179,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E179)=0,1,0),IF('Registo da Rotação'!D179="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A179,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B179,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C179,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E179)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C188="",0,IF('Registo da Rotação'!D188="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C188,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E188)=0,1,0),IF('Registo da Rotação'!D188="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C188,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E188)=0,1,0),IF('Registo da Rotação'!D188="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C188,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E188)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB25" s="8">
-        <f>IF('Registo da Rotação'!C179="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B179,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H179="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C188="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B188,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H188="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC25" s="1"/>
@@ -10795,56 +11255,56 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="8">
-        <f>IF('Registo da Rotação'!A75="",0,IF(COUNTA('Registo da Rotação'!B75:K75)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A84="",0,IF(COUNTA('Registo da Rotação'!B84:K84)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P26" s="8">
-        <f>IF('Registo da Rotação'!A75="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C75)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A84="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C84)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q26" s="8">
-        <f>IF('Registo da Rotação'!A75="",0,IF(OR('Registo da Rotação'!F75='Registo da Rotação'!G75,'Registo da Rotação'!F75='Registo da Rotação'!H75,'Registo da Rotação'!G75='Registo da Rotação'!H75),1,0))</f>
+        <f>IF('Registo da Rotação'!A84="",0,IF(OR('Registo da Rotação'!F84='Registo da Rotação'!G84,'Registo da Rotação'!F84='Registo da Rotação'!H84,'Registo da Rotação'!G84='Registo da Rotação'!H84),1,0))</f>
         <v>0</v>
       </c>
       <c r="R26" s="8">
-        <f>IF('Registo da Rotação'!A75="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C75,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I75="Ainda não avaliado",'Registo da Rotação'!J75="Ainda não avaliado",'Registo da Rotação'!K75="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A84="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C84,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I84="Ainda não avaliado",'Registo da Rotação'!J84="Ainda não avaliado",'Registo da Rotação'!K84="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S26" s="8">
-        <f>IF('Registo da Rotação'!A75="",0,IF(AND('Registo da Rotação'!G75=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F74='Registo da Rotação'!F75),'Registo da Rotação'!$G$54:'Registo da Rotação'!G74),""),'Registo da Rotação'!H75=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F74='Registo da Rotação'!F75),'Registo da Rotação'!$H$54:'Registo da Rotação'!H74),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A84="",0,IF(AND('Registo da Rotação'!G84=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84),'Registo da Rotação'!$G$54:'Registo da Rotação'!G83),""),'Registo da Rotação'!H84=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84),'Registo da Rotação'!$H$54:'Registo da Rotação'!H83),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T26" s="8">
-        <f>IF('Registo da Rotação'!A75="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F74='Registo da Rotação'!F75)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G74='Registo da Rotação'!G75)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H74='Registo da Rotação'!H75)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F74)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F75,'Listas de apoio'!$A$5='Registo da Rotação'!G75,'Listas de apoio'!$A$5='Registo da Rotação'!H75),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F74='Registo da Rotação'!F75),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F74)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F74='Registo da Rotação'!F75)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G74='Registo da Rotação'!G75)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H74='Registo da Rotação'!H75)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F74)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G74='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H74='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F75,'Listas de apoio'!$A$6='Registo da Rotação'!G75,'Listas de apoio'!$A$6='Registo da Rotação'!H75),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F74='Registo da Rotação'!F75),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F74)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F74='Registo da Rotação'!F75)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G74='Registo da Rotação'!G75)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H74='Registo da Rotação'!H75)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F74)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G74='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H74='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F75,'Listas de apoio'!$A$7='Registo da Rotação'!G75,'Listas de apoio'!$A$7='Registo da Rotação'!H75),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F74='Registo da Rotação'!F75),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F74)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F74='Registo da Rotação'!F75)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G74='Registo da Rotação'!G75)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H74='Registo da Rotação'!H75)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F74)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G74='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H74='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F75,'Listas de apoio'!$A$8='Registo da Rotação'!G75,'Listas de apoio'!$A$8='Registo da Rotação'!H75),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F74='Registo da Rotação'!F75),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F74)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F74='Registo da Rotação'!F75)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G74='Registo da Rotação'!G75)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H74='Registo da Rotação'!H75)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F74)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G74='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H74='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A84="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Registo da Rotação'!G84)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Registo da Rotação'!H84)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F84,'Listas de apoio'!$A$5='Registo da Rotação'!G84,'Listas de apoio'!$A$5='Registo da Rotação'!H84),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Registo da Rotação'!G84)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Registo da Rotação'!H84)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F84,'Listas de apoio'!$A$6='Registo da Rotação'!G84,'Listas de apoio'!$A$6='Registo da Rotação'!H84),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Registo da Rotação'!G84)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Registo da Rotação'!H84)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F84,'Listas de apoio'!$A$7='Registo da Rotação'!G84,'Listas de apoio'!$A$7='Registo da Rotação'!H84),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Registo da Rotação'!G84)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Registo da Rotação'!H84)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F84,'Listas de apoio'!$A$8='Registo da Rotação'!G84,'Listas de apoio'!$A$8='Registo da Rotação'!H84),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Registo da Rotação'!G84)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Registo da Rotação'!H84)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U26" s="8">
-        <f>IF('Registo da Rotação'!A75="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A75)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C75,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D75)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A84="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A84)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C84,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D84)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V26" s="1"/>
       <c r="W26" s="8">
-        <f>IF('Registo da Rotação'!C180="",0,IF(COUNTA('Registo da Rotação'!A180:H180)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C189="",0,IF(COUNTA('Registo da Rotação'!A189:H189)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X26" s="8">
-        <f>IF('Registo da Rotação'!C180="",0,IF('Registo da Rotação'!E180='Registo da Rotação'!F180,1,0))</f>
+        <f>IF('Registo da Rotação'!C189="",0,IF('Registo da Rotação'!E189='Registo da Rotação'!F189,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y26" s="8">
-        <f>IF('Registo da Rotação'!C180="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B180)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C189="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B189)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z26" s="8">
-        <f>IF('Registo da Rotação'!C180="",0,IF('Registo da Rotação'!D180="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C180,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F180)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C180,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F180)&gt;0,1,0),IF('Registo da Rotação'!D180="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C180,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F180)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C180,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F180)&gt;0,1,0),IF('Registo da Rotação'!D180="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C180,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F180)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C180,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F180)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C189="",0,IF('Registo da Rotação'!D189="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C189,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F189)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C189,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F189)&gt;0,1,0),IF('Registo da Rotação'!D189="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C189,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F189)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C189,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F189)&gt;0,1,0),IF('Registo da Rotação'!D189="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C189,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F189)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C189,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F189)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA26" s="8">
-        <f>IF('Registo da Rotação'!C180="",0,IF('Registo da Rotação'!D180="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C180,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E180)=0,1,0),IF('Registo da Rotação'!D180="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C180,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E180)=0,1,0),IF('Registo da Rotação'!D180="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A180,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B180,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C180,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E180)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C189="",0,IF('Registo da Rotação'!D189="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C189,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E189)=0,1,0),IF('Registo da Rotação'!D189="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C189,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E189)=0,1,0),IF('Registo da Rotação'!D189="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C189,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E189)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB26" s="8">
-        <f>IF('Registo da Rotação'!C180="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B180,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H180="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C189="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B189,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H189="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC26" s="1"/>
@@ -10870,56 +11330,56 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="8">
-        <f>IF('Registo da Rotação'!A76="",0,IF(COUNTA('Registo da Rotação'!B76:K76)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A85="",0,IF(COUNTA('Registo da Rotação'!B85:K85)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P27" s="8">
-        <f>IF('Registo da Rotação'!A76="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C76)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A85="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C85)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q27" s="8">
-        <f>IF('Registo da Rotação'!A76="",0,IF(OR('Registo da Rotação'!F76='Registo da Rotação'!G76,'Registo da Rotação'!F76='Registo da Rotação'!H76,'Registo da Rotação'!G76='Registo da Rotação'!H76),1,0))</f>
+        <f>IF('Registo da Rotação'!A85="",0,IF(OR('Registo da Rotação'!F85='Registo da Rotação'!G85,'Registo da Rotação'!F85='Registo da Rotação'!H85,'Registo da Rotação'!G85='Registo da Rotação'!H85),1,0))</f>
         <v>0</v>
       </c>
       <c r="R27" s="8">
-        <f>IF('Registo da Rotação'!A76="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C76,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I76="Ainda não avaliado",'Registo da Rotação'!J76="Ainda não avaliado",'Registo da Rotação'!K76="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A85="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C85,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I85="Ainda não avaliado",'Registo da Rotação'!J85="Ainda não avaliado",'Registo da Rotação'!K85="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S27" s="8">
-        <f>IF('Registo da Rotação'!A76="",0,IF(AND('Registo da Rotação'!G76=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76),'Registo da Rotação'!$G$54:'Registo da Rotação'!G75),""),'Registo da Rotação'!H76=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76),'Registo da Rotação'!$H$54:'Registo da Rotação'!H75),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A85="",0,IF(AND('Registo da Rotação'!G85=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85),'Registo da Rotação'!$G$54:'Registo da Rotação'!G84),""),'Registo da Rotação'!H85=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85),'Registo da Rotação'!$H$54:'Registo da Rotação'!H84),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T27" s="8">
-        <f>IF('Registo da Rotação'!A76="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Registo da Rotação'!G76)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Registo da Rotação'!H76)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F76,'Listas de apoio'!$A$5='Registo da Rotação'!G76,'Listas de apoio'!$A$5='Registo da Rotação'!H76),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Registo da Rotação'!G76)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Registo da Rotação'!H76)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F76,'Listas de apoio'!$A$6='Registo da Rotação'!G76,'Listas de apoio'!$A$6='Registo da Rotação'!H76),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Registo da Rotação'!G76)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Registo da Rotação'!H76)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F76,'Listas de apoio'!$A$7='Registo da Rotação'!G76,'Listas de apoio'!$A$7='Registo da Rotação'!H76),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Registo da Rotação'!G76)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Registo da Rotação'!H76)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F76,'Listas de apoio'!$A$8='Registo da Rotação'!G76,'Listas de apoio'!$A$8='Registo da Rotação'!H76),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F75='Registo da Rotação'!F76)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Registo da Rotação'!G76)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Registo da Rotação'!H76)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F75)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G75='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H75='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A85="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Registo da Rotação'!G85)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Registo da Rotação'!H85)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F85,'Listas de apoio'!$A$5='Registo da Rotação'!G85,'Listas de apoio'!$A$5='Registo da Rotação'!H85),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Registo da Rotação'!G85)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Registo da Rotação'!H85)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F85,'Listas de apoio'!$A$6='Registo da Rotação'!G85,'Listas de apoio'!$A$6='Registo da Rotação'!H85),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Registo da Rotação'!G85)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Registo da Rotação'!H85)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F85,'Listas de apoio'!$A$7='Registo da Rotação'!G85,'Listas de apoio'!$A$7='Registo da Rotação'!H85),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Registo da Rotação'!G85)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Registo da Rotação'!H85)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F85,'Listas de apoio'!$A$8='Registo da Rotação'!G85,'Listas de apoio'!$A$8='Registo da Rotação'!H85),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Registo da Rotação'!G85)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Registo da Rotação'!H85)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U27" s="8">
-        <f>IF('Registo da Rotação'!A76="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A76)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C76,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D76)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A85="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A85)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C85,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D85)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V27" s="1"/>
       <c r="W27" s="8">
-        <f>IF('Registo da Rotação'!C181="",0,IF(COUNTA('Registo da Rotação'!A181:H181)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C190="",0,IF(COUNTA('Registo da Rotação'!A190:H190)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X27" s="8">
-        <f>IF('Registo da Rotação'!C181="",0,IF('Registo da Rotação'!E181='Registo da Rotação'!F181,1,0))</f>
+        <f>IF('Registo da Rotação'!C190="",0,IF('Registo da Rotação'!E190='Registo da Rotação'!F190,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y27" s="8">
-        <f>IF('Registo da Rotação'!C181="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B181)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C190="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B190)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z27" s="8">
-        <f>IF('Registo da Rotação'!C181="",0,IF('Registo da Rotação'!D181="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C181,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F181)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C181,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F181)&gt;0,1,0),IF('Registo da Rotação'!D181="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C181,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F181)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C181,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F181)&gt;0,1,0),IF('Registo da Rotação'!D181="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C181,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F181)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C181,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F181)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C190="",0,IF('Registo da Rotação'!D190="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C190,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F190)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C190,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F190)&gt;0,1,0),IF('Registo da Rotação'!D190="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C190,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F190)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C190,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F190)&gt;0,1,0),IF('Registo da Rotação'!D190="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C190,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F190)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C190,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F190)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA27" s="8">
-        <f>IF('Registo da Rotação'!C181="",0,IF('Registo da Rotação'!D181="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C181,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E181)=0,1,0),IF('Registo da Rotação'!D181="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C181,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E181)=0,1,0),IF('Registo da Rotação'!D181="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A181,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B181,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C181,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E181)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C190="",0,IF('Registo da Rotação'!D190="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C190,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E190)=0,1,0),IF('Registo da Rotação'!D190="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C190,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E190)=0,1,0),IF('Registo da Rotação'!D190="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C190,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E190)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB27" s="8">
-        <f>IF('Registo da Rotação'!C181="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B181,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H181="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C190="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B190,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H190="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC27" s="1"/>
@@ -10945,56 +11405,56 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="8">
-        <f>IF('Registo da Rotação'!A77="",0,IF(COUNTA('Registo da Rotação'!B77:K77)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A86="",0,IF(COUNTA('Registo da Rotação'!B86:K86)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P28" s="8">
-        <f>IF('Registo da Rotação'!A77="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C77)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A86="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C86)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q28" s="8">
-        <f>IF('Registo da Rotação'!A77="",0,IF(OR('Registo da Rotação'!F77='Registo da Rotação'!G77,'Registo da Rotação'!F77='Registo da Rotação'!H77,'Registo da Rotação'!G77='Registo da Rotação'!H77),1,0))</f>
+        <f>IF('Registo da Rotação'!A86="",0,IF(OR('Registo da Rotação'!F86='Registo da Rotação'!G86,'Registo da Rotação'!F86='Registo da Rotação'!H86,'Registo da Rotação'!G86='Registo da Rotação'!H86),1,0))</f>
         <v>0</v>
       </c>
       <c r="R28" s="8">
-        <f>IF('Registo da Rotação'!A77="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C77,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I77="Ainda não avaliado",'Registo da Rotação'!J77="Ainda não avaliado",'Registo da Rotação'!K77="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A86="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C86,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I86="Ainda não avaliado",'Registo da Rotação'!J86="Ainda não avaliado",'Registo da Rotação'!K86="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S28" s="8">
-        <f>IF('Registo da Rotação'!A77="",0,IF(AND('Registo da Rotação'!G77=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77),'Registo da Rotação'!$G$54:'Registo da Rotação'!G76),""),'Registo da Rotação'!H77=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77),'Registo da Rotação'!$H$54:'Registo da Rotação'!H76),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A86="",0,IF(AND('Registo da Rotação'!G86=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86),'Registo da Rotação'!$G$54:'Registo da Rotação'!G85),""),'Registo da Rotação'!H86=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86),'Registo da Rotação'!$H$54:'Registo da Rotação'!H85),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T28" s="8">
-        <f>IF('Registo da Rotação'!A77="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Registo da Rotação'!G77)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Registo da Rotação'!H77)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F77,'Listas de apoio'!$A$5='Registo da Rotação'!G77,'Listas de apoio'!$A$5='Registo da Rotação'!H77),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Registo da Rotação'!G77)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Registo da Rotação'!H77)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F77,'Listas de apoio'!$A$6='Registo da Rotação'!G77,'Listas de apoio'!$A$6='Registo da Rotação'!H77),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Registo da Rotação'!G77)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Registo da Rotação'!H77)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F77,'Listas de apoio'!$A$7='Registo da Rotação'!G77,'Listas de apoio'!$A$7='Registo da Rotação'!H77),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Registo da Rotação'!G77)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Registo da Rotação'!H77)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F77,'Listas de apoio'!$A$8='Registo da Rotação'!G77,'Listas de apoio'!$A$8='Registo da Rotação'!H77),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F76='Registo da Rotação'!F77)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Registo da Rotação'!G77)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Registo da Rotação'!H77)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F76)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G76='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H76='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A86="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Registo da Rotação'!G86)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Registo da Rotação'!H86)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F86,'Listas de apoio'!$A$5='Registo da Rotação'!G86,'Listas de apoio'!$A$5='Registo da Rotação'!H86),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Registo da Rotação'!G86)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Registo da Rotação'!H86)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F86,'Listas de apoio'!$A$6='Registo da Rotação'!G86,'Listas de apoio'!$A$6='Registo da Rotação'!H86),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Registo da Rotação'!G86)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Registo da Rotação'!H86)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F86,'Listas de apoio'!$A$7='Registo da Rotação'!G86,'Listas de apoio'!$A$7='Registo da Rotação'!H86),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Registo da Rotação'!G86)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Registo da Rotação'!H86)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F86,'Listas de apoio'!$A$8='Registo da Rotação'!G86,'Listas de apoio'!$A$8='Registo da Rotação'!H86),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Registo da Rotação'!G86)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Registo da Rotação'!H86)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U28" s="8">
-        <f>IF('Registo da Rotação'!A77="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A77)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C77,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D77)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A86="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A86)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C86,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D86)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V28" s="1"/>
       <c r="W28" s="8">
-        <f>IF('Registo da Rotação'!C182="",0,IF(COUNTA('Registo da Rotação'!A182:H182)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C191="",0,IF(COUNTA('Registo da Rotação'!A191:H191)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X28" s="8">
-        <f>IF('Registo da Rotação'!C182="",0,IF('Registo da Rotação'!E182='Registo da Rotação'!F182,1,0))</f>
+        <f>IF('Registo da Rotação'!C191="",0,IF('Registo da Rotação'!E191='Registo da Rotação'!F191,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y28" s="8">
-        <f>IF('Registo da Rotação'!C182="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B182)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C191="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B191)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z28" s="8">
-        <f>IF('Registo da Rotação'!C182="",0,IF('Registo da Rotação'!D182="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C182,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F182)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C182,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F182)&gt;0,1,0),IF('Registo da Rotação'!D182="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C182,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F182)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C182,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F182)&gt;0,1,0),IF('Registo da Rotação'!D182="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C182,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F182)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C182,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F182)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C191="",0,IF('Registo da Rotação'!D191="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C191,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F191)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C191,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F191)&gt;0,1,0),IF('Registo da Rotação'!D191="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C191,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F191)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C191,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F191)&gt;0,1,0),IF('Registo da Rotação'!D191="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C191,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F191)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C191,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F191)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA28" s="8">
-        <f>IF('Registo da Rotação'!C182="",0,IF('Registo da Rotação'!D182="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C182,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E182)=0,1,0),IF('Registo da Rotação'!D182="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C182,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E182)=0,1,0),IF('Registo da Rotação'!D182="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A182,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B182,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C182,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E182)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C191="",0,IF('Registo da Rotação'!D191="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C191,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E191)=0,1,0),IF('Registo da Rotação'!D191="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C191,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E191)=0,1,0),IF('Registo da Rotação'!D191="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C191,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E191)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB28" s="8">
-        <f>IF('Registo da Rotação'!C182="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B182,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H182="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C191="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B191,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H191="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC28" s="1"/>
@@ -11020,56 +11480,56 @@
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="8">
-        <f>IF('Registo da Rotação'!A78="",0,IF(COUNTA('Registo da Rotação'!B78:K78)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A87="",0,IF(COUNTA('Registo da Rotação'!B87:K87)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P29" s="8">
-        <f>IF('Registo da Rotação'!A78="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C78)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A87="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C87)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q29" s="8">
-        <f>IF('Registo da Rotação'!A78="",0,IF(OR('Registo da Rotação'!F78='Registo da Rotação'!G78,'Registo da Rotação'!F78='Registo da Rotação'!H78,'Registo da Rotação'!G78='Registo da Rotação'!H78),1,0))</f>
+        <f>IF('Registo da Rotação'!A87="",0,IF(OR('Registo da Rotação'!F87='Registo da Rotação'!G87,'Registo da Rotação'!F87='Registo da Rotação'!H87,'Registo da Rotação'!G87='Registo da Rotação'!H87),1,0))</f>
         <v>0</v>
       </c>
       <c r="R29" s="8">
-        <f>IF('Registo da Rotação'!A78="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C78,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I78="Ainda não avaliado",'Registo da Rotação'!J78="Ainda não avaliado",'Registo da Rotação'!K78="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A87="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C87,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I87="Ainda não avaliado",'Registo da Rotação'!J87="Ainda não avaliado",'Registo da Rotação'!K87="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S29" s="8">
-        <f>IF('Registo da Rotação'!A78="",0,IF(AND('Registo da Rotação'!G78=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78),'Registo da Rotação'!$G$54:'Registo da Rotação'!G77),""),'Registo da Rotação'!H78=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78),'Registo da Rotação'!$H$54:'Registo da Rotação'!H77),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A87="",0,IF(AND('Registo da Rotação'!G87=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87),'Registo da Rotação'!$G$54:'Registo da Rotação'!G86),""),'Registo da Rotação'!H87=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87),'Registo da Rotação'!$H$54:'Registo da Rotação'!H86),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T29" s="8">
-        <f>IF('Registo da Rotação'!A78="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Registo da Rotação'!G78)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Registo da Rotação'!H78)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F78,'Listas de apoio'!$A$5='Registo da Rotação'!G78,'Listas de apoio'!$A$5='Registo da Rotação'!H78),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Registo da Rotação'!G78)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Registo da Rotação'!H78)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F78,'Listas de apoio'!$A$6='Registo da Rotação'!G78,'Listas de apoio'!$A$6='Registo da Rotação'!H78),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Registo da Rotação'!G78)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Registo da Rotação'!H78)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F78,'Listas de apoio'!$A$7='Registo da Rotação'!G78,'Listas de apoio'!$A$7='Registo da Rotação'!H78),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Registo da Rotação'!G78)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Registo da Rotação'!H78)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F78,'Listas de apoio'!$A$8='Registo da Rotação'!G78,'Listas de apoio'!$A$8='Registo da Rotação'!H78),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F77='Registo da Rotação'!F78)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Registo da Rotação'!G78)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Registo da Rotação'!H78)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F77)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G77='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H77='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A87="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Registo da Rotação'!G87)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Registo da Rotação'!H87)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F87,'Listas de apoio'!$A$5='Registo da Rotação'!G87,'Listas de apoio'!$A$5='Registo da Rotação'!H87),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Registo da Rotação'!G87)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Registo da Rotação'!H87)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F87,'Listas de apoio'!$A$6='Registo da Rotação'!G87,'Listas de apoio'!$A$6='Registo da Rotação'!H87),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Registo da Rotação'!G87)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Registo da Rotação'!H87)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F87,'Listas de apoio'!$A$7='Registo da Rotação'!G87,'Listas de apoio'!$A$7='Registo da Rotação'!H87),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Registo da Rotação'!G87)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Registo da Rotação'!H87)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F87,'Listas de apoio'!$A$8='Registo da Rotação'!G87,'Listas de apoio'!$A$8='Registo da Rotação'!H87),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Registo da Rotação'!G87)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Registo da Rotação'!H87)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U29" s="8">
-        <f>IF('Registo da Rotação'!A78="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A78)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C78,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D78)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A87="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A87)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C87,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D87)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V29" s="1"/>
       <c r="W29" s="8">
-        <f>IF('Registo da Rotação'!C183="",0,IF(COUNTA('Registo da Rotação'!A183:H183)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C192="",0,IF(COUNTA('Registo da Rotação'!A192:H192)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X29" s="8">
-        <f>IF('Registo da Rotação'!C183="",0,IF('Registo da Rotação'!E183='Registo da Rotação'!F183,1,0))</f>
+        <f>IF('Registo da Rotação'!C192="",0,IF('Registo da Rotação'!E192='Registo da Rotação'!F192,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y29" s="8">
-        <f>IF('Registo da Rotação'!C183="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B183)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C192="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B192)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z29" s="8">
-        <f>IF('Registo da Rotação'!C183="",0,IF('Registo da Rotação'!D183="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C183,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F183)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C183,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F183)&gt;0,1,0),IF('Registo da Rotação'!D183="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C183,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F183)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C183,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F183)&gt;0,1,0),IF('Registo da Rotação'!D183="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C183,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F183)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C183,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F183)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C192="",0,IF('Registo da Rotação'!D192="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C192,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F192)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C192,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F192)&gt;0,1,0),IF('Registo da Rotação'!D192="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C192,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F192)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C192,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F192)&gt;0,1,0),IF('Registo da Rotação'!D192="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C192,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F192)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C192,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F192)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA29" s="8">
-        <f>IF('Registo da Rotação'!C183="",0,IF('Registo da Rotação'!D183="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C183,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E183)=0,1,0),IF('Registo da Rotação'!D183="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C183,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E183)=0,1,0),IF('Registo da Rotação'!D183="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A183,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B183,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C183,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E183)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C192="",0,IF('Registo da Rotação'!D192="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C192,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E192)=0,1,0),IF('Registo da Rotação'!D192="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C192,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E192)=0,1,0),IF('Registo da Rotação'!D192="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C192,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E192)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB29" s="8">
-        <f>IF('Registo da Rotação'!C183="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B183,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H183="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C192="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B192,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H192="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC29" s="1"/>
@@ -11095,56 +11555,56 @@
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="8">
-        <f>IF('Registo da Rotação'!A79="",0,IF(COUNTA('Registo da Rotação'!B79:K79)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A88="",0,IF(COUNTA('Registo da Rotação'!B88:K88)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P30" s="8">
-        <f>IF('Registo da Rotação'!A79="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C79)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A88="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C88)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q30" s="8">
-        <f>IF('Registo da Rotação'!A79="",0,IF(OR('Registo da Rotação'!F79='Registo da Rotação'!G79,'Registo da Rotação'!F79='Registo da Rotação'!H79,'Registo da Rotação'!G79='Registo da Rotação'!H79),1,0))</f>
+        <f>IF('Registo da Rotação'!A88="",0,IF(OR('Registo da Rotação'!F88='Registo da Rotação'!G88,'Registo da Rotação'!F88='Registo da Rotação'!H88,'Registo da Rotação'!G88='Registo da Rotação'!H88),1,0))</f>
         <v>0</v>
       </c>
       <c r="R30" s="8">
-        <f>IF('Registo da Rotação'!A79="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C79,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I79="Ainda não avaliado",'Registo da Rotação'!J79="Ainda não avaliado",'Registo da Rotação'!K79="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A88="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C88,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I88="Ainda não avaliado",'Registo da Rotação'!J88="Ainda não avaliado",'Registo da Rotação'!K88="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S30" s="8">
-        <f>IF('Registo da Rotação'!A79="",0,IF(AND('Registo da Rotação'!G79=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79),'Registo da Rotação'!$G$54:'Registo da Rotação'!G78),""),'Registo da Rotação'!H79=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79),'Registo da Rotação'!$H$54:'Registo da Rotação'!H78),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A88="",0,IF(AND('Registo da Rotação'!G88=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88),'Registo da Rotação'!$G$54:'Registo da Rotação'!G87),""),'Registo da Rotação'!H88=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88),'Registo da Rotação'!$H$54:'Registo da Rotação'!H87),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T30" s="8">
-        <f>IF('Registo da Rotação'!A79="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Registo da Rotação'!G79)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Registo da Rotação'!H79)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F79,'Listas de apoio'!$A$5='Registo da Rotação'!G79,'Listas de apoio'!$A$5='Registo da Rotação'!H79),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Registo da Rotação'!G79)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Registo da Rotação'!H79)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F79,'Listas de apoio'!$A$6='Registo da Rotação'!G79,'Listas de apoio'!$A$6='Registo da Rotação'!H79),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Registo da Rotação'!G79)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Registo da Rotação'!H79)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F79,'Listas de apoio'!$A$7='Registo da Rotação'!G79,'Listas de apoio'!$A$7='Registo da Rotação'!H79),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Registo da Rotação'!G79)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Registo da Rotação'!H79)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F79,'Listas de apoio'!$A$8='Registo da Rotação'!G79,'Listas de apoio'!$A$8='Registo da Rotação'!H79),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F78='Registo da Rotação'!F79)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Registo da Rotação'!G79)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Registo da Rotação'!H79)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F78)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G78='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H78='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A88="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Registo da Rotação'!G88)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Registo da Rotação'!H88)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F88,'Listas de apoio'!$A$5='Registo da Rotação'!G88,'Listas de apoio'!$A$5='Registo da Rotação'!H88),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Registo da Rotação'!G88)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Registo da Rotação'!H88)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F88,'Listas de apoio'!$A$6='Registo da Rotação'!G88,'Listas de apoio'!$A$6='Registo da Rotação'!H88),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Registo da Rotação'!G88)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Registo da Rotação'!H88)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F88,'Listas de apoio'!$A$7='Registo da Rotação'!G88,'Listas de apoio'!$A$7='Registo da Rotação'!H88),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Registo da Rotação'!G88)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Registo da Rotação'!H88)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F88,'Listas de apoio'!$A$8='Registo da Rotação'!G88,'Listas de apoio'!$A$8='Registo da Rotação'!H88),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Registo da Rotação'!G88)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Registo da Rotação'!H88)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U30" s="8">
-        <f>IF('Registo da Rotação'!A79="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A79)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C79,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D79)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A88="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A88)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C88,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D88)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V30" s="1"/>
       <c r="W30" s="8">
-        <f>IF('Registo da Rotação'!C184="",0,IF(COUNTA('Registo da Rotação'!A184:H184)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C193="",0,IF(COUNTA('Registo da Rotação'!A193:H193)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X30" s="8">
-        <f>IF('Registo da Rotação'!C184="",0,IF('Registo da Rotação'!E184='Registo da Rotação'!F184,1,0))</f>
+        <f>IF('Registo da Rotação'!C193="",0,IF('Registo da Rotação'!E193='Registo da Rotação'!F193,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y30" s="8">
-        <f>IF('Registo da Rotação'!C184="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B184)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C193="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B193)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z30" s="8">
-        <f>IF('Registo da Rotação'!C184="",0,IF('Registo da Rotação'!D184="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C184,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F184)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C184,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F184)&gt;0,1,0),IF('Registo da Rotação'!D184="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C184,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F184)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C184,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F184)&gt;0,1,0),IF('Registo da Rotação'!D184="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C184,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F184)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C184,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F184)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C193="",0,IF('Registo da Rotação'!D193="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C193,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F193)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C193,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F193)&gt;0,1,0),IF('Registo da Rotação'!D193="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C193,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F193)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C193,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F193)&gt;0,1,0),IF('Registo da Rotação'!D193="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C193,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F193)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C193,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F193)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA30" s="8">
-        <f>IF('Registo da Rotação'!C184="",0,IF('Registo da Rotação'!D184="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C184,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E184)=0,1,0),IF('Registo da Rotação'!D184="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C184,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E184)=0,1,0),IF('Registo da Rotação'!D184="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A184,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B184,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C184,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E184)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C193="",0,IF('Registo da Rotação'!D193="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C193,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E193)=0,1,0),IF('Registo da Rotação'!D193="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C193,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E193)=0,1,0),IF('Registo da Rotação'!D193="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C193,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E193)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB30" s="8">
-        <f>IF('Registo da Rotação'!C184="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B184,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H184="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C193="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B193,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H193="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC30" s="1"/>
@@ -11170,56 +11630,56 @@
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="8">
-        <f>IF('Registo da Rotação'!A80="",0,IF(COUNTA('Registo da Rotação'!B80:K80)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A89="",0,IF(COUNTA('Registo da Rotação'!B89:K89)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P31" s="8">
-        <f>IF('Registo da Rotação'!A80="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C80)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A89="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C89)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q31" s="8">
-        <f>IF('Registo da Rotação'!A80="",0,IF(OR('Registo da Rotação'!F80='Registo da Rotação'!G80,'Registo da Rotação'!F80='Registo da Rotação'!H80,'Registo da Rotação'!G80='Registo da Rotação'!H80),1,0))</f>
+        <f>IF('Registo da Rotação'!A89="",0,IF(OR('Registo da Rotação'!F89='Registo da Rotação'!G89,'Registo da Rotação'!F89='Registo da Rotação'!H89,'Registo da Rotação'!G89='Registo da Rotação'!H89),1,0))</f>
         <v>0</v>
       </c>
       <c r="R31" s="8">
-        <f>IF('Registo da Rotação'!A80="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C80,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I80="Ainda não avaliado",'Registo da Rotação'!J80="Ainda não avaliado",'Registo da Rotação'!K80="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A89="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C89,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I89="Ainda não avaliado",'Registo da Rotação'!J89="Ainda não avaliado",'Registo da Rotação'!K89="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S31" s="8">
-        <f>IF('Registo da Rotação'!A80="",0,IF(AND('Registo da Rotação'!G80=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80),'Registo da Rotação'!$G$54:'Registo da Rotação'!G79),""),'Registo da Rotação'!H80=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80),'Registo da Rotação'!$H$54:'Registo da Rotação'!H79),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A89="",0,IF(AND('Registo da Rotação'!G89=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89),'Registo da Rotação'!$G$54:'Registo da Rotação'!G88),""),'Registo da Rotação'!H89=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89),'Registo da Rotação'!$H$54:'Registo da Rotação'!H88),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T31" s="8">
-        <f>IF('Registo da Rotação'!A80="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Registo da Rotação'!G80)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Registo da Rotação'!H80)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F80,'Listas de apoio'!$A$5='Registo da Rotação'!G80,'Listas de apoio'!$A$5='Registo da Rotação'!H80),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Registo da Rotação'!G80)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Registo da Rotação'!H80)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F80,'Listas de apoio'!$A$6='Registo da Rotação'!G80,'Listas de apoio'!$A$6='Registo da Rotação'!H80),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Registo da Rotação'!G80)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Registo da Rotação'!H80)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F80,'Listas de apoio'!$A$7='Registo da Rotação'!G80,'Listas de apoio'!$A$7='Registo da Rotação'!H80),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Registo da Rotação'!G80)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Registo da Rotação'!H80)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F80,'Listas de apoio'!$A$8='Registo da Rotação'!G80,'Listas de apoio'!$A$8='Registo da Rotação'!H80),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F79='Registo da Rotação'!F80)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Registo da Rotação'!G80)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Registo da Rotação'!H80)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F79)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G79='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H79='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A89="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Registo da Rotação'!G89)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Registo da Rotação'!H89)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F89,'Listas de apoio'!$A$5='Registo da Rotação'!G89,'Listas de apoio'!$A$5='Registo da Rotação'!H89),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Registo da Rotação'!G89)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Registo da Rotação'!H89)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F89,'Listas de apoio'!$A$6='Registo da Rotação'!G89,'Listas de apoio'!$A$6='Registo da Rotação'!H89),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Registo da Rotação'!G89)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Registo da Rotação'!H89)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F89,'Listas de apoio'!$A$7='Registo da Rotação'!G89,'Listas de apoio'!$A$7='Registo da Rotação'!H89),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Registo da Rotação'!G89)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Registo da Rotação'!H89)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F89,'Listas de apoio'!$A$8='Registo da Rotação'!G89,'Listas de apoio'!$A$8='Registo da Rotação'!H89),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Registo da Rotação'!G89)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Registo da Rotação'!H89)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U31" s="8">
-        <f>IF('Registo da Rotação'!A80="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A80)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C80,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D80)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A89="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A89)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C89,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D89)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V31" s="1"/>
       <c r="W31" s="8">
-        <f>IF('Registo da Rotação'!C185="",0,IF(COUNTA('Registo da Rotação'!A185:H185)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C194="",0,IF(COUNTA('Registo da Rotação'!A194:H194)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X31" s="8">
-        <f>IF('Registo da Rotação'!C185="",0,IF('Registo da Rotação'!E185='Registo da Rotação'!F185,1,0))</f>
+        <f>IF('Registo da Rotação'!C194="",0,IF('Registo da Rotação'!E194='Registo da Rotação'!F194,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y31" s="8">
-        <f>IF('Registo da Rotação'!C185="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B185)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C194="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B194)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z31" s="8">
-        <f>IF('Registo da Rotação'!C185="",0,IF('Registo da Rotação'!D185="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C185,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F185)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C185,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F185)&gt;0,1,0),IF('Registo da Rotação'!D185="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C185,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F185)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C185,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F185)&gt;0,1,0),IF('Registo da Rotação'!D185="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C185,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F185)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C185,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F185)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C194="",0,IF('Registo da Rotação'!D194="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C194,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F194)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C194,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F194)&gt;0,1,0),IF('Registo da Rotação'!D194="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C194,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F194)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C194,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F194)&gt;0,1,0),IF('Registo da Rotação'!D194="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C194,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F194)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C194,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F194)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA31" s="8">
-        <f>IF('Registo da Rotação'!C185="",0,IF('Registo da Rotação'!D185="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C185,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E185)=0,1,0),IF('Registo da Rotação'!D185="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C185,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E185)=0,1,0),IF('Registo da Rotação'!D185="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A185,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B185,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C185,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E185)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C194="",0,IF('Registo da Rotação'!D194="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C194,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E194)=0,1,0),IF('Registo da Rotação'!D194="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C194,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E194)=0,1,0),IF('Registo da Rotação'!D194="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C194,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E194)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB31" s="8">
-        <f>IF('Registo da Rotação'!C185="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B185,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H185="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C194="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B194,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H194="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC31" s="1"/>
@@ -11245,56 +11705,56 @@
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
       <c r="O32" s="8">
-        <f>IF('Registo da Rotação'!A81="",0,IF(COUNTA('Registo da Rotação'!B81:K81)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A90="",0,IF(COUNTA('Registo da Rotação'!B90:K90)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P32" s="8">
-        <f>IF('Registo da Rotação'!A81="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C81)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A90="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C90)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q32" s="8">
-        <f>IF('Registo da Rotação'!A81="",0,IF(OR('Registo da Rotação'!F81='Registo da Rotação'!G81,'Registo da Rotação'!F81='Registo da Rotação'!H81,'Registo da Rotação'!G81='Registo da Rotação'!H81),1,0))</f>
+        <f>IF('Registo da Rotação'!A90="",0,IF(OR('Registo da Rotação'!F90='Registo da Rotação'!G90,'Registo da Rotação'!F90='Registo da Rotação'!H90,'Registo da Rotação'!G90='Registo da Rotação'!H90),1,0))</f>
         <v>0</v>
       </c>
       <c r="R32" s="8">
-        <f>IF('Registo da Rotação'!A81="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C81,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I81="Ainda não avaliado",'Registo da Rotação'!J81="Ainda não avaliado",'Registo da Rotação'!K81="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A90="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C90,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I90="Ainda não avaliado",'Registo da Rotação'!J90="Ainda não avaliado",'Registo da Rotação'!K90="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S32" s="8">
-        <f>IF('Registo da Rotação'!A81="",0,IF(AND('Registo da Rotação'!G81=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81),'Registo da Rotação'!$G$54:'Registo da Rotação'!G80),""),'Registo da Rotação'!H81=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81),'Registo da Rotação'!$H$54:'Registo da Rotação'!H80),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A90="",0,IF(AND('Registo da Rotação'!G90=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90),'Registo da Rotação'!$G$54:'Registo da Rotação'!G89),""),'Registo da Rotação'!H90=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90),'Registo da Rotação'!$H$54:'Registo da Rotação'!H89),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T32" s="8">
-        <f>IF('Registo da Rotação'!A81="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Registo da Rotação'!G81)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Registo da Rotação'!H81)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F81,'Listas de apoio'!$A$5='Registo da Rotação'!G81,'Listas de apoio'!$A$5='Registo da Rotação'!H81),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Registo da Rotação'!G81)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Registo da Rotação'!H81)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F81,'Listas de apoio'!$A$6='Registo da Rotação'!G81,'Listas de apoio'!$A$6='Registo da Rotação'!H81),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Registo da Rotação'!G81)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Registo da Rotação'!H81)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F81,'Listas de apoio'!$A$7='Registo da Rotação'!G81,'Listas de apoio'!$A$7='Registo da Rotação'!H81),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Registo da Rotação'!G81)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Registo da Rotação'!H81)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F81,'Listas de apoio'!$A$8='Registo da Rotação'!G81,'Listas de apoio'!$A$8='Registo da Rotação'!H81),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F80='Registo da Rotação'!F81)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Registo da Rotação'!G81)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Registo da Rotação'!H81)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F80)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G80='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H80='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A90="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Registo da Rotação'!G90)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Registo da Rotação'!H90)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F90,'Listas de apoio'!$A$5='Registo da Rotação'!G90,'Listas de apoio'!$A$5='Registo da Rotação'!H90),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Registo da Rotação'!G90)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Registo da Rotação'!H90)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F90,'Listas de apoio'!$A$6='Registo da Rotação'!G90,'Listas de apoio'!$A$6='Registo da Rotação'!H90),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Registo da Rotação'!G90)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Registo da Rotação'!H90)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F90,'Listas de apoio'!$A$7='Registo da Rotação'!G90,'Listas de apoio'!$A$7='Registo da Rotação'!H90),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Registo da Rotação'!G90)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Registo da Rotação'!H90)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F90,'Listas de apoio'!$A$8='Registo da Rotação'!G90,'Listas de apoio'!$A$8='Registo da Rotação'!H90),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Registo da Rotação'!G90)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Registo da Rotação'!H90)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U32" s="8">
-        <f>IF('Registo da Rotação'!A81="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A81)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C81,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D81)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A90="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A90)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C90,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D90)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V32" s="1"/>
       <c r="W32" s="8">
-        <f>IF('Registo da Rotação'!C186="",0,IF(COUNTA('Registo da Rotação'!A186:H186)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C195="",0,IF(COUNTA('Registo da Rotação'!A195:H195)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X32" s="8">
-        <f>IF('Registo da Rotação'!C186="",0,IF('Registo da Rotação'!E186='Registo da Rotação'!F186,1,0))</f>
+        <f>IF('Registo da Rotação'!C195="",0,IF('Registo da Rotação'!E195='Registo da Rotação'!F195,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y32" s="8">
-        <f>IF('Registo da Rotação'!C186="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B186)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C195="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B195)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z32" s="8">
-        <f>IF('Registo da Rotação'!C186="",0,IF('Registo da Rotação'!D186="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C186,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F186)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C186,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F186)&gt;0,1,0),IF('Registo da Rotação'!D186="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C186,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F186)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C186,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F186)&gt;0,1,0),IF('Registo da Rotação'!D186="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C186,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F186)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C186,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F186)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C195="",0,IF('Registo da Rotação'!D195="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C195,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F195)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C195,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F195)&gt;0,1,0),IF('Registo da Rotação'!D195="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C195,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F195)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C195,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F195)&gt;0,1,0),IF('Registo da Rotação'!D195="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C195,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F195)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C195,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F195)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA32" s="8">
-        <f>IF('Registo da Rotação'!C186="",0,IF('Registo da Rotação'!D186="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C186,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E186)=0,1,0),IF('Registo da Rotação'!D186="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C186,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E186)=0,1,0),IF('Registo da Rotação'!D186="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A186,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B186,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C186,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E186)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C195="",0,IF('Registo da Rotação'!D195="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C195,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E195)=0,1,0),IF('Registo da Rotação'!D195="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C195,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E195)=0,1,0),IF('Registo da Rotação'!D195="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C195,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E195)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB32" s="8">
-        <f>IF('Registo da Rotação'!C186="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B186,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H186="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C195="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B195,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H195="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC32" s="1"/>
@@ -11320,56 +11780,56 @@
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
       <c r="O33" s="8">
-        <f>IF('Registo da Rotação'!A82="",0,IF(COUNTA('Registo da Rotação'!B82:K82)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A91="",0,IF(COUNTA('Registo da Rotação'!B91:K91)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P33" s="8">
-        <f>IF('Registo da Rotação'!A82="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C82)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A91="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C91)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q33" s="8">
-        <f>IF('Registo da Rotação'!A82="",0,IF(OR('Registo da Rotação'!F82='Registo da Rotação'!G82,'Registo da Rotação'!F82='Registo da Rotação'!H82,'Registo da Rotação'!G82='Registo da Rotação'!H82),1,0))</f>
+        <f>IF('Registo da Rotação'!A91="",0,IF(OR('Registo da Rotação'!F91='Registo da Rotação'!G91,'Registo da Rotação'!F91='Registo da Rotação'!H91,'Registo da Rotação'!G91='Registo da Rotação'!H91),1,0))</f>
         <v>0</v>
       </c>
       <c r="R33" s="8">
-        <f>IF('Registo da Rotação'!A82="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C82,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I82="Ainda não avaliado",'Registo da Rotação'!J82="Ainda não avaliado",'Registo da Rotação'!K82="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A91="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C91,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I91="Ainda não avaliado",'Registo da Rotação'!J91="Ainda não avaliado",'Registo da Rotação'!K91="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S33" s="8">
-        <f>IF('Registo da Rotação'!A82="",0,IF(AND('Registo da Rotação'!G82=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82),'Registo da Rotação'!$G$54:'Registo da Rotação'!G81),""),'Registo da Rotação'!H82=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82),'Registo da Rotação'!$H$54:'Registo da Rotação'!H81),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A91="",0,IF(AND('Registo da Rotação'!G91=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91),'Registo da Rotação'!$G$54:'Registo da Rotação'!G90),""),'Registo da Rotação'!H91=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91),'Registo da Rotação'!$H$54:'Registo da Rotação'!H90),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T33" s="8">
-        <f>IF('Registo da Rotação'!A82="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Registo da Rotação'!G82)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Registo da Rotação'!H82)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F82,'Listas de apoio'!$A$5='Registo da Rotação'!G82,'Listas de apoio'!$A$5='Registo da Rotação'!H82),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Registo da Rotação'!G82)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Registo da Rotação'!H82)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F82,'Listas de apoio'!$A$6='Registo da Rotação'!G82,'Listas de apoio'!$A$6='Registo da Rotação'!H82),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Registo da Rotação'!G82)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Registo da Rotação'!H82)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F82,'Listas de apoio'!$A$7='Registo da Rotação'!G82,'Listas de apoio'!$A$7='Registo da Rotação'!H82),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Registo da Rotação'!G82)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Registo da Rotação'!H82)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F82,'Listas de apoio'!$A$8='Registo da Rotação'!G82,'Listas de apoio'!$A$8='Registo da Rotação'!H82),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F81='Registo da Rotação'!F82)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Registo da Rotação'!G82)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Registo da Rotação'!H82)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F81)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G81='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H81='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A91="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Registo da Rotação'!G91)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Registo da Rotação'!H91)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F91,'Listas de apoio'!$A$5='Registo da Rotação'!G91,'Listas de apoio'!$A$5='Registo da Rotação'!H91),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Registo da Rotação'!G91)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Registo da Rotação'!H91)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F91,'Listas de apoio'!$A$6='Registo da Rotação'!G91,'Listas de apoio'!$A$6='Registo da Rotação'!H91),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Registo da Rotação'!G91)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Registo da Rotação'!H91)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F91,'Listas de apoio'!$A$7='Registo da Rotação'!G91,'Listas de apoio'!$A$7='Registo da Rotação'!H91),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Registo da Rotação'!G91)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Registo da Rotação'!H91)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F91,'Listas de apoio'!$A$8='Registo da Rotação'!G91,'Listas de apoio'!$A$8='Registo da Rotação'!H91),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Registo da Rotação'!G91)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Registo da Rotação'!H91)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U33" s="8">
-        <f>IF('Registo da Rotação'!A82="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A82)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C82,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D82)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A91="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A91)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C91,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D91)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V33" s="1"/>
       <c r="W33" s="8">
-        <f>IF('Registo da Rotação'!C187="",0,IF(COUNTA('Registo da Rotação'!A187:H187)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C196="",0,IF(COUNTA('Registo da Rotação'!A196:H196)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X33" s="8">
-        <f>IF('Registo da Rotação'!C187="",0,IF('Registo da Rotação'!E187='Registo da Rotação'!F187,1,0))</f>
+        <f>IF('Registo da Rotação'!C196="",0,IF('Registo da Rotação'!E196='Registo da Rotação'!F196,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y33" s="8">
-        <f>IF('Registo da Rotação'!C187="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B187)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C196="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B196)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z33" s="8">
-        <f>IF('Registo da Rotação'!C187="",0,IF('Registo da Rotação'!D187="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C187,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F187)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C187,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F187)&gt;0,1,0),IF('Registo da Rotação'!D187="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C187,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F187)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C187,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F187)&gt;0,1,0),IF('Registo da Rotação'!D187="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C187,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F187)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C187,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F187)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C196="",0,IF('Registo da Rotação'!D196="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C196,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F196)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C196,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F196)&gt;0,1,0),IF('Registo da Rotação'!D196="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C196,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F196)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C196,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F196)&gt;0,1,0),IF('Registo da Rotação'!D196="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C196,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F196)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C196,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F196)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA33" s="8">
-        <f>IF('Registo da Rotação'!C187="",0,IF('Registo da Rotação'!D187="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C187,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E187)=0,1,0),IF('Registo da Rotação'!D187="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C187,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E187)=0,1,0),IF('Registo da Rotação'!D187="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A187,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B187,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C187,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E187)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C196="",0,IF('Registo da Rotação'!D196="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C196,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E196)=0,1,0),IF('Registo da Rotação'!D196="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C196,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E196)=0,1,0),IF('Registo da Rotação'!D196="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C196,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E196)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB33" s="8">
-        <f>IF('Registo da Rotação'!C187="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B187,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H187="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C196="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B196,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H196="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC33" s="1"/>
@@ -11395,56 +11855,56 @@
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
       <c r="O34" s="8">
-        <f>IF('Registo da Rotação'!A83="",0,IF(COUNTA('Registo da Rotação'!B83:K83)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A92="",0,IF(COUNTA('Registo da Rotação'!B92:K92)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P34" s="8">
-        <f>IF('Registo da Rotação'!A83="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C83)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A92="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C92)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q34" s="8">
-        <f>IF('Registo da Rotação'!A83="",0,IF(OR('Registo da Rotação'!F83='Registo da Rotação'!G83,'Registo da Rotação'!F83='Registo da Rotação'!H83,'Registo da Rotação'!G83='Registo da Rotação'!H83),1,0))</f>
+        <f>IF('Registo da Rotação'!A92="",0,IF(OR('Registo da Rotação'!F92='Registo da Rotação'!G92,'Registo da Rotação'!F92='Registo da Rotação'!H92,'Registo da Rotação'!G92='Registo da Rotação'!H92),1,0))</f>
         <v>0</v>
       </c>
       <c r="R34" s="8">
-        <f>IF('Registo da Rotação'!A83="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C83,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I83="Ainda não avaliado",'Registo da Rotação'!J83="Ainda não avaliado",'Registo da Rotação'!K83="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A92="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C92,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I92="Ainda não avaliado",'Registo da Rotação'!J92="Ainda não avaliado",'Registo da Rotação'!K92="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S34" s="8">
-        <f>IF('Registo da Rotação'!A83="",0,IF(AND('Registo da Rotação'!G83=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83),'Registo da Rotação'!$G$54:'Registo da Rotação'!G82),""),'Registo da Rotação'!H83=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83),'Registo da Rotação'!$H$54:'Registo da Rotação'!H82),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A92="",0,IF(AND('Registo da Rotação'!G92=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92),'Registo da Rotação'!$G$54:'Registo da Rotação'!G91),""),'Registo da Rotação'!H92=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92),'Registo da Rotação'!$H$54:'Registo da Rotação'!H91),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T34" s="8">
-        <f>IF('Registo da Rotação'!A83="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Registo da Rotação'!G83)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Registo da Rotação'!H83)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F83,'Listas de apoio'!$A$5='Registo da Rotação'!G83,'Listas de apoio'!$A$5='Registo da Rotação'!H83),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Registo da Rotação'!G83)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Registo da Rotação'!H83)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F83,'Listas de apoio'!$A$6='Registo da Rotação'!G83,'Listas de apoio'!$A$6='Registo da Rotação'!H83),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Registo da Rotação'!G83)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Registo da Rotação'!H83)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F83,'Listas de apoio'!$A$7='Registo da Rotação'!G83,'Listas de apoio'!$A$7='Registo da Rotação'!H83),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Registo da Rotação'!G83)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Registo da Rotação'!H83)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F83,'Listas de apoio'!$A$8='Registo da Rotação'!G83,'Listas de apoio'!$A$8='Registo da Rotação'!H83),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F82='Registo da Rotação'!F83)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Registo da Rotação'!G83)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Registo da Rotação'!H83)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F82)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G82='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H82='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A92="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Registo da Rotação'!G92)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Registo da Rotação'!H92)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F92,'Listas de apoio'!$A$5='Registo da Rotação'!G92,'Listas de apoio'!$A$5='Registo da Rotação'!H92),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Registo da Rotação'!G92)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Registo da Rotação'!H92)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F92,'Listas de apoio'!$A$6='Registo da Rotação'!G92,'Listas de apoio'!$A$6='Registo da Rotação'!H92),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Registo da Rotação'!G92)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Registo da Rotação'!H92)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F92,'Listas de apoio'!$A$7='Registo da Rotação'!G92,'Listas de apoio'!$A$7='Registo da Rotação'!H92),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Registo da Rotação'!G92)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Registo da Rotação'!H92)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F92,'Listas de apoio'!$A$8='Registo da Rotação'!G92,'Listas de apoio'!$A$8='Registo da Rotação'!H92),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Registo da Rotação'!G92)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Registo da Rotação'!H92)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U34" s="8">
-        <f>IF('Registo da Rotação'!A83="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A83)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C83,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D83)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A92="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A92)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C92,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D92)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V34" s="1"/>
       <c r="W34" s="8">
-        <f>IF('Registo da Rotação'!C188="",0,IF(COUNTA('Registo da Rotação'!A188:H188)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C197="",0,IF(COUNTA('Registo da Rotação'!A197:H197)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X34" s="8">
-        <f>IF('Registo da Rotação'!C188="",0,IF('Registo da Rotação'!E188='Registo da Rotação'!F188,1,0))</f>
+        <f>IF('Registo da Rotação'!C197="",0,IF('Registo da Rotação'!E197='Registo da Rotação'!F197,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y34" s="8">
-        <f>IF('Registo da Rotação'!C188="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B188)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C197="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B197)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z34" s="8">
-        <f>IF('Registo da Rotação'!C188="",0,IF('Registo da Rotação'!D188="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C188,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F188)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C188,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F188)&gt;0,1,0),IF('Registo da Rotação'!D188="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C188,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F188)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C188,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F188)&gt;0,1,0),IF('Registo da Rotação'!D188="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C188,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F188)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C188,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F188)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C197="",0,IF('Registo da Rotação'!D197="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C197,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F197)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C197,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F197)&gt;0,1,0),IF('Registo da Rotação'!D197="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C197,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F197)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C197,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F197)&gt;0,1,0),IF('Registo da Rotação'!D197="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C197,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F197)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C197,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F197)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA34" s="8">
-        <f>IF('Registo da Rotação'!C188="",0,IF('Registo da Rotação'!D188="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C188,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E188)=0,1,0),IF('Registo da Rotação'!D188="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C188,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E188)=0,1,0),IF('Registo da Rotação'!D188="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A188,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B188,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C188,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E188)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C197="",0,IF('Registo da Rotação'!D197="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C197,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E197)=0,1,0),IF('Registo da Rotação'!D197="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C197,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E197)=0,1,0),IF('Registo da Rotação'!D197="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C197,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E197)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB34" s="8">
-        <f>IF('Registo da Rotação'!C188="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B188,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H188="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C197="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B197,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H197="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC34" s="1"/>
@@ -11470,56 +11930,56 @@
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
       <c r="O35" s="8">
-        <f>IF('Registo da Rotação'!A84="",0,IF(COUNTA('Registo da Rotação'!B84:K84)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A93="",0,IF(COUNTA('Registo da Rotação'!B93:K93)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P35" s="8">
-        <f>IF('Registo da Rotação'!A84="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C84)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A93="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C93)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q35" s="8">
-        <f>IF('Registo da Rotação'!A84="",0,IF(OR('Registo da Rotação'!F84='Registo da Rotação'!G84,'Registo da Rotação'!F84='Registo da Rotação'!H84,'Registo da Rotação'!G84='Registo da Rotação'!H84),1,0))</f>
+        <f>IF('Registo da Rotação'!A93="",0,IF(OR('Registo da Rotação'!F93='Registo da Rotação'!G93,'Registo da Rotação'!F93='Registo da Rotação'!H93,'Registo da Rotação'!G93='Registo da Rotação'!H93),1,0))</f>
         <v>0</v>
       </c>
       <c r="R35" s="8">
-        <f>IF('Registo da Rotação'!A84="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C84,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I84="Ainda não avaliado",'Registo da Rotação'!J84="Ainda não avaliado",'Registo da Rotação'!K84="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A93="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C93,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I93="Ainda não avaliado",'Registo da Rotação'!J93="Ainda não avaliado",'Registo da Rotação'!K93="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S35" s="8">
-        <f>IF('Registo da Rotação'!A84="",0,IF(AND('Registo da Rotação'!G84=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84),'Registo da Rotação'!$G$54:'Registo da Rotação'!G83),""),'Registo da Rotação'!H84=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84),'Registo da Rotação'!$H$54:'Registo da Rotação'!H83),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A93="",0,IF(AND('Registo da Rotação'!G93=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93),'Registo da Rotação'!$G$54:'Registo da Rotação'!G92),""),'Registo da Rotação'!H93=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93),'Registo da Rotação'!$H$54:'Registo da Rotação'!H92),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T35" s="8">
-        <f>IF('Registo da Rotação'!A84="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Registo da Rotação'!G84)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Registo da Rotação'!H84)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F84,'Listas de apoio'!$A$5='Registo da Rotação'!G84,'Listas de apoio'!$A$5='Registo da Rotação'!H84),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Registo da Rotação'!G84)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Registo da Rotação'!H84)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F84,'Listas de apoio'!$A$6='Registo da Rotação'!G84,'Listas de apoio'!$A$6='Registo da Rotação'!H84),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Registo da Rotação'!G84)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Registo da Rotação'!H84)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F84,'Listas de apoio'!$A$7='Registo da Rotação'!G84,'Listas de apoio'!$A$7='Registo da Rotação'!H84),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Registo da Rotação'!G84)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Registo da Rotação'!H84)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F84,'Listas de apoio'!$A$8='Registo da Rotação'!G84,'Listas de apoio'!$A$8='Registo da Rotação'!H84),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F83='Registo da Rotação'!F84)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Registo da Rotação'!G84)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Registo da Rotação'!H84)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F83)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G83='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H83='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A93="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Registo da Rotação'!G93)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Registo da Rotação'!H93)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F93,'Listas de apoio'!$A$5='Registo da Rotação'!G93,'Listas de apoio'!$A$5='Registo da Rotação'!H93),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Registo da Rotação'!G93)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Registo da Rotação'!H93)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F93,'Listas de apoio'!$A$6='Registo da Rotação'!G93,'Listas de apoio'!$A$6='Registo da Rotação'!H93),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Registo da Rotação'!G93)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Registo da Rotação'!H93)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F93,'Listas de apoio'!$A$7='Registo da Rotação'!G93,'Listas de apoio'!$A$7='Registo da Rotação'!H93),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Registo da Rotação'!G93)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Registo da Rotação'!H93)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F93,'Listas de apoio'!$A$8='Registo da Rotação'!G93,'Listas de apoio'!$A$8='Registo da Rotação'!H93),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Registo da Rotação'!G93)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Registo da Rotação'!H93)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U35" s="8">
-        <f>IF('Registo da Rotação'!A84="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A84)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C84,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D84)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A93="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A93)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C93,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D93)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V35" s="1"/>
       <c r="W35" s="8">
-        <f>IF('Registo da Rotação'!C189="",0,IF(COUNTA('Registo da Rotação'!A189:H189)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C198="",0,IF(COUNTA('Registo da Rotação'!A198:H198)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X35" s="8">
-        <f>IF('Registo da Rotação'!C189="",0,IF('Registo da Rotação'!E189='Registo da Rotação'!F189,1,0))</f>
+        <f>IF('Registo da Rotação'!C198="",0,IF('Registo da Rotação'!E198='Registo da Rotação'!F198,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y35" s="8">
-        <f>IF('Registo da Rotação'!C189="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B189)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C198="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B198)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z35" s="8">
-        <f>IF('Registo da Rotação'!C189="",0,IF('Registo da Rotação'!D189="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C189,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F189)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C189,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F189)&gt;0,1,0),IF('Registo da Rotação'!D189="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C189,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F189)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C189,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F189)&gt;0,1,0),IF('Registo da Rotação'!D189="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C189,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F189)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C189,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F189)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C198="",0,IF('Registo da Rotação'!D198="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C198,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F198)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C198,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F198)&gt;0,1,0),IF('Registo da Rotação'!D198="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C198,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F198)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C198,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F198)&gt;0,1,0),IF('Registo da Rotação'!D198="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C198,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F198)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C198,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F198)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA35" s="8">
-        <f>IF('Registo da Rotação'!C189="",0,IF('Registo da Rotação'!D189="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C189,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E189)=0,1,0),IF('Registo da Rotação'!D189="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C189,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E189)=0,1,0),IF('Registo da Rotação'!D189="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A189,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B189,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C189,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E189)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C198="",0,IF('Registo da Rotação'!D198="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C198,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E198)=0,1,0),IF('Registo da Rotação'!D198="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C198,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E198)=0,1,0),IF('Registo da Rotação'!D198="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C198,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E198)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB35" s="8">
-        <f>IF('Registo da Rotação'!C189="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B189,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H189="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C198="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B198,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H198="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC35" s="1"/>
@@ -11545,56 +12005,56 @@
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
       <c r="O36" s="8">
-        <f>IF('Registo da Rotação'!A85="",0,IF(COUNTA('Registo da Rotação'!B85:K85)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A94="",0,IF(COUNTA('Registo da Rotação'!B94:K94)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P36" s="8">
-        <f>IF('Registo da Rotação'!A85="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C85)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A94="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C94)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q36" s="8">
-        <f>IF('Registo da Rotação'!A85="",0,IF(OR('Registo da Rotação'!F85='Registo da Rotação'!G85,'Registo da Rotação'!F85='Registo da Rotação'!H85,'Registo da Rotação'!G85='Registo da Rotação'!H85),1,0))</f>
+        <f>IF('Registo da Rotação'!A94="",0,IF(OR('Registo da Rotação'!F94='Registo da Rotação'!G94,'Registo da Rotação'!F94='Registo da Rotação'!H94,'Registo da Rotação'!G94='Registo da Rotação'!H94),1,0))</f>
         <v>0</v>
       </c>
       <c r="R36" s="8">
-        <f>IF('Registo da Rotação'!A85="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C85,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I85="Ainda não avaliado",'Registo da Rotação'!J85="Ainda não avaliado",'Registo da Rotação'!K85="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A94="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C94,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I94="Ainda não avaliado",'Registo da Rotação'!J94="Ainda não avaliado",'Registo da Rotação'!K94="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S36" s="8">
-        <f>IF('Registo da Rotação'!A85="",0,IF(AND('Registo da Rotação'!G85=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85),'Registo da Rotação'!$G$54:'Registo da Rotação'!G84),""),'Registo da Rotação'!H85=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85),'Registo da Rotação'!$H$54:'Registo da Rotação'!H84),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A94="",0,IF(AND('Registo da Rotação'!G94=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94),'Registo da Rotação'!$G$54:'Registo da Rotação'!G93),""),'Registo da Rotação'!H94=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94),'Registo da Rotação'!$H$54:'Registo da Rotação'!H93),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T36" s="8">
-        <f>IF('Registo da Rotação'!A85="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Registo da Rotação'!G85)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Registo da Rotação'!H85)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F85,'Listas de apoio'!$A$5='Registo da Rotação'!G85,'Listas de apoio'!$A$5='Registo da Rotação'!H85),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Registo da Rotação'!G85)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Registo da Rotação'!H85)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F85,'Listas de apoio'!$A$6='Registo da Rotação'!G85,'Listas de apoio'!$A$6='Registo da Rotação'!H85),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Registo da Rotação'!G85)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Registo da Rotação'!H85)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F85,'Listas de apoio'!$A$7='Registo da Rotação'!G85,'Listas de apoio'!$A$7='Registo da Rotação'!H85),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Registo da Rotação'!G85)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Registo da Rotação'!H85)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F85,'Listas de apoio'!$A$8='Registo da Rotação'!G85,'Listas de apoio'!$A$8='Registo da Rotação'!H85),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F84='Registo da Rotação'!F85)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Registo da Rotação'!G85)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Registo da Rotação'!H85)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F84)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G84='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H84='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A94="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Registo da Rotação'!G94)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Registo da Rotação'!H94)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F94,'Listas de apoio'!$A$5='Registo da Rotação'!G94,'Listas de apoio'!$A$5='Registo da Rotação'!H94),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Registo da Rotação'!G94)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Registo da Rotação'!H94)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F94,'Listas de apoio'!$A$6='Registo da Rotação'!G94,'Listas de apoio'!$A$6='Registo da Rotação'!H94),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Registo da Rotação'!G94)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Registo da Rotação'!H94)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F94,'Listas de apoio'!$A$7='Registo da Rotação'!G94,'Listas de apoio'!$A$7='Registo da Rotação'!H94),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Registo da Rotação'!G94)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Registo da Rotação'!H94)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F94,'Listas de apoio'!$A$8='Registo da Rotação'!G94,'Listas de apoio'!$A$8='Registo da Rotação'!H94),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Registo da Rotação'!G94)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Registo da Rotação'!H94)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U36" s="8">
-        <f>IF('Registo da Rotação'!A85="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A85)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C85,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D85)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A94="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A94)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C94,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D94)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V36" s="1"/>
       <c r="W36" s="8">
-        <f>IF('Registo da Rotação'!C190="",0,IF(COUNTA('Registo da Rotação'!A190:H190)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C199="",0,IF(COUNTA('Registo da Rotação'!A199:H199)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X36" s="8">
-        <f>IF('Registo da Rotação'!C190="",0,IF('Registo da Rotação'!E190='Registo da Rotação'!F190,1,0))</f>
+        <f>IF('Registo da Rotação'!C199="",0,IF('Registo da Rotação'!E199='Registo da Rotação'!F199,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y36" s="8">
-        <f>IF('Registo da Rotação'!C190="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B190)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C199="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B199)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z36" s="8">
-        <f>IF('Registo da Rotação'!C190="",0,IF('Registo da Rotação'!D190="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C190,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F190)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C190,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F190)&gt;0,1,0),IF('Registo da Rotação'!D190="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C190,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F190)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C190,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F190)&gt;0,1,0),IF('Registo da Rotação'!D190="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C190,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F190)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C190,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F190)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C199="",0,IF('Registo da Rotação'!D199="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C199,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F199)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C199,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F199)&gt;0,1,0),IF('Registo da Rotação'!D199="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C199,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F199)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C199,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F199)&gt;0,1,0),IF('Registo da Rotação'!D199="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C199,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F199)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C199,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F199)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA36" s="8">
-        <f>IF('Registo da Rotação'!C190="",0,IF('Registo da Rotação'!D190="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C190,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E190)=0,1,0),IF('Registo da Rotação'!D190="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C190,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E190)=0,1,0),IF('Registo da Rotação'!D190="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A190,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B190,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C190,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E190)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C199="",0,IF('Registo da Rotação'!D199="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C199,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E199)=0,1,0),IF('Registo da Rotação'!D199="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C199,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E199)=0,1,0),IF('Registo da Rotação'!D199="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C199,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E199)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB36" s="8">
-        <f>IF('Registo da Rotação'!C190="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B190,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H190="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C199="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B199,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H199="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC36" s="1"/>
@@ -11620,56 +12080,56 @@
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
       <c r="O37" s="8">
-        <f>IF('Registo da Rotação'!A86="",0,IF(COUNTA('Registo da Rotação'!B86:K86)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A95="",0,IF(COUNTA('Registo da Rotação'!B95:K95)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P37" s="8">
-        <f>IF('Registo da Rotação'!A86="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C86)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A95="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C95)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q37" s="8">
-        <f>IF('Registo da Rotação'!A86="",0,IF(OR('Registo da Rotação'!F86='Registo da Rotação'!G86,'Registo da Rotação'!F86='Registo da Rotação'!H86,'Registo da Rotação'!G86='Registo da Rotação'!H86),1,0))</f>
+        <f>IF('Registo da Rotação'!A95="",0,IF(OR('Registo da Rotação'!F95='Registo da Rotação'!G95,'Registo da Rotação'!F95='Registo da Rotação'!H95,'Registo da Rotação'!G95='Registo da Rotação'!H95),1,0))</f>
         <v>0</v>
       </c>
       <c r="R37" s="8">
-        <f>IF('Registo da Rotação'!A86="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C86,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I86="Ainda não avaliado",'Registo da Rotação'!J86="Ainda não avaliado",'Registo da Rotação'!K86="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A95="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C95,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I95="Ainda não avaliado",'Registo da Rotação'!J95="Ainda não avaliado",'Registo da Rotação'!K95="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S37" s="8">
-        <f>IF('Registo da Rotação'!A86="",0,IF(AND('Registo da Rotação'!G86=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86),'Registo da Rotação'!$G$54:'Registo da Rotação'!G85),""),'Registo da Rotação'!H86=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86),'Registo da Rotação'!$H$54:'Registo da Rotação'!H85),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A95="",0,IF(AND('Registo da Rotação'!G95=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95),'Registo da Rotação'!$G$54:'Registo da Rotação'!G94),""),'Registo da Rotação'!H95=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95),'Registo da Rotação'!$H$54:'Registo da Rotação'!H94),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T37" s="8">
-        <f>IF('Registo da Rotação'!A86="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Registo da Rotação'!G86)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Registo da Rotação'!H86)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F86,'Listas de apoio'!$A$5='Registo da Rotação'!G86,'Listas de apoio'!$A$5='Registo da Rotação'!H86),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Registo da Rotação'!G86)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Registo da Rotação'!H86)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F86,'Listas de apoio'!$A$6='Registo da Rotação'!G86,'Listas de apoio'!$A$6='Registo da Rotação'!H86),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Registo da Rotação'!G86)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Registo da Rotação'!H86)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F86,'Listas de apoio'!$A$7='Registo da Rotação'!G86,'Listas de apoio'!$A$7='Registo da Rotação'!H86),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Registo da Rotação'!G86)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Registo da Rotação'!H86)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F86,'Listas de apoio'!$A$8='Registo da Rotação'!G86,'Listas de apoio'!$A$8='Registo da Rotação'!H86),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F85='Registo da Rotação'!F86)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Registo da Rotação'!G86)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Registo da Rotação'!H86)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F85)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G85='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H85='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A95="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Registo da Rotação'!G95)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Registo da Rotação'!H95)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F95,'Listas de apoio'!$A$5='Registo da Rotação'!G95,'Listas de apoio'!$A$5='Registo da Rotação'!H95),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Registo da Rotação'!G95)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Registo da Rotação'!H95)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F95,'Listas de apoio'!$A$6='Registo da Rotação'!G95,'Listas de apoio'!$A$6='Registo da Rotação'!H95),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Registo da Rotação'!G95)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Registo da Rotação'!H95)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F95,'Listas de apoio'!$A$7='Registo da Rotação'!G95,'Listas de apoio'!$A$7='Registo da Rotação'!H95),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Registo da Rotação'!G95)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Registo da Rotação'!H95)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F95,'Listas de apoio'!$A$8='Registo da Rotação'!G95,'Listas de apoio'!$A$8='Registo da Rotação'!H95),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Registo da Rotação'!G95)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Registo da Rotação'!H95)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U37" s="8">
-        <f>IF('Registo da Rotação'!A86="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A86)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C86,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D86)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A95="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A95)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C95,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D95)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V37" s="1"/>
       <c r="W37" s="8">
-        <f>IF('Registo da Rotação'!C191="",0,IF(COUNTA('Registo da Rotação'!A191:H191)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C200="",0,IF(COUNTA('Registo da Rotação'!A200:H200)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X37" s="8">
-        <f>IF('Registo da Rotação'!C191="",0,IF('Registo da Rotação'!E191='Registo da Rotação'!F191,1,0))</f>
+        <f>IF('Registo da Rotação'!C200="",0,IF('Registo da Rotação'!E200='Registo da Rotação'!F200,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y37" s="8">
-        <f>IF('Registo da Rotação'!C191="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B191)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C200="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B200)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z37" s="8">
-        <f>IF('Registo da Rotação'!C191="",0,IF('Registo da Rotação'!D191="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C191,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F191)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C191,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F191)&gt;0,1,0),IF('Registo da Rotação'!D191="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C191,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F191)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C191,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F191)&gt;0,1,0),IF('Registo da Rotação'!D191="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C191,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F191)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C191,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F191)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C200="",0,IF('Registo da Rotação'!D200="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C200,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F200)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C200,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F200)&gt;0,1,0),IF('Registo da Rotação'!D200="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C200,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F200)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C200,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F200)&gt;0,1,0),IF('Registo da Rotação'!D200="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C200,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F200)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C200,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F200)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA37" s="8">
-        <f>IF('Registo da Rotação'!C191="",0,IF('Registo da Rotação'!D191="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C191,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E191)=0,1,0),IF('Registo da Rotação'!D191="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C191,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E191)=0,1,0),IF('Registo da Rotação'!D191="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A191,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B191,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C191,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E191)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C200="",0,IF('Registo da Rotação'!D200="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C200,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E200)=0,1,0),IF('Registo da Rotação'!D200="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C200,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E200)=0,1,0),IF('Registo da Rotação'!D200="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C200,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E200)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB37" s="8">
-        <f>IF('Registo da Rotação'!C191="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B191,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H191="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C200="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B200,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H200="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC37" s="1"/>
@@ -11695,56 +12155,56 @@
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="8">
-        <f>IF('Registo da Rotação'!A87="",0,IF(COUNTA('Registo da Rotação'!B87:K87)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A96="",0,IF(COUNTA('Registo da Rotação'!B96:K96)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P38" s="8">
-        <f>IF('Registo da Rotação'!A87="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C87)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A96="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C96)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q38" s="8">
-        <f>IF('Registo da Rotação'!A87="",0,IF(OR('Registo da Rotação'!F87='Registo da Rotação'!G87,'Registo da Rotação'!F87='Registo da Rotação'!H87,'Registo da Rotação'!G87='Registo da Rotação'!H87),1,0))</f>
+        <f>IF('Registo da Rotação'!A96="",0,IF(OR('Registo da Rotação'!F96='Registo da Rotação'!G96,'Registo da Rotação'!F96='Registo da Rotação'!H96,'Registo da Rotação'!G96='Registo da Rotação'!H96),1,0))</f>
         <v>0</v>
       </c>
       <c r="R38" s="8">
-        <f>IF('Registo da Rotação'!A87="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C87,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I87="Ainda não avaliado",'Registo da Rotação'!J87="Ainda não avaliado",'Registo da Rotação'!K87="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A96="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C96,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I96="Ainda não avaliado",'Registo da Rotação'!J96="Ainda não avaliado",'Registo da Rotação'!K96="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S38" s="8">
-        <f>IF('Registo da Rotação'!A87="",0,IF(AND('Registo da Rotação'!G87=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87),'Registo da Rotação'!$G$54:'Registo da Rotação'!G86),""),'Registo da Rotação'!H87=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87),'Registo da Rotação'!$H$54:'Registo da Rotação'!H86),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A96="",0,IF(AND('Registo da Rotação'!G96=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96),'Registo da Rotação'!$G$54:'Registo da Rotação'!G95),""),'Registo da Rotação'!H96=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96),'Registo da Rotação'!$H$54:'Registo da Rotação'!H95),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T38" s="8">
-        <f>IF('Registo da Rotação'!A87="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Registo da Rotação'!G87)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Registo da Rotação'!H87)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F87,'Listas de apoio'!$A$5='Registo da Rotação'!G87,'Listas de apoio'!$A$5='Registo da Rotação'!H87),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Registo da Rotação'!G87)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Registo da Rotação'!H87)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F87,'Listas de apoio'!$A$6='Registo da Rotação'!G87,'Listas de apoio'!$A$6='Registo da Rotação'!H87),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Registo da Rotação'!G87)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Registo da Rotação'!H87)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F87,'Listas de apoio'!$A$7='Registo da Rotação'!G87,'Listas de apoio'!$A$7='Registo da Rotação'!H87),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Registo da Rotação'!G87)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Registo da Rotação'!H87)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F87,'Listas de apoio'!$A$8='Registo da Rotação'!G87,'Listas de apoio'!$A$8='Registo da Rotação'!H87),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F86='Registo da Rotação'!F87)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Registo da Rotação'!G87)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Registo da Rotação'!H87)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F86)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G86='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H86='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A96="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Registo da Rotação'!G96)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Registo da Rotação'!H96)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F96,'Listas de apoio'!$A$5='Registo da Rotação'!G96,'Listas de apoio'!$A$5='Registo da Rotação'!H96),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Registo da Rotação'!G96)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Registo da Rotação'!H96)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F96,'Listas de apoio'!$A$6='Registo da Rotação'!G96,'Listas de apoio'!$A$6='Registo da Rotação'!H96),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Registo da Rotação'!G96)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Registo da Rotação'!H96)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F96,'Listas de apoio'!$A$7='Registo da Rotação'!G96,'Listas de apoio'!$A$7='Registo da Rotação'!H96),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Registo da Rotação'!G96)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Registo da Rotação'!H96)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F96,'Listas de apoio'!$A$8='Registo da Rotação'!G96,'Listas de apoio'!$A$8='Registo da Rotação'!H96),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Registo da Rotação'!G96)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Registo da Rotação'!H96)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U38" s="8">
-        <f>IF('Registo da Rotação'!A87="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A87)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C87,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D87)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A96="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A96)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C96,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D96)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V38" s="1"/>
       <c r="W38" s="8">
-        <f>IF('Registo da Rotação'!C192="",0,IF(COUNTA('Registo da Rotação'!A192:H192)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C201="",0,IF(COUNTA('Registo da Rotação'!A201:H201)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X38" s="8">
-        <f>IF('Registo da Rotação'!C192="",0,IF('Registo da Rotação'!E192='Registo da Rotação'!F192,1,0))</f>
+        <f>IF('Registo da Rotação'!C201="",0,IF('Registo da Rotação'!E201='Registo da Rotação'!F201,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y38" s="8">
-        <f>IF('Registo da Rotação'!C192="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B192)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C201="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B201)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z38" s="8">
-        <f>IF('Registo da Rotação'!C192="",0,IF('Registo da Rotação'!D192="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C192,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F192)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C192,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F192)&gt;0,1,0),IF('Registo da Rotação'!D192="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C192,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F192)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C192,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F192)&gt;0,1,0),IF('Registo da Rotação'!D192="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C192,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F192)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C192,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F192)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C201="",0,IF('Registo da Rotação'!D201="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C201,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F201)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C201,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F201)&gt;0,1,0),IF('Registo da Rotação'!D201="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C201,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F201)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C201,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F201)&gt;0,1,0),IF('Registo da Rotação'!D201="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C201,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F201)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C201,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F201)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA38" s="8">
-        <f>IF('Registo da Rotação'!C192="",0,IF('Registo da Rotação'!D192="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C192,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E192)=0,1,0),IF('Registo da Rotação'!D192="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C192,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E192)=0,1,0),IF('Registo da Rotação'!D192="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A192,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B192,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C192,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E192)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C201="",0,IF('Registo da Rotação'!D201="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C201,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E201)=0,1,0),IF('Registo da Rotação'!D201="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C201,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E201)=0,1,0),IF('Registo da Rotação'!D201="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C201,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E201)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB38" s="8">
-        <f>IF('Registo da Rotação'!C192="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B192,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H192="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C201="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B201,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H201="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC38" s="1"/>
@@ -11770,56 +12230,56 @@
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
       <c r="O39" s="8">
-        <f>IF('Registo da Rotação'!A88="",0,IF(COUNTA('Registo da Rotação'!B88:K88)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A97="",0,IF(COUNTA('Registo da Rotação'!B97:K97)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P39" s="8">
-        <f>IF('Registo da Rotação'!A88="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C88)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A97="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C97)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q39" s="8">
-        <f>IF('Registo da Rotação'!A88="",0,IF(OR('Registo da Rotação'!F88='Registo da Rotação'!G88,'Registo da Rotação'!F88='Registo da Rotação'!H88,'Registo da Rotação'!G88='Registo da Rotação'!H88),1,0))</f>
+        <f>IF('Registo da Rotação'!A97="",0,IF(OR('Registo da Rotação'!F97='Registo da Rotação'!G97,'Registo da Rotação'!F97='Registo da Rotação'!H97,'Registo da Rotação'!G97='Registo da Rotação'!H97),1,0))</f>
         <v>0</v>
       </c>
       <c r="R39" s="8">
-        <f>IF('Registo da Rotação'!A88="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C88,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I88="Ainda não avaliado",'Registo da Rotação'!J88="Ainda não avaliado",'Registo da Rotação'!K88="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A97="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C97,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I97="Ainda não avaliado",'Registo da Rotação'!J97="Ainda não avaliado",'Registo da Rotação'!K97="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S39" s="8">
-        <f>IF('Registo da Rotação'!A88="",0,IF(AND('Registo da Rotação'!G88=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88),'Registo da Rotação'!$G$54:'Registo da Rotação'!G87),""),'Registo da Rotação'!H88=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88),'Registo da Rotação'!$H$54:'Registo da Rotação'!H87),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A97="",0,IF(AND('Registo da Rotação'!G97=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97),'Registo da Rotação'!$G$54:'Registo da Rotação'!G96),""),'Registo da Rotação'!H97=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97),'Registo da Rotação'!$H$54:'Registo da Rotação'!H96),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T39" s="8">
-        <f>IF('Registo da Rotação'!A88="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Registo da Rotação'!G88)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Registo da Rotação'!H88)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F88,'Listas de apoio'!$A$5='Registo da Rotação'!G88,'Listas de apoio'!$A$5='Registo da Rotação'!H88),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Registo da Rotação'!G88)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Registo da Rotação'!H88)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F88,'Listas de apoio'!$A$6='Registo da Rotação'!G88,'Listas de apoio'!$A$6='Registo da Rotação'!H88),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Registo da Rotação'!G88)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Registo da Rotação'!H88)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F88,'Listas de apoio'!$A$7='Registo da Rotação'!G88,'Listas de apoio'!$A$7='Registo da Rotação'!H88),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Registo da Rotação'!G88)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Registo da Rotação'!H88)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F88,'Listas de apoio'!$A$8='Registo da Rotação'!G88,'Listas de apoio'!$A$8='Registo da Rotação'!H88),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F87='Registo da Rotação'!F88)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Registo da Rotação'!G88)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Registo da Rotação'!H88)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F87)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G87='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H87='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A97="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Registo da Rotação'!G97)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Registo da Rotação'!H97)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F97,'Listas de apoio'!$A$5='Registo da Rotação'!G97,'Listas de apoio'!$A$5='Registo da Rotação'!H97),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Registo da Rotação'!G97)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Registo da Rotação'!H97)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F97,'Listas de apoio'!$A$6='Registo da Rotação'!G97,'Listas de apoio'!$A$6='Registo da Rotação'!H97),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Registo da Rotação'!G97)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Registo da Rotação'!H97)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F97,'Listas de apoio'!$A$7='Registo da Rotação'!G97,'Listas de apoio'!$A$7='Registo da Rotação'!H97),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Registo da Rotação'!G97)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Registo da Rotação'!H97)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F97,'Listas de apoio'!$A$8='Registo da Rotação'!G97,'Listas de apoio'!$A$8='Registo da Rotação'!H97),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Registo da Rotação'!G97)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Registo da Rotação'!H97)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U39" s="8">
-        <f>IF('Registo da Rotação'!A88="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A88)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C88,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D88)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A97="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A97)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C97,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D97)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V39" s="1"/>
       <c r="W39" s="8">
-        <f>IF('Registo da Rotação'!C193="",0,IF(COUNTA('Registo da Rotação'!A193:H193)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C202="",0,IF(COUNTA('Registo da Rotação'!A202:H202)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X39" s="8">
-        <f>IF('Registo da Rotação'!C193="",0,IF('Registo da Rotação'!E193='Registo da Rotação'!F193,1,0))</f>
+        <f>IF('Registo da Rotação'!C202="",0,IF('Registo da Rotação'!E202='Registo da Rotação'!F202,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y39" s="8">
-        <f>IF('Registo da Rotação'!C193="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B193)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C202="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B202)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z39" s="8">
-        <f>IF('Registo da Rotação'!C193="",0,IF('Registo da Rotação'!D193="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C193,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F193)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C193,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F193)&gt;0,1,0),IF('Registo da Rotação'!D193="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C193,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F193)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C193,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F193)&gt;0,1,0),IF('Registo da Rotação'!D193="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C193,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F193)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C193,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F193)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C202="",0,IF('Registo da Rotação'!D202="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C202,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F202)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C202,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F202)&gt;0,1,0),IF('Registo da Rotação'!D202="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C202,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F202)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C202,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F202)&gt;0,1,0),IF('Registo da Rotação'!D202="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C202,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F202)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C202,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F202)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA39" s="8">
-        <f>IF('Registo da Rotação'!C193="",0,IF('Registo da Rotação'!D193="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C193,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E193)=0,1,0),IF('Registo da Rotação'!D193="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C193,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E193)=0,1,0),IF('Registo da Rotação'!D193="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A193,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B193,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C193,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E193)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C202="",0,IF('Registo da Rotação'!D202="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C202,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E202)=0,1,0),IF('Registo da Rotação'!D202="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C202,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E202)=0,1,0),IF('Registo da Rotação'!D202="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C202,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E202)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB39" s="8">
-        <f>IF('Registo da Rotação'!C193="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B193,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H193="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C202="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B202,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H202="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC39" s="1"/>
@@ -11845,56 +12305,56 @@
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
       <c r="O40" s="8">
-        <f>IF('Registo da Rotação'!A89="",0,IF(COUNTA('Registo da Rotação'!B89:K89)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A98="",0,IF(COUNTA('Registo da Rotação'!B98:K98)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P40" s="8">
-        <f>IF('Registo da Rotação'!A89="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C89)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A98="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C98)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q40" s="8">
-        <f>IF('Registo da Rotação'!A89="",0,IF(OR('Registo da Rotação'!F89='Registo da Rotação'!G89,'Registo da Rotação'!F89='Registo da Rotação'!H89,'Registo da Rotação'!G89='Registo da Rotação'!H89),1,0))</f>
+        <f>IF('Registo da Rotação'!A98="",0,IF(OR('Registo da Rotação'!F98='Registo da Rotação'!G98,'Registo da Rotação'!F98='Registo da Rotação'!H98,'Registo da Rotação'!G98='Registo da Rotação'!H98),1,0))</f>
         <v>0</v>
       </c>
       <c r="R40" s="8">
-        <f>IF('Registo da Rotação'!A89="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C89,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I89="Ainda não avaliado",'Registo da Rotação'!J89="Ainda não avaliado",'Registo da Rotação'!K89="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A98="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C98,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I98="Ainda não avaliado",'Registo da Rotação'!J98="Ainda não avaliado",'Registo da Rotação'!K98="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S40" s="8">
-        <f>IF('Registo da Rotação'!A89="",0,IF(AND('Registo da Rotação'!G89=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89),'Registo da Rotação'!$G$54:'Registo da Rotação'!G88),""),'Registo da Rotação'!H89=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89),'Registo da Rotação'!$H$54:'Registo da Rotação'!H88),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A98="",0,IF(AND('Registo da Rotação'!G98=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98),'Registo da Rotação'!$G$54:'Registo da Rotação'!G97),""),'Registo da Rotação'!H98=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98),'Registo da Rotação'!$H$54:'Registo da Rotação'!H97),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T40" s="8">
-        <f>IF('Registo da Rotação'!A89="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Registo da Rotação'!G89)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Registo da Rotação'!H89)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F89,'Listas de apoio'!$A$5='Registo da Rotação'!G89,'Listas de apoio'!$A$5='Registo da Rotação'!H89),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Registo da Rotação'!G89)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Registo da Rotação'!H89)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F89,'Listas de apoio'!$A$6='Registo da Rotação'!G89,'Listas de apoio'!$A$6='Registo da Rotação'!H89),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Registo da Rotação'!G89)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Registo da Rotação'!H89)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F89,'Listas de apoio'!$A$7='Registo da Rotação'!G89,'Listas de apoio'!$A$7='Registo da Rotação'!H89),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Registo da Rotação'!G89)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Registo da Rotação'!H89)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F89,'Listas de apoio'!$A$8='Registo da Rotação'!G89,'Listas de apoio'!$A$8='Registo da Rotação'!H89),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F88='Registo da Rotação'!F89)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Registo da Rotação'!G89)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Registo da Rotação'!H89)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F88)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G88='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H88='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A98="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Registo da Rotação'!G98)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Registo da Rotação'!H98)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F98,'Listas de apoio'!$A$5='Registo da Rotação'!G98,'Listas de apoio'!$A$5='Registo da Rotação'!H98),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Registo da Rotação'!G98)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Registo da Rotação'!H98)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F98,'Listas de apoio'!$A$6='Registo da Rotação'!G98,'Listas de apoio'!$A$6='Registo da Rotação'!H98),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Registo da Rotação'!G98)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Registo da Rotação'!H98)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F98,'Listas de apoio'!$A$7='Registo da Rotação'!G98,'Listas de apoio'!$A$7='Registo da Rotação'!H98),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Registo da Rotação'!G98)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Registo da Rotação'!H98)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F98,'Listas de apoio'!$A$8='Registo da Rotação'!G98,'Listas de apoio'!$A$8='Registo da Rotação'!H98),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Registo da Rotação'!G98)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Registo da Rotação'!H98)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U40" s="8">
-        <f>IF('Registo da Rotação'!A89="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A89)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C89,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D89)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A98="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A98)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C98,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D98)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V40" s="1"/>
       <c r="W40" s="8">
-        <f>IF('Registo da Rotação'!C194="",0,IF(COUNTA('Registo da Rotação'!A194:H194)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C203="",0,IF(COUNTA('Registo da Rotação'!A203:H203)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X40" s="8">
-        <f>IF('Registo da Rotação'!C194="",0,IF('Registo da Rotação'!E194='Registo da Rotação'!F194,1,0))</f>
+        <f>IF('Registo da Rotação'!C203="",0,IF('Registo da Rotação'!E203='Registo da Rotação'!F203,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y40" s="8">
-        <f>IF('Registo da Rotação'!C194="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B194)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C203="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B203)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z40" s="8">
-        <f>IF('Registo da Rotação'!C194="",0,IF('Registo da Rotação'!D194="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C194,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F194)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C194,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F194)&gt;0,1,0),IF('Registo da Rotação'!D194="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C194,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F194)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C194,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F194)&gt;0,1,0),IF('Registo da Rotação'!D194="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C194,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F194)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C194,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F194)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C203="",0,IF('Registo da Rotação'!D203="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C203,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F203)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C203,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F203)&gt;0,1,0),IF('Registo da Rotação'!D203="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C203,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F203)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C203,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F203)&gt;0,1,0),IF('Registo da Rotação'!D203="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C203,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F203)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C203,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F203)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA40" s="8">
-        <f>IF('Registo da Rotação'!C194="",0,IF('Registo da Rotação'!D194="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C194,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E194)=0,1,0),IF('Registo da Rotação'!D194="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C194,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E194)=0,1,0),IF('Registo da Rotação'!D194="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A194,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B194,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C194,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E194)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C203="",0,IF('Registo da Rotação'!D203="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C203,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E203)=0,1,0),IF('Registo da Rotação'!D203="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C203,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E203)=0,1,0),IF('Registo da Rotação'!D203="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C203,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E203)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB40" s="8">
-        <f>IF('Registo da Rotação'!C194="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B194,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H194="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C203="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B203,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H203="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC40" s="1"/>
@@ -11920,56 +12380,56 @@
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
       <c r="O41" s="8">
-        <f>IF('Registo da Rotação'!A90="",0,IF(COUNTA('Registo da Rotação'!B90:K90)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A99="",0,IF(COUNTA('Registo da Rotação'!B99:K99)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P41" s="8">
-        <f>IF('Registo da Rotação'!A90="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C90)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A99="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C99)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q41" s="8">
-        <f>IF('Registo da Rotação'!A90="",0,IF(OR('Registo da Rotação'!F90='Registo da Rotação'!G90,'Registo da Rotação'!F90='Registo da Rotação'!H90,'Registo da Rotação'!G90='Registo da Rotação'!H90),1,0))</f>
+        <f>IF('Registo da Rotação'!A99="",0,IF(OR('Registo da Rotação'!F99='Registo da Rotação'!G99,'Registo da Rotação'!F99='Registo da Rotação'!H99,'Registo da Rotação'!G99='Registo da Rotação'!H99),1,0))</f>
         <v>0</v>
       </c>
       <c r="R41" s="8">
-        <f>IF('Registo da Rotação'!A90="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C90,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I90="Ainda não avaliado",'Registo da Rotação'!J90="Ainda não avaliado",'Registo da Rotação'!K90="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A99="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C99,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I99="Ainda não avaliado",'Registo da Rotação'!J99="Ainda não avaliado",'Registo da Rotação'!K99="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S41" s="8">
-        <f>IF('Registo da Rotação'!A90="",0,IF(AND('Registo da Rotação'!G90=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90),'Registo da Rotação'!$G$54:'Registo da Rotação'!G89),""),'Registo da Rotação'!H90=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90),'Registo da Rotação'!$H$54:'Registo da Rotação'!H89),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A99="",0,IF(AND('Registo da Rotação'!G99=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99),'Registo da Rotação'!$G$54:'Registo da Rotação'!G98),""),'Registo da Rotação'!H99=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99),'Registo da Rotação'!$H$54:'Registo da Rotação'!H98),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T41" s="8">
-        <f>IF('Registo da Rotação'!A90="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Registo da Rotação'!G90)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Registo da Rotação'!H90)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F90,'Listas de apoio'!$A$5='Registo da Rotação'!G90,'Listas de apoio'!$A$5='Registo da Rotação'!H90),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Registo da Rotação'!G90)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Registo da Rotação'!H90)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F90,'Listas de apoio'!$A$6='Registo da Rotação'!G90,'Listas de apoio'!$A$6='Registo da Rotação'!H90),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Registo da Rotação'!G90)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Registo da Rotação'!H90)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F90,'Listas de apoio'!$A$7='Registo da Rotação'!G90,'Listas de apoio'!$A$7='Registo da Rotação'!H90),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Registo da Rotação'!G90)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Registo da Rotação'!H90)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F90,'Listas de apoio'!$A$8='Registo da Rotação'!G90,'Listas de apoio'!$A$8='Registo da Rotação'!H90),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F89='Registo da Rotação'!F90)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Registo da Rotação'!G90)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Registo da Rotação'!H90)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F89)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G89='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H89='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A99="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Registo da Rotação'!G99)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Registo da Rotação'!H99)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F99,'Listas de apoio'!$A$5='Registo da Rotação'!G99,'Listas de apoio'!$A$5='Registo da Rotação'!H99),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Registo da Rotação'!G99)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Registo da Rotação'!H99)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F99,'Listas de apoio'!$A$6='Registo da Rotação'!G99,'Listas de apoio'!$A$6='Registo da Rotação'!H99),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Registo da Rotação'!G99)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Registo da Rotação'!H99)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F99,'Listas de apoio'!$A$7='Registo da Rotação'!G99,'Listas de apoio'!$A$7='Registo da Rotação'!H99),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Registo da Rotação'!G99)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Registo da Rotação'!H99)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F99,'Listas de apoio'!$A$8='Registo da Rotação'!G99,'Listas de apoio'!$A$8='Registo da Rotação'!H99),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Registo da Rotação'!G99)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Registo da Rotação'!H99)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U41" s="8">
-        <f>IF('Registo da Rotação'!A90="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A90)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C90,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D90)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A99="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A99)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C99,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D99)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V41" s="1"/>
       <c r="W41" s="8">
-        <f>IF('Registo da Rotação'!C195="",0,IF(COUNTA('Registo da Rotação'!A195:H195)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C204="",0,IF(COUNTA('Registo da Rotação'!A204:H204)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X41" s="8">
-        <f>IF('Registo da Rotação'!C195="",0,IF('Registo da Rotação'!E195='Registo da Rotação'!F195,1,0))</f>
+        <f>IF('Registo da Rotação'!C204="",0,IF('Registo da Rotação'!E204='Registo da Rotação'!F204,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y41" s="8">
-        <f>IF('Registo da Rotação'!C195="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B195)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C204="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B204)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z41" s="8">
-        <f>IF('Registo da Rotação'!C195="",0,IF('Registo da Rotação'!D195="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C195,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F195)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C195,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F195)&gt;0,1,0),IF('Registo da Rotação'!D195="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C195,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F195)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C195,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F195)&gt;0,1,0),IF('Registo da Rotação'!D195="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C195,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F195)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C195,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F195)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C204="",0,IF('Registo da Rotação'!D204="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C204,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F204)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C204,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F204)&gt;0,1,0),IF('Registo da Rotação'!D204="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C204,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F204)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C204,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F204)&gt;0,1,0),IF('Registo da Rotação'!D204="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C204,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F204)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C204,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F204)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA41" s="8">
-        <f>IF('Registo da Rotação'!C195="",0,IF('Registo da Rotação'!D195="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C195,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E195)=0,1,0),IF('Registo da Rotação'!D195="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C195,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E195)=0,1,0),IF('Registo da Rotação'!D195="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A195,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B195,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C195,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E195)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C204="",0,IF('Registo da Rotação'!D204="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C204,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E204)=0,1,0),IF('Registo da Rotação'!D204="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C204,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E204)=0,1,0),IF('Registo da Rotação'!D204="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C204,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E204)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB41" s="8">
-        <f>IF('Registo da Rotação'!C195="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B195,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H195="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C204="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B204,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H204="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC41" s="1"/>
@@ -11995,56 +12455,56 @@
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
       <c r="O42" s="8">
-        <f>IF('Registo da Rotação'!A91="",0,IF(COUNTA('Registo da Rotação'!B91:K91)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A100="",0,IF(COUNTA('Registo da Rotação'!B100:K100)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P42" s="8">
-        <f>IF('Registo da Rotação'!A91="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C91)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A100="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C100)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q42" s="8">
-        <f>IF('Registo da Rotação'!A91="",0,IF(OR('Registo da Rotação'!F91='Registo da Rotação'!G91,'Registo da Rotação'!F91='Registo da Rotação'!H91,'Registo da Rotação'!G91='Registo da Rotação'!H91),1,0))</f>
+        <f>IF('Registo da Rotação'!A100="",0,IF(OR('Registo da Rotação'!F100='Registo da Rotação'!G100,'Registo da Rotação'!F100='Registo da Rotação'!H100,'Registo da Rotação'!G100='Registo da Rotação'!H100),1,0))</f>
         <v>0</v>
       </c>
       <c r="R42" s="8">
-        <f>IF('Registo da Rotação'!A91="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C91,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I91="Ainda não avaliado",'Registo da Rotação'!J91="Ainda não avaliado",'Registo da Rotação'!K91="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A100="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C100,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I100="Ainda não avaliado",'Registo da Rotação'!J100="Ainda não avaliado",'Registo da Rotação'!K100="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S42" s="8">
-        <f>IF('Registo da Rotação'!A91="",0,IF(AND('Registo da Rotação'!G91=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91),'Registo da Rotação'!$G$54:'Registo da Rotação'!G90),""),'Registo da Rotação'!H91=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91),'Registo da Rotação'!$H$54:'Registo da Rotação'!H90),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A100="",0,IF(AND('Registo da Rotação'!G100=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100),'Registo da Rotação'!$G$54:'Registo da Rotação'!G99),""),'Registo da Rotação'!H100=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100),'Registo da Rotação'!$H$54:'Registo da Rotação'!H99),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T42" s="8">
-        <f>IF('Registo da Rotação'!A91="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Registo da Rotação'!G91)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Registo da Rotação'!H91)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F91,'Listas de apoio'!$A$5='Registo da Rotação'!G91,'Listas de apoio'!$A$5='Registo da Rotação'!H91),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Registo da Rotação'!G91)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Registo da Rotação'!H91)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F91,'Listas de apoio'!$A$6='Registo da Rotação'!G91,'Listas de apoio'!$A$6='Registo da Rotação'!H91),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Registo da Rotação'!G91)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Registo da Rotação'!H91)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F91,'Listas de apoio'!$A$7='Registo da Rotação'!G91,'Listas de apoio'!$A$7='Registo da Rotação'!H91),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Registo da Rotação'!G91)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Registo da Rotação'!H91)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F91,'Listas de apoio'!$A$8='Registo da Rotação'!G91,'Listas de apoio'!$A$8='Registo da Rotação'!H91),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F90='Registo da Rotação'!F91)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Registo da Rotação'!G91)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Registo da Rotação'!H91)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F90)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G90='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H90='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A100="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Registo da Rotação'!G100)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Registo da Rotação'!H100)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F100,'Listas de apoio'!$A$5='Registo da Rotação'!G100,'Listas de apoio'!$A$5='Registo da Rotação'!H100),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Registo da Rotação'!G100)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Registo da Rotação'!H100)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F100,'Listas de apoio'!$A$6='Registo da Rotação'!G100,'Listas de apoio'!$A$6='Registo da Rotação'!H100),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Registo da Rotação'!G100)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Registo da Rotação'!H100)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F100,'Listas de apoio'!$A$7='Registo da Rotação'!G100,'Listas de apoio'!$A$7='Registo da Rotação'!H100),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Registo da Rotação'!G100)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Registo da Rotação'!H100)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F100,'Listas de apoio'!$A$8='Registo da Rotação'!G100,'Listas de apoio'!$A$8='Registo da Rotação'!H100),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Registo da Rotação'!G100)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Registo da Rotação'!H100)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U42" s="8">
-        <f>IF('Registo da Rotação'!A91="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A91)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C91,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D91)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A100="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A100)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C100,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D100)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V42" s="1"/>
       <c r="W42" s="8">
-        <f>IF('Registo da Rotação'!C196="",0,IF(COUNTA('Registo da Rotação'!A196:H196)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C205="",0,IF(COUNTA('Registo da Rotação'!A205:H205)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X42" s="8">
-        <f>IF('Registo da Rotação'!C196="",0,IF('Registo da Rotação'!E196='Registo da Rotação'!F196,1,0))</f>
+        <f>IF('Registo da Rotação'!C205="",0,IF('Registo da Rotação'!E205='Registo da Rotação'!F205,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y42" s="8">
-        <f>IF('Registo da Rotação'!C196="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B196)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C205="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B205)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z42" s="8">
-        <f>IF('Registo da Rotação'!C196="",0,IF('Registo da Rotação'!D196="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C196,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F196)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C196,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F196)&gt;0,1,0),IF('Registo da Rotação'!D196="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C196,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F196)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C196,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F196)&gt;0,1,0),IF('Registo da Rotação'!D196="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C196,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F196)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C196,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F196)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C205="",0,IF('Registo da Rotação'!D205="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C205,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F205)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C205,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F205)&gt;0,1,0),IF('Registo da Rotação'!D205="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C205,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F205)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C205,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F205)&gt;0,1,0),IF('Registo da Rotação'!D205="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C205,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F205)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C205,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F205)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA42" s="8">
-        <f>IF('Registo da Rotação'!C196="",0,IF('Registo da Rotação'!D196="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C196,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E196)=0,1,0),IF('Registo da Rotação'!D196="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C196,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E196)=0,1,0),IF('Registo da Rotação'!D196="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A196,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B196,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C196,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E196)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C205="",0,IF('Registo da Rotação'!D205="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C205,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E205)=0,1,0),IF('Registo da Rotação'!D205="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C205,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E205)=0,1,0),IF('Registo da Rotação'!D205="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C205,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E205)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB42" s="8">
-        <f>IF('Registo da Rotação'!C196="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B196,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H196="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C205="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B205,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H205="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC42" s="1"/>
@@ -12070,56 +12530,56 @@
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
       <c r="O43" s="8">
-        <f>IF('Registo da Rotação'!A92="",0,IF(COUNTA('Registo da Rotação'!B92:K92)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A101="",0,IF(COUNTA('Registo da Rotação'!B101:K101)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P43" s="8">
-        <f>IF('Registo da Rotação'!A92="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C92)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A101="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C101)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q43" s="8">
-        <f>IF('Registo da Rotação'!A92="",0,IF(OR('Registo da Rotação'!F92='Registo da Rotação'!G92,'Registo da Rotação'!F92='Registo da Rotação'!H92,'Registo da Rotação'!G92='Registo da Rotação'!H92),1,0))</f>
+        <f>IF('Registo da Rotação'!A101="",0,IF(OR('Registo da Rotação'!F101='Registo da Rotação'!G101,'Registo da Rotação'!F101='Registo da Rotação'!H101,'Registo da Rotação'!G101='Registo da Rotação'!H101),1,0))</f>
         <v>0</v>
       </c>
       <c r="R43" s="8">
-        <f>IF('Registo da Rotação'!A92="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C92,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I92="Ainda não avaliado",'Registo da Rotação'!J92="Ainda não avaliado",'Registo da Rotação'!K92="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A101="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C101,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I101="Ainda não avaliado",'Registo da Rotação'!J101="Ainda não avaliado",'Registo da Rotação'!K101="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S43" s="8">
-        <f>IF('Registo da Rotação'!A92="",0,IF(AND('Registo da Rotação'!G92=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92),'Registo da Rotação'!$G$54:'Registo da Rotação'!G91),""),'Registo da Rotação'!H92=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92),'Registo da Rotação'!$H$54:'Registo da Rotação'!H91),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A101="",0,IF(AND('Registo da Rotação'!G101=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101),'Registo da Rotação'!$G$54:'Registo da Rotação'!G100),""),'Registo da Rotação'!H101=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101),'Registo da Rotação'!$H$54:'Registo da Rotação'!H100),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T43" s="8">
-        <f>IF('Registo da Rotação'!A92="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Registo da Rotação'!G92)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Registo da Rotação'!H92)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F92,'Listas de apoio'!$A$5='Registo da Rotação'!G92,'Listas de apoio'!$A$5='Registo da Rotação'!H92),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Registo da Rotação'!G92)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Registo da Rotação'!H92)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F92,'Listas de apoio'!$A$6='Registo da Rotação'!G92,'Listas de apoio'!$A$6='Registo da Rotação'!H92),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Registo da Rotação'!G92)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Registo da Rotação'!H92)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F92,'Listas de apoio'!$A$7='Registo da Rotação'!G92,'Listas de apoio'!$A$7='Registo da Rotação'!H92),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Registo da Rotação'!G92)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Registo da Rotação'!H92)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F92,'Listas de apoio'!$A$8='Registo da Rotação'!G92,'Listas de apoio'!$A$8='Registo da Rotação'!H92),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F91='Registo da Rotação'!F92)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Registo da Rotação'!G92)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Registo da Rotação'!H92)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F91)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G91='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H91='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A101="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Registo da Rotação'!G101)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Registo da Rotação'!H101)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F101,'Listas de apoio'!$A$5='Registo da Rotação'!G101,'Listas de apoio'!$A$5='Registo da Rotação'!H101),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Registo da Rotação'!G101)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Registo da Rotação'!H101)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F101,'Listas de apoio'!$A$6='Registo da Rotação'!G101,'Listas de apoio'!$A$6='Registo da Rotação'!H101),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Registo da Rotação'!G101)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Registo da Rotação'!H101)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F101,'Listas de apoio'!$A$7='Registo da Rotação'!G101,'Listas de apoio'!$A$7='Registo da Rotação'!H101),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Registo da Rotação'!G101)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Registo da Rotação'!H101)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F101,'Listas de apoio'!$A$8='Registo da Rotação'!G101,'Listas de apoio'!$A$8='Registo da Rotação'!H101),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Registo da Rotação'!G101)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Registo da Rotação'!H101)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U43" s="8">
-        <f>IF('Registo da Rotação'!A92="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A92)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C92,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D92)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A101="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A101)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C101,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D101)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V43" s="1"/>
       <c r="W43" s="8">
-        <f>IF('Registo da Rotação'!C197="",0,IF(COUNTA('Registo da Rotação'!A197:H197)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C206="",0,IF(COUNTA('Registo da Rotação'!A206:H206)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X43" s="8">
-        <f>IF('Registo da Rotação'!C197="",0,IF('Registo da Rotação'!E197='Registo da Rotação'!F197,1,0))</f>
+        <f>IF('Registo da Rotação'!C206="",0,IF('Registo da Rotação'!E206='Registo da Rotação'!F206,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y43" s="8">
-        <f>IF('Registo da Rotação'!C197="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B197)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C206="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B206)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z43" s="8">
-        <f>IF('Registo da Rotação'!C197="",0,IF('Registo da Rotação'!D197="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C197,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F197)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C197,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F197)&gt;0,1,0),IF('Registo da Rotação'!D197="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C197,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F197)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C197,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F197)&gt;0,1,0),IF('Registo da Rotação'!D197="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C197,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F197)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C197,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F197)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C206="",0,IF('Registo da Rotação'!D206="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C206,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F206)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C206,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F206)&gt;0,1,0),IF('Registo da Rotação'!D206="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C206,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F206)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C206,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F206)&gt;0,1,0),IF('Registo da Rotação'!D206="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C206,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F206)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C206,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F206)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA43" s="8">
-        <f>IF('Registo da Rotação'!C197="",0,IF('Registo da Rotação'!D197="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C197,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E197)=0,1,0),IF('Registo da Rotação'!D197="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C197,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E197)=0,1,0),IF('Registo da Rotação'!D197="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A197,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B197,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C197,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E197)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C206="",0,IF('Registo da Rotação'!D206="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C206,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E206)=0,1,0),IF('Registo da Rotação'!D206="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C206,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E206)=0,1,0),IF('Registo da Rotação'!D206="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C206,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E206)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB43" s="8">
-        <f>IF('Registo da Rotação'!C197="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B197,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H197="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C206="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B206,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H206="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC43" s="1"/>
@@ -12145,56 +12605,56 @@
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="8">
-        <f>IF('Registo da Rotação'!A93="",0,IF(COUNTA('Registo da Rotação'!B93:K93)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A102="",0,IF(COUNTA('Registo da Rotação'!B102:K102)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P44" s="8">
-        <f>IF('Registo da Rotação'!A93="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C93)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A102="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C102)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q44" s="8">
-        <f>IF('Registo da Rotação'!A93="",0,IF(OR('Registo da Rotação'!F93='Registo da Rotação'!G93,'Registo da Rotação'!F93='Registo da Rotação'!H93,'Registo da Rotação'!G93='Registo da Rotação'!H93),1,0))</f>
+        <f>IF('Registo da Rotação'!A102="",0,IF(OR('Registo da Rotação'!F102='Registo da Rotação'!G102,'Registo da Rotação'!F102='Registo da Rotação'!H102,'Registo da Rotação'!G102='Registo da Rotação'!H102),1,0))</f>
         <v>0</v>
       </c>
       <c r="R44" s="8">
-        <f>IF('Registo da Rotação'!A93="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C93,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I93="Ainda não avaliado",'Registo da Rotação'!J93="Ainda não avaliado",'Registo da Rotação'!K93="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A102="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C102,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I102="Ainda não avaliado",'Registo da Rotação'!J102="Ainda não avaliado",'Registo da Rotação'!K102="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S44" s="8">
-        <f>IF('Registo da Rotação'!A93="",0,IF(AND('Registo da Rotação'!G93=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93),'Registo da Rotação'!$G$54:'Registo da Rotação'!G92),""),'Registo da Rotação'!H93=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93),'Registo da Rotação'!$H$54:'Registo da Rotação'!H92),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A102="",0,IF(AND('Registo da Rotação'!G102=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102),'Registo da Rotação'!$G$54:'Registo da Rotação'!G101),""),'Registo da Rotação'!H102=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102),'Registo da Rotação'!$H$54:'Registo da Rotação'!H101),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T44" s="8">
-        <f>IF('Registo da Rotação'!A93="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Registo da Rotação'!G93)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Registo da Rotação'!H93)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F93,'Listas de apoio'!$A$5='Registo da Rotação'!G93,'Listas de apoio'!$A$5='Registo da Rotação'!H93),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Registo da Rotação'!G93)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Registo da Rotação'!H93)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F93,'Listas de apoio'!$A$6='Registo da Rotação'!G93,'Listas de apoio'!$A$6='Registo da Rotação'!H93),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Registo da Rotação'!G93)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Registo da Rotação'!H93)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F93,'Listas de apoio'!$A$7='Registo da Rotação'!G93,'Listas de apoio'!$A$7='Registo da Rotação'!H93),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Registo da Rotação'!G93)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Registo da Rotação'!H93)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F93,'Listas de apoio'!$A$8='Registo da Rotação'!G93,'Listas de apoio'!$A$8='Registo da Rotação'!H93),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F92='Registo da Rotação'!F93)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Registo da Rotação'!G93)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Registo da Rotação'!H93)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F92)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G92='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H92='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A102="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Registo da Rotação'!G102)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Registo da Rotação'!H102)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F102,'Listas de apoio'!$A$5='Registo da Rotação'!G102,'Listas de apoio'!$A$5='Registo da Rotação'!H102),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Registo da Rotação'!G102)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Registo da Rotação'!H102)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F102,'Listas de apoio'!$A$6='Registo da Rotação'!G102,'Listas de apoio'!$A$6='Registo da Rotação'!H102),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Registo da Rotação'!G102)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Registo da Rotação'!H102)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F102,'Listas de apoio'!$A$7='Registo da Rotação'!G102,'Listas de apoio'!$A$7='Registo da Rotação'!H102),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Registo da Rotação'!G102)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Registo da Rotação'!H102)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F102,'Listas de apoio'!$A$8='Registo da Rotação'!G102,'Listas de apoio'!$A$8='Registo da Rotação'!H102),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Registo da Rotação'!G102)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Registo da Rotação'!H102)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U44" s="8">
-        <f>IF('Registo da Rotação'!A93="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A93)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C93,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D93)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A102="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A102)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C102,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D102)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V44" s="1"/>
       <c r="W44" s="8">
-        <f>IF('Registo da Rotação'!C198="",0,IF(COUNTA('Registo da Rotação'!A198:H198)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C207="",0,IF(COUNTA('Registo da Rotação'!A207:H207)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X44" s="8">
-        <f>IF('Registo da Rotação'!C198="",0,IF('Registo da Rotação'!E198='Registo da Rotação'!F198,1,0))</f>
+        <f>IF('Registo da Rotação'!C207="",0,IF('Registo da Rotação'!E207='Registo da Rotação'!F207,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y44" s="8">
-        <f>IF('Registo da Rotação'!C198="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B198)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C207="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B207)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z44" s="8">
-        <f>IF('Registo da Rotação'!C198="",0,IF('Registo da Rotação'!D198="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C198,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F198)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C198,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F198)&gt;0,1,0),IF('Registo da Rotação'!D198="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C198,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F198)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C198,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F198)&gt;0,1,0),IF('Registo da Rotação'!D198="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C198,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F198)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C198,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F198)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C207="",0,IF('Registo da Rotação'!D207="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C207,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F207)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C207,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F207)&gt;0,1,0),IF('Registo da Rotação'!D207="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C207,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F207)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C207,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F207)&gt;0,1,0),IF('Registo da Rotação'!D207="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C207,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F207)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C207,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F207)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA44" s="8">
-        <f>IF('Registo da Rotação'!C198="",0,IF('Registo da Rotação'!D198="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C198,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E198)=0,1,0),IF('Registo da Rotação'!D198="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C198,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E198)=0,1,0),IF('Registo da Rotação'!D198="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A198,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B198,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C198,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E198)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C207="",0,IF('Registo da Rotação'!D207="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C207,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E207)=0,1,0),IF('Registo da Rotação'!D207="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C207,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E207)=0,1,0),IF('Registo da Rotação'!D207="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C207,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E207)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB44" s="8">
-        <f>IF('Registo da Rotação'!C198="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B198,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H198="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C207="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B207,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H207="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC44" s="1"/>
@@ -12220,56 +12680,56 @@
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
       <c r="O45" s="8">
-        <f>IF('Registo da Rotação'!A94="",0,IF(COUNTA('Registo da Rotação'!B94:K94)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A103="",0,IF(COUNTA('Registo da Rotação'!B103:K103)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P45" s="8">
-        <f>IF('Registo da Rotação'!A94="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C94)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A103="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C103)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q45" s="8">
-        <f>IF('Registo da Rotação'!A94="",0,IF(OR('Registo da Rotação'!F94='Registo da Rotação'!G94,'Registo da Rotação'!F94='Registo da Rotação'!H94,'Registo da Rotação'!G94='Registo da Rotação'!H94),1,0))</f>
+        <f>IF('Registo da Rotação'!A103="",0,IF(OR('Registo da Rotação'!F103='Registo da Rotação'!G103,'Registo da Rotação'!F103='Registo da Rotação'!H103,'Registo da Rotação'!G103='Registo da Rotação'!H103),1,0))</f>
         <v>0</v>
       </c>
       <c r="R45" s="8">
-        <f>IF('Registo da Rotação'!A94="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C94,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I94="Ainda não avaliado",'Registo da Rotação'!J94="Ainda não avaliado",'Registo da Rotação'!K94="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A103="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C103,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I103="Ainda não avaliado",'Registo da Rotação'!J103="Ainda não avaliado",'Registo da Rotação'!K103="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S45" s="8">
-        <f>IF('Registo da Rotação'!A94="",0,IF(AND('Registo da Rotação'!G94=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94),'Registo da Rotação'!$G$54:'Registo da Rotação'!G93),""),'Registo da Rotação'!H94=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94),'Registo da Rotação'!$H$54:'Registo da Rotação'!H93),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A103="",0,IF(AND('Registo da Rotação'!G103=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103),'Registo da Rotação'!$G$54:'Registo da Rotação'!G102),""),'Registo da Rotação'!H103=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103),'Registo da Rotação'!$H$54:'Registo da Rotação'!H102),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T45" s="8">
-        <f>IF('Registo da Rotação'!A94="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Registo da Rotação'!G94)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Registo da Rotação'!H94)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F94,'Listas de apoio'!$A$5='Registo da Rotação'!G94,'Listas de apoio'!$A$5='Registo da Rotação'!H94),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Registo da Rotação'!G94)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Registo da Rotação'!H94)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F94,'Listas de apoio'!$A$6='Registo da Rotação'!G94,'Listas de apoio'!$A$6='Registo da Rotação'!H94),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Registo da Rotação'!G94)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Registo da Rotação'!H94)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F94,'Listas de apoio'!$A$7='Registo da Rotação'!G94,'Listas de apoio'!$A$7='Registo da Rotação'!H94),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Registo da Rotação'!G94)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Registo da Rotação'!H94)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F94,'Listas de apoio'!$A$8='Registo da Rotação'!G94,'Listas de apoio'!$A$8='Registo da Rotação'!H94),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F93='Registo da Rotação'!F94)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Registo da Rotação'!G94)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Registo da Rotação'!H94)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F93)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G93='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H93='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A103="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Registo da Rotação'!G103)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Registo da Rotação'!H103)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F103,'Listas de apoio'!$A$5='Registo da Rotação'!G103,'Listas de apoio'!$A$5='Registo da Rotação'!H103),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Registo da Rotação'!G103)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Registo da Rotação'!H103)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F103,'Listas de apoio'!$A$6='Registo da Rotação'!G103,'Listas de apoio'!$A$6='Registo da Rotação'!H103),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Registo da Rotação'!G103)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Registo da Rotação'!H103)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F103,'Listas de apoio'!$A$7='Registo da Rotação'!G103,'Listas de apoio'!$A$7='Registo da Rotação'!H103),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Registo da Rotação'!G103)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Registo da Rotação'!H103)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F103,'Listas de apoio'!$A$8='Registo da Rotação'!G103,'Listas de apoio'!$A$8='Registo da Rotação'!H103),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Registo da Rotação'!G103)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Registo da Rotação'!H103)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U45" s="8">
-        <f>IF('Registo da Rotação'!A94="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A94)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C94,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D94)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A103="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A103)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C103,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D103)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V45" s="1"/>
       <c r="W45" s="8">
-        <f>IF('Registo da Rotação'!C199="",0,IF(COUNTA('Registo da Rotação'!A199:H199)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C208="",0,IF(COUNTA('Registo da Rotação'!A208:H208)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X45" s="8">
-        <f>IF('Registo da Rotação'!C199="",0,IF('Registo da Rotação'!E199='Registo da Rotação'!F199,1,0))</f>
+        <f>IF('Registo da Rotação'!C208="",0,IF('Registo da Rotação'!E208='Registo da Rotação'!F208,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y45" s="8">
-        <f>IF('Registo da Rotação'!C199="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B199)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C208="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B208)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z45" s="8">
-        <f>IF('Registo da Rotação'!C199="",0,IF('Registo da Rotação'!D199="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C199,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F199)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C199,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F199)&gt;0,1,0),IF('Registo da Rotação'!D199="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C199,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F199)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C199,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F199)&gt;0,1,0),IF('Registo da Rotação'!D199="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C199,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F199)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C199,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F199)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C208="",0,IF('Registo da Rotação'!D208="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C208,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F208)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C208,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F208)&gt;0,1,0),IF('Registo da Rotação'!D208="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C208,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F208)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C208,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F208)&gt;0,1,0),IF('Registo da Rotação'!D208="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C208,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F208)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C208,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F208)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA45" s="8">
-        <f>IF('Registo da Rotação'!C199="",0,IF('Registo da Rotação'!D199="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C199,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E199)=0,1,0),IF('Registo da Rotação'!D199="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C199,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E199)=0,1,0),IF('Registo da Rotação'!D199="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A199,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B199,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C199,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E199)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C208="",0,IF('Registo da Rotação'!D208="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C208,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E208)=0,1,0),IF('Registo da Rotação'!D208="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C208,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E208)=0,1,0),IF('Registo da Rotação'!D208="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C208,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E208)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB45" s="8">
-        <f>IF('Registo da Rotação'!C199="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B199,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H199="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C208="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B208,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H208="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC45" s="1"/>
@@ -12295,56 +12755,56 @@
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
       <c r="O46" s="8">
-        <f>IF('Registo da Rotação'!A95="",0,IF(COUNTA('Registo da Rotação'!B95:K95)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A104="",0,IF(COUNTA('Registo da Rotação'!B104:K104)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P46" s="8">
-        <f>IF('Registo da Rotação'!A95="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C95)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A104="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C104)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q46" s="8">
-        <f>IF('Registo da Rotação'!A95="",0,IF(OR('Registo da Rotação'!F95='Registo da Rotação'!G95,'Registo da Rotação'!F95='Registo da Rotação'!H95,'Registo da Rotação'!G95='Registo da Rotação'!H95),1,0))</f>
+        <f>IF('Registo da Rotação'!A104="",0,IF(OR('Registo da Rotação'!F104='Registo da Rotação'!G104,'Registo da Rotação'!F104='Registo da Rotação'!H104,'Registo da Rotação'!G104='Registo da Rotação'!H104),1,0))</f>
         <v>0</v>
       </c>
       <c r="R46" s="8">
-        <f>IF('Registo da Rotação'!A95="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C95,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I95="Ainda não avaliado",'Registo da Rotação'!J95="Ainda não avaliado",'Registo da Rotação'!K95="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A104="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C104,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I104="Ainda não avaliado",'Registo da Rotação'!J104="Ainda não avaliado",'Registo da Rotação'!K104="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S46" s="8">
-        <f>IF('Registo da Rotação'!A95="",0,IF(AND('Registo da Rotação'!G95=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95),'Registo da Rotação'!$G$54:'Registo da Rotação'!G94),""),'Registo da Rotação'!H95=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95),'Registo da Rotação'!$H$54:'Registo da Rotação'!H94),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A104="",0,IF(AND('Registo da Rotação'!G104=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104),'Registo da Rotação'!$G$54:'Registo da Rotação'!G103),""),'Registo da Rotação'!H104=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104),'Registo da Rotação'!$H$54:'Registo da Rotação'!H103),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T46" s="8">
-        <f>IF('Registo da Rotação'!A95="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Registo da Rotação'!G95)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Registo da Rotação'!H95)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F95,'Listas de apoio'!$A$5='Registo da Rotação'!G95,'Listas de apoio'!$A$5='Registo da Rotação'!H95),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Registo da Rotação'!G95)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Registo da Rotação'!H95)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F95,'Listas de apoio'!$A$6='Registo da Rotação'!G95,'Listas de apoio'!$A$6='Registo da Rotação'!H95),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Registo da Rotação'!G95)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Registo da Rotação'!H95)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F95,'Listas de apoio'!$A$7='Registo da Rotação'!G95,'Listas de apoio'!$A$7='Registo da Rotação'!H95),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Registo da Rotação'!G95)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Registo da Rotação'!H95)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F95,'Listas de apoio'!$A$8='Registo da Rotação'!G95,'Listas de apoio'!$A$8='Registo da Rotação'!H95),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F94='Registo da Rotação'!F95)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Registo da Rotação'!G95)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Registo da Rotação'!H95)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F94)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G94='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H94='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A104="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Registo da Rotação'!G104)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Registo da Rotação'!H104)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F104,'Listas de apoio'!$A$5='Registo da Rotação'!G104,'Listas de apoio'!$A$5='Registo da Rotação'!H104),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Registo da Rotação'!G104)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Registo da Rotação'!H104)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F104,'Listas de apoio'!$A$6='Registo da Rotação'!G104,'Listas de apoio'!$A$6='Registo da Rotação'!H104),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Registo da Rotação'!G104)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Registo da Rotação'!H104)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F104,'Listas de apoio'!$A$7='Registo da Rotação'!G104,'Listas de apoio'!$A$7='Registo da Rotação'!H104),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Registo da Rotação'!G104)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Registo da Rotação'!H104)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F104,'Listas de apoio'!$A$8='Registo da Rotação'!G104,'Listas de apoio'!$A$8='Registo da Rotação'!H104),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Registo da Rotação'!G104)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Registo da Rotação'!H104)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U46" s="8">
-        <f>IF('Registo da Rotação'!A95="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A95)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C95,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D95)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A104="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A104)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C104,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D104)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V46" s="1"/>
       <c r="W46" s="8">
-        <f>IF('Registo da Rotação'!C200="",0,IF(COUNTA('Registo da Rotação'!A200:H200)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C209="",0,IF(COUNTA('Registo da Rotação'!A209:H209)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X46" s="8">
-        <f>IF('Registo da Rotação'!C200="",0,IF('Registo da Rotação'!E200='Registo da Rotação'!F200,1,0))</f>
+        <f>IF('Registo da Rotação'!C209="",0,IF('Registo da Rotação'!E209='Registo da Rotação'!F209,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y46" s="8">
-        <f>IF('Registo da Rotação'!C200="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B200)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C209="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B209)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z46" s="8">
-        <f>IF('Registo da Rotação'!C200="",0,IF('Registo da Rotação'!D200="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C200,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F200)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C200,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F200)&gt;0,1,0),IF('Registo da Rotação'!D200="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C200,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F200)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C200,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F200)&gt;0,1,0),IF('Registo da Rotação'!D200="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C200,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F200)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C200,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F200)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C209="",0,IF('Registo da Rotação'!D209="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A209,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B209,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C209,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F209)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A209,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B209,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C209,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F209)&gt;0,1,0),IF('Registo da Rotação'!D209="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A209,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B209,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C209,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F209)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A209,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B209,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C209,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F209)&gt;0,1,0),IF('Registo da Rotação'!D209="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A209,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B209,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C209,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F209)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A209,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B209,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C209,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F209)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA46" s="8">
-        <f>IF('Registo da Rotação'!C200="",0,IF('Registo da Rotação'!D200="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C200,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E200)=0,1,0),IF('Registo da Rotação'!D200="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C200,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E200)=0,1,0),IF('Registo da Rotação'!D200="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A200,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B200,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C200,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E200)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C209="",0,IF('Registo da Rotação'!D209="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A209,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B209,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C209,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E209)=0,1,0),IF('Registo da Rotação'!D209="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A209,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B209,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C209,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E209)=0,1,0),IF('Registo da Rotação'!D209="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A209,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B209,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C209,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E209)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB46" s="8">
-        <f>IF('Registo da Rotação'!C200="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B200,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H200="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C209="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B209,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H209="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC46" s="1"/>
@@ -12370,56 +12830,56 @@
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
       <c r="O47" s="8">
-        <f>IF('Registo da Rotação'!A96="",0,IF(COUNTA('Registo da Rotação'!B96:K96)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A105="",0,IF(COUNTA('Registo da Rotação'!B105:K105)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P47" s="8">
-        <f>IF('Registo da Rotação'!A96="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C96)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A105="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C105)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q47" s="8">
-        <f>IF('Registo da Rotação'!A96="",0,IF(OR('Registo da Rotação'!F96='Registo da Rotação'!G96,'Registo da Rotação'!F96='Registo da Rotação'!H96,'Registo da Rotação'!G96='Registo da Rotação'!H96),1,0))</f>
+        <f>IF('Registo da Rotação'!A105="",0,IF(OR('Registo da Rotação'!F105='Registo da Rotação'!G105,'Registo da Rotação'!F105='Registo da Rotação'!H105,'Registo da Rotação'!G105='Registo da Rotação'!H105),1,0))</f>
         <v>0</v>
       </c>
       <c r="R47" s="8">
-        <f>IF('Registo da Rotação'!A96="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C96,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I96="Ainda não avaliado",'Registo da Rotação'!J96="Ainda não avaliado",'Registo da Rotação'!K96="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A105="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C105,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I105="Ainda não avaliado",'Registo da Rotação'!J105="Ainda não avaliado",'Registo da Rotação'!K105="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S47" s="8">
-        <f>IF('Registo da Rotação'!A96="",0,IF(AND('Registo da Rotação'!G96=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96),'Registo da Rotação'!$G$54:'Registo da Rotação'!G95),""),'Registo da Rotação'!H96=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96),'Registo da Rotação'!$H$54:'Registo da Rotação'!H95),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A105="",0,IF(AND('Registo da Rotação'!G105=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105),'Registo da Rotação'!$G$54:'Registo da Rotação'!G104),""),'Registo da Rotação'!H105=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105),'Registo da Rotação'!$H$54:'Registo da Rotação'!H104),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T47" s="8">
-        <f>IF('Registo da Rotação'!A96="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Registo da Rotação'!G96)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Registo da Rotação'!H96)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F96,'Listas de apoio'!$A$5='Registo da Rotação'!G96,'Listas de apoio'!$A$5='Registo da Rotação'!H96),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Registo da Rotação'!G96)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Registo da Rotação'!H96)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F96,'Listas de apoio'!$A$6='Registo da Rotação'!G96,'Listas de apoio'!$A$6='Registo da Rotação'!H96),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Registo da Rotação'!G96)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Registo da Rotação'!H96)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F96,'Listas de apoio'!$A$7='Registo da Rotação'!G96,'Listas de apoio'!$A$7='Registo da Rotação'!H96),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Registo da Rotação'!G96)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Registo da Rotação'!H96)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F96,'Listas de apoio'!$A$8='Registo da Rotação'!G96,'Listas de apoio'!$A$8='Registo da Rotação'!H96),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F95='Registo da Rotação'!F96)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Registo da Rotação'!G96)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Registo da Rotação'!H96)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F95)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G95='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H95='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A105="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Registo da Rotação'!G105)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Registo da Rotação'!H105)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F105,'Listas de apoio'!$A$5='Registo da Rotação'!G105,'Listas de apoio'!$A$5='Registo da Rotação'!H105),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Registo da Rotação'!G105)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Registo da Rotação'!H105)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F105,'Listas de apoio'!$A$6='Registo da Rotação'!G105,'Listas de apoio'!$A$6='Registo da Rotação'!H105),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Registo da Rotação'!G105)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Registo da Rotação'!H105)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F105,'Listas de apoio'!$A$7='Registo da Rotação'!G105,'Listas de apoio'!$A$7='Registo da Rotação'!H105),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Registo da Rotação'!G105)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Registo da Rotação'!H105)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F105,'Listas de apoio'!$A$8='Registo da Rotação'!G105,'Listas de apoio'!$A$8='Registo da Rotação'!H105),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Registo da Rotação'!G105)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Registo da Rotação'!H105)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U47" s="8">
-        <f>IF('Registo da Rotação'!A96="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A96)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C96,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D96)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A105="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A105)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C105,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D105)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V47" s="1"/>
       <c r="W47" s="8">
-        <f>IF('Registo da Rotação'!C201="",0,IF(COUNTA('Registo da Rotação'!A201:H201)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C210="",0,IF(COUNTA('Registo da Rotação'!A210:H210)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X47" s="8">
-        <f>IF('Registo da Rotação'!C201="",0,IF('Registo da Rotação'!E201='Registo da Rotação'!F201,1,0))</f>
+        <f>IF('Registo da Rotação'!C210="",0,IF('Registo da Rotação'!E210='Registo da Rotação'!F210,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y47" s="8">
-        <f>IF('Registo da Rotação'!C201="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B201)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C210="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B210)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z47" s="8">
-        <f>IF('Registo da Rotação'!C201="",0,IF('Registo da Rotação'!D201="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C201,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F201)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C201,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F201)&gt;0,1,0),IF('Registo da Rotação'!D201="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C201,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F201)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C201,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F201)&gt;0,1,0),IF('Registo da Rotação'!D201="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C201,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F201)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C201,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F201)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C210="",0,IF('Registo da Rotação'!D210="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A210,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B210,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C210,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F210)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A210,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B210,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C210,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F210)&gt;0,1,0),IF('Registo da Rotação'!D210="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A210,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B210,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C210,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F210)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A210,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B210,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C210,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F210)&gt;0,1,0),IF('Registo da Rotação'!D210="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A210,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B210,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C210,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F210)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A210,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B210,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C210,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F210)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA47" s="8">
-        <f>IF('Registo da Rotação'!C201="",0,IF('Registo da Rotação'!D201="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C201,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E201)=0,1,0),IF('Registo da Rotação'!D201="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C201,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E201)=0,1,0),IF('Registo da Rotação'!D201="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A201,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B201,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C201,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E201)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C210="",0,IF('Registo da Rotação'!D210="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A210,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B210,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C210,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E210)=0,1,0),IF('Registo da Rotação'!D210="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A210,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B210,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C210,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E210)=0,1,0),IF('Registo da Rotação'!D210="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A210,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B210,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C210,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E210)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB47" s="8">
-        <f>IF('Registo da Rotação'!C201="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B201,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H201="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C210="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B210,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H210="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC47" s="1"/>
@@ -12445,56 +12905,56 @@
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
       <c r="O48" s="8">
-        <f>IF('Registo da Rotação'!A97="",0,IF(COUNTA('Registo da Rotação'!B97:K97)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A106="",0,IF(COUNTA('Registo da Rotação'!B106:K106)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P48" s="8">
-        <f>IF('Registo da Rotação'!A97="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C97)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A106="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C106)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q48" s="8">
-        <f>IF('Registo da Rotação'!A97="",0,IF(OR('Registo da Rotação'!F97='Registo da Rotação'!G97,'Registo da Rotação'!F97='Registo da Rotação'!H97,'Registo da Rotação'!G97='Registo da Rotação'!H97),1,0))</f>
+        <f>IF('Registo da Rotação'!A106="",0,IF(OR('Registo da Rotação'!F106='Registo da Rotação'!G106,'Registo da Rotação'!F106='Registo da Rotação'!H106,'Registo da Rotação'!G106='Registo da Rotação'!H106),1,0))</f>
         <v>0</v>
       </c>
       <c r="R48" s="8">
-        <f>IF('Registo da Rotação'!A97="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C97,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I97="Ainda não avaliado",'Registo da Rotação'!J97="Ainda não avaliado",'Registo da Rotação'!K97="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A106="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C106,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I106="Ainda não avaliado",'Registo da Rotação'!J106="Ainda não avaliado",'Registo da Rotação'!K106="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S48" s="8">
-        <f>IF('Registo da Rotação'!A97="",0,IF(AND('Registo da Rotação'!G97=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97),'Registo da Rotação'!$G$54:'Registo da Rotação'!G96),""),'Registo da Rotação'!H97=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97),'Registo da Rotação'!$H$54:'Registo da Rotação'!H96),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A106="",0,IF(AND('Registo da Rotação'!G106=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106),'Registo da Rotação'!$G$54:'Registo da Rotação'!G105),""),'Registo da Rotação'!H106=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106),'Registo da Rotação'!$H$54:'Registo da Rotação'!H105),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T48" s="8">
-        <f>IF('Registo da Rotação'!A97="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Registo da Rotação'!G97)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Registo da Rotação'!H97)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F97,'Listas de apoio'!$A$5='Registo da Rotação'!G97,'Listas de apoio'!$A$5='Registo da Rotação'!H97),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Registo da Rotação'!G97)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Registo da Rotação'!H97)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F97,'Listas de apoio'!$A$6='Registo da Rotação'!G97,'Listas de apoio'!$A$6='Registo da Rotação'!H97),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Registo da Rotação'!G97)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Registo da Rotação'!H97)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F97,'Listas de apoio'!$A$7='Registo da Rotação'!G97,'Listas de apoio'!$A$7='Registo da Rotação'!H97),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Registo da Rotação'!G97)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Registo da Rotação'!H97)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F97,'Listas de apoio'!$A$8='Registo da Rotação'!G97,'Listas de apoio'!$A$8='Registo da Rotação'!H97),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F96='Registo da Rotação'!F97)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Registo da Rotação'!G97)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Registo da Rotação'!H97)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F96)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G96='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H96='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A106="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Registo da Rotação'!G106)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Registo da Rotação'!H106)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F106,'Listas de apoio'!$A$5='Registo da Rotação'!G106,'Listas de apoio'!$A$5='Registo da Rotação'!H106),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Registo da Rotação'!G106)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Registo da Rotação'!H106)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F106,'Listas de apoio'!$A$6='Registo da Rotação'!G106,'Listas de apoio'!$A$6='Registo da Rotação'!H106),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Registo da Rotação'!G106)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Registo da Rotação'!H106)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F106,'Listas de apoio'!$A$7='Registo da Rotação'!G106,'Listas de apoio'!$A$7='Registo da Rotação'!H106),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Registo da Rotação'!G106)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Registo da Rotação'!H106)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F106,'Listas de apoio'!$A$8='Registo da Rotação'!G106,'Listas de apoio'!$A$8='Registo da Rotação'!H106),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Registo da Rotação'!G106)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Registo da Rotação'!H106)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U48" s="8">
-        <f>IF('Registo da Rotação'!A97="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A97)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C97,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D97)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A106="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A106)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C106,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D106)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V48" s="1"/>
       <c r="W48" s="8">
-        <f>IF('Registo da Rotação'!C202="",0,IF(COUNTA('Registo da Rotação'!A202:H202)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C211="",0,IF(COUNTA('Registo da Rotação'!A211:H211)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X48" s="8">
-        <f>IF('Registo da Rotação'!C202="",0,IF('Registo da Rotação'!E202='Registo da Rotação'!F202,1,0))</f>
+        <f>IF('Registo da Rotação'!C211="",0,IF('Registo da Rotação'!E211='Registo da Rotação'!F211,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y48" s="8">
-        <f>IF('Registo da Rotação'!C202="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B202)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C211="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B211)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z48" s="8">
-        <f>IF('Registo da Rotação'!C202="",0,IF('Registo da Rotação'!D202="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C202,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F202)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C202,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F202)&gt;0,1,0),IF('Registo da Rotação'!D202="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C202,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F202)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C202,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F202)&gt;0,1,0),IF('Registo da Rotação'!D202="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C202,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F202)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C202,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F202)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C211="",0,IF('Registo da Rotação'!D211="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A211,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B211,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C211,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F211)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A211,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B211,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C211,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F211)&gt;0,1,0),IF('Registo da Rotação'!D211="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A211,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B211,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C211,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F211)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A211,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B211,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C211,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F211)&gt;0,1,0),IF('Registo da Rotação'!D211="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A211,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B211,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C211,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F211)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A211,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B211,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C211,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F211)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA48" s="8">
-        <f>IF('Registo da Rotação'!C202="",0,IF('Registo da Rotação'!D202="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C202,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E202)=0,1,0),IF('Registo da Rotação'!D202="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C202,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E202)=0,1,0),IF('Registo da Rotação'!D202="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A202,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B202,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C202,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E202)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C211="",0,IF('Registo da Rotação'!D211="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A211,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B211,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C211,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E211)=0,1,0),IF('Registo da Rotação'!D211="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A211,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B211,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C211,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E211)=0,1,0),IF('Registo da Rotação'!D211="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A211,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B211,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C211,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E211)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB48" s="8">
-        <f>IF('Registo da Rotação'!C202="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B202,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H202="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C211="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B211,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H211="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC48" s="1"/>
@@ -12520,56 +12980,56 @@
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
       <c r="O49" s="8">
-        <f>IF('Registo da Rotação'!A98="",0,IF(COUNTA('Registo da Rotação'!B98:K98)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A107="",0,IF(COUNTA('Registo da Rotação'!B107:K107)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P49" s="8">
-        <f>IF('Registo da Rotação'!A98="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C98)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A107="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C107)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q49" s="8">
-        <f>IF('Registo da Rotação'!A98="",0,IF(OR('Registo da Rotação'!F98='Registo da Rotação'!G98,'Registo da Rotação'!F98='Registo da Rotação'!H98,'Registo da Rotação'!G98='Registo da Rotação'!H98),1,0))</f>
+        <f>IF('Registo da Rotação'!A107="",0,IF(OR('Registo da Rotação'!F107='Registo da Rotação'!G107,'Registo da Rotação'!F107='Registo da Rotação'!H107,'Registo da Rotação'!G107='Registo da Rotação'!H107),1,0))</f>
         <v>0</v>
       </c>
       <c r="R49" s="8">
-        <f>IF('Registo da Rotação'!A98="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C98,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I98="Ainda não avaliado",'Registo da Rotação'!J98="Ainda não avaliado",'Registo da Rotação'!K98="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A107="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C107,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I107="Ainda não avaliado",'Registo da Rotação'!J107="Ainda não avaliado",'Registo da Rotação'!K107="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S49" s="8">
-        <f>IF('Registo da Rotação'!A98="",0,IF(AND('Registo da Rotação'!G98=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98),'Registo da Rotação'!$G$54:'Registo da Rotação'!G97),""),'Registo da Rotação'!H98=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98),'Registo da Rotação'!$H$54:'Registo da Rotação'!H97),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A107="",0,IF(AND('Registo da Rotação'!G107=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107),'Registo da Rotação'!$G$54:'Registo da Rotação'!G106),""),'Registo da Rotação'!H107=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107),'Registo da Rotação'!$H$54:'Registo da Rotação'!H106),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T49" s="8">
-        <f>IF('Registo da Rotação'!A98="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Registo da Rotação'!G98)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Registo da Rotação'!H98)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F98,'Listas de apoio'!$A$5='Registo da Rotação'!G98,'Listas de apoio'!$A$5='Registo da Rotação'!H98),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Registo da Rotação'!G98)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Registo da Rotação'!H98)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F98,'Listas de apoio'!$A$6='Registo da Rotação'!G98,'Listas de apoio'!$A$6='Registo da Rotação'!H98),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Registo da Rotação'!G98)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Registo da Rotação'!H98)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F98,'Listas de apoio'!$A$7='Registo da Rotação'!G98,'Listas de apoio'!$A$7='Registo da Rotação'!H98),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Registo da Rotação'!G98)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Registo da Rotação'!H98)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F98,'Listas de apoio'!$A$8='Registo da Rotação'!G98,'Listas de apoio'!$A$8='Registo da Rotação'!H98),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F97='Registo da Rotação'!F98)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Registo da Rotação'!G98)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Registo da Rotação'!H98)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F97)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G97='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H97='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A107="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Registo da Rotação'!G107)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Registo da Rotação'!H107)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F107,'Listas de apoio'!$A$5='Registo da Rotação'!G107,'Listas de apoio'!$A$5='Registo da Rotação'!H107),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Registo da Rotação'!G107)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Registo da Rotação'!H107)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F107,'Listas de apoio'!$A$6='Registo da Rotação'!G107,'Listas de apoio'!$A$6='Registo da Rotação'!H107),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Registo da Rotação'!G107)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Registo da Rotação'!H107)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F107,'Listas de apoio'!$A$7='Registo da Rotação'!G107,'Listas de apoio'!$A$7='Registo da Rotação'!H107),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Registo da Rotação'!G107)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Registo da Rotação'!H107)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F107,'Listas de apoio'!$A$8='Registo da Rotação'!G107,'Listas de apoio'!$A$8='Registo da Rotação'!H107),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Registo da Rotação'!G107)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Registo da Rotação'!H107)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U49" s="8">
-        <f>IF('Registo da Rotação'!A98="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A98)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C98,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D98)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A107="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A107)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C107,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D107)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V49" s="1"/>
       <c r="W49" s="8">
-        <f>IF('Registo da Rotação'!C203="",0,IF(COUNTA('Registo da Rotação'!A203:H203)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C212="",0,IF(COUNTA('Registo da Rotação'!A212:H212)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X49" s="8">
-        <f>IF('Registo da Rotação'!C203="",0,IF('Registo da Rotação'!E203='Registo da Rotação'!F203,1,0))</f>
+        <f>IF('Registo da Rotação'!C212="",0,IF('Registo da Rotação'!E212='Registo da Rotação'!F212,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y49" s="8">
-        <f>IF('Registo da Rotação'!C203="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B203)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C212="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B212)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z49" s="8">
-        <f>IF('Registo da Rotação'!C203="",0,IF('Registo da Rotação'!D203="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C203,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F203)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C203,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F203)&gt;0,1,0),IF('Registo da Rotação'!D203="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C203,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F203)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C203,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F203)&gt;0,1,0),IF('Registo da Rotação'!D203="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C203,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F203)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C203,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F203)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C212="",0,IF('Registo da Rotação'!D212="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A212,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B212,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C212,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F212)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A212,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B212,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C212,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F212)&gt;0,1,0),IF('Registo da Rotação'!D212="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A212,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B212,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C212,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F212)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A212,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B212,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C212,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F212)&gt;0,1,0),IF('Registo da Rotação'!D212="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A212,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B212,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C212,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F212)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A212,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B212,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C212,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F212)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA49" s="8">
-        <f>IF('Registo da Rotação'!C203="",0,IF('Registo da Rotação'!D203="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C203,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E203)=0,1,0),IF('Registo da Rotação'!D203="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C203,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E203)=0,1,0),IF('Registo da Rotação'!D203="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A203,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B203,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C203,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E203)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C212="",0,IF('Registo da Rotação'!D212="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A212,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B212,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C212,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E212)=0,1,0),IF('Registo da Rotação'!D212="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A212,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B212,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C212,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E212)=0,1,0),IF('Registo da Rotação'!D212="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A212,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B212,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C212,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E212)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB49" s="8">
-        <f>IF('Registo da Rotação'!C203="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B203,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H203="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C212="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B212,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H212="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC49" s="1"/>
@@ -12595,56 +13055,56 @@
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
       <c r="O50" s="8">
-        <f>IF('Registo da Rotação'!A99="",0,IF(COUNTA('Registo da Rotação'!B99:K99)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A108="",0,IF(COUNTA('Registo da Rotação'!B108:K108)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P50" s="8">
-        <f>IF('Registo da Rotação'!A99="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C99)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A108="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C108)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q50" s="8">
-        <f>IF('Registo da Rotação'!A99="",0,IF(OR('Registo da Rotação'!F99='Registo da Rotação'!G99,'Registo da Rotação'!F99='Registo da Rotação'!H99,'Registo da Rotação'!G99='Registo da Rotação'!H99),1,0))</f>
+        <f>IF('Registo da Rotação'!A108="",0,IF(OR('Registo da Rotação'!F108='Registo da Rotação'!G108,'Registo da Rotação'!F108='Registo da Rotação'!H108,'Registo da Rotação'!G108='Registo da Rotação'!H108),1,0))</f>
         <v>0</v>
       </c>
       <c r="R50" s="8">
-        <f>IF('Registo da Rotação'!A99="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C99,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I99="Ainda não avaliado",'Registo da Rotação'!J99="Ainda não avaliado",'Registo da Rotação'!K99="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A108="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C108,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I108="Ainda não avaliado",'Registo da Rotação'!J108="Ainda não avaliado",'Registo da Rotação'!K108="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S50" s="8">
-        <f>IF('Registo da Rotação'!A99="",0,IF(AND('Registo da Rotação'!G99=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99),'Registo da Rotação'!$G$54:'Registo da Rotação'!G98),""),'Registo da Rotação'!H99=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99),'Registo da Rotação'!$H$54:'Registo da Rotação'!H98),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A108="",0,IF(AND('Registo da Rotação'!G108=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108),'Registo da Rotação'!$G$54:'Registo da Rotação'!G107),""),'Registo da Rotação'!H108=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108),'Registo da Rotação'!$H$54:'Registo da Rotação'!H107),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T50" s="8">
-        <f>IF('Registo da Rotação'!A99="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Registo da Rotação'!G99)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Registo da Rotação'!H99)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F99,'Listas de apoio'!$A$5='Registo da Rotação'!G99,'Listas de apoio'!$A$5='Registo da Rotação'!H99),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Registo da Rotação'!G99)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Registo da Rotação'!H99)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F99,'Listas de apoio'!$A$6='Registo da Rotação'!G99,'Listas de apoio'!$A$6='Registo da Rotação'!H99),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Registo da Rotação'!G99)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Registo da Rotação'!H99)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F99,'Listas de apoio'!$A$7='Registo da Rotação'!G99,'Listas de apoio'!$A$7='Registo da Rotação'!H99),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Registo da Rotação'!G99)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Registo da Rotação'!H99)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F99,'Listas de apoio'!$A$8='Registo da Rotação'!G99,'Listas de apoio'!$A$8='Registo da Rotação'!H99),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F98='Registo da Rotação'!F99)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Registo da Rotação'!G99)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Registo da Rotação'!H99)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F98)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G98='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H98='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A108="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Registo da Rotação'!G108)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Registo da Rotação'!H108)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F108,'Listas de apoio'!$A$5='Registo da Rotação'!G108,'Listas de apoio'!$A$5='Registo da Rotação'!H108),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Registo da Rotação'!G108)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Registo da Rotação'!H108)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F108,'Listas de apoio'!$A$6='Registo da Rotação'!G108,'Listas de apoio'!$A$6='Registo da Rotação'!H108),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Registo da Rotação'!G108)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Registo da Rotação'!H108)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F108,'Listas de apoio'!$A$7='Registo da Rotação'!G108,'Listas de apoio'!$A$7='Registo da Rotação'!H108),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Registo da Rotação'!G108)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Registo da Rotação'!H108)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F108,'Listas de apoio'!$A$8='Registo da Rotação'!G108,'Listas de apoio'!$A$8='Registo da Rotação'!H108),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Registo da Rotação'!G108)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Registo da Rotação'!H108)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U50" s="8">
-        <f>IF('Registo da Rotação'!A99="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A99)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C99,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D99)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A108="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A108)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C108,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D108)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V50" s="1"/>
       <c r="W50" s="8">
-        <f>IF('Registo da Rotação'!C204="",0,IF(COUNTA('Registo da Rotação'!A204:H204)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C213="",0,IF(COUNTA('Registo da Rotação'!A213:H213)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X50" s="8">
-        <f>IF('Registo da Rotação'!C204="",0,IF('Registo da Rotação'!E204='Registo da Rotação'!F204,1,0))</f>
+        <f>IF('Registo da Rotação'!C213="",0,IF('Registo da Rotação'!E213='Registo da Rotação'!F213,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y50" s="8">
-        <f>IF('Registo da Rotação'!C204="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B204)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C213="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B213)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z50" s="8">
-        <f>IF('Registo da Rotação'!C204="",0,IF('Registo da Rotação'!D204="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C204,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F204)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C204,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F204)&gt;0,1,0),IF('Registo da Rotação'!D204="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C204,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F204)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C204,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F204)&gt;0,1,0),IF('Registo da Rotação'!D204="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C204,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F204)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C204,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F204)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C213="",0,IF('Registo da Rotação'!D213="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A213,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B213,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C213,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F213)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A213,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B213,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C213,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F213)&gt;0,1,0),IF('Registo da Rotação'!D213="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A213,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B213,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C213,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F213)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A213,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B213,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C213,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F213)&gt;0,1,0),IF('Registo da Rotação'!D213="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A213,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B213,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C213,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F213)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A213,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B213,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C213,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F213)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA50" s="8">
-        <f>IF('Registo da Rotação'!C204="",0,IF('Registo da Rotação'!D204="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C204,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E204)=0,1,0),IF('Registo da Rotação'!D204="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C204,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E204)=0,1,0),IF('Registo da Rotação'!D204="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A204,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B204,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C204,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E204)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C213="",0,IF('Registo da Rotação'!D213="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A213,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B213,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C213,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E213)=0,1,0),IF('Registo da Rotação'!D213="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A213,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B213,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C213,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E213)=0,1,0),IF('Registo da Rotação'!D213="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A213,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B213,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C213,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E213)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB50" s="8">
-        <f>IF('Registo da Rotação'!C204="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B204,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H204="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C213="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B213,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H213="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC50" s="1"/>
@@ -12670,56 +13130,56 @@
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
       <c r="O51" s="8">
-        <f>IF('Registo da Rotação'!A100="",0,IF(COUNTA('Registo da Rotação'!B100:K100)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A109="",0,IF(COUNTA('Registo da Rotação'!B109:K109)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P51" s="8">
-        <f>IF('Registo da Rotação'!A100="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C100)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A109="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C109)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q51" s="8">
-        <f>IF('Registo da Rotação'!A100="",0,IF(OR('Registo da Rotação'!F100='Registo da Rotação'!G100,'Registo da Rotação'!F100='Registo da Rotação'!H100,'Registo da Rotação'!G100='Registo da Rotação'!H100),1,0))</f>
+        <f>IF('Registo da Rotação'!A109="",0,IF(OR('Registo da Rotação'!F109='Registo da Rotação'!G109,'Registo da Rotação'!F109='Registo da Rotação'!H109,'Registo da Rotação'!G109='Registo da Rotação'!H109),1,0))</f>
         <v>0</v>
       </c>
       <c r="R51" s="8">
-        <f>IF('Registo da Rotação'!A100="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C100,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I100="Ainda não avaliado",'Registo da Rotação'!J100="Ainda não avaliado",'Registo da Rotação'!K100="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A109="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C109,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I109="Ainda não avaliado",'Registo da Rotação'!J109="Ainda não avaliado",'Registo da Rotação'!K109="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S51" s="8">
-        <f>IF('Registo da Rotação'!A100="",0,IF(AND('Registo da Rotação'!G100=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100),'Registo da Rotação'!$G$54:'Registo da Rotação'!G99),""),'Registo da Rotação'!H100=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100),'Registo da Rotação'!$H$54:'Registo da Rotação'!H99),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A109="",0,IF(AND('Registo da Rotação'!G109=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109),'Registo da Rotação'!$G$54:'Registo da Rotação'!G108),""),'Registo da Rotação'!H109=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109),'Registo da Rotação'!$H$54:'Registo da Rotação'!H108),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T51" s="8">
-        <f>IF('Registo da Rotação'!A100="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Registo da Rotação'!G100)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Registo da Rotação'!H100)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F100,'Listas de apoio'!$A$5='Registo da Rotação'!G100,'Listas de apoio'!$A$5='Registo da Rotação'!H100),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Registo da Rotação'!G100)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Registo da Rotação'!H100)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F100,'Listas de apoio'!$A$6='Registo da Rotação'!G100,'Listas de apoio'!$A$6='Registo da Rotação'!H100),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Registo da Rotação'!G100)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Registo da Rotação'!H100)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F100,'Listas de apoio'!$A$7='Registo da Rotação'!G100,'Listas de apoio'!$A$7='Registo da Rotação'!H100),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Registo da Rotação'!G100)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Registo da Rotação'!H100)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F100,'Listas de apoio'!$A$8='Registo da Rotação'!G100,'Listas de apoio'!$A$8='Registo da Rotação'!H100),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F99='Registo da Rotação'!F100)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Registo da Rotação'!G100)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Registo da Rotação'!H100)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F99)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G99='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H99='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A109="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Registo da Rotação'!G109)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Registo da Rotação'!H109)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F109,'Listas de apoio'!$A$5='Registo da Rotação'!G109,'Listas de apoio'!$A$5='Registo da Rotação'!H109),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Registo da Rotação'!G109)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Registo da Rotação'!H109)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F109,'Listas de apoio'!$A$6='Registo da Rotação'!G109,'Listas de apoio'!$A$6='Registo da Rotação'!H109),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Registo da Rotação'!G109)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Registo da Rotação'!H109)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F109,'Listas de apoio'!$A$7='Registo da Rotação'!G109,'Listas de apoio'!$A$7='Registo da Rotação'!H109),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Registo da Rotação'!G109)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Registo da Rotação'!H109)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F109,'Listas de apoio'!$A$8='Registo da Rotação'!G109,'Listas de apoio'!$A$8='Registo da Rotação'!H109),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Registo da Rotação'!G109)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Registo da Rotação'!H109)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U51" s="8">
-        <f>IF('Registo da Rotação'!A100="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A100)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C100,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D100)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A109="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A109)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C109,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D109)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V51" s="1"/>
       <c r="W51" s="8">
-        <f>IF('Registo da Rotação'!C205="",0,IF(COUNTA('Registo da Rotação'!A205:H205)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C214="",0,IF(COUNTA('Registo da Rotação'!A214:H214)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X51" s="8">
-        <f>IF('Registo da Rotação'!C205="",0,IF('Registo da Rotação'!E205='Registo da Rotação'!F205,1,0))</f>
+        <f>IF('Registo da Rotação'!C214="",0,IF('Registo da Rotação'!E214='Registo da Rotação'!F214,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y51" s="8">
-        <f>IF('Registo da Rotação'!C205="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B205)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C214="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B214)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z51" s="8">
-        <f>IF('Registo da Rotação'!C205="",0,IF('Registo da Rotação'!D205="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C205,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F205)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C205,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F205)&gt;0,1,0),IF('Registo da Rotação'!D205="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C205,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F205)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C205,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F205)&gt;0,1,0),IF('Registo da Rotação'!D205="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C205,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F205)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C205,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F205)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C214="",0,IF('Registo da Rotação'!D214="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A214,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B214,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C214,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F214)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A214,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B214,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C214,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F214)&gt;0,1,0),IF('Registo da Rotação'!D214="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A214,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B214,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C214,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F214)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A214,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B214,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C214,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F214)&gt;0,1,0),IF('Registo da Rotação'!D214="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A214,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B214,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C214,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F214)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A214,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B214,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C214,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F214)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA51" s="8">
-        <f>IF('Registo da Rotação'!C205="",0,IF('Registo da Rotação'!D205="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C205,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E205)=0,1,0),IF('Registo da Rotação'!D205="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C205,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E205)=0,1,0),IF('Registo da Rotação'!D205="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A205,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B205,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C205,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E205)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C214="",0,IF('Registo da Rotação'!D214="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A214,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B214,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C214,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E214)=0,1,0),IF('Registo da Rotação'!D214="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A214,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B214,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C214,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E214)=0,1,0),IF('Registo da Rotação'!D214="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A214,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B214,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C214,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E214)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB51" s="8">
-        <f>IF('Registo da Rotação'!C205="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B205,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H205="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C214="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B214,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H214="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC51" s="1"/>
@@ -12745,56 +13205,56 @@
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
       <c r="O52" s="8">
-        <f>IF('Registo da Rotação'!A101="",0,IF(COUNTA('Registo da Rotação'!B101:K101)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A110="",0,IF(COUNTA('Registo da Rotação'!B110:K110)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P52" s="8">
-        <f>IF('Registo da Rotação'!A101="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C101)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A110="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C110)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q52" s="8">
-        <f>IF('Registo da Rotação'!A101="",0,IF(OR('Registo da Rotação'!F101='Registo da Rotação'!G101,'Registo da Rotação'!F101='Registo da Rotação'!H101,'Registo da Rotação'!G101='Registo da Rotação'!H101),1,0))</f>
+        <f>IF('Registo da Rotação'!A110="",0,IF(OR('Registo da Rotação'!F110='Registo da Rotação'!G110,'Registo da Rotação'!F110='Registo da Rotação'!H110,'Registo da Rotação'!G110='Registo da Rotação'!H110),1,0))</f>
         <v>0</v>
       </c>
       <c r="R52" s="8">
-        <f>IF('Registo da Rotação'!A101="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C101,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I101="Ainda não avaliado",'Registo da Rotação'!J101="Ainda não avaliado",'Registo da Rotação'!K101="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A110="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C110,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I110="Ainda não avaliado",'Registo da Rotação'!J110="Ainda não avaliado",'Registo da Rotação'!K110="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S52" s="8">
-        <f>IF('Registo da Rotação'!A101="",0,IF(AND('Registo da Rotação'!G101=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101),'Registo da Rotação'!$G$54:'Registo da Rotação'!G100),""),'Registo da Rotação'!H101=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101),'Registo da Rotação'!$H$54:'Registo da Rotação'!H100),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A110="",0,IF(AND('Registo da Rotação'!G110=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110),'Registo da Rotação'!$G$54:'Registo da Rotação'!G109),""),'Registo da Rotação'!H110=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110),'Registo da Rotação'!$H$54:'Registo da Rotação'!H109),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T52" s="8">
-        <f>IF('Registo da Rotação'!A101="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Registo da Rotação'!G101)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Registo da Rotação'!H101)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F101,'Listas de apoio'!$A$5='Registo da Rotação'!G101,'Listas de apoio'!$A$5='Registo da Rotação'!H101),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Registo da Rotação'!G101)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Registo da Rotação'!H101)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F101,'Listas de apoio'!$A$6='Registo da Rotação'!G101,'Listas de apoio'!$A$6='Registo da Rotação'!H101),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Registo da Rotação'!G101)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Registo da Rotação'!H101)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F101,'Listas de apoio'!$A$7='Registo da Rotação'!G101,'Listas de apoio'!$A$7='Registo da Rotação'!H101),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Registo da Rotação'!G101)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Registo da Rotação'!H101)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F101,'Listas de apoio'!$A$8='Registo da Rotação'!G101,'Listas de apoio'!$A$8='Registo da Rotação'!H101),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F100='Registo da Rotação'!F101)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Registo da Rotação'!G101)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Registo da Rotação'!H101)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F100)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G100='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H100='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A110="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Registo da Rotação'!G110)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Registo da Rotação'!H110)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F110,'Listas de apoio'!$A$5='Registo da Rotação'!G110,'Listas de apoio'!$A$5='Registo da Rotação'!H110),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Registo da Rotação'!G110)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Registo da Rotação'!H110)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F110,'Listas de apoio'!$A$6='Registo da Rotação'!G110,'Listas de apoio'!$A$6='Registo da Rotação'!H110),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Registo da Rotação'!G110)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Registo da Rotação'!H110)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F110,'Listas de apoio'!$A$7='Registo da Rotação'!G110,'Listas de apoio'!$A$7='Registo da Rotação'!H110),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Registo da Rotação'!G110)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Registo da Rotação'!H110)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F110,'Listas de apoio'!$A$8='Registo da Rotação'!G110,'Listas de apoio'!$A$8='Registo da Rotação'!H110),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Registo da Rotação'!G110)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Registo da Rotação'!H110)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U52" s="8">
-        <f>IF('Registo da Rotação'!A101="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A101)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C101,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D101)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A110="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A110)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C110,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D110)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V52" s="1"/>
       <c r="W52" s="8">
-        <f>IF('Registo da Rotação'!C206="",0,IF(COUNTA('Registo da Rotação'!A206:H206)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C215="",0,IF(COUNTA('Registo da Rotação'!A215:H215)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X52" s="8">
-        <f>IF('Registo da Rotação'!C206="",0,IF('Registo da Rotação'!E206='Registo da Rotação'!F206,1,0))</f>
+        <f>IF('Registo da Rotação'!C215="",0,IF('Registo da Rotação'!E215='Registo da Rotação'!F215,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y52" s="8">
-        <f>IF('Registo da Rotação'!C206="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B206)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C215="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B215)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z52" s="8">
-        <f>IF('Registo da Rotação'!C206="",0,IF('Registo da Rotação'!D206="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C206,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F206)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C206,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F206)&gt;0,1,0),IF('Registo da Rotação'!D206="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C206,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F206)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C206,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F206)&gt;0,1,0),IF('Registo da Rotação'!D206="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C206,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F206)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C206,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F206)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C215="",0,IF('Registo da Rotação'!D215="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A215,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B215,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C215,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F215)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A215,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B215,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C215,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F215)&gt;0,1,0),IF('Registo da Rotação'!D215="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A215,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B215,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C215,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F215)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A215,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B215,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C215,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F215)&gt;0,1,0),IF('Registo da Rotação'!D215="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A215,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B215,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C215,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F215)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A215,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B215,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C215,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F215)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA52" s="8">
-        <f>IF('Registo da Rotação'!C206="",0,IF('Registo da Rotação'!D206="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C206,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E206)=0,1,0),IF('Registo da Rotação'!D206="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C206,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E206)=0,1,0),IF('Registo da Rotação'!D206="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A206,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B206,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C206,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E206)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C215="",0,IF('Registo da Rotação'!D215="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A215,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B215,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C215,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E215)=0,1,0),IF('Registo da Rotação'!D215="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A215,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B215,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C215,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E215)=0,1,0),IF('Registo da Rotação'!D215="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A215,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B215,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C215,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E215)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB52" s="8">
-        <f>IF('Registo da Rotação'!C206="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B206,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H206="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C215="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B215,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H215="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC52" s="1"/>
@@ -12820,56 +13280,56 @@
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
       <c r="O53" s="8">
-        <f>IF('Registo da Rotação'!A102="",0,IF(COUNTA('Registo da Rotação'!B102:K102)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A111="",0,IF(COUNTA('Registo da Rotação'!B111:K111)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P53" s="8">
-        <f>IF('Registo da Rotação'!A102="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C102)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A111="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C111)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q53" s="8">
-        <f>IF('Registo da Rotação'!A102="",0,IF(OR('Registo da Rotação'!F102='Registo da Rotação'!G102,'Registo da Rotação'!F102='Registo da Rotação'!H102,'Registo da Rotação'!G102='Registo da Rotação'!H102),1,0))</f>
+        <f>IF('Registo da Rotação'!A111="",0,IF(OR('Registo da Rotação'!F111='Registo da Rotação'!G111,'Registo da Rotação'!F111='Registo da Rotação'!H111,'Registo da Rotação'!G111='Registo da Rotação'!H111),1,0))</f>
         <v>0</v>
       </c>
       <c r="R53" s="8">
-        <f>IF('Registo da Rotação'!A102="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C102,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I102="Ainda não avaliado",'Registo da Rotação'!J102="Ainda não avaliado",'Registo da Rotação'!K102="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A111="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C111,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I111="Ainda não avaliado",'Registo da Rotação'!J111="Ainda não avaliado",'Registo da Rotação'!K111="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S53" s="8">
-        <f>IF('Registo da Rotação'!A102="",0,IF(AND('Registo da Rotação'!G102=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102),'Registo da Rotação'!$G$54:'Registo da Rotação'!G101),""),'Registo da Rotação'!H102=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102),'Registo da Rotação'!$H$54:'Registo da Rotação'!H101),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A111="",0,IF(AND('Registo da Rotação'!G111=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111),'Registo da Rotação'!$G$54:'Registo da Rotação'!G110),""),'Registo da Rotação'!H111=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111),'Registo da Rotação'!$H$54:'Registo da Rotação'!H110),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T53" s="8">
-        <f>IF('Registo da Rotação'!A102="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Registo da Rotação'!G102)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Registo da Rotação'!H102)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F102,'Listas de apoio'!$A$5='Registo da Rotação'!G102,'Listas de apoio'!$A$5='Registo da Rotação'!H102),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Registo da Rotação'!G102)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Registo da Rotação'!H102)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F102,'Listas de apoio'!$A$6='Registo da Rotação'!G102,'Listas de apoio'!$A$6='Registo da Rotação'!H102),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Registo da Rotação'!G102)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Registo da Rotação'!H102)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F102,'Listas de apoio'!$A$7='Registo da Rotação'!G102,'Listas de apoio'!$A$7='Registo da Rotação'!H102),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Registo da Rotação'!G102)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Registo da Rotação'!H102)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F102,'Listas de apoio'!$A$8='Registo da Rotação'!G102,'Listas de apoio'!$A$8='Registo da Rotação'!H102),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F101='Registo da Rotação'!F102)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Registo da Rotação'!G102)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Registo da Rotação'!H102)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F101)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G101='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H101='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A111="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Registo da Rotação'!G111)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Registo da Rotação'!H111)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F111,'Listas de apoio'!$A$5='Registo da Rotação'!G111,'Listas de apoio'!$A$5='Registo da Rotação'!H111),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Registo da Rotação'!G111)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Registo da Rotação'!H111)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F111,'Listas de apoio'!$A$6='Registo da Rotação'!G111,'Listas de apoio'!$A$6='Registo da Rotação'!H111),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Registo da Rotação'!G111)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Registo da Rotação'!H111)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F111,'Listas de apoio'!$A$7='Registo da Rotação'!G111,'Listas de apoio'!$A$7='Registo da Rotação'!H111),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Registo da Rotação'!G111)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Registo da Rotação'!H111)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F111,'Listas de apoio'!$A$8='Registo da Rotação'!G111,'Listas de apoio'!$A$8='Registo da Rotação'!H111),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Registo da Rotação'!G111)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Registo da Rotação'!H111)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U53" s="8">
-        <f>IF('Registo da Rotação'!A102="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A102)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C102,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D102)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A111="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A111)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C111,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D111)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V53" s="1"/>
       <c r="W53" s="8">
-        <f>IF('Registo da Rotação'!C207="",0,IF(COUNTA('Registo da Rotação'!A207:H207)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C216="",0,IF(COUNTA('Registo da Rotação'!A216:H216)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X53" s="8">
-        <f>IF('Registo da Rotação'!C207="",0,IF('Registo da Rotação'!E207='Registo da Rotação'!F207,1,0))</f>
+        <f>IF('Registo da Rotação'!C216="",0,IF('Registo da Rotação'!E216='Registo da Rotação'!F216,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y53" s="8">
-        <f>IF('Registo da Rotação'!C207="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B207)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C216="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B216)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z53" s="8">
-        <f>IF('Registo da Rotação'!C207="",0,IF('Registo da Rotação'!D207="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C207,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F207)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C207,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F207)&gt;0,1,0),IF('Registo da Rotação'!D207="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C207,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F207)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C207,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F207)&gt;0,1,0),IF('Registo da Rotação'!D207="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C207,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F207)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C207,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F207)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C216="",0,IF('Registo da Rotação'!D216="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A216,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B216,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C216,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F216)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A216,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B216,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C216,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F216)&gt;0,1,0),IF('Registo da Rotação'!D216="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A216,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B216,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C216,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F216)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A216,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B216,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C216,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F216)&gt;0,1,0),IF('Registo da Rotação'!D216="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A216,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B216,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C216,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F216)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A216,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B216,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C216,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F216)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA53" s="8">
-        <f>IF('Registo da Rotação'!C207="",0,IF('Registo da Rotação'!D207="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C207,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E207)=0,1,0),IF('Registo da Rotação'!D207="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C207,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E207)=0,1,0),IF('Registo da Rotação'!D207="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A207,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B207,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C207,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E207)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C216="",0,IF('Registo da Rotação'!D216="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A216,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B216,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C216,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E216)=0,1,0),IF('Registo da Rotação'!D216="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A216,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B216,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C216,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E216)=0,1,0),IF('Registo da Rotação'!D216="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A216,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B216,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C216,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E216)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB53" s="8">
-        <f>IF('Registo da Rotação'!C207="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B207,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H207="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C216="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B216,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H216="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC53" s="1"/>
@@ -12895,56 +13355,56 @@
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
       <c r="O54" s="8">
-        <f>IF('Registo da Rotação'!A103="",0,IF(COUNTA('Registo da Rotação'!B103:K103)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A112="",0,IF(COUNTA('Registo da Rotação'!B112:K112)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P54" s="8">
-        <f>IF('Registo da Rotação'!A103="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C103)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A112="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C112)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q54" s="8">
-        <f>IF('Registo da Rotação'!A103="",0,IF(OR('Registo da Rotação'!F103='Registo da Rotação'!G103,'Registo da Rotação'!F103='Registo da Rotação'!H103,'Registo da Rotação'!G103='Registo da Rotação'!H103),1,0))</f>
+        <f>IF('Registo da Rotação'!A112="",0,IF(OR('Registo da Rotação'!F112='Registo da Rotação'!G112,'Registo da Rotação'!F112='Registo da Rotação'!H112,'Registo da Rotação'!G112='Registo da Rotação'!H112),1,0))</f>
         <v>0</v>
       </c>
       <c r="R54" s="8">
-        <f>IF('Registo da Rotação'!A103="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C103,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I103="Ainda não avaliado",'Registo da Rotação'!J103="Ainda não avaliado",'Registo da Rotação'!K103="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A112="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C112,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I112="Ainda não avaliado",'Registo da Rotação'!J112="Ainda não avaliado",'Registo da Rotação'!K112="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S54" s="8">
-        <f>IF('Registo da Rotação'!A103="",0,IF(AND('Registo da Rotação'!G103=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103),'Registo da Rotação'!$G$54:'Registo da Rotação'!G102),""),'Registo da Rotação'!H103=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103),'Registo da Rotação'!$H$54:'Registo da Rotação'!H102),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A112="",0,IF(AND('Registo da Rotação'!G112=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112),'Registo da Rotação'!$G$54:'Registo da Rotação'!G111),""),'Registo da Rotação'!H112=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112),'Registo da Rotação'!$H$54:'Registo da Rotação'!H111),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T54" s="8">
-        <f>IF('Registo da Rotação'!A103="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Registo da Rotação'!G103)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Registo da Rotação'!H103)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F103,'Listas de apoio'!$A$5='Registo da Rotação'!G103,'Listas de apoio'!$A$5='Registo da Rotação'!H103),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Registo da Rotação'!G103)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Registo da Rotação'!H103)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F103,'Listas de apoio'!$A$6='Registo da Rotação'!G103,'Listas de apoio'!$A$6='Registo da Rotação'!H103),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Registo da Rotação'!G103)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Registo da Rotação'!H103)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F103,'Listas de apoio'!$A$7='Registo da Rotação'!G103,'Listas de apoio'!$A$7='Registo da Rotação'!H103),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Registo da Rotação'!G103)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Registo da Rotação'!H103)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F103,'Listas de apoio'!$A$8='Registo da Rotação'!G103,'Listas de apoio'!$A$8='Registo da Rotação'!H103),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F102='Registo da Rotação'!F103)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Registo da Rotação'!G103)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Registo da Rotação'!H103)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F102)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G102='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H102='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A112="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Registo da Rotação'!G112)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Registo da Rotação'!H112)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F112,'Listas de apoio'!$A$5='Registo da Rotação'!G112,'Listas de apoio'!$A$5='Registo da Rotação'!H112),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Registo da Rotação'!G112)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Registo da Rotação'!H112)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F112,'Listas de apoio'!$A$6='Registo da Rotação'!G112,'Listas de apoio'!$A$6='Registo da Rotação'!H112),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Registo da Rotação'!G112)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Registo da Rotação'!H112)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F112,'Listas de apoio'!$A$7='Registo da Rotação'!G112,'Listas de apoio'!$A$7='Registo da Rotação'!H112),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Registo da Rotação'!G112)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Registo da Rotação'!H112)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F112,'Listas de apoio'!$A$8='Registo da Rotação'!G112,'Listas de apoio'!$A$8='Registo da Rotação'!H112),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Registo da Rotação'!G112)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Registo da Rotação'!H112)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U54" s="8">
-        <f>IF('Registo da Rotação'!A103="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A103)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C103,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D103)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A112="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A112)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C112,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D112)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V54" s="1"/>
       <c r="W54" s="8">
-        <f>IF('Registo da Rotação'!C208="",0,IF(COUNTA('Registo da Rotação'!A208:H208)&lt;8,1,0))</f>
+        <f>IF('Registo da Rotação'!C217="",0,IF(COUNTA('Registo da Rotação'!A217:H217)&lt;8,1,0))</f>
         <v>0</v>
       </c>
       <c r="X54" s="8">
-        <f>IF('Registo da Rotação'!C208="",0,IF('Registo da Rotação'!E208='Registo da Rotação'!F208,1,0))</f>
+        <f>IF('Registo da Rotação'!C217="",0,IF('Registo da Rotação'!E217='Registo da Rotação'!F217,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y54" s="8">
-        <f>IF('Registo da Rotação'!C208="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B208)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!C217="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B217)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z54" s="8">
-        <f>IF('Registo da Rotação'!C208="",0,IF('Registo da Rotação'!D208="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C208,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F208)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C208,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F208)&gt;0,1,0),IF('Registo da Rotação'!D208="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C208,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F208)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C208,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!F208)&gt;0,1,0),IF('Registo da Rotação'!D208="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C208,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!F208)+COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C208,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!F208)&gt;0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C217="",0,IF('Registo da Rotação'!D217="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A217,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B217,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C217,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F217)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A217,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B217,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C217,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F217)&gt;0,1,0),IF('Registo da Rotação'!D217="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A217,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B217,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C217,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F217)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A217,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B217,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C217,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!F217)&gt;0,1,0),IF('Registo da Rotação'!D217="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A217,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B217,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C217,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!F217)+COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A217,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B217,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C217,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!F217)&gt;0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AA54" s="8">
-        <f>IF('Registo da Rotação'!C208="",0,IF('Registo da Rotação'!D208="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C208,'Registo da Rotação'!$F$54:$F$153,'Registo da Rotação'!E208)=0,1,0),IF('Registo da Rotação'!D208="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C208,'Registo da Rotação'!$G$54:$G$153,'Registo da Rotação'!E208)=0,1,0),IF('Registo da Rotação'!D208="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$153,'Registo da Rotação'!A208,'Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!B208,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!C208,'Registo da Rotação'!$H$54:$H$153,'Registo da Rotação'!E208)=0,1,0),0))))</f>
+        <f>IF('Registo da Rotação'!C217="",0,IF('Registo da Rotação'!D217="Executor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A217,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B217,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C217,'Registo da Rotação'!$F$54:$F$162,'Registo da Rotação'!E217)=0,1,0),IF('Registo da Rotação'!D217="Revisor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A217,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B217,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C217,'Registo da Rotação'!$G$54:$G$162,'Registo da Rotação'!E217)=0,1,0),IF('Registo da Rotação'!D217="Auditor",IF(COUNTIFS('Registo da Rotação'!$B$54:$B$162,'Registo da Rotação'!A217,'Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!B217,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!C217,'Registo da Rotação'!$H$54:$H$162,'Registo da Rotação'!E217)=0,1,0),0))))</f>
         <v>0</v>
       </c>
       <c r="AB54" s="8">
-        <f>IF('Registo da Rotação'!C208="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B208,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H208="Ainda não avaliado"),1,0))</f>
+        <f>IF('Registo da Rotação'!C217="",0,IF(AND(COUNTIFS('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!B217,'Registo da Rotação'!$D$6:$D$25,"Concluído")&gt;0,'Registo da Rotação'!H217="Ainda não avaliado"),1,0))</f>
         <v>0</v>
       </c>
       <c r="AC54" s="1"/>
@@ -12970,31 +13430,31 @@
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
       <c r="O55" s="8">
-        <f>IF('Registo da Rotação'!A104="",0,IF(COUNTA('Registo da Rotação'!B104:K104)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A113="",0,IF(COUNTA('Registo da Rotação'!B113:K113)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P55" s="8">
-        <f>IF('Registo da Rotação'!A104="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C104)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A113="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C113)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q55" s="8">
-        <f>IF('Registo da Rotação'!A104="",0,IF(OR('Registo da Rotação'!F104='Registo da Rotação'!G104,'Registo da Rotação'!F104='Registo da Rotação'!H104,'Registo da Rotação'!G104='Registo da Rotação'!H104),1,0))</f>
+        <f>IF('Registo da Rotação'!A113="",0,IF(OR('Registo da Rotação'!F113='Registo da Rotação'!G113,'Registo da Rotação'!F113='Registo da Rotação'!H113,'Registo da Rotação'!G113='Registo da Rotação'!H113),1,0))</f>
         <v>0</v>
       </c>
       <c r="R55" s="8">
-        <f>IF('Registo da Rotação'!A104="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C104,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I104="Ainda não avaliado",'Registo da Rotação'!J104="Ainda não avaliado",'Registo da Rotação'!K104="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A113="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C113,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I113="Ainda não avaliado",'Registo da Rotação'!J113="Ainda não avaliado",'Registo da Rotação'!K113="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S55" s="8">
-        <f>IF('Registo da Rotação'!A104="",0,IF(AND('Registo da Rotação'!G104=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104),'Registo da Rotação'!$G$54:'Registo da Rotação'!G103),""),'Registo da Rotação'!H104=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104),'Registo da Rotação'!$H$54:'Registo da Rotação'!H103),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A113="",0,IF(AND('Registo da Rotação'!G113=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113),'Registo da Rotação'!$G$54:'Registo da Rotação'!G112),""),'Registo da Rotação'!H113=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113),'Registo da Rotação'!$H$54:'Registo da Rotação'!H112),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T55" s="8">
-        <f>IF('Registo da Rotação'!A104="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Registo da Rotação'!G104)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Registo da Rotação'!H104)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F104,'Listas de apoio'!$A$5='Registo da Rotação'!G104,'Listas de apoio'!$A$5='Registo da Rotação'!H104),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Registo da Rotação'!G104)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Registo da Rotação'!H104)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F104,'Listas de apoio'!$A$6='Registo da Rotação'!G104,'Listas de apoio'!$A$6='Registo da Rotação'!H104),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Registo da Rotação'!G104)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Registo da Rotação'!H104)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F104,'Listas de apoio'!$A$7='Registo da Rotação'!G104,'Listas de apoio'!$A$7='Registo da Rotação'!H104),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Registo da Rotação'!G104)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Registo da Rotação'!H104)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F104,'Listas de apoio'!$A$8='Registo da Rotação'!G104,'Listas de apoio'!$A$8='Registo da Rotação'!H104),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F103='Registo da Rotação'!F104)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Registo da Rotação'!G104)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Registo da Rotação'!H104)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F103)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G103='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H103='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A113="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Registo da Rotação'!G113)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Registo da Rotação'!H113)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F113,'Listas de apoio'!$A$5='Registo da Rotação'!G113,'Listas de apoio'!$A$5='Registo da Rotação'!H113),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Registo da Rotação'!G113)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Registo da Rotação'!H113)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F113,'Listas de apoio'!$A$6='Registo da Rotação'!G113,'Listas de apoio'!$A$6='Registo da Rotação'!H113),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Registo da Rotação'!G113)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Registo da Rotação'!H113)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F113,'Listas de apoio'!$A$7='Registo da Rotação'!G113,'Listas de apoio'!$A$7='Registo da Rotação'!H113),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Registo da Rotação'!G113)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Registo da Rotação'!H113)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F113,'Listas de apoio'!$A$8='Registo da Rotação'!G113,'Listas de apoio'!$A$8='Registo da Rotação'!H113),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Registo da Rotação'!G113)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Registo da Rotação'!H113)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U55" s="8">
-        <f>IF('Registo da Rotação'!A104="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A104)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C104,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D104)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A113="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A113)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C113,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D113)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V55" s="1"/>
@@ -13027,31 +13487,31 @@
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
       <c r="O56" s="8">
-        <f>IF('Registo da Rotação'!A105="",0,IF(COUNTA('Registo da Rotação'!B105:K105)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A114="",0,IF(COUNTA('Registo da Rotação'!B114:K114)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P56" s="8">
-        <f>IF('Registo da Rotação'!A105="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C105)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A114="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C114)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q56" s="8">
-        <f>IF('Registo da Rotação'!A105="",0,IF(OR('Registo da Rotação'!F105='Registo da Rotação'!G105,'Registo da Rotação'!F105='Registo da Rotação'!H105,'Registo da Rotação'!G105='Registo da Rotação'!H105),1,0))</f>
+        <f>IF('Registo da Rotação'!A114="",0,IF(OR('Registo da Rotação'!F114='Registo da Rotação'!G114,'Registo da Rotação'!F114='Registo da Rotação'!H114,'Registo da Rotação'!G114='Registo da Rotação'!H114),1,0))</f>
         <v>0</v>
       </c>
       <c r="R56" s="8">
-        <f>IF('Registo da Rotação'!A105="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C105,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I105="Ainda não avaliado",'Registo da Rotação'!J105="Ainda não avaliado",'Registo da Rotação'!K105="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A114="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C114,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I114="Ainda não avaliado",'Registo da Rotação'!J114="Ainda não avaliado",'Registo da Rotação'!K114="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S56" s="8">
-        <f>IF('Registo da Rotação'!A105="",0,IF(AND('Registo da Rotação'!G105=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105),'Registo da Rotação'!$G$54:'Registo da Rotação'!G104),""),'Registo da Rotação'!H105=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105),'Registo da Rotação'!$H$54:'Registo da Rotação'!H104),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A114="",0,IF(AND('Registo da Rotação'!G114=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114),'Registo da Rotação'!$G$54:'Registo da Rotação'!G113),""),'Registo da Rotação'!H114=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114),'Registo da Rotação'!$H$54:'Registo da Rotação'!H113),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T56" s="8">
-        <f>IF('Registo da Rotação'!A105="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Registo da Rotação'!G105)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Registo da Rotação'!H105)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F105,'Listas de apoio'!$A$5='Registo da Rotação'!G105,'Listas de apoio'!$A$5='Registo da Rotação'!H105),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Registo da Rotação'!G105)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Registo da Rotação'!H105)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F105,'Listas de apoio'!$A$6='Registo da Rotação'!G105,'Listas de apoio'!$A$6='Registo da Rotação'!H105),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Registo da Rotação'!G105)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Registo da Rotação'!H105)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F105,'Listas de apoio'!$A$7='Registo da Rotação'!G105,'Listas de apoio'!$A$7='Registo da Rotação'!H105),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Registo da Rotação'!G105)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Registo da Rotação'!H105)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F105,'Listas de apoio'!$A$8='Registo da Rotação'!G105,'Listas de apoio'!$A$8='Registo da Rotação'!H105),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F104='Registo da Rotação'!F105)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Registo da Rotação'!G105)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Registo da Rotação'!H105)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F104)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G104='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H104='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A114="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Registo da Rotação'!G114)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Registo da Rotação'!H114)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F114,'Listas de apoio'!$A$5='Registo da Rotação'!G114,'Listas de apoio'!$A$5='Registo da Rotação'!H114),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Registo da Rotação'!G114)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Registo da Rotação'!H114)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F114,'Listas de apoio'!$A$6='Registo da Rotação'!G114,'Listas de apoio'!$A$6='Registo da Rotação'!H114),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Registo da Rotação'!G114)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Registo da Rotação'!H114)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F114,'Listas de apoio'!$A$7='Registo da Rotação'!G114,'Listas de apoio'!$A$7='Registo da Rotação'!H114),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Registo da Rotação'!G114)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Registo da Rotação'!H114)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F114,'Listas de apoio'!$A$8='Registo da Rotação'!G114,'Listas de apoio'!$A$8='Registo da Rotação'!H114),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Registo da Rotação'!G114)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Registo da Rotação'!H114)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U56" s="8">
-        <f>IF('Registo da Rotação'!A105="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A105)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C105,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D105)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A114="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A114)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C114,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D114)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V56" s="1"/>
@@ -13084,31 +13544,31 @@
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
       <c r="O57" s="8">
-        <f>IF('Registo da Rotação'!A106="",0,IF(COUNTA('Registo da Rotação'!B106:K106)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A115="",0,IF(COUNTA('Registo da Rotação'!B115:K115)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P57" s="8">
-        <f>IF('Registo da Rotação'!A106="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C106)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A115="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C115)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q57" s="8">
-        <f>IF('Registo da Rotação'!A106="",0,IF(OR('Registo da Rotação'!F106='Registo da Rotação'!G106,'Registo da Rotação'!F106='Registo da Rotação'!H106,'Registo da Rotação'!G106='Registo da Rotação'!H106),1,0))</f>
+        <f>IF('Registo da Rotação'!A115="",0,IF(OR('Registo da Rotação'!F115='Registo da Rotação'!G115,'Registo da Rotação'!F115='Registo da Rotação'!H115,'Registo da Rotação'!G115='Registo da Rotação'!H115),1,0))</f>
         <v>0</v>
       </c>
       <c r="R57" s="8">
-        <f>IF('Registo da Rotação'!A106="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C106,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I106="Ainda não avaliado",'Registo da Rotação'!J106="Ainda não avaliado",'Registo da Rotação'!K106="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A115="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C115,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I115="Ainda não avaliado",'Registo da Rotação'!J115="Ainda não avaliado",'Registo da Rotação'!K115="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S57" s="8">
-        <f>IF('Registo da Rotação'!A106="",0,IF(AND('Registo da Rotação'!G106=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106),'Registo da Rotação'!$G$54:'Registo da Rotação'!G105),""),'Registo da Rotação'!H106=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106),'Registo da Rotação'!$H$54:'Registo da Rotação'!H105),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A115="",0,IF(AND('Registo da Rotação'!G115=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115),'Registo da Rotação'!$G$54:'Registo da Rotação'!G114),""),'Registo da Rotação'!H115=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115),'Registo da Rotação'!$H$54:'Registo da Rotação'!H114),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T57" s="8">
-        <f>IF('Registo da Rotação'!A106="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Registo da Rotação'!G106)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Registo da Rotação'!H106)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F106,'Listas de apoio'!$A$5='Registo da Rotação'!G106,'Listas de apoio'!$A$5='Registo da Rotação'!H106),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Registo da Rotação'!G106)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Registo da Rotação'!H106)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F106,'Listas de apoio'!$A$6='Registo da Rotação'!G106,'Listas de apoio'!$A$6='Registo da Rotação'!H106),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Registo da Rotação'!G106)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Registo da Rotação'!H106)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F106,'Listas de apoio'!$A$7='Registo da Rotação'!G106,'Listas de apoio'!$A$7='Registo da Rotação'!H106),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Registo da Rotação'!G106)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Registo da Rotação'!H106)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F106,'Listas de apoio'!$A$8='Registo da Rotação'!G106,'Listas de apoio'!$A$8='Registo da Rotação'!H106),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F105='Registo da Rotação'!F106)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Registo da Rotação'!G106)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Registo da Rotação'!H106)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F105)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G105='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H105='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A115="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Registo da Rotação'!G115)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Registo da Rotação'!H115)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F115,'Listas de apoio'!$A$5='Registo da Rotação'!G115,'Listas de apoio'!$A$5='Registo da Rotação'!H115),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Registo da Rotação'!G115)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Registo da Rotação'!H115)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F115,'Listas de apoio'!$A$6='Registo da Rotação'!G115,'Listas de apoio'!$A$6='Registo da Rotação'!H115),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Registo da Rotação'!G115)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Registo da Rotação'!H115)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F115,'Listas de apoio'!$A$7='Registo da Rotação'!G115,'Listas de apoio'!$A$7='Registo da Rotação'!H115),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Registo da Rotação'!G115)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Registo da Rotação'!H115)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F115,'Listas de apoio'!$A$8='Registo da Rotação'!G115,'Listas de apoio'!$A$8='Registo da Rotação'!H115),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Registo da Rotação'!G115)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Registo da Rotação'!H115)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U57" s="8">
-        <f>IF('Registo da Rotação'!A106="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A106)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C106,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D106)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A115="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A115)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C115,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D115)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V57" s="1"/>
@@ -13141,31 +13601,31 @@
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
       <c r="O58" s="8">
-        <f>IF('Registo da Rotação'!A107="",0,IF(COUNTA('Registo da Rotação'!B107:K107)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A116="",0,IF(COUNTA('Registo da Rotação'!B116:K116)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P58" s="8">
-        <f>IF('Registo da Rotação'!A107="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C107)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A116="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C116)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q58" s="8">
-        <f>IF('Registo da Rotação'!A107="",0,IF(OR('Registo da Rotação'!F107='Registo da Rotação'!G107,'Registo da Rotação'!F107='Registo da Rotação'!H107,'Registo da Rotação'!G107='Registo da Rotação'!H107),1,0))</f>
+        <f>IF('Registo da Rotação'!A116="",0,IF(OR('Registo da Rotação'!F116='Registo da Rotação'!G116,'Registo da Rotação'!F116='Registo da Rotação'!H116,'Registo da Rotação'!G116='Registo da Rotação'!H116),1,0))</f>
         <v>0</v>
       </c>
       <c r="R58" s="8">
-        <f>IF('Registo da Rotação'!A107="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C107,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I107="Ainda não avaliado",'Registo da Rotação'!J107="Ainda não avaliado",'Registo da Rotação'!K107="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A116="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C116,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I116="Ainda não avaliado",'Registo da Rotação'!J116="Ainda não avaliado",'Registo da Rotação'!K116="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S58" s="8">
-        <f>IF('Registo da Rotação'!A107="",0,IF(AND('Registo da Rotação'!G107=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107),'Registo da Rotação'!$G$54:'Registo da Rotação'!G106),""),'Registo da Rotação'!H107=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107),'Registo da Rotação'!$H$54:'Registo da Rotação'!H106),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A116="",0,IF(AND('Registo da Rotação'!G116=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116),'Registo da Rotação'!$G$54:'Registo da Rotação'!G115),""),'Registo da Rotação'!H116=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116),'Registo da Rotação'!$H$54:'Registo da Rotação'!H115),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T58" s="8">
-        <f>IF('Registo da Rotação'!A107="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Registo da Rotação'!G107)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Registo da Rotação'!H107)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F107,'Listas de apoio'!$A$5='Registo da Rotação'!G107,'Listas de apoio'!$A$5='Registo da Rotação'!H107),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Registo da Rotação'!G107)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Registo da Rotação'!H107)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F107,'Listas de apoio'!$A$6='Registo da Rotação'!G107,'Listas de apoio'!$A$6='Registo da Rotação'!H107),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Registo da Rotação'!G107)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Registo da Rotação'!H107)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F107,'Listas de apoio'!$A$7='Registo da Rotação'!G107,'Listas de apoio'!$A$7='Registo da Rotação'!H107),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Registo da Rotação'!G107)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Registo da Rotação'!H107)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F107,'Listas de apoio'!$A$8='Registo da Rotação'!G107,'Listas de apoio'!$A$8='Registo da Rotação'!H107),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F106='Registo da Rotação'!F107)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Registo da Rotação'!G107)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Registo da Rotação'!H107)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F106)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G106='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H106='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A116="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Registo da Rotação'!G116)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Registo da Rotação'!H116)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F116,'Listas de apoio'!$A$5='Registo da Rotação'!G116,'Listas de apoio'!$A$5='Registo da Rotação'!H116),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Registo da Rotação'!G116)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Registo da Rotação'!H116)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F116,'Listas de apoio'!$A$6='Registo da Rotação'!G116,'Listas de apoio'!$A$6='Registo da Rotação'!H116),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Registo da Rotação'!G116)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Registo da Rotação'!H116)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F116,'Listas de apoio'!$A$7='Registo da Rotação'!G116,'Listas de apoio'!$A$7='Registo da Rotação'!H116),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Registo da Rotação'!G116)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Registo da Rotação'!H116)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F116,'Listas de apoio'!$A$8='Registo da Rotação'!G116,'Listas de apoio'!$A$8='Registo da Rotação'!H116),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Registo da Rotação'!G116)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Registo da Rotação'!H116)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U58" s="8">
-        <f>IF('Registo da Rotação'!A107="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A107)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C107,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D107)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A116="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A116)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C116,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D116)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V58" s="1"/>
@@ -13198,31 +13658,31 @@
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
       <c r="O59" s="8">
-        <f>IF('Registo da Rotação'!A108="",0,IF(COUNTA('Registo da Rotação'!B108:K108)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A117="",0,IF(COUNTA('Registo da Rotação'!B117:K117)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P59" s="8">
-        <f>IF('Registo da Rotação'!A108="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C108)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A117="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C117)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q59" s="8">
-        <f>IF('Registo da Rotação'!A108="",0,IF(OR('Registo da Rotação'!F108='Registo da Rotação'!G108,'Registo da Rotação'!F108='Registo da Rotação'!H108,'Registo da Rotação'!G108='Registo da Rotação'!H108),1,0))</f>
+        <f>IF('Registo da Rotação'!A117="",0,IF(OR('Registo da Rotação'!F117='Registo da Rotação'!G117,'Registo da Rotação'!F117='Registo da Rotação'!H117,'Registo da Rotação'!G117='Registo da Rotação'!H117),1,0))</f>
         <v>0</v>
       </c>
       <c r="R59" s="8">
-        <f>IF('Registo da Rotação'!A108="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C108,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I108="Ainda não avaliado",'Registo da Rotação'!J108="Ainda não avaliado",'Registo da Rotação'!K108="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A117="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C117,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I117="Ainda não avaliado",'Registo da Rotação'!J117="Ainda não avaliado",'Registo da Rotação'!K117="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S59" s="8">
-        <f>IF('Registo da Rotação'!A108="",0,IF(AND('Registo da Rotação'!G108=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108),'Registo da Rotação'!$G$54:'Registo da Rotação'!G107),""),'Registo da Rotação'!H108=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108),'Registo da Rotação'!$H$54:'Registo da Rotação'!H107),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A117="",0,IF(AND('Registo da Rotação'!G117=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117),'Registo da Rotação'!$G$54:'Registo da Rotação'!G116),""),'Registo da Rotação'!H117=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117),'Registo da Rotação'!$H$54:'Registo da Rotação'!H116),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T59" s="8">
-        <f>IF('Registo da Rotação'!A108="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Registo da Rotação'!G108)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Registo da Rotação'!H108)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F108,'Listas de apoio'!$A$5='Registo da Rotação'!G108,'Listas de apoio'!$A$5='Registo da Rotação'!H108),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Registo da Rotação'!G108)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Registo da Rotação'!H108)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F108,'Listas de apoio'!$A$6='Registo da Rotação'!G108,'Listas de apoio'!$A$6='Registo da Rotação'!H108),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Registo da Rotação'!G108)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Registo da Rotação'!H108)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F108,'Listas de apoio'!$A$7='Registo da Rotação'!G108,'Listas de apoio'!$A$7='Registo da Rotação'!H108),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Registo da Rotação'!G108)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Registo da Rotação'!H108)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F108,'Listas de apoio'!$A$8='Registo da Rotação'!G108,'Listas de apoio'!$A$8='Registo da Rotação'!H108),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F107='Registo da Rotação'!F108)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Registo da Rotação'!G108)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Registo da Rotação'!H108)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F107)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G107='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H107='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A117="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Registo da Rotação'!G117)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Registo da Rotação'!H117)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F117,'Listas de apoio'!$A$5='Registo da Rotação'!G117,'Listas de apoio'!$A$5='Registo da Rotação'!H117),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Registo da Rotação'!G117)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Registo da Rotação'!H117)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F117,'Listas de apoio'!$A$6='Registo da Rotação'!G117,'Listas de apoio'!$A$6='Registo da Rotação'!H117),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Registo da Rotação'!G117)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Registo da Rotação'!H117)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F117,'Listas de apoio'!$A$7='Registo da Rotação'!G117,'Listas de apoio'!$A$7='Registo da Rotação'!H117),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Registo da Rotação'!G117)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Registo da Rotação'!H117)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F117,'Listas de apoio'!$A$8='Registo da Rotação'!G117,'Listas de apoio'!$A$8='Registo da Rotação'!H117),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Registo da Rotação'!G117)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Registo da Rotação'!H117)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U59" s="8">
-        <f>IF('Registo da Rotação'!A108="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A108)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C108,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D108)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A117="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A117)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C117,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D117)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V59" s="1"/>
@@ -13255,31 +13715,31 @@
       <c r="M60" s="1"/>
       <c r="N60" s="1"/>
       <c r="O60" s="8">
-        <f>IF('Registo da Rotação'!A109="",0,IF(COUNTA('Registo da Rotação'!B109:K109)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A118="",0,IF(COUNTA('Registo da Rotação'!B118:K118)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P60" s="8">
-        <f>IF('Registo da Rotação'!A109="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C109)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A118="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C118)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q60" s="8">
-        <f>IF('Registo da Rotação'!A109="",0,IF(OR('Registo da Rotação'!F109='Registo da Rotação'!G109,'Registo da Rotação'!F109='Registo da Rotação'!H109,'Registo da Rotação'!G109='Registo da Rotação'!H109),1,0))</f>
+        <f>IF('Registo da Rotação'!A118="",0,IF(OR('Registo da Rotação'!F118='Registo da Rotação'!G118,'Registo da Rotação'!F118='Registo da Rotação'!H118,'Registo da Rotação'!G118='Registo da Rotação'!H118),1,0))</f>
         <v>0</v>
       </c>
       <c r="R60" s="8">
-        <f>IF('Registo da Rotação'!A109="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C109,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I109="Ainda não avaliado",'Registo da Rotação'!J109="Ainda não avaliado",'Registo da Rotação'!K109="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A118="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C118,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I118="Ainda não avaliado",'Registo da Rotação'!J118="Ainda não avaliado",'Registo da Rotação'!K118="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S60" s="8">
-        <f>IF('Registo da Rotação'!A109="",0,IF(AND('Registo da Rotação'!G109=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109),'Registo da Rotação'!$G$54:'Registo da Rotação'!G108),""),'Registo da Rotação'!H109=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109),'Registo da Rotação'!$H$54:'Registo da Rotação'!H108),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A118="",0,IF(AND('Registo da Rotação'!G118=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118),'Registo da Rotação'!$G$54:'Registo da Rotação'!G117),""),'Registo da Rotação'!H118=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118),'Registo da Rotação'!$H$54:'Registo da Rotação'!H117),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T60" s="8">
-        <f>IF('Registo da Rotação'!A109="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Registo da Rotação'!G109)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Registo da Rotação'!H109)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F109,'Listas de apoio'!$A$5='Registo da Rotação'!G109,'Listas de apoio'!$A$5='Registo da Rotação'!H109),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Registo da Rotação'!G109)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Registo da Rotação'!H109)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F109,'Listas de apoio'!$A$6='Registo da Rotação'!G109,'Listas de apoio'!$A$6='Registo da Rotação'!H109),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Registo da Rotação'!G109)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Registo da Rotação'!H109)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F109,'Listas de apoio'!$A$7='Registo da Rotação'!G109,'Listas de apoio'!$A$7='Registo da Rotação'!H109),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Registo da Rotação'!G109)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Registo da Rotação'!H109)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F109,'Listas de apoio'!$A$8='Registo da Rotação'!G109,'Listas de apoio'!$A$8='Registo da Rotação'!H109),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F108='Registo da Rotação'!F109)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Registo da Rotação'!G109)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Registo da Rotação'!H109)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F108)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G108='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H108='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A118="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Registo da Rotação'!G118)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Registo da Rotação'!H118)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F118,'Listas de apoio'!$A$5='Registo da Rotação'!G118,'Listas de apoio'!$A$5='Registo da Rotação'!H118),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Registo da Rotação'!G118)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Registo da Rotação'!H118)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F118,'Listas de apoio'!$A$6='Registo da Rotação'!G118,'Listas de apoio'!$A$6='Registo da Rotação'!H118),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Registo da Rotação'!G118)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Registo da Rotação'!H118)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F118,'Listas de apoio'!$A$7='Registo da Rotação'!G118,'Listas de apoio'!$A$7='Registo da Rotação'!H118),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Registo da Rotação'!G118)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Registo da Rotação'!H118)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F118,'Listas de apoio'!$A$8='Registo da Rotação'!G118,'Listas de apoio'!$A$8='Registo da Rotação'!H118),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Registo da Rotação'!G118)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Registo da Rotação'!H118)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U60" s="8">
-        <f>IF('Registo da Rotação'!A109="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A109)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C109,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D109)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A118="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A118)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C118,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D118)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V60" s="1"/>
@@ -13312,31 +13772,31 @@
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
       <c r="O61" s="8">
-        <f>IF('Registo da Rotação'!A110="",0,IF(COUNTA('Registo da Rotação'!B110:K110)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A119="",0,IF(COUNTA('Registo da Rotação'!B119:K119)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P61" s="8">
-        <f>IF('Registo da Rotação'!A110="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C110)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A119="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C119)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q61" s="8">
-        <f>IF('Registo da Rotação'!A110="",0,IF(OR('Registo da Rotação'!F110='Registo da Rotação'!G110,'Registo da Rotação'!F110='Registo da Rotação'!H110,'Registo da Rotação'!G110='Registo da Rotação'!H110),1,0))</f>
+        <f>IF('Registo da Rotação'!A119="",0,IF(OR('Registo da Rotação'!F119='Registo da Rotação'!G119,'Registo da Rotação'!F119='Registo da Rotação'!H119,'Registo da Rotação'!G119='Registo da Rotação'!H119),1,0))</f>
         <v>0</v>
       </c>
       <c r="R61" s="8">
-        <f>IF('Registo da Rotação'!A110="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C110,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I110="Ainda não avaliado",'Registo da Rotação'!J110="Ainda não avaliado",'Registo da Rotação'!K110="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A119="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C119,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I119="Ainda não avaliado",'Registo da Rotação'!J119="Ainda não avaliado",'Registo da Rotação'!K119="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S61" s="8">
-        <f>IF('Registo da Rotação'!A110="",0,IF(AND('Registo da Rotação'!G110=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110),'Registo da Rotação'!$G$54:'Registo da Rotação'!G109),""),'Registo da Rotação'!H110=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110),'Registo da Rotação'!$H$54:'Registo da Rotação'!H109),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A119="",0,IF(AND('Registo da Rotação'!G119=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119),'Registo da Rotação'!$G$54:'Registo da Rotação'!G118),""),'Registo da Rotação'!H119=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119),'Registo da Rotação'!$H$54:'Registo da Rotação'!H118),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T61" s="8">
-        <f>IF('Registo da Rotação'!A110="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Registo da Rotação'!G110)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Registo da Rotação'!H110)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F110,'Listas de apoio'!$A$5='Registo da Rotação'!G110,'Listas de apoio'!$A$5='Registo da Rotação'!H110),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Registo da Rotação'!G110)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Registo da Rotação'!H110)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F110,'Listas de apoio'!$A$6='Registo da Rotação'!G110,'Listas de apoio'!$A$6='Registo da Rotação'!H110),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Registo da Rotação'!G110)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Registo da Rotação'!H110)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F110,'Listas de apoio'!$A$7='Registo da Rotação'!G110,'Listas de apoio'!$A$7='Registo da Rotação'!H110),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Registo da Rotação'!G110)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Registo da Rotação'!H110)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F110,'Listas de apoio'!$A$8='Registo da Rotação'!G110,'Listas de apoio'!$A$8='Registo da Rotação'!H110),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F109='Registo da Rotação'!F110)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Registo da Rotação'!G110)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Registo da Rotação'!H110)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F109)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G109='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H109='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A119="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Registo da Rotação'!G119)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Registo da Rotação'!H119)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F119,'Listas de apoio'!$A$5='Registo da Rotação'!G119,'Listas de apoio'!$A$5='Registo da Rotação'!H119),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Registo da Rotação'!G119)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Registo da Rotação'!H119)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F119,'Listas de apoio'!$A$6='Registo da Rotação'!G119,'Listas de apoio'!$A$6='Registo da Rotação'!H119),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Registo da Rotação'!G119)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Registo da Rotação'!H119)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F119,'Listas de apoio'!$A$7='Registo da Rotação'!G119,'Listas de apoio'!$A$7='Registo da Rotação'!H119),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Registo da Rotação'!G119)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Registo da Rotação'!H119)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F119,'Listas de apoio'!$A$8='Registo da Rotação'!G119,'Listas de apoio'!$A$8='Registo da Rotação'!H119),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Registo da Rotação'!G119)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Registo da Rotação'!H119)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U61" s="8">
-        <f>IF('Registo da Rotação'!A110="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A110)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C110,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D110)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A119="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A119)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C119,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D119)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V61" s="1"/>
@@ -13369,31 +13829,31 @@
       <c r="M62" s="1"/>
       <c r="N62" s="1"/>
       <c r="O62" s="8">
-        <f>IF('Registo da Rotação'!A111="",0,IF(COUNTA('Registo da Rotação'!B111:K111)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A120="",0,IF(COUNTA('Registo da Rotação'!B120:K120)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P62" s="8">
-        <f>IF('Registo da Rotação'!A111="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C111)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A120="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C120)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q62" s="8">
-        <f>IF('Registo da Rotação'!A111="",0,IF(OR('Registo da Rotação'!F111='Registo da Rotação'!G111,'Registo da Rotação'!F111='Registo da Rotação'!H111,'Registo da Rotação'!G111='Registo da Rotação'!H111),1,0))</f>
+        <f>IF('Registo da Rotação'!A120="",0,IF(OR('Registo da Rotação'!F120='Registo da Rotação'!G120,'Registo da Rotação'!F120='Registo da Rotação'!H120,'Registo da Rotação'!G120='Registo da Rotação'!H120),1,0))</f>
         <v>0</v>
       </c>
       <c r="R62" s="8">
-        <f>IF('Registo da Rotação'!A111="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C111,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I111="Ainda não avaliado",'Registo da Rotação'!J111="Ainda não avaliado",'Registo da Rotação'!K111="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A120="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C120,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I120="Ainda não avaliado",'Registo da Rotação'!J120="Ainda não avaliado",'Registo da Rotação'!K120="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S62" s="8">
-        <f>IF('Registo da Rotação'!A111="",0,IF(AND('Registo da Rotação'!G111=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111),'Registo da Rotação'!$G$54:'Registo da Rotação'!G110),""),'Registo da Rotação'!H111=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111),'Registo da Rotação'!$H$54:'Registo da Rotação'!H110),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A120="",0,IF(AND('Registo da Rotação'!G120=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120),'Registo da Rotação'!$G$54:'Registo da Rotação'!G119),""),'Registo da Rotação'!H120=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120),'Registo da Rotação'!$H$54:'Registo da Rotação'!H119),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T62" s="8">
-        <f>IF('Registo da Rotação'!A111="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Registo da Rotação'!G111)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Registo da Rotação'!H111)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F111,'Listas de apoio'!$A$5='Registo da Rotação'!G111,'Listas de apoio'!$A$5='Registo da Rotação'!H111),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Registo da Rotação'!G111)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Registo da Rotação'!H111)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F111,'Listas de apoio'!$A$6='Registo da Rotação'!G111,'Listas de apoio'!$A$6='Registo da Rotação'!H111),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Registo da Rotação'!G111)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Registo da Rotação'!H111)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F111,'Listas de apoio'!$A$7='Registo da Rotação'!G111,'Listas de apoio'!$A$7='Registo da Rotação'!H111),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Registo da Rotação'!G111)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Registo da Rotação'!H111)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F111,'Listas de apoio'!$A$8='Registo da Rotação'!G111,'Listas de apoio'!$A$8='Registo da Rotação'!H111),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F110='Registo da Rotação'!F111)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Registo da Rotação'!G111)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Registo da Rotação'!H111)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F110)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G110='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H110='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A120="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Registo da Rotação'!G120)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Registo da Rotação'!H120)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F120,'Listas de apoio'!$A$5='Registo da Rotação'!G120,'Listas de apoio'!$A$5='Registo da Rotação'!H120),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Registo da Rotação'!G120)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Registo da Rotação'!H120)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F120,'Listas de apoio'!$A$6='Registo da Rotação'!G120,'Listas de apoio'!$A$6='Registo da Rotação'!H120),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Registo da Rotação'!G120)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Registo da Rotação'!H120)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F120,'Listas de apoio'!$A$7='Registo da Rotação'!G120,'Listas de apoio'!$A$7='Registo da Rotação'!H120),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Registo da Rotação'!G120)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Registo da Rotação'!H120)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F120,'Listas de apoio'!$A$8='Registo da Rotação'!G120,'Listas de apoio'!$A$8='Registo da Rotação'!H120),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Registo da Rotação'!G120)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Registo da Rotação'!H120)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U62" s="8">
-        <f>IF('Registo da Rotação'!A111="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A111)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C111,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D111)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A120="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A120)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C120,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D120)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V62" s="1"/>
@@ -13426,31 +13886,31 @@
       <c r="M63" s="1"/>
       <c r="N63" s="1"/>
       <c r="O63" s="8">
-        <f>IF('Registo da Rotação'!A112="",0,IF(COUNTA('Registo da Rotação'!B112:K112)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A121="",0,IF(COUNTA('Registo da Rotação'!B121:K121)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P63" s="8">
-        <f>IF('Registo da Rotação'!A112="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C112)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A121="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C121)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q63" s="8">
-        <f>IF('Registo da Rotação'!A112="",0,IF(OR('Registo da Rotação'!F112='Registo da Rotação'!G112,'Registo da Rotação'!F112='Registo da Rotação'!H112,'Registo da Rotação'!G112='Registo da Rotação'!H112),1,0))</f>
+        <f>IF('Registo da Rotação'!A121="",0,IF(OR('Registo da Rotação'!F121='Registo da Rotação'!G121,'Registo da Rotação'!F121='Registo da Rotação'!H121,'Registo da Rotação'!G121='Registo da Rotação'!H121),1,0))</f>
         <v>0</v>
       </c>
       <c r="R63" s="8">
-        <f>IF('Registo da Rotação'!A112="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C112,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I112="Ainda não avaliado",'Registo da Rotação'!J112="Ainda não avaliado",'Registo da Rotação'!K112="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A121="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C121,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I121="Ainda não avaliado",'Registo da Rotação'!J121="Ainda não avaliado",'Registo da Rotação'!K121="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S63" s="8">
-        <f>IF('Registo da Rotação'!A112="",0,IF(AND('Registo da Rotação'!G112=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112),'Registo da Rotação'!$G$54:'Registo da Rotação'!G111),""),'Registo da Rotação'!H112=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112),'Registo da Rotação'!$H$54:'Registo da Rotação'!H111),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A121="",0,IF(AND('Registo da Rotação'!G121=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121),'Registo da Rotação'!$G$54:'Registo da Rotação'!G120),""),'Registo da Rotação'!H121=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121),'Registo da Rotação'!$H$54:'Registo da Rotação'!H120),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T63" s="8">
-        <f>IF('Registo da Rotação'!A112="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Registo da Rotação'!G112)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Registo da Rotação'!H112)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F112,'Listas de apoio'!$A$5='Registo da Rotação'!G112,'Listas de apoio'!$A$5='Registo da Rotação'!H112),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Registo da Rotação'!G112)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Registo da Rotação'!H112)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F112,'Listas de apoio'!$A$6='Registo da Rotação'!G112,'Listas de apoio'!$A$6='Registo da Rotação'!H112),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Registo da Rotação'!G112)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Registo da Rotação'!H112)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F112,'Listas de apoio'!$A$7='Registo da Rotação'!G112,'Listas de apoio'!$A$7='Registo da Rotação'!H112),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Registo da Rotação'!G112)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Registo da Rotação'!H112)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F112,'Listas de apoio'!$A$8='Registo da Rotação'!G112,'Listas de apoio'!$A$8='Registo da Rotação'!H112),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F111='Registo da Rotação'!F112)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Registo da Rotação'!G112)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Registo da Rotação'!H112)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F111)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G111='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H111='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A121="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Registo da Rotação'!G121)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Registo da Rotação'!H121)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F121,'Listas de apoio'!$A$5='Registo da Rotação'!G121,'Listas de apoio'!$A$5='Registo da Rotação'!H121),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Registo da Rotação'!G121)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Registo da Rotação'!H121)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F121,'Listas de apoio'!$A$6='Registo da Rotação'!G121,'Listas de apoio'!$A$6='Registo da Rotação'!H121),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Registo da Rotação'!G121)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Registo da Rotação'!H121)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F121,'Listas de apoio'!$A$7='Registo da Rotação'!G121,'Listas de apoio'!$A$7='Registo da Rotação'!H121),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Registo da Rotação'!G121)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Registo da Rotação'!H121)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F121,'Listas de apoio'!$A$8='Registo da Rotação'!G121,'Listas de apoio'!$A$8='Registo da Rotação'!H121),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Registo da Rotação'!G121)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Registo da Rotação'!H121)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U63" s="8">
-        <f>IF('Registo da Rotação'!A112="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A112)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C112,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D112)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A121="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A121)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C121,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D121)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V63" s="1"/>
@@ -13483,31 +13943,31 @@
       <c r="M64" s="1"/>
       <c r="N64" s="1"/>
       <c r="O64" s="8">
-        <f>IF('Registo da Rotação'!A113="",0,IF(COUNTA('Registo da Rotação'!B113:K113)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A122="",0,IF(COUNTA('Registo da Rotação'!B122:K122)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P64" s="8">
-        <f>IF('Registo da Rotação'!A113="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C113)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A122="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C122)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q64" s="8">
-        <f>IF('Registo da Rotação'!A113="",0,IF(OR('Registo da Rotação'!F113='Registo da Rotação'!G113,'Registo da Rotação'!F113='Registo da Rotação'!H113,'Registo da Rotação'!G113='Registo da Rotação'!H113),1,0))</f>
+        <f>IF('Registo da Rotação'!A122="",0,IF(OR('Registo da Rotação'!F122='Registo da Rotação'!G122,'Registo da Rotação'!F122='Registo da Rotação'!H122,'Registo da Rotação'!G122='Registo da Rotação'!H122),1,0))</f>
         <v>0</v>
       </c>
       <c r="R64" s="8">
-        <f>IF('Registo da Rotação'!A113="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C113,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I113="Ainda não avaliado",'Registo da Rotação'!J113="Ainda não avaliado",'Registo da Rotação'!K113="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A122="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C122,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I122="Ainda não avaliado",'Registo da Rotação'!J122="Ainda não avaliado",'Registo da Rotação'!K122="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S64" s="8">
-        <f>IF('Registo da Rotação'!A113="",0,IF(AND('Registo da Rotação'!G113=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113),'Registo da Rotação'!$G$54:'Registo da Rotação'!G112),""),'Registo da Rotação'!H113=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113),'Registo da Rotação'!$H$54:'Registo da Rotação'!H112),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A122="",0,IF(AND('Registo da Rotação'!G122=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122),'Registo da Rotação'!$G$54:'Registo da Rotação'!G121),""),'Registo da Rotação'!H122=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122),'Registo da Rotação'!$H$54:'Registo da Rotação'!H121),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T64" s="8">
-        <f>IF('Registo da Rotação'!A113="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Registo da Rotação'!G113)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Registo da Rotação'!H113)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F113,'Listas de apoio'!$A$5='Registo da Rotação'!G113,'Listas de apoio'!$A$5='Registo da Rotação'!H113),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Registo da Rotação'!G113)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Registo da Rotação'!H113)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F113,'Listas de apoio'!$A$6='Registo da Rotação'!G113,'Listas de apoio'!$A$6='Registo da Rotação'!H113),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Registo da Rotação'!G113)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Registo da Rotação'!H113)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F113,'Listas de apoio'!$A$7='Registo da Rotação'!G113,'Listas de apoio'!$A$7='Registo da Rotação'!H113),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Registo da Rotação'!G113)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Registo da Rotação'!H113)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F113,'Listas de apoio'!$A$8='Registo da Rotação'!G113,'Listas de apoio'!$A$8='Registo da Rotação'!H113),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F112='Registo da Rotação'!F113)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Registo da Rotação'!G113)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Registo da Rotação'!H113)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F112)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G112='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H112='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A122="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Registo da Rotação'!G122)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Registo da Rotação'!H122)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F122,'Listas de apoio'!$A$5='Registo da Rotação'!G122,'Listas de apoio'!$A$5='Registo da Rotação'!H122),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Registo da Rotação'!G122)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Registo da Rotação'!H122)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F122,'Listas de apoio'!$A$6='Registo da Rotação'!G122,'Listas de apoio'!$A$6='Registo da Rotação'!H122),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Registo da Rotação'!G122)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Registo da Rotação'!H122)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F122,'Listas de apoio'!$A$7='Registo da Rotação'!G122,'Listas de apoio'!$A$7='Registo da Rotação'!H122),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Registo da Rotação'!G122)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Registo da Rotação'!H122)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F122,'Listas de apoio'!$A$8='Registo da Rotação'!G122,'Listas de apoio'!$A$8='Registo da Rotação'!H122),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Registo da Rotação'!G122)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Registo da Rotação'!H122)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U64" s="8">
-        <f>IF('Registo da Rotação'!A113="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A113)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C113,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D113)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A122="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A122)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C122,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D122)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V64" s="1"/>
@@ -13540,31 +14000,31 @@
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
       <c r="O65" s="8">
-        <f>IF('Registo da Rotação'!A114="",0,IF(COUNTA('Registo da Rotação'!B114:K114)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A123="",0,IF(COUNTA('Registo da Rotação'!B123:K123)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P65" s="8">
-        <f>IF('Registo da Rotação'!A114="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C114)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A123="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C123)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q65" s="8">
-        <f>IF('Registo da Rotação'!A114="",0,IF(OR('Registo da Rotação'!F114='Registo da Rotação'!G114,'Registo da Rotação'!F114='Registo da Rotação'!H114,'Registo da Rotação'!G114='Registo da Rotação'!H114),1,0))</f>
+        <f>IF('Registo da Rotação'!A123="",0,IF(OR('Registo da Rotação'!F123='Registo da Rotação'!G123,'Registo da Rotação'!F123='Registo da Rotação'!H123,'Registo da Rotação'!G123='Registo da Rotação'!H123),1,0))</f>
         <v>0</v>
       </c>
       <c r="R65" s="8">
-        <f>IF('Registo da Rotação'!A114="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C114,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I114="Ainda não avaliado",'Registo da Rotação'!J114="Ainda não avaliado",'Registo da Rotação'!K114="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A123="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C123,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I123="Ainda não avaliado",'Registo da Rotação'!J123="Ainda não avaliado",'Registo da Rotação'!K123="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S65" s="8">
-        <f>IF('Registo da Rotação'!A114="",0,IF(AND('Registo da Rotação'!G114=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114),'Registo da Rotação'!$G$54:'Registo da Rotação'!G113),""),'Registo da Rotação'!H114=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114),'Registo da Rotação'!$H$54:'Registo da Rotação'!H113),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A123="",0,IF(AND('Registo da Rotação'!G123=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123),'Registo da Rotação'!$G$54:'Registo da Rotação'!G122),""),'Registo da Rotação'!H123=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123),'Registo da Rotação'!$H$54:'Registo da Rotação'!H122),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T65" s="8">
-        <f>IF('Registo da Rotação'!A114="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Registo da Rotação'!G114)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Registo da Rotação'!H114)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F114,'Listas de apoio'!$A$5='Registo da Rotação'!G114,'Listas de apoio'!$A$5='Registo da Rotação'!H114),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Registo da Rotação'!G114)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Registo da Rotação'!H114)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F114,'Listas de apoio'!$A$6='Registo da Rotação'!G114,'Listas de apoio'!$A$6='Registo da Rotação'!H114),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Registo da Rotação'!G114)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Registo da Rotação'!H114)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F114,'Listas de apoio'!$A$7='Registo da Rotação'!G114,'Listas de apoio'!$A$7='Registo da Rotação'!H114),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Registo da Rotação'!G114)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Registo da Rotação'!H114)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F114,'Listas de apoio'!$A$8='Registo da Rotação'!G114,'Listas de apoio'!$A$8='Registo da Rotação'!H114),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F113='Registo da Rotação'!F114)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Registo da Rotação'!G114)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Registo da Rotação'!H114)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F113)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G113='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H113='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A123="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Registo da Rotação'!G123)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Registo da Rotação'!H123)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F123,'Listas de apoio'!$A$5='Registo da Rotação'!G123,'Listas de apoio'!$A$5='Registo da Rotação'!H123),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Registo da Rotação'!G123)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Registo da Rotação'!H123)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F123,'Listas de apoio'!$A$6='Registo da Rotação'!G123,'Listas de apoio'!$A$6='Registo da Rotação'!H123),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Registo da Rotação'!G123)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Registo da Rotação'!H123)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F123,'Listas de apoio'!$A$7='Registo da Rotação'!G123,'Listas de apoio'!$A$7='Registo da Rotação'!H123),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Registo da Rotação'!G123)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Registo da Rotação'!H123)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F123,'Listas de apoio'!$A$8='Registo da Rotação'!G123,'Listas de apoio'!$A$8='Registo da Rotação'!H123),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Registo da Rotação'!G123)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Registo da Rotação'!H123)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U65" s="8">
-        <f>IF('Registo da Rotação'!A114="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A114)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C114,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D114)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A123="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A123)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C123,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D123)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V65" s="1"/>
@@ -13597,31 +14057,31 @@
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
       <c r="O66" s="8">
-        <f>IF('Registo da Rotação'!A115="",0,IF(COUNTA('Registo da Rotação'!B115:K115)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A124="",0,IF(COUNTA('Registo da Rotação'!B124:K124)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P66" s="8">
-        <f>IF('Registo da Rotação'!A115="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C115)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A124="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C124)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q66" s="8">
-        <f>IF('Registo da Rotação'!A115="",0,IF(OR('Registo da Rotação'!F115='Registo da Rotação'!G115,'Registo da Rotação'!F115='Registo da Rotação'!H115,'Registo da Rotação'!G115='Registo da Rotação'!H115),1,0))</f>
+        <f>IF('Registo da Rotação'!A124="",0,IF(OR('Registo da Rotação'!F124='Registo da Rotação'!G124,'Registo da Rotação'!F124='Registo da Rotação'!H124,'Registo da Rotação'!G124='Registo da Rotação'!H124),1,0))</f>
         <v>0</v>
       </c>
       <c r="R66" s="8">
-        <f>IF('Registo da Rotação'!A115="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C115,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I115="Ainda não avaliado",'Registo da Rotação'!J115="Ainda não avaliado",'Registo da Rotação'!K115="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A124="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C124,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I124="Ainda não avaliado",'Registo da Rotação'!J124="Ainda não avaliado",'Registo da Rotação'!K124="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S66" s="8">
-        <f>IF('Registo da Rotação'!A115="",0,IF(AND('Registo da Rotação'!G115=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115),'Registo da Rotação'!$G$54:'Registo da Rotação'!G114),""),'Registo da Rotação'!H115=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115),'Registo da Rotação'!$H$54:'Registo da Rotação'!H114),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A124="",0,IF(AND('Registo da Rotação'!G124=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124),'Registo da Rotação'!$G$54:'Registo da Rotação'!G123),""),'Registo da Rotação'!H124=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124),'Registo da Rotação'!$H$54:'Registo da Rotação'!H123),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T66" s="8">
-        <f>IF('Registo da Rotação'!A115="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Registo da Rotação'!G115)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Registo da Rotação'!H115)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F115,'Listas de apoio'!$A$5='Registo da Rotação'!G115,'Listas de apoio'!$A$5='Registo da Rotação'!H115),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Registo da Rotação'!G115)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Registo da Rotação'!H115)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F115,'Listas de apoio'!$A$6='Registo da Rotação'!G115,'Listas de apoio'!$A$6='Registo da Rotação'!H115),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Registo da Rotação'!G115)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Registo da Rotação'!H115)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F115,'Listas de apoio'!$A$7='Registo da Rotação'!G115,'Listas de apoio'!$A$7='Registo da Rotação'!H115),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Registo da Rotação'!G115)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Registo da Rotação'!H115)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F115,'Listas de apoio'!$A$8='Registo da Rotação'!G115,'Listas de apoio'!$A$8='Registo da Rotação'!H115),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F114='Registo da Rotação'!F115)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Registo da Rotação'!G115)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Registo da Rotação'!H115)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F114)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G114='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H114='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A124="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Registo da Rotação'!G124)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Registo da Rotação'!H124)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F124,'Listas de apoio'!$A$5='Registo da Rotação'!G124,'Listas de apoio'!$A$5='Registo da Rotação'!H124),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Registo da Rotação'!G124)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Registo da Rotação'!H124)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F124,'Listas de apoio'!$A$6='Registo da Rotação'!G124,'Listas de apoio'!$A$6='Registo da Rotação'!H124),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Registo da Rotação'!G124)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Registo da Rotação'!H124)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F124,'Listas de apoio'!$A$7='Registo da Rotação'!G124,'Listas de apoio'!$A$7='Registo da Rotação'!H124),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Registo da Rotação'!G124)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Registo da Rotação'!H124)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F124,'Listas de apoio'!$A$8='Registo da Rotação'!G124,'Listas de apoio'!$A$8='Registo da Rotação'!H124),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Registo da Rotação'!G124)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Registo da Rotação'!H124)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U66" s="8">
-        <f>IF('Registo da Rotação'!A115="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A115)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C115,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D115)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A124="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A124)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C124,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D124)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V66" s="1"/>
@@ -13654,31 +14114,31 @@
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
       <c r="O67" s="8">
-        <f>IF('Registo da Rotação'!A116="",0,IF(COUNTA('Registo da Rotação'!B116:K116)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A125="",0,IF(COUNTA('Registo da Rotação'!B125:K125)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P67" s="8">
-        <f>IF('Registo da Rotação'!A116="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C116)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A125="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C125)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q67" s="8">
-        <f>IF('Registo da Rotação'!A116="",0,IF(OR('Registo da Rotação'!F116='Registo da Rotação'!G116,'Registo da Rotação'!F116='Registo da Rotação'!H116,'Registo da Rotação'!G116='Registo da Rotação'!H116),1,0))</f>
+        <f>IF('Registo da Rotação'!A125="",0,IF(OR('Registo da Rotação'!F125='Registo da Rotação'!G125,'Registo da Rotação'!F125='Registo da Rotação'!H125,'Registo da Rotação'!G125='Registo da Rotação'!H125),1,0))</f>
         <v>0</v>
       </c>
       <c r="R67" s="8">
-        <f>IF('Registo da Rotação'!A116="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C116,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I116="Ainda não avaliado",'Registo da Rotação'!J116="Ainda não avaliado",'Registo da Rotação'!K116="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A125="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C125,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I125="Ainda não avaliado",'Registo da Rotação'!J125="Ainda não avaliado",'Registo da Rotação'!K125="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S67" s="8">
-        <f>IF('Registo da Rotação'!A116="",0,IF(AND('Registo da Rotação'!G116=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116),'Registo da Rotação'!$G$54:'Registo da Rotação'!G115),""),'Registo da Rotação'!H116=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116),'Registo da Rotação'!$H$54:'Registo da Rotação'!H115),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A125="",0,IF(AND('Registo da Rotação'!G125=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125),'Registo da Rotação'!$G$54:'Registo da Rotação'!G124),""),'Registo da Rotação'!H125=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125),'Registo da Rotação'!$H$54:'Registo da Rotação'!H124),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T67" s="8">
-        <f>IF('Registo da Rotação'!A116="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Registo da Rotação'!G116)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Registo da Rotação'!H116)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F116,'Listas de apoio'!$A$5='Registo da Rotação'!G116,'Listas de apoio'!$A$5='Registo da Rotação'!H116),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Registo da Rotação'!G116)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Registo da Rotação'!H116)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F116,'Listas de apoio'!$A$6='Registo da Rotação'!G116,'Listas de apoio'!$A$6='Registo da Rotação'!H116),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Registo da Rotação'!G116)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Registo da Rotação'!H116)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F116,'Listas de apoio'!$A$7='Registo da Rotação'!G116,'Listas de apoio'!$A$7='Registo da Rotação'!H116),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Registo da Rotação'!G116)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Registo da Rotação'!H116)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F116,'Listas de apoio'!$A$8='Registo da Rotação'!G116,'Listas de apoio'!$A$8='Registo da Rotação'!H116),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F115='Registo da Rotação'!F116)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Registo da Rotação'!G116)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Registo da Rotação'!H116)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F115)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G115='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H115='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A125="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Registo da Rotação'!G125)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Registo da Rotação'!H125)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F125,'Listas de apoio'!$A$5='Registo da Rotação'!G125,'Listas de apoio'!$A$5='Registo da Rotação'!H125),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Registo da Rotação'!G125)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Registo da Rotação'!H125)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F125,'Listas de apoio'!$A$6='Registo da Rotação'!G125,'Listas de apoio'!$A$6='Registo da Rotação'!H125),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Registo da Rotação'!G125)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Registo da Rotação'!H125)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F125,'Listas de apoio'!$A$7='Registo da Rotação'!G125,'Listas de apoio'!$A$7='Registo da Rotação'!H125),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Registo da Rotação'!G125)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Registo da Rotação'!H125)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F125,'Listas de apoio'!$A$8='Registo da Rotação'!G125,'Listas de apoio'!$A$8='Registo da Rotação'!H125),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Registo da Rotação'!G125)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Registo da Rotação'!H125)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U67" s="8">
-        <f>IF('Registo da Rotação'!A116="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A116)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C116,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D116)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A125="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A125)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C125,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D125)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V67" s="1"/>
@@ -13711,31 +14171,31 @@
       <c r="M68" s="1"/>
       <c r="N68" s="1"/>
       <c r="O68" s="8">
-        <f>IF('Registo da Rotação'!A117="",0,IF(COUNTA('Registo da Rotação'!B117:K117)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A126="",0,IF(COUNTA('Registo da Rotação'!B126:K126)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P68" s="8">
-        <f>IF('Registo da Rotação'!A117="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C117)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A126="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C126)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q68" s="8">
-        <f>IF('Registo da Rotação'!A117="",0,IF(OR('Registo da Rotação'!F117='Registo da Rotação'!G117,'Registo da Rotação'!F117='Registo da Rotação'!H117,'Registo da Rotação'!G117='Registo da Rotação'!H117),1,0))</f>
+        <f>IF('Registo da Rotação'!A126="",0,IF(OR('Registo da Rotação'!F126='Registo da Rotação'!G126,'Registo da Rotação'!F126='Registo da Rotação'!H126,'Registo da Rotação'!G126='Registo da Rotação'!H126),1,0))</f>
         <v>0</v>
       </c>
       <c r="R68" s="8">
-        <f>IF('Registo da Rotação'!A117="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C117,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I117="Ainda não avaliado",'Registo da Rotação'!J117="Ainda não avaliado",'Registo da Rotação'!K117="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A126="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C126,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I126="Ainda não avaliado",'Registo da Rotação'!J126="Ainda não avaliado",'Registo da Rotação'!K126="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S68" s="8">
-        <f>IF('Registo da Rotação'!A117="",0,IF(AND('Registo da Rotação'!G117=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117),'Registo da Rotação'!$G$54:'Registo da Rotação'!G116),""),'Registo da Rotação'!H117=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117),'Registo da Rotação'!$H$54:'Registo da Rotação'!H116),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A126="",0,IF(AND('Registo da Rotação'!G126=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126),'Registo da Rotação'!$G$54:'Registo da Rotação'!G125),""),'Registo da Rotação'!H126=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126),'Registo da Rotação'!$H$54:'Registo da Rotação'!H125),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T68" s="8">
-        <f>IF('Registo da Rotação'!A117="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Registo da Rotação'!G117)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Registo da Rotação'!H117)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F117,'Listas de apoio'!$A$5='Registo da Rotação'!G117,'Listas de apoio'!$A$5='Registo da Rotação'!H117),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Registo da Rotação'!G117)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Registo da Rotação'!H117)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F117,'Listas de apoio'!$A$6='Registo da Rotação'!G117,'Listas de apoio'!$A$6='Registo da Rotação'!H117),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Registo da Rotação'!G117)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Registo da Rotação'!H117)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F117,'Listas de apoio'!$A$7='Registo da Rotação'!G117,'Listas de apoio'!$A$7='Registo da Rotação'!H117),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Registo da Rotação'!G117)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Registo da Rotação'!H117)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F117,'Listas de apoio'!$A$8='Registo da Rotação'!G117,'Listas de apoio'!$A$8='Registo da Rotação'!H117),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F116='Registo da Rotação'!F117)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Registo da Rotação'!G117)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Registo da Rotação'!H117)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F116)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G116='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H116='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A126="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Registo da Rotação'!G126)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Registo da Rotação'!H126)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F126,'Listas de apoio'!$A$5='Registo da Rotação'!G126,'Listas de apoio'!$A$5='Registo da Rotação'!H126),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Registo da Rotação'!G126)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Registo da Rotação'!H126)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F126,'Listas de apoio'!$A$6='Registo da Rotação'!G126,'Listas de apoio'!$A$6='Registo da Rotação'!H126),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Registo da Rotação'!G126)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Registo da Rotação'!H126)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F126,'Listas de apoio'!$A$7='Registo da Rotação'!G126,'Listas de apoio'!$A$7='Registo da Rotação'!H126),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Registo da Rotação'!G126)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Registo da Rotação'!H126)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F126,'Listas de apoio'!$A$8='Registo da Rotação'!G126,'Listas de apoio'!$A$8='Registo da Rotação'!H126),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Registo da Rotação'!G126)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Registo da Rotação'!H126)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U68" s="8">
-        <f>IF('Registo da Rotação'!A117="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A117)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C117,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D117)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A126="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A126)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C126,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D126)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V68" s="1"/>
@@ -13768,31 +14228,31 @@
       <c r="M69" s="1"/>
       <c r="N69" s="1"/>
       <c r="O69" s="8">
-        <f>IF('Registo da Rotação'!A118="",0,IF(COUNTA('Registo da Rotação'!B118:K118)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A127="",0,IF(COUNTA('Registo da Rotação'!B127:K127)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P69" s="8">
-        <f>IF('Registo da Rotação'!A118="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C118)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A127="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C127)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q69" s="8">
-        <f>IF('Registo da Rotação'!A118="",0,IF(OR('Registo da Rotação'!F118='Registo da Rotação'!G118,'Registo da Rotação'!F118='Registo da Rotação'!H118,'Registo da Rotação'!G118='Registo da Rotação'!H118),1,0))</f>
+        <f>IF('Registo da Rotação'!A127="",0,IF(OR('Registo da Rotação'!F127='Registo da Rotação'!G127,'Registo da Rotação'!F127='Registo da Rotação'!H127,'Registo da Rotação'!G127='Registo da Rotação'!H127),1,0))</f>
         <v>0</v>
       </c>
       <c r="R69" s="8">
-        <f>IF('Registo da Rotação'!A118="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C118,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I118="Ainda não avaliado",'Registo da Rotação'!J118="Ainda não avaliado",'Registo da Rotação'!K118="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A127="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C127,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I127="Ainda não avaliado",'Registo da Rotação'!J127="Ainda não avaliado",'Registo da Rotação'!K127="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S69" s="8">
-        <f>IF('Registo da Rotação'!A118="",0,IF(AND('Registo da Rotação'!G118=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118),'Registo da Rotação'!$G$54:'Registo da Rotação'!G117),""),'Registo da Rotação'!H118=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118),'Registo da Rotação'!$H$54:'Registo da Rotação'!H117),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A127="",0,IF(AND('Registo da Rotação'!G127=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127),'Registo da Rotação'!$G$54:'Registo da Rotação'!G126),""),'Registo da Rotação'!H127=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127),'Registo da Rotação'!$H$54:'Registo da Rotação'!H126),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T69" s="8">
-        <f>IF('Registo da Rotação'!A118="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Registo da Rotação'!G118)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Registo da Rotação'!H118)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F118,'Listas de apoio'!$A$5='Registo da Rotação'!G118,'Listas de apoio'!$A$5='Registo da Rotação'!H118),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Registo da Rotação'!G118)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Registo da Rotação'!H118)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F118,'Listas de apoio'!$A$6='Registo da Rotação'!G118,'Listas de apoio'!$A$6='Registo da Rotação'!H118),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Registo da Rotação'!G118)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Registo da Rotação'!H118)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F118,'Listas de apoio'!$A$7='Registo da Rotação'!G118,'Listas de apoio'!$A$7='Registo da Rotação'!H118),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Registo da Rotação'!G118)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Registo da Rotação'!H118)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F118,'Listas de apoio'!$A$8='Registo da Rotação'!G118,'Listas de apoio'!$A$8='Registo da Rotação'!H118),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F117='Registo da Rotação'!F118)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Registo da Rotação'!G118)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Registo da Rotação'!H118)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F117)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G117='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H117='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A127="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Registo da Rotação'!G127)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Registo da Rotação'!H127)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F127,'Listas de apoio'!$A$5='Registo da Rotação'!G127,'Listas de apoio'!$A$5='Registo da Rotação'!H127),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Registo da Rotação'!G127)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Registo da Rotação'!H127)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F127,'Listas de apoio'!$A$6='Registo da Rotação'!G127,'Listas de apoio'!$A$6='Registo da Rotação'!H127),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Registo da Rotação'!G127)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Registo da Rotação'!H127)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F127,'Listas de apoio'!$A$7='Registo da Rotação'!G127,'Listas de apoio'!$A$7='Registo da Rotação'!H127),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Registo da Rotação'!G127)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Registo da Rotação'!H127)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F127,'Listas de apoio'!$A$8='Registo da Rotação'!G127,'Listas de apoio'!$A$8='Registo da Rotação'!H127),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Registo da Rotação'!G127)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Registo da Rotação'!H127)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U69" s="8">
-        <f>IF('Registo da Rotação'!A118="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A118)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C118,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D118)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A127="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A127)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C127,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D127)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V69" s="1"/>
@@ -13825,31 +14285,31 @@
       <c r="M70" s="1"/>
       <c r="N70" s="1"/>
       <c r="O70" s="8">
-        <f>IF('Registo da Rotação'!A119="",0,IF(COUNTA('Registo da Rotação'!B119:K119)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A128="",0,IF(COUNTA('Registo da Rotação'!B128:K128)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P70" s="8">
-        <f>IF('Registo da Rotação'!A119="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C119)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A128="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C128)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q70" s="8">
-        <f>IF('Registo da Rotação'!A119="",0,IF(OR('Registo da Rotação'!F119='Registo da Rotação'!G119,'Registo da Rotação'!F119='Registo da Rotação'!H119,'Registo da Rotação'!G119='Registo da Rotação'!H119),1,0))</f>
+        <f>IF('Registo da Rotação'!A128="",0,IF(OR('Registo da Rotação'!F128='Registo da Rotação'!G128,'Registo da Rotação'!F128='Registo da Rotação'!H128,'Registo da Rotação'!G128='Registo da Rotação'!H128),1,0))</f>
         <v>0</v>
       </c>
       <c r="R70" s="8">
-        <f>IF('Registo da Rotação'!A119="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C119,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I119="Ainda não avaliado",'Registo da Rotação'!J119="Ainda não avaliado",'Registo da Rotação'!K119="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A128="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C128,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I128="Ainda não avaliado",'Registo da Rotação'!J128="Ainda não avaliado",'Registo da Rotação'!K128="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S70" s="8">
-        <f>IF('Registo da Rotação'!A119="",0,IF(AND('Registo da Rotação'!G119=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119),'Registo da Rotação'!$G$54:'Registo da Rotação'!G118),""),'Registo da Rotação'!H119=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119),'Registo da Rotação'!$H$54:'Registo da Rotação'!H118),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A128="",0,IF(AND('Registo da Rotação'!G128=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128),'Registo da Rotação'!$G$54:'Registo da Rotação'!G127),""),'Registo da Rotação'!H128=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128),'Registo da Rotação'!$H$54:'Registo da Rotação'!H127),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T70" s="8">
-        <f>IF('Registo da Rotação'!A119="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Registo da Rotação'!G119)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Registo da Rotação'!H119)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F119,'Listas de apoio'!$A$5='Registo da Rotação'!G119,'Listas de apoio'!$A$5='Registo da Rotação'!H119),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Registo da Rotação'!G119)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Registo da Rotação'!H119)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F119,'Listas de apoio'!$A$6='Registo da Rotação'!G119,'Listas de apoio'!$A$6='Registo da Rotação'!H119),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Registo da Rotação'!G119)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Registo da Rotação'!H119)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F119,'Listas de apoio'!$A$7='Registo da Rotação'!G119,'Listas de apoio'!$A$7='Registo da Rotação'!H119),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Registo da Rotação'!G119)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Registo da Rotação'!H119)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F119,'Listas de apoio'!$A$8='Registo da Rotação'!G119,'Listas de apoio'!$A$8='Registo da Rotação'!H119),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F118='Registo da Rotação'!F119)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Registo da Rotação'!G119)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Registo da Rotação'!H119)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F118)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G118='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H118='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A128="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Registo da Rotação'!G128)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Registo da Rotação'!H128)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F128,'Listas de apoio'!$A$5='Registo da Rotação'!G128,'Listas de apoio'!$A$5='Registo da Rotação'!H128),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Registo da Rotação'!G128)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Registo da Rotação'!H128)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F128,'Listas de apoio'!$A$6='Registo da Rotação'!G128,'Listas de apoio'!$A$6='Registo da Rotação'!H128),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Registo da Rotação'!G128)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Registo da Rotação'!H128)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F128,'Listas de apoio'!$A$7='Registo da Rotação'!G128,'Listas de apoio'!$A$7='Registo da Rotação'!H128),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Registo da Rotação'!G128)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Registo da Rotação'!H128)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F128,'Listas de apoio'!$A$8='Registo da Rotação'!G128,'Listas de apoio'!$A$8='Registo da Rotação'!H128),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Registo da Rotação'!G128)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Registo da Rotação'!H128)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U70" s="8">
-        <f>IF('Registo da Rotação'!A119="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A119)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C119,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D119)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A128="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A128)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C128,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D128)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V70" s="1"/>
@@ -13882,31 +14342,31 @@
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
       <c r="O71" s="8">
-        <f>IF('Registo da Rotação'!A120="",0,IF(COUNTA('Registo da Rotação'!B120:K120)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A129="",0,IF(COUNTA('Registo da Rotação'!B129:K129)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P71" s="8">
-        <f>IF('Registo da Rotação'!A120="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C120)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A129="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C129)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q71" s="8">
-        <f>IF('Registo da Rotação'!A120="",0,IF(OR('Registo da Rotação'!F120='Registo da Rotação'!G120,'Registo da Rotação'!F120='Registo da Rotação'!H120,'Registo da Rotação'!G120='Registo da Rotação'!H120),1,0))</f>
+        <f>IF('Registo da Rotação'!A129="",0,IF(OR('Registo da Rotação'!F129='Registo da Rotação'!G129,'Registo da Rotação'!F129='Registo da Rotação'!H129,'Registo da Rotação'!G129='Registo da Rotação'!H129),1,0))</f>
         <v>0</v>
       </c>
       <c r="R71" s="8">
-        <f>IF('Registo da Rotação'!A120="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C120,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I120="Ainda não avaliado",'Registo da Rotação'!J120="Ainda não avaliado",'Registo da Rotação'!K120="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A129="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C129,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I129="Ainda não avaliado",'Registo da Rotação'!J129="Ainda não avaliado",'Registo da Rotação'!K129="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S71" s="8">
-        <f>IF('Registo da Rotação'!A120="",0,IF(AND('Registo da Rotação'!G120=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120),'Registo da Rotação'!$G$54:'Registo da Rotação'!G119),""),'Registo da Rotação'!H120=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120),'Registo da Rotação'!$H$54:'Registo da Rotação'!H119),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A129="",0,IF(AND('Registo da Rotação'!G129=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129),'Registo da Rotação'!$G$54:'Registo da Rotação'!G128),""),'Registo da Rotação'!H129=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129),'Registo da Rotação'!$H$54:'Registo da Rotação'!H128),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T71" s="8">
-        <f>IF('Registo da Rotação'!A120="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Registo da Rotação'!G120)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Registo da Rotação'!H120)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F120,'Listas de apoio'!$A$5='Registo da Rotação'!G120,'Listas de apoio'!$A$5='Registo da Rotação'!H120),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Registo da Rotação'!G120)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Registo da Rotação'!H120)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F120,'Listas de apoio'!$A$6='Registo da Rotação'!G120,'Listas de apoio'!$A$6='Registo da Rotação'!H120),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Registo da Rotação'!G120)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Registo da Rotação'!H120)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F120,'Listas de apoio'!$A$7='Registo da Rotação'!G120,'Listas de apoio'!$A$7='Registo da Rotação'!H120),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Registo da Rotação'!G120)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Registo da Rotação'!H120)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F120,'Listas de apoio'!$A$8='Registo da Rotação'!G120,'Listas de apoio'!$A$8='Registo da Rotação'!H120),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F119='Registo da Rotação'!F120)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Registo da Rotação'!G120)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Registo da Rotação'!H120)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F119)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G119='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H119='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A129="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Registo da Rotação'!G129)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Registo da Rotação'!H129)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F129,'Listas de apoio'!$A$5='Registo da Rotação'!G129,'Listas de apoio'!$A$5='Registo da Rotação'!H129),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Registo da Rotação'!G129)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Registo da Rotação'!H129)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F129,'Listas de apoio'!$A$6='Registo da Rotação'!G129,'Listas de apoio'!$A$6='Registo da Rotação'!H129),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Registo da Rotação'!G129)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Registo da Rotação'!H129)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F129,'Listas de apoio'!$A$7='Registo da Rotação'!G129,'Listas de apoio'!$A$7='Registo da Rotação'!H129),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Registo da Rotação'!G129)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Registo da Rotação'!H129)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F129,'Listas de apoio'!$A$8='Registo da Rotação'!G129,'Listas de apoio'!$A$8='Registo da Rotação'!H129),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Registo da Rotação'!G129)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Registo da Rotação'!H129)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U71" s="8">
-        <f>IF('Registo da Rotação'!A120="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A120)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C120,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D120)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A129="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A129)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C129,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D129)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V71" s="1"/>
@@ -13939,31 +14399,31 @@
       <c r="M72" s="1"/>
       <c r="N72" s="1"/>
       <c r="O72" s="8">
-        <f>IF('Registo da Rotação'!A121="",0,IF(COUNTA('Registo da Rotação'!B121:K121)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A130="",0,IF(COUNTA('Registo da Rotação'!B130:K130)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P72" s="8">
-        <f>IF('Registo da Rotação'!A121="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C121)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A130="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C130)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q72" s="8">
-        <f>IF('Registo da Rotação'!A121="",0,IF(OR('Registo da Rotação'!F121='Registo da Rotação'!G121,'Registo da Rotação'!F121='Registo da Rotação'!H121,'Registo da Rotação'!G121='Registo da Rotação'!H121),1,0))</f>
+        <f>IF('Registo da Rotação'!A130="",0,IF(OR('Registo da Rotação'!F130='Registo da Rotação'!G130,'Registo da Rotação'!F130='Registo da Rotação'!H130,'Registo da Rotação'!G130='Registo da Rotação'!H130),1,0))</f>
         <v>0</v>
       </c>
       <c r="R72" s="8">
-        <f>IF('Registo da Rotação'!A121="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C121,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I121="Ainda não avaliado",'Registo da Rotação'!J121="Ainda não avaliado",'Registo da Rotação'!K121="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A130="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C130,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I130="Ainda não avaliado",'Registo da Rotação'!J130="Ainda não avaliado",'Registo da Rotação'!K130="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S72" s="8">
-        <f>IF('Registo da Rotação'!A121="",0,IF(AND('Registo da Rotação'!G121=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121),'Registo da Rotação'!$G$54:'Registo da Rotação'!G120),""),'Registo da Rotação'!H121=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121),'Registo da Rotação'!$H$54:'Registo da Rotação'!H120),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A130="",0,IF(AND('Registo da Rotação'!G130=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130),'Registo da Rotação'!$G$54:'Registo da Rotação'!G129),""),'Registo da Rotação'!H130=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130),'Registo da Rotação'!$H$54:'Registo da Rotação'!H129),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T72" s="8">
-        <f>IF('Registo da Rotação'!A121="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Registo da Rotação'!G121)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Registo da Rotação'!H121)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F121,'Listas de apoio'!$A$5='Registo da Rotação'!G121,'Listas de apoio'!$A$5='Registo da Rotação'!H121),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Registo da Rotação'!G121)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Registo da Rotação'!H121)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F121,'Listas de apoio'!$A$6='Registo da Rotação'!G121,'Listas de apoio'!$A$6='Registo da Rotação'!H121),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Registo da Rotação'!G121)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Registo da Rotação'!H121)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F121,'Listas de apoio'!$A$7='Registo da Rotação'!G121,'Listas de apoio'!$A$7='Registo da Rotação'!H121),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Registo da Rotação'!G121)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Registo da Rotação'!H121)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F121,'Listas de apoio'!$A$8='Registo da Rotação'!G121,'Listas de apoio'!$A$8='Registo da Rotação'!H121),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F120='Registo da Rotação'!F121)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Registo da Rotação'!G121)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Registo da Rotação'!H121)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F120)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G120='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H120='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A130="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Registo da Rotação'!G130)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Registo da Rotação'!H130)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F130,'Listas de apoio'!$A$5='Registo da Rotação'!G130,'Listas de apoio'!$A$5='Registo da Rotação'!H130),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Registo da Rotação'!G130)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Registo da Rotação'!H130)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F130,'Listas de apoio'!$A$6='Registo da Rotação'!G130,'Listas de apoio'!$A$6='Registo da Rotação'!H130),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Registo da Rotação'!G130)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Registo da Rotação'!H130)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F130,'Listas de apoio'!$A$7='Registo da Rotação'!G130,'Listas de apoio'!$A$7='Registo da Rotação'!H130),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Registo da Rotação'!G130)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Registo da Rotação'!H130)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F130,'Listas de apoio'!$A$8='Registo da Rotação'!G130,'Listas de apoio'!$A$8='Registo da Rotação'!H130),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Registo da Rotação'!G130)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Registo da Rotação'!H130)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U72" s="8">
-        <f>IF('Registo da Rotação'!A121="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A121)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C121,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D121)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A130="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A130)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C130,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D130)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V72" s="1"/>
@@ -13996,31 +14456,31 @@
       <c r="M73" s="1"/>
       <c r="N73" s="1"/>
       <c r="O73" s="8">
-        <f>IF('Registo da Rotação'!A122="",0,IF(COUNTA('Registo da Rotação'!B122:K122)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A131="",0,IF(COUNTA('Registo da Rotação'!B131:K131)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P73" s="8">
-        <f>IF('Registo da Rotação'!A122="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C122)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A131="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C131)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q73" s="8">
-        <f>IF('Registo da Rotação'!A122="",0,IF(OR('Registo da Rotação'!F122='Registo da Rotação'!G122,'Registo da Rotação'!F122='Registo da Rotação'!H122,'Registo da Rotação'!G122='Registo da Rotação'!H122),1,0))</f>
+        <f>IF('Registo da Rotação'!A131="",0,IF(OR('Registo da Rotação'!F131='Registo da Rotação'!G131,'Registo da Rotação'!F131='Registo da Rotação'!H131,'Registo da Rotação'!G131='Registo da Rotação'!H131),1,0))</f>
         <v>0</v>
       </c>
       <c r="R73" s="8">
-        <f>IF('Registo da Rotação'!A122="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C122,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I122="Ainda não avaliado",'Registo da Rotação'!J122="Ainda não avaliado",'Registo da Rotação'!K122="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A131="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C131,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I131="Ainda não avaliado",'Registo da Rotação'!J131="Ainda não avaliado",'Registo da Rotação'!K131="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S73" s="8">
-        <f>IF('Registo da Rotação'!A122="",0,IF(AND('Registo da Rotação'!G122=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122),'Registo da Rotação'!$G$54:'Registo da Rotação'!G121),""),'Registo da Rotação'!H122=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122),'Registo da Rotação'!$H$54:'Registo da Rotação'!H121),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A131="",0,IF(AND('Registo da Rotação'!G131=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131),'Registo da Rotação'!$G$54:'Registo da Rotação'!G130),""),'Registo da Rotação'!H131=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131),'Registo da Rotação'!$H$54:'Registo da Rotação'!H130),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T73" s="8">
-        <f>IF('Registo da Rotação'!A122="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Registo da Rotação'!G122)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Registo da Rotação'!H122)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F122,'Listas de apoio'!$A$5='Registo da Rotação'!G122,'Listas de apoio'!$A$5='Registo da Rotação'!H122),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Registo da Rotação'!G122)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Registo da Rotação'!H122)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F122,'Listas de apoio'!$A$6='Registo da Rotação'!G122,'Listas de apoio'!$A$6='Registo da Rotação'!H122),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Registo da Rotação'!G122)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Registo da Rotação'!H122)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F122,'Listas de apoio'!$A$7='Registo da Rotação'!G122,'Listas de apoio'!$A$7='Registo da Rotação'!H122),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Registo da Rotação'!G122)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Registo da Rotação'!H122)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F122,'Listas de apoio'!$A$8='Registo da Rotação'!G122,'Listas de apoio'!$A$8='Registo da Rotação'!H122),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F121='Registo da Rotação'!F122)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Registo da Rotação'!G122)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Registo da Rotação'!H122)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F121)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G121='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H121='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A131="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Registo da Rotação'!G131)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Registo da Rotação'!H131)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F131,'Listas de apoio'!$A$5='Registo da Rotação'!G131,'Listas de apoio'!$A$5='Registo da Rotação'!H131),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Registo da Rotação'!G131)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Registo da Rotação'!H131)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F131,'Listas de apoio'!$A$6='Registo da Rotação'!G131,'Listas de apoio'!$A$6='Registo da Rotação'!H131),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Registo da Rotação'!G131)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Registo da Rotação'!H131)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F131,'Listas de apoio'!$A$7='Registo da Rotação'!G131,'Listas de apoio'!$A$7='Registo da Rotação'!H131),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Registo da Rotação'!G131)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Registo da Rotação'!H131)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F131,'Listas de apoio'!$A$8='Registo da Rotação'!G131,'Listas de apoio'!$A$8='Registo da Rotação'!H131),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Registo da Rotação'!G131)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Registo da Rotação'!H131)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U73" s="8">
-        <f>IF('Registo da Rotação'!A122="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A122)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C122,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D122)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A131="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A131)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C131,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D131)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V73" s="1"/>
@@ -14053,31 +14513,31 @@
       <c r="M74" s="1"/>
       <c r="N74" s="1"/>
       <c r="O74" s="8">
-        <f>IF('Registo da Rotação'!A123="",0,IF(COUNTA('Registo da Rotação'!B123:K123)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A132="",0,IF(COUNTA('Registo da Rotação'!B132:K132)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P74" s="8">
-        <f>IF('Registo da Rotação'!A123="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C123)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A132="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C132)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q74" s="8">
-        <f>IF('Registo da Rotação'!A123="",0,IF(OR('Registo da Rotação'!F123='Registo da Rotação'!G123,'Registo da Rotação'!F123='Registo da Rotação'!H123,'Registo da Rotação'!G123='Registo da Rotação'!H123),1,0))</f>
+        <f>IF('Registo da Rotação'!A132="",0,IF(OR('Registo da Rotação'!F132='Registo da Rotação'!G132,'Registo da Rotação'!F132='Registo da Rotação'!H132,'Registo da Rotação'!G132='Registo da Rotação'!H132),1,0))</f>
         <v>0</v>
       </c>
       <c r="R74" s="8">
-        <f>IF('Registo da Rotação'!A123="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C123,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I123="Ainda não avaliado",'Registo da Rotação'!J123="Ainda não avaliado",'Registo da Rotação'!K123="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A132="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C132,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I132="Ainda não avaliado",'Registo da Rotação'!J132="Ainda não avaliado",'Registo da Rotação'!K132="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S74" s="8">
-        <f>IF('Registo da Rotação'!A123="",0,IF(AND('Registo da Rotação'!G123=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123),'Registo da Rotação'!$G$54:'Registo da Rotação'!G122),""),'Registo da Rotação'!H123=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123),'Registo da Rotação'!$H$54:'Registo da Rotação'!H122),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A132="",0,IF(AND('Registo da Rotação'!G132=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132),'Registo da Rotação'!$G$54:'Registo da Rotação'!G131),""),'Registo da Rotação'!H132=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132),'Registo da Rotação'!$H$54:'Registo da Rotação'!H131),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T74" s="8">
-        <f>IF('Registo da Rotação'!A123="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Registo da Rotação'!G123)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Registo da Rotação'!H123)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F123,'Listas de apoio'!$A$5='Registo da Rotação'!G123,'Listas de apoio'!$A$5='Registo da Rotação'!H123),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Registo da Rotação'!G123)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Registo da Rotação'!H123)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F123,'Listas de apoio'!$A$6='Registo da Rotação'!G123,'Listas de apoio'!$A$6='Registo da Rotação'!H123),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Registo da Rotação'!G123)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Registo da Rotação'!H123)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F123,'Listas de apoio'!$A$7='Registo da Rotação'!G123,'Listas de apoio'!$A$7='Registo da Rotação'!H123),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Registo da Rotação'!G123)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Registo da Rotação'!H123)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F123,'Listas de apoio'!$A$8='Registo da Rotação'!G123,'Listas de apoio'!$A$8='Registo da Rotação'!H123),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F122='Registo da Rotação'!F123)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Registo da Rotação'!G123)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Registo da Rotação'!H123)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F122)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G122='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H122='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A132="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Registo da Rotação'!G132)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Registo da Rotação'!H132)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F132,'Listas de apoio'!$A$5='Registo da Rotação'!G132,'Listas de apoio'!$A$5='Registo da Rotação'!H132),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Registo da Rotação'!G132)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Registo da Rotação'!H132)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F132,'Listas de apoio'!$A$6='Registo da Rotação'!G132,'Listas de apoio'!$A$6='Registo da Rotação'!H132),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Registo da Rotação'!G132)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Registo da Rotação'!H132)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F132,'Listas de apoio'!$A$7='Registo da Rotação'!G132,'Listas de apoio'!$A$7='Registo da Rotação'!H132),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Registo da Rotação'!G132)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Registo da Rotação'!H132)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F132,'Listas de apoio'!$A$8='Registo da Rotação'!G132,'Listas de apoio'!$A$8='Registo da Rotação'!H132),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Registo da Rotação'!G132)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Registo da Rotação'!H132)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U74" s="8">
-        <f>IF('Registo da Rotação'!A123="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A123)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C123,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D123)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A132="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A132)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C132,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D132)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V74" s="1"/>
@@ -14110,31 +14570,31 @@
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
       <c r="O75" s="8">
-        <f>IF('Registo da Rotação'!A124="",0,IF(COUNTA('Registo da Rotação'!B124:K124)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A133="",0,IF(COUNTA('Registo da Rotação'!B133:K133)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P75" s="8">
-        <f>IF('Registo da Rotação'!A124="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C124)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A133="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C133)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q75" s="8">
-        <f>IF('Registo da Rotação'!A124="",0,IF(OR('Registo da Rotação'!F124='Registo da Rotação'!G124,'Registo da Rotação'!F124='Registo da Rotação'!H124,'Registo da Rotação'!G124='Registo da Rotação'!H124),1,0))</f>
+        <f>IF('Registo da Rotação'!A133="",0,IF(OR('Registo da Rotação'!F133='Registo da Rotação'!G133,'Registo da Rotação'!F133='Registo da Rotação'!H133,'Registo da Rotação'!G133='Registo da Rotação'!H133),1,0))</f>
         <v>0</v>
       </c>
       <c r="R75" s="8">
-        <f>IF('Registo da Rotação'!A124="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C124,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I124="Ainda não avaliado",'Registo da Rotação'!J124="Ainda não avaliado",'Registo da Rotação'!K124="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A133="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C133,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I133="Ainda não avaliado",'Registo da Rotação'!J133="Ainda não avaliado",'Registo da Rotação'!K133="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S75" s="8">
-        <f>IF('Registo da Rotação'!A124="",0,IF(AND('Registo da Rotação'!G124=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124),'Registo da Rotação'!$G$54:'Registo da Rotação'!G123),""),'Registo da Rotação'!H124=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124),'Registo da Rotação'!$H$54:'Registo da Rotação'!H123),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A133="",0,IF(AND('Registo da Rotação'!G133=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133),'Registo da Rotação'!$G$54:'Registo da Rotação'!G132),""),'Registo da Rotação'!H133=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133),'Registo da Rotação'!$H$54:'Registo da Rotação'!H132),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T75" s="8">
-        <f>IF('Registo da Rotação'!A124="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Registo da Rotação'!G124)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Registo da Rotação'!H124)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F124,'Listas de apoio'!$A$5='Registo da Rotação'!G124,'Listas de apoio'!$A$5='Registo da Rotação'!H124),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Registo da Rotação'!G124)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Registo da Rotação'!H124)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F124,'Listas de apoio'!$A$6='Registo da Rotação'!G124,'Listas de apoio'!$A$6='Registo da Rotação'!H124),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Registo da Rotação'!G124)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Registo da Rotação'!H124)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F124,'Listas de apoio'!$A$7='Registo da Rotação'!G124,'Listas de apoio'!$A$7='Registo da Rotação'!H124),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Registo da Rotação'!G124)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Registo da Rotação'!H124)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F124,'Listas de apoio'!$A$8='Registo da Rotação'!G124,'Listas de apoio'!$A$8='Registo da Rotação'!H124),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F123='Registo da Rotação'!F124)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Registo da Rotação'!G124)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Registo da Rotação'!H124)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F123)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G123='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H123='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A133="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Registo da Rotação'!G133)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Registo da Rotação'!H133)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F133,'Listas de apoio'!$A$5='Registo da Rotação'!G133,'Listas de apoio'!$A$5='Registo da Rotação'!H133),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Registo da Rotação'!G133)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Registo da Rotação'!H133)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F133,'Listas de apoio'!$A$6='Registo da Rotação'!G133,'Listas de apoio'!$A$6='Registo da Rotação'!H133),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Registo da Rotação'!G133)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Registo da Rotação'!H133)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F133,'Listas de apoio'!$A$7='Registo da Rotação'!G133,'Listas de apoio'!$A$7='Registo da Rotação'!H133),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Registo da Rotação'!G133)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Registo da Rotação'!H133)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F133,'Listas de apoio'!$A$8='Registo da Rotação'!G133,'Listas de apoio'!$A$8='Registo da Rotação'!H133),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Registo da Rotação'!G133)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Registo da Rotação'!H133)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U75" s="8">
-        <f>IF('Registo da Rotação'!A124="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A124)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C124,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D124)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A133="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A133)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C133,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D133)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V75" s="1"/>
@@ -14167,31 +14627,31 @@
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
       <c r="O76" s="8">
-        <f>IF('Registo da Rotação'!A125="",0,IF(COUNTA('Registo da Rotação'!B125:K125)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A134="",0,IF(COUNTA('Registo da Rotação'!B134:K134)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P76" s="8">
-        <f>IF('Registo da Rotação'!A125="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C125)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A134="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C134)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q76" s="8">
-        <f>IF('Registo da Rotação'!A125="",0,IF(OR('Registo da Rotação'!F125='Registo da Rotação'!G125,'Registo da Rotação'!F125='Registo da Rotação'!H125,'Registo da Rotação'!G125='Registo da Rotação'!H125),1,0))</f>
+        <f>IF('Registo da Rotação'!A134="",0,IF(OR('Registo da Rotação'!F134='Registo da Rotação'!G134,'Registo da Rotação'!F134='Registo da Rotação'!H134,'Registo da Rotação'!G134='Registo da Rotação'!H134),1,0))</f>
         <v>0</v>
       </c>
       <c r="R76" s="8">
-        <f>IF('Registo da Rotação'!A125="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C125,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I125="Ainda não avaliado",'Registo da Rotação'!J125="Ainda não avaliado",'Registo da Rotação'!K125="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A134="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C134,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I134="Ainda não avaliado",'Registo da Rotação'!J134="Ainda não avaliado",'Registo da Rotação'!K134="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S76" s="8">
-        <f>IF('Registo da Rotação'!A125="",0,IF(AND('Registo da Rotação'!G125=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125),'Registo da Rotação'!$G$54:'Registo da Rotação'!G124),""),'Registo da Rotação'!H125=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125),'Registo da Rotação'!$H$54:'Registo da Rotação'!H124),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A134="",0,IF(AND('Registo da Rotação'!G134=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134),'Registo da Rotação'!$G$54:'Registo da Rotação'!G133),""),'Registo da Rotação'!H134=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134),'Registo da Rotação'!$H$54:'Registo da Rotação'!H133),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T76" s="8">
-        <f>IF('Registo da Rotação'!A125="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Registo da Rotação'!G125)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Registo da Rotação'!H125)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F125,'Listas de apoio'!$A$5='Registo da Rotação'!G125,'Listas de apoio'!$A$5='Registo da Rotação'!H125),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Registo da Rotação'!G125)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Registo da Rotação'!H125)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F125,'Listas de apoio'!$A$6='Registo da Rotação'!G125,'Listas de apoio'!$A$6='Registo da Rotação'!H125),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Registo da Rotação'!G125)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Registo da Rotação'!H125)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F125,'Listas de apoio'!$A$7='Registo da Rotação'!G125,'Listas de apoio'!$A$7='Registo da Rotação'!H125),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Registo da Rotação'!G125)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Registo da Rotação'!H125)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F125,'Listas de apoio'!$A$8='Registo da Rotação'!G125,'Listas de apoio'!$A$8='Registo da Rotação'!H125),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F124='Registo da Rotação'!F125)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Registo da Rotação'!G125)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Registo da Rotação'!H125)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F124)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G124='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H124='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A134="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Registo da Rotação'!G134)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Registo da Rotação'!H134)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F134,'Listas de apoio'!$A$5='Registo da Rotação'!G134,'Listas de apoio'!$A$5='Registo da Rotação'!H134),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Registo da Rotação'!G134)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Registo da Rotação'!H134)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F134,'Listas de apoio'!$A$6='Registo da Rotação'!G134,'Listas de apoio'!$A$6='Registo da Rotação'!H134),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Registo da Rotação'!G134)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Registo da Rotação'!H134)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F134,'Listas de apoio'!$A$7='Registo da Rotação'!G134,'Listas de apoio'!$A$7='Registo da Rotação'!H134),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Registo da Rotação'!G134)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Registo da Rotação'!H134)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F134,'Listas de apoio'!$A$8='Registo da Rotação'!G134,'Listas de apoio'!$A$8='Registo da Rotação'!H134),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Registo da Rotação'!G134)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Registo da Rotação'!H134)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U76" s="8">
-        <f>IF('Registo da Rotação'!A125="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A125)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C125,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D125)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A134="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A134)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C134,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D134)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V76" s="1"/>
@@ -14224,31 +14684,31 @@
       <c r="M77" s="1"/>
       <c r="N77" s="1"/>
       <c r="O77" s="8">
-        <f>IF('Registo da Rotação'!A126="",0,IF(COUNTA('Registo da Rotação'!B126:K126)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A135="",0,IF(COUNTA('Registo da Rotação'!B135:K135)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P77" s="8">
-        <f>IF('Registo da Rotação'!A126="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C126)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A135="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C135)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q77" s="8">
-        <f>IF('Registo da Rotação'!A126="",0,IF(OR('Registo da Rotação'!F126='Registo da Rotação'!G126,'Registo da Rotação'!F126='Registo da Rotação'!H126,'Registo da Rotação'!G126='Registo da Rotação'!H126),1,0))</f>
+        <f>IF('Registo da Rotação'!A135="",0,IF(OR('Registo da Rotação'!F135='Registo da Rotação'!G135,'Registo da Rotação'!F135='Registo da Rotação'!H135,'Registo da Rotação'!G135='Registo da Rotação'!H135),1,0))</f>
         <v>0</v>
       </c>
       <c r="R77" s="8">
-        <f>IF('Registo da Rotação'!A126="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C126,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I126="Ainda não avaliado",'Registo da Rotação'!J126="Ainda não avaliado",'Registo da Rotação'!K126="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A135="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C135,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I135="Ainda não avaliado",'Registo da Rotação'!J135="Ainda não avaliado",'Registo da Rotação'!K135="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S77" s="8">
-        <f>IF('Registo da Rotação'!A126="",0,IF(AND('Registo da Rotação'!G126=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126),'Registo da Rotação'!$G$54:'Registo da Rotação'!G125),""),'Registo da Rotação'!H126=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126),'Registo da Rotação'!$H$54:'Registo da Rotação'!H125),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A135="",0,IF(AND('Registo da Rotação'!G135=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135),'Registo da Rotação'!$G$54:'Registo da Rotação'!G134),""),'Registo da Rotação'!H135=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135),'Registo da Rotação'!$H$54:'Registo da Rotação'!H134),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T77" s="8">
-        <f>IF('Registo da Rotação'!A126="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Registo da Rotação'!G126)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Registo da Rotação'!H126)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F126,'Listas de apoio'!$A$5='Registo da Rotação'!G126,'Listas de apoio'!$A$5='Registo da Rotação'!H126),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Registo da Rotação'!G126)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Registo da Rotação'!H126)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F126,'Listas de apoio'!$A$6='Registo da Rotação'!G126,'Listas de apoio'!$A$6='Registo da Rotação'!H126),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Registo da Rotação'!G126)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Registo da Rotação'!H126)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F126,'Listas de apoio'!$A$7='Registo da Rotação'!G126,'Listas de apoio'!$A$7='Registo da Rotação'!H126),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Registo da Rotação'!G126)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Registo da Rotação'!H126)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F126,'Listas de apoio'!$A$8='Registo da Rotação'!G126,'Listas de apoio'!$A$8='Registo da Rotação'!H126),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F125='Registo da Rotação'!F126)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Registo da Rotação'!G126)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Registo da Rotação'!H126)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F125)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G125='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H125='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A135="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Registo da Rotação'!G135)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Registo da Rotação'!H135)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F135,'Listas de apoio'!$A$5='Registo da Rotação'!G135,'Listas de apoio'!$A$5='Registo da Rotação'!H135),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Registo da Rotação'!G135)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Registo da Rotação'!H135)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F135,'Listas de apoio'!$A$6='Registo da Rotação'!G135,'Listas de apoio'!$A$6='Registo da Rotação'!H135),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Registo da Rotação'!G135)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Registo da Rotação'!H135)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F135,'Listas de apoio'!$A$7='Registo da Rotação'!G135,'Listas de apoio'!$A$7='Registo da Rotação'!H135),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Registo da Rotação'!G135)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Registo da Rotação'!H135)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F135,'Listas de apoio'!$A$8='Registo da Rotação'!G135,'Listas de apoio'!$A$8='Registo da Rotação'!H135),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Registo da Rotação'!G135)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Registo da Rotação'!H135)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U77" s="8">
-        <f>IF('Registo da Rotação'!A126="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A126)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C126,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D126)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A135="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A135)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C135,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D135)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V77" s="1"/>
@@ -14281,31 +14741,31 @@
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
       <c r="O78" s="8">
-        <f>IF('Registo da Rotação'!A127="",0,IF(COUNTA('Registo da Rotação'!B127:K127)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A136="",0,IF(COUNTA('Registo da Rotação'!B136:K136)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P78" s="8">
-        <f>IF('Registo da Rotação'!A127="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C127)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A136="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C136)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q78" s="8">
-        <f>IF('Registo da Rotação'!A127="",0,IF(OR('Registo da Rotação'!F127='Registo da Rotação'!G127,'Registo da Rotação'!F127='Registo da Rotação'!H127,'Registo da Rotação'!G127='Registo da Rotação'!H127),1,0))</f>
+        <f>IF('Registo da Rotação'!A136="",0,IF(OR('Registo da Rotação'!F136='Registo da Rotação'!G136,'Registo da Rotação'!F136='Registo da Rotação'!H136,'Registo da Rotação'!G136='Registo da Rotação'!H136),1,0))</f>
         <v>0</v>
       </c>
       <c r="R78" s="8">
-        <f>IF('Registo da Rotação'!A127="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C127,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I127="Ainda não avaliado",'Registo da Rotação'!J127="Ainda não avaliado",'Registo da Rotação'!K127="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A136="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C136,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I136="Ainda não avaliado",'Registo da Rotação'!J136="Ainda não avaliado",'Registo da Rotação'!K136="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S78" s="8">
-        <f>IF('Registo da Rotação'!A127="",0,IF(AND('Registo da Rotação'!G127=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127),'Registo da Rotação'!$G$54:'Registo da Rotação'!G126),""),'Registo da Rotação'!H127=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127),'Registo da Rotação'!$H$54:'Registo da Rotação'!H126),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A136="",0,IF(AND('Registo da Rotação'!G136=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136),'Registo da Rotação'!$G$54:'Registo da Rotação'!G135),""),'Registo da Rotação'!H136=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136),'Registo da Rotação'!$H$54:'Registo da Rotação'!H135),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T78" s="8">
-        <f>IF('Registo da Rotação'!A127="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Registo da Rotação'!G127)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Registo da Rotação'!H127)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F127,'Listas de apoio'!$A$5='Registo da Rotação'!G127,'Listas de apoio'!$A$5='Registo da Rotação'!H127),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Registo da Rotação'!G127)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Registo da Rotação'!H127)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F127,'Listas de apoio'!$A$6='Registo da Rotação'!G127,'Listas de apoio'!$A$6='Registo da Rotação'!H127),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Registo da Rotação'!G127)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Registo da Rotação'!H127)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F127,'Listas de apoio'!$A$7='Registo da Rotação'!G127,'Listas de apoio'!$A$7='Registo da Rotação'!H127),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Registo da Rotação'!G127)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Registo da Rotação'!H127)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F127,'Listas de apoio'!$A$8='Registo da Rotação'!G127,'Listas de apoio'!$A$8='Registo da Rotação'!H127),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F126='Registo da Rotação'!F127)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Registo da Rotação'!G127)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Registo da Rotação'!H127)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F126)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G126='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H126='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A136="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Registo da Rotação'!G136)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Registo da Rotação'!H136)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F136,'Listas de apoio'!$A$5='Registo da Rotação'!G136,'Listas de apoio'!$A$5='Registo da Rotação'!H136),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Registo da Rotação'!G136)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Registo da Rotação'!H136)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F136,'Listas de apoio'!$A$6='Registo da Rotação'!G136,'Listas de apoio'!$A$6='Registo da Rotação'!H136),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Registo da Rotação'!G136)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Registo da Rotação'!H136)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F136,'Listas de apoio'!$A$7='Registo da Rotação'!G136,'Listas de apoio'!$A$7='Registo da Rotação'!H136),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Registo da Rotação'!G136)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Registo da Rotação'!H136)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F136,'Listas de apoio'!$A$8='Registo da Rotação'!G136,'Listas de apoio'!$A$8='Registo da Rotação'!H136),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Registo da Rotação'!G136)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Registo da Rotação'!H136)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U78" s="8">
-        <f>IF('Registo da Rotação'!A127="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A127)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C127,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D127)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A136="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A136)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C136,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D136)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V78" s="1"/>
@@ -14338,31 +14798,31 @@
       <c r="M79" s="1"/>
       <c r="N79" s="1"/>
       <c r="O79" s="8">
-        <f>IF('Registo da Rotação'!A128="",0,IF(COUNTA('Registo da Rotação'!B128:K128)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A137="",0,IF(COUNTA('Registo da Rotação'!B137:K137)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P79" s="8">
-        <f>IF('Registo da Rotação'!A128="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C128)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A137="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C137)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q79" s="8">
-        <f>IF('Registo da Rotação'!A128="",0,IF(OR('Registo da Rotação'!F128='Registo da Rotação'!G128,'Registo da Rotação'!F128='Registo da Rotação'!H128,'Registo da Rotação'!G128='Registo da Rotação'!H128),1,0))</f>
+        <f>IF('Registo da Rotação'!A137="",0,IF(OR('Registo da Rotação'!F137='Registo da Rotação'!G137,'Registo da Rotação'!F137='Registo da Rotação'!H137,'Registo da Rotação'!G137='Registo da Rotação'!H137),1,0))</f>
         <v>0</v>
       </c>
       <c r="R79" s="8">
-        <f>IF('Registo da Rotação'!A128="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C128,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I128="Ainda não avaliado",'Registo da Rotação'!J128="Ainda não avaliado",'Registo da Rotação'!K128="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A137="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C137,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I137="Ainda não avaliado",'Registo da Rotação'!J137="Ainda não avaliado",'Registo da Rotação'!K137="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S79" s="8">
-        <f>IF('Registo da Rotação'!A128="",0,IF(AND('Registo da Rotação'!G128=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128),'Registo da Rotação'!$G$54:'Registo da Rotação'!G127),""),'Registo da Rotação'!H128=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128),'Registo da Rotação'!$H$54:'Registo da Rotação'!H127),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A137="",0,IF(AND('Registo da Rotação'!G137=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137),'Registo da Rotação'!$G$54:'Registo da Rotação'!G136),""),'Registo da Rotação'!H137=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137),'Registo da Rotação'!$H$54:'Registo da Rotação'!H136),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T79" s="8">
-        <f>IF('Registo da Rotação'!A128="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Registo da Rotação'!G128)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Registo da Rotação'!H128)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F128,'Listas de apoio'!$A$5='Registo da Rotação'!G128,'Listas de apoio'!$A$5='Registo da Rotação'!H128),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Registo da Rotação'!G128)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Registo da Rotação'!H128)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F128,'Listas de apoio'!$A$6='Registo da Rotação'!G128,'Listas de apoio'!$A$6='Registo da Rotação'!H128),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Registo da Rotação'!G128)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Registo da Rotação'!H128)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F128,'Listas de apoio'!$A$7='Registo da Rotação'!G128,'Listas de apoio'!$A$7='Registo da Rotação'!H128),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Registo da Rotação'!G128)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Registo da Rotação'!H128)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F128,'Listas de apoio'!$A$8='Registo da Rotação'!G128,'Listas de apoio'!$A$8='Registo da Rotação'!H128),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F127='Registo da Rotação'!F128)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Registo da Rotação'!G128)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Registo da Rotação'!H128)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F127)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G127='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H127='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A137="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Registo da Rotação'!G137)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Registo da Rotação'!H137)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F137,'Listas de apoio'!$A$5='Registo da Rotação'!G137,'Listas de apoio'!$A$5='Registo da Rotação'!H137),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Registo da Rotação'!G137)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Registo da Rotação'!H137)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F137,'Listas de apoio'!$A$6='Registo da Rotação'!G137,'Listas de apoio'!$A$6='Registo da Rotação'!H137),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Registo da Rotação'!G137)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Registo da Rotação'!H137)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F137,'Listas de apoio'!$A$7='Registo da Rotação'!G137,'Listas de apoio'!$A$7='Registo da Rotação'!H137),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Registo da Rotação'!G137)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Registo da Rotação'!H137)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F137,'Listas de apoio'!$A$8='Registo da Rotação'!G137,'Listas de apoio'!$A$8='Registo da Rotação'!H137),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Registo da Rotação'!G137)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Registo da Rotação'!H137)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U79" s="8">
-        <f>IF('Registo da Rotação'!A128="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A128)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C128,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D128)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A137="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A137)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C137,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D137)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V79" s="1"/>
@@ -14395,31 +14855,31 @@
       <c r="M80" s="1"/>
       <c r="N80" s="1"/>
       <c r="O80" s="8">
-        <f>IF('Registo da Rotação'!A129="",0,IF(COUNTA('Registo da Rotação'!B129:K129)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A138="",0,IF(COUNTA('Registo da Rotação'!B138:K138)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P80" s="8">
-        <f>IF('Registo da Rotação'!A129="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C129)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A138="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C138)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q80" s="8">
-        <f>IF('Registo da Rotação'!A129="",0,IF(OR('Registo da Rotação'!F129='Registo da Rotação'!G129,'Registo da Rotação'!F129='Registo da Rotação'!H129,'Registo da Rotação'!G129='Registo da Rotação'!H129),1,0))</f>
+        <f>IF('Registo da Rotação'!A138="",0,IF(OR('Registo da Rotação'!F138='Registo da Rotação'!G138,'Registo da Rotação'!F138='Registo da Rotação'!H138,'Registo da Rotação'!G138='Registo da Rotação'!H138),1,0))</f>
         <v>0</v>
       </c>
       <c r="R80" s="8">
-        <f>IF('Registo da Rotação'!A129="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C129,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I129="Ainda não avaliado",'Registo da Rotação'!J129="Ainda não avaliado",'Registo da Rotação'!K129="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A138="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C138,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I138="Ainda não avaliado",'Registo da Rotação'!J138="Ainda não avaliado",'Registo da Rotação'!K138="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S80" s="8">
-        <f>IF('Registo da Rotação'!A129="",0,IF(AND('Registo da Rotação'!G129=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129),'Registo da Rotação'!$G$54:'Registo da Rotação'!G128),""),'Registo da Rotação'!H129=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129),'Registo da Rotação'!$H$54:'Registo da Rotação'!H128),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A138="",0,IF(AND('Registo da Rotação'!G138=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138),'Registo da Rotação'!$G$54:'Registo da Rotação'!G137),""),'Registo da Rotação'!H138=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138),'Registo da Rotação'!$H$54:'Registo da Rotação'!H137),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T80" s="8">
-        <f>IF('Registo da Rotação'!A129="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Registo da Rotação'!G129)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Registo da Rotação'!H129)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F129,'Listas de apoio'!$A$5='Registo da Rotação'!G129,'Listas de apoio'!$A$5='Registo da Rotação'!H129),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Registo da Rotação'!G129)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Registo da Rotação'!H129)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F129,'Listas de apoio'!$A$6='Registo da Rotação'!G129,'Listas de apoio'!$A$6='Registo da Rotação'!H129),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Registo da Rotação'!G129)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Registo da Rotação'!H129)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F129,'Listas de apoio'!$A$7='Registo da Rotação'!G129,'Listas de apoio'!$A$7='Registo da Rotação'!H129),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Registo da Rotação'!G129)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Registo da Rotação'!H129)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F129,'Listas de apoio'!$A$8='Registo da Rotação'!G129,'Listas de apoio'!$A$8='Registo da Rotação'!H129),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F128='Registo da Rotação'!F129)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Registo da Rotação'!G129)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Registo da Rotação'!H129)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F128)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G128='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H128='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A138="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Registo da Rotação'!G138)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Registo da Rotação'!H138)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F138,'Listas de apoio'!$A$5='Registo da Rotação'!G138,'Listas de apoio'!$A$5='Registo da Rotação'!H138),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Registo da Rotação'!G138)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Registo da Rotação'!H138)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F138,'Listas de apoio'!$A$6='Registo da Rotação'!G138,'Listas de apoio'!$A$6='Registo da Rotação'!H138),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Registo da Rotação'!G138)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Registo da Rotação'!H138)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F138,'Listas de apoio'!$A$7='Registo da Rotação'!G138,'Listas de apoio'!$A$7='Registo da Rotação'!H138),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Registo da Rotação'!G138)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Registo da Rotação'!H138)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F138,'Listas de apoio'!$A$8='Registo da Rotação'!G138,'Listas de apoio'!$A$8='Registo da Rotação'!H138),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Registo da Rotação'!G138)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Registo da Rotação'!H138)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U80" s="8">
-        <f>IF('Registo da Rotação'!A129="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A129)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C129,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D129)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A138="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A138)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C138,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D138)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V80" s="1"/>
@@ -14452,31 +14912,31 @@
       <c r="M81" s="1"/>
       <c r="N81" s="1"/>
       <c r="O81" s="8">
-        <f>IF('Registo da Rotação'!A130="",0,IF(COUNTA('Registo da Rotação'!B130:K130)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A139="",0,IF(COUNTA('Registo da Rotação'!B139:K139)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P81" s="8">
-        <f>IF('Registo da Rotação'!A130="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C130)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A139="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C139)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q81" s="8">
-        <f>IF('Registo da Rotação'!A130="",0,IF(OR('Registo da Rotação'!F130='Registo da Rotação'!G130,'Registo da Rotação'!F130='Registo da Rotação'!H130,'Registo da Rotação'!G130='Registo da Rotação'!H130),1,0))</f>
+        <f>IF('Registo da Rotação'!A139="",0,IF(OR('Registo da Rotação'!F139='Registo da Rotação'!G139,'Registo da Rotação'!F139='Registo da Rotação'!H139,'Registo da Rotação'!G139='Registo da Rotação'!H139),1,0))</f>
         <v>0</v>
       </c>
       <c r="R81" s="8">
-        <f>IF('Registo da Rotação'!A130="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C130,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I130="Ainda não avaliado",'Registo da Rotação'!J130="Ainda não avaliado",'Registo da Rotação'!K130="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A139="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C139,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I139="Ainda não avaliado",'Registo da Rotação'!J139="Ainda não avaliado",'Registo da Rotação'!K139="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S81" s="8">
-        <f>IF('Registo da Rotação'!A130="",0,IF(AND('Registo da Rotação'!G130=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130),'Registo da Rotação'!$G$54:'Registo da Rotação'!G129),""),'Registo da Rotação'!H130=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130),'Registo da Rotação'!$H$54:'Registo da Rotação'!H129),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A139="",0,IF(AND('Registo da Rotação'!G139=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139),'Registo da Rotação'!$G$54:'Registo da Rotação'!G138),""),'Registo da Rotação'!H139=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139),'Registo da Rotação'!$H$54:'Registo da Rotação'!H138),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T81" s="8">
-        <f>IF('Registo da Rotação'!A130="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Registo da Rotação'!G130)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Registo da Rotação'!H130)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F130,'Listas de apoio'!$A$5='Registo da Rotação'!G130,'Listas de apoio'!$A$5='Registo da Rotação'!H130),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Registo da Rotação'!G130)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Registo da Rotação'!H130)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F130,'Listas de apoio'!$A$6='Registo da Rotação'!G130,'Listas de apoio'!$A$6='Registo da Rotação'!H130),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Registo da Rotação'!G130)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Registo da Rotação'!H130)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F130,'Listas de apoio'!$A$7='Registo da Rotação'!G130,'Listas de apoio'!$A$7='Registo da Rotação'!H130),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Registo da Rotação'!G130)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Registo da Rotação'!H130)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F130,'Listas de apoio'!$A$8='Registo da Rotação'!G130,'Listas de apoio'!$A$8='Registo da Rotação'!H130),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F129='Registo da Rotação'!F130)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Registo da Rotação'!G130)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Registo da Rotação'!H130)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F129)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G129='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H129='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A139="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Registo da Rotação'!G139)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Registo da Rotação'!H139)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F139,'Listas de apoio'!$A$5='Registo da Rotação'!G139,'Listas de apoio'!$A$5='Registo da Rotação'!H139),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Registo da Rotação'!G139)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Registo da Rotação'!H139)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F139,'Listas de apoio'!$A$6='Registo da Rotação'!G139,'Listas de apoio'!$A$6='Registo da Rotação'!H139),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Registo da Rotação'!G139)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Registo da Rotação'!H139)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F139,'Listas de apoio'!$A$7='Registo da Rotação'!G139,'Listas de apoio'!$A$7='Registo da Rotação'!H139),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Registo da Rotação'!G139)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Registo da Rotação'!H139)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F139,'Listas de apoio'!$A$8='Registo da Rotação'!G139,'Listas de apoio'!$A$8='Registo da Rotação'!H139),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Registo da Rotação'!G139)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Registo da Rotação'!H139)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U81" s="8">
-        <f>IF('Registo da Rotação'!A130="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A130)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C130,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D130)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A139="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A139)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C139,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D139)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V81" s="1"/>
@@ -14509,31 +14969,31 @@
       <c r="M82" s="1"/>
       <c r="N82" s="1"/>
       <c r="O82" s="8">
-        <f>IF('Registo da Rotação'!A131="",0,IF(COUNTA('Registo da Rotação'!B131:K131)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A140="",0,IF(COUNTA('Registo da Rotação'!B140:K140)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P82" s="8">
-        <f>IF('Registo da Rotação'!A131="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C131)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A140="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C140)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q82" s="8">
-        <f>IF('Registo da Rotação'!A131="",0,IF(OR('Registo da Rotação'!F131='Registo da Rotação'!G131,'Registo da Rotação'!F131='Registo da Rotação'!H131,'Registo da Rotação'!G131='Registo da Rotação'!H131),1,0))</f>
+        <f>IF('Registo da Rotação'!A140="",0,IF(OR('Registo da Rotação'!F140='Registo da Rotação'!G140,'Registo da Rotação'!F140='Registo da Rotação'!H140,'Registo da Rotação'!G140='Registo da Rotação'!H140),1,0))</f>
         <v>0</v>
       </c>
       <c r="R82" s="8">
-        <f>IF('Registo da Rotação'!A131="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C131,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I131="Ainda não avaliado",'Registo da Rotação'!J131="Ainda não avaliado",'Registo da Rotação'!K131="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A140="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C140,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I140="Ainda não avaliado",'Registo da Rotação'!J140="Ainda não avaliado",'Registo da Rotação'!K140="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S82" s="8">
-        <f>IF('Registo da Rotação'!A131="",0,IF(AND('Registo da Rotação'!G131=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131),'Registo da Rotação'!$G$54:'Registo da Rotação'!G130),""),'Registo da Rotação'!H131=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131),'Registo da Rotação'!$H$54:'Registo da Rotação'!H130),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A140="",0,IF(AND('Registo da Rotação'!G140=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140),'Registo da Rotação'!$G$54:'Registo da Rotação'!G139),""),'Registo da Rotação'!H140=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140),'Registo da Rotação'!$H$54:'Registo da Rotação'!H139),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T82" s="8">
-        <f>IF('Registo da Rotação'!A131="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Registo da Rotação'!G131)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Registo da Rotação'!H131)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F131,'Listas de apoio'!$A$5='Registo da Rotação'!G131,'Listas de apoio'!$A$5='Registo da Rotação'!H131),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Registo da Rotação'!G131)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Registo da Rotação'!H131)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F131,'Listas de apoio'!$A$6='Registo da Rotação'!G131,'Listas de apoio'!$A$6='Registo da Rotação'!H131),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Registo da Rotação'!G131)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Registo da Rotação'!H131)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F131,'Listas de apoio'!$A$7='Registo da Rotação'!G131,'Listas de apoio'!$A$7='Registo da Rotação'!H131),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Registo da Rotação'!G131)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Registo da Rotação'!H131)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F131,'Listas de apoio'!$A$8='Registo da Rotação'!G131,'Listas de apoio'!$A$8='Registo da Rotação'!H131),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F130='Registo da Rotação'!F131)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Registo da Rotação'!G131)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Registo da Rotação'!H131)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F130)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G130='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H130='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A140="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Registo da Rotação'!G140)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Registo da Rotação'!H140)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F140,'Listas de apoio'!$A$5='Registo da Rotação'!G140,'Listas de apoio'!$A$5='Registo da Rotação'!H140),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Registo da Rotação'!G140)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Registo da Rotação'!H140)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F140,'Listas de apoio'!$A$6='Registo da Rotação'!G140,'Listas de apoio'!$A$6='Registo da Rotação'!H140),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Registo da Rotação'!G140)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Registo da Rotação'!H140)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F140,'Listas de apoio'!$A$7='Registo da Rotação'!G140,'Listas de apoio'!$A$7='Registo da Rotação'!H140),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Registo da Rotação'!G140)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Registo da Rotação'!H140)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F140,'Listas de apoio'!$A$8='Registo da Rotação'!G140,'Listas de apoio'!$A$8='Registo da Rotação'!H140),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Registo da Rotação'!G140)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Registo da Rotação'!H140)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U82" s="8">
-        <f>IF('Registo da Rotação'!A131="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A131)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C131,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D131)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A140="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A140)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C140,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D140)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V82" s="1"/>
@@ -14566,31 +15026,31 @@
       <c r="M83" s="1"/>
       <c r="N83" s="1"/>
       <c r="O83" s="8">
-        <f>IF('Registo da Rotação'!A132="",0,IF(COUNTA('Registo da Rotação'!B132:K132)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A141="",0,IF(COUNTA('Registo da Rotação'!B141:K141)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P83" s="8">
-        <f>IF('Registo da Rotação'!A132="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C132)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A141="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C141)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q83" s="8">
-        <f>IF('Registo da Rotação'!A132="",0,IF(OR('Registo da Rotação'!F132='Registo da Rotação'!G132,'Registo da Rotação'!F132='Registo da Rotação'!H132,'Registo da Rotação'!G132='Registo da Rotação'!H132),1,0))</f>
+        <f>IF('Registo da Rotação'!A141="",0,IF(OR('Registo da Rotação'!F141='Registo da Rotação'!G141,'Registo da Rotação'!F141='Registo da Rotação'!H141,'Registo da Rotação'!G141='Registo da Rotação'!H141),1,0))</f>
         <v>0</v>
       </c>
       <c r="R83" s="8">
-        <f>IF('Registo da Rotação'!A132="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C132,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I132="Ainda não avaliado",'Registo da Rotação'!J132="Ainda não avaliado",'Registo da Rotação'!K132="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A141="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C141,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I141="Ainda não avaliado",'Registo da Rotação'!J141="Ainda não avaliado",'Registo da Rotação'!K141="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S83" s="8">
-        <f>IF('Registo da Rotação'!A132="",0,IF(AND('Registo da Rotação'!G132=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132),'Registo da Rotação'!$G$54:'Registo da Rotação'!G131),""),'Registo da Rotação'!H132=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132),'Registo da Rotação'!$H$54:'Registo da Rotação'!H131),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A141="",0,IF(AND('Registo da Rotação'!G141=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141),'Registo da Rotação'!$G$54:'Registo da Rotação'!G140),""),'Registo da Rotação'!H141=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141),'Registo da Rotação'!$H$54:'Registo da Rotação'!H140),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T83" s="8">
-        <f>IF('Registo da Rotação'!A132="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Registo da Rotação'!G132)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Registo da Rotação'!H132)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F132,'Listas de apoio'!$A$5='Registo da Rotação'!G132,'Listas de apoio'!$A$5='Registo da Rotação'!H132),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Registo da Rotação'!G132)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Registo da Rotação'!H132)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F132,'Listas de apoio'!$A$6='Registo da Rotação'!G132,'Listas de apoio'!$A$6='Registo da Rotação'!H132),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Registo da Rotação'!G132)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Registo da Rotação'!H132)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F132,'Listas de apoio'!$A$7='Registo da Rotação'!G132,'Listas de apoio'!$A$7='Registo da Rotação'!H132),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Registo da Rotação'!G132)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Registo da Rotação'!H132)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F132,'Listas de apoio'!$A$8='Registo da Rotação'!G132,'Listas de apoio'!$A$8='Registo da Rotação'!H132),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F131='Registo da Rotação'!F132)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Registo da Rotação'!G132)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Registo da Rotação'!H132)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F131)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G131='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H131='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A141="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Registo da Rotação'!G141)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Registo da Rotação'!H141)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F141,'Listas de apoio'!$A$5='Registo da Rotação'!G141,'Listas de apoio'!$A$5='Registo da Rotação'!H141),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Registo da Rotação'!G141)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Registo da Rotação'!H141)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F141,'Listas de apoio'!$A$6='Registo da Rotação'!G141,'Listas de apoio'!$A$6='Registo da Rotação'!H141),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Registo da Rotação'!G141)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Registo da Rotação'!H141)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F141,'Listas de apoio'!$A$7='Registo da Rotação'!G141,'Listas de apoio'!$A$7='Registo da Rotação'!H141),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Registo da Rotação'!G141)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Registo da Rotação'!H141)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F141,'Listas de apoio'!$A$8='Registo da Rotação'!G141,'Listas de apoio'!$A$8='Registo da Rotação'!H141),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Registo da Rotação'!G141)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Registo da Rotação'!H141)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U83" s="8">
-        <f>IF('Registo da Rotação'!A132="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A132)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C132,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D132)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A141="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A141)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C141,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D141)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V83" s="1"/>
@@ -14623,31 +15083,31 @@
       <c r="M84" s="1"/>
       <c r="N84" s="1"/>
       <c r="O84" s="8">
-        <f>IF('Registo da Rotação'!A133="",0,IF(COUNTA('Registo da Rotação'!B133:K133)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A142="",0,IF(COUNTA('Registo da Rotação'!B142:K142)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P84" s="8">
-        <f>IF('Registo da Rotação'!A133="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C133)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A142="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C142)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q84" s="8">
-        <f>IF('Registo da Rotação'!A133="",0,IF(OR('Registo da Rotação'!F133='Registo da Rotação'!G133,'Registo da Rotação'!F133='Registo da Rotação'!H133,'Registo da Rotação'!G133='Registo da Rotação'!H133),1,0))</f>
+        <f>IF('Registo da Rotação'!A142="",0,IF(OR('Registo da Rotação'!F142='Registo da Rotação'!G142,'Registo da Rotação'!F142='Registo da Rotação'!H142,'Registo da Rotação'!G142='Registo da Rotação'!H142),1,0))</f>
         <v>0</v>
       </c>
       <c r="R84" s="8">
-        <f>IF('Registo da Rotação'!A133="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C133,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I133="Ainda não avaliado",'Registo da Rotação'!J133="Ainda não avaliado",'Registo da Rotação'!K133="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A142="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C142,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I142="Ainda não avaliado",'Registo da Rotação'!J142="Ainda não avaliado",'Registo da Rotação'!K142="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S84" s="8">
-        <f>IF('Registo da Rotação'!A133="",0,IF(AND('Registo da Rotação'!G133=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133),'Registo da Rotação'!$G$54:'Registo da Rotação'!G132),""),'Registo da Rotação'!H133=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133),'Registo da Rotação'!$H$54:'Registo da Rotação'!H132),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A142="",0,IF(AND('Registo da Rotação'!G142=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142),'Registo da Rotação'!$G$54:'Registo da Rotação'!G141),""),'Registo da Rotação'!H142=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142),'Registo da Rotação'!$H$54:'Registo da Rotação'!H141),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T84" s="8">
-        <f>IF('Registo da Rotação'!A133="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Registo da Rotação'!G133)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Registo da Rotação'!H133)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F133,'Listas de apoio'!$A$5='Registo da Rotação'!G133,'Listas de apoio'!$A$5='Registo da Rotação'!H133),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Registo da Rotação'!G133)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Registo da Rotação'!H133)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F133,'Listas de apoio'!$A$6='Registo da Rotação'!G133,'Listas de apoio'!$A$6='Registo da Rotação'!H133),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Registo da Rotação'!G133)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Registo da Rotação'!H133)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F133,'Listas de apoio'!$A$7='Registo da Rotação'!G133,'Listas de apoio'!$A$7='Registo da Rotação'!H133),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Registo da Rotação'!G133)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Registo da Rotação'!H133)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F133,'Listas de apoio'!$A$8='Registo da Rotação'!G133,'Listas de apoio'!$A$8='Registo da Rotação'!H133),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F132='Registo da Rotação'!F133)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Registo da Rotação'!G133)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Registo da Rotação'!H133)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F132)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G132='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H132='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A142="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Registo da Rotação'!G142)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Registo da Rotação'!H142)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F142,'Listas de apoio'!$A$5='Registo da Rotação'!G142,'Listas de apoio'!$A$5='Registo da Rotação'!H142),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Registo da Rotação'!G142)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Registo da Rotação'!H142)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F142,'Listas de apoio'!$A$6='Registo da Rotação'!G142,'Listas de apoio'!$A$6='Registo da Rotação'!H142),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Registo da Rotação'!G142)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Registo da Rotação'!H142)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F142,'Listas de apoio'!$A$7='Registo da Rotação'!G142,'Listas de apoio'!$A$7='Registo da Rotação'!H142),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Registo da Rotação'!G142)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Registo da Rotação'!H142)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F142,'Listas de apoio'!$A$8='Registo da Rotação'!G142,'Listas de apoio'!$A$8='Registo da Rotação'!H142),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Registo da Rotação'!G142)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Registo da Rotação'!H142)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U84" s="8">
-        <f>IF('Registo da Rotação'!A133="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A133)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C133,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D133)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A142="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A142)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C142,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D142)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V84" s="1"/>
@@ -14680,31 +15140,31 @@
       <c r="M85" s="1"/>
       <c r="N85" s="1"/>
       <c r="O85" s="8">
-        <f>IF('Registo da Rotação'!A134="",0,IF(COUNTA('Registo da Rotação'!B134:K134)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A143="",0,IF(COUNTA('Registo da Rotação'!B143:K143)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P85" s="8">
-        <f>IF('Registo da Rotação'!A134="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C134)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A143="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C143)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q85" s="8">
-        <f>IF('Registo da Rotação'!A134="",0,IF(OR('Registo da Rotação'!F134='Registo da Rotação'!G134,'Registo da Rotação'!F134='Registo da Rotação'!H134,'Registo da Rotação'!G134='Registo da Rotação'!H134),1,0))</f>
+        <f>IF('Registo da Rotação'!A143="",0,IF(OR('Registo da Rotação'!F143='Registo da Rotação'!G143,'Registo da Rotação'!F143='Registo da Rotação'!H143,'Registo da Rotação'!G143='Registo da Rotação'!H143),1,0))</f>
         <v>0</v>
       </c>
       <c r="R85" s="8">
-        <f>IF('Registo da Rotação'!A134="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C134,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I134="Ainda não avaliado",'Registo da Rotação'!J134="Ainda não avaliado",'Registo da Rotação'!K134="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A143="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C143,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I143="Ainda não avaliado",'Registo da Rotação'!J143="Ainda não avaliado",'Registo da Rotação'!K143="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S85" s="8">
-        <f>IF('Registo da Rotação'!A134="",0,IF(AND('Registo da Rotação'!G134=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134),'Registo da Rotação'!$G$54:'Registo da Rotação'!G133),""),'Registo da Rotação'!H134=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134),'Registo da Rotação'!$H$54:'Registo da Rotação'!H133),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A143="",0,IF(AND('Registo da Rotação'!G143=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143),'Registo da Rotação'!$G$54:'Registo da Rotação'!G142),""),'Registo da Rotação'!H143=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143),'Registo da Rotação'!$H$54:'Registo da Rotação'!H142),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T85" s="8">
-        <f>IF('Registo da Rotação'!A134="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Registo da Rotação'!G134)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Registo da Rotação'!H134)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F134,'Listas de apoio'!$A$5='Registo da Rotação'!G134,'Listas de apoio'!$A$5='Registo da Rotação'!H134),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Registo da Rotação'!G134)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Registo da Rotação'!H134)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F134,'Listas de apoio'!$A$6='Registo da Rotação'!G134,'Listas de apoio'!$A$6='Registo da Rotação'!H134),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Registo da Rotação'!G134)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Registo da Rotação'!H134)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F134,'Listas de apoio'!$A$7='Registo da Rotação'!G134,'Listas de apoio'!$A$7='Registo da Rotação'!H134),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Registo da Rotação'!G134)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Registo da Rotação'!H134)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F134,'Listas de apoio'!$A$8='Registo da Rotação'!G134,'Listas de apoio'!$A$8='Registo da Rotação'!H134),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F133='Registo da Rotação'!F134)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Registo da Rotação'!G134)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Registo da Rotação'!H134)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F133)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G133='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H133='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A143="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Registo da Rotação'!G143)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Registo da Rotação'!H143)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F143,'Listas de apoio'!$A$5='Registo da Rotação'!G143,'Listas de apoio'!$A$5='Registo da Rotação'!H143),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Registo da Rotação'!G143)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Registo da Rotação'!H143)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F143,'Listas de apoio'!$A$6='Registo da Rotação'!G143,'Listas de apoio'!$A$6='Registo da Rotação'!H143),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Registo da Rotação'!G143)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Registo da Rotação'!H143)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F143,'Listas de apoio'!$A$7='Registo da Rotação'!G143,'Listas de apoio'!$A$7='Registo da Rotação'!H143),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Registo da Rotação'!G143)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Registo da Rotação'!H143)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F143,'Listas de apoio'!$A$8='Registo da Rotação'!G143,'Listas de apoio'!$A$8='Registo da Rotação'!H143),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Registo da Rotação'!G143)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Registo da Rotação'!H143)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U85" s="8">
-        <f>IF('Registo da Rotação'!A134="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A134)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C134,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D134)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A143="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A143)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C143,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D143)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V85" s="1"/>
@@ -14737,31 +15197,31 @@
       <c r="M86" s="1"/>
       <c r="N86" s="1"/>
       <c r="O86" s="8">
-        <f>IF('Registo da Rotação'!A135="",0,IF(COUNTA('Registo da Rotação'!B135:K135)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A144="",0,IF(COUNTA('Registo da Rotação'!B144:K144)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P86" s="8">
-        <f>IF('Registo da Rotação'!A135="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C135)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A144="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C144)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q86" s="8">
-        <f>IF('Registo da Rotação'!A135="",0,IF(OR('Registo da Rotação'!F135='Registo da Rotação'!G135,'Registo da Rotação'!F135='Registo da Rotação'!H135,'Registo da Rotação'!G135='Registo da Rotação'!H135),1,0))</f>
+        <f>IF('Registo da Rotação'!A144="",0,IF(OR('Registo da Rotação'!F144='Registo da Rotação'!G144,'Registo da Rotação'!F144='Registo da Rotação'!H144,'Registo da Rotação'!G144='Registo da Rotação'!H144),1,0))</f>
         <v>0</v>
       </c>
       <c r="R86" s="8">
-        <f>IF('Registo da Rotação'!A135="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C135,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I135="Ainda não avaliado",'Registo da Rotação'!J135="Ainda não avaliado",'Registo da Rotação'!K135="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A144="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C144,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I144="Ainda não avaliado",'Registo da Rotação'!J144="Ainda não avaliado",'Registo da Rotação'!K144="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S86" s="8">
-        <f>IF('Registo da Rotação'!A135="",0,IF(AND('Registo da Rotação'!G135=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135),'Registo da Rotação'!$G$54:'Registo da Rotação'!G134),""),'Registo da Rotação'!H135=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135),'Registo da Rotação'!$H$54:'Registo da Rotação'!H134),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A144="",0,IF(AND('Registo da Rotação'!G144=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144),'Registo da Rotação'!$G$54:'Registo da Rotação'!G143),""),'Registo da Rotação'!H144=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144),'Registo da Rotação'!$H$54:'Registo da Rotação'!H143),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T86" s="8">
-        <f>IF('Registo da Rotação'!A135="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Registo da Rotação'!G135)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Registo da Rotação'!H135)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F135,'Listas de apoio'!$A$5='Registo da Rotação'!G135,'Listas de apoio'!$A$5='Registo da Rotação'!H135),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Registo da Rotação'!G135)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Registo da Rotação'!H135)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F135,'Listas de apoio'!$A$6='Registo da Rotação'!G135,'Listas de apoio'!$A$6='Registo da Rotação'!H135),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Registo da Rotação'!G135)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Registo da Rotação'!H135)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F135,'Listas de apoio'!$A$7='Registo da Rotação'!G135,'Listas de apoio'!$A$7='Registo da Rotação'!H135),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Registo da Rotação'!G135)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Registo da Rotação'!H135)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F135,'Listas de apoio'!$A$8='Registo da Rotação'!G135,'Listas de apoio'!$A$8='Registo da Rotação'!H135),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F134='Registo da Rotação'!F135)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Registo da Rotação'!G135)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Registo da Rotação'!H135)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F134)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G134='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H134='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A144="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Registo da Rotação'!G144)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Registo da Rotação'!H144)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F144,'Listas de apoio'!$A$5='Registo da Rotação'!G144,'Listas de apoio'!$A$5='Registo da Rotação'!H144),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Registo da Rotação'!G144)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Registo da Rotação'!H144)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F144,'Listas de apoio'!$A$6='Registo da Rotação'!G144,'Listas de apoio'!$A$6='Registo da Rotação'!H144),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Registo da Rotação'!G144)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Registo da Rotação'!H144)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F144,'Listas de apoio'!$A$7='Registo da Rotação'!G144,'Listas de apoio'!$A$7='Registo da Rotação'!H144),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Registo da Rotação'!G144)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Registo da Rotação'!H144)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F144,'Listas de apoio'!$A$8='Registo da Rotação'!G144,'Listas de apoio'!$A$8='Registo da Rotação'!H144),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Registo da Rotação'!G144)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Registo da Rotação'!H144)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U86" s="8">
-        <f>IF('Registo da Rotação'!A135="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A135)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C135,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D135)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A144="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A144)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C144,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D144)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V86" s="1"/>
@@ -14794,31 +15254,31 @@
       <c r="M87" s="1"/>
       <c r="N87" s="1"/>
       <c r="O87" s="8">
-        <f>IF('Registo da Rotação'!A136="",0,IF(COUNTA('Registo da Rotação'!B136:K136)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A145="",0,IF(COUNTA('Registo da Rotação'!B145:K145)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P87" s="8">
-        <f>IF('Registo da Rotação'!A136="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C136)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A145="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C145)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q87" s="8">
-        <f>IF('Registo da Rotação'!A136="",0,IF(OR('Registo da Rotação'!F136='Registo da Rotação'!G136,'Registo da Rotação'!F136='Registo da Rotação'!H136,'Registo da Rotação'!G136='Registo da Rotação'!H136),1,0))</f>
+        <f>IF('Registo da Rotação'!A145="",0,IF(OR('Registo da Rotação'!F145='Registo da Rotação'!G145,'Registo da Rotação'!F145='Registo da Rotação'!H145,'Registo da Rotação'!G145='Registo da Rotação'!H145),1,0))</f>
         <v>0</v>
       </c>
       <c r="R87" s="8">
-        <f>IF('Registo da Rotação'!A136="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C136,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I136="Ainda não avaliado",'Registo da Rotação'!J136="Ainda não avaliado",'Registo da Rotação'!K136="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A145="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C145,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I145="Ainda não avaliado",'Registo da Rotação'!J145="Ainda não avaliado",'Registo da Rotação'!K145="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S87" s="8">
-        <f>IF('Registo da Rotação'!A136="",0,IF(AND('Registo da Rotação'!G136=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136),'Registo da Rotação'!$G$54:'Registo da Rotação'!G135),""),'Registo da Rotação'!H136=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136),'Registo da Rotação'!$H$54:'Registo da Rotação'!H135),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A145="",0,IF(AND('Registo da Rotação'!G145=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145),'Registo da Rotação'!$G$54:'Registo da Rotação'!G144),""),'Registo da Rotação'!H145=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145),'Registo da Rotação'!$H$54:'Registo da Rotação'!H144),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T87" s="8">
-        <f>IF('Registo da Rotação'!A136="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Registo da Rotação'!G136)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Registo da Rotação'!H136)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F136,'Listas de apoio'!$A$5='Registo da Rotação'!G136,'Listas de apoio'!$A$5='Registo da Rotação'!H136),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Registo da Rotação'!G136)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Registo da Rotação'!H136)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F136,'Listas de apoio'!$A$6='Registo da Rotação'!G136,'Listas de apoio'!$A$6='Registo da Rotação'!H136),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Registo da Rotação'!G136)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Registo da Rotação'!H136)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F136,'Listas de apoio'!$A$7='Registo da Rotação'!G136,'Listas de apoio'!$A$7='Registo da Rotação'!H136),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Registo da Rotação'!G136)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Registo da Rotação'!H136)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F136,'Listas de apoio'!$A$8='Registo da Rotação'!G136,'Listas de apoio'!$A$8='Registo da Rotação'!H136),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F135='Registo da Rotação'!F136)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Registo da Rotação'!G136)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Registo da Rotação'!H136)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F135)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G135='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H135='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A145="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Registo da Rotação'!G145)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Registo da Rotação'!H145)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F145,'Listas de apoio'!$A$5='Registo da Rotação'!G145,'Listas de apoio'!$A$5='Registo da Rotação'!H145),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Registo da Rotação'!G145)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Registo da Rotação'!H145)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F145,'Listas de apoio'!$A$6='Registo da Rotação'!G145,'Listas de apoio'!$A$6='Registo da Rotação'!H145),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Registo da Rotação'!G145)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Registo da Rotação'!H145)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F145,'Listas de apoio'!$A$7='Registo da Rotação'!G145,'Listas de apoio'!$A$7='Registo da Rotação'!H145),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Registo da Rotação'!G145)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Registo da Rotação'!H145)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F145,'Listas de apoio'!$A$8='Registo da Rotação'!G145,'Listas de apoio'!$A$8='Registo da Rotação'!H145),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Registo da Rotação'!G145)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Registo da Rotação'!H145)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U87" s="8">
-        <f>IF('Registo da Rotação'!A136="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A136)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C136,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D136)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A145="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A145)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C145,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D145)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V87" s="1"/>
@@ -14851,31 +15311,31 @@
       <c r="M88" s="1"/>
       <c r="N88" s="1"/>
       <c r="O88" s="8">
-        <f>IF('Registo da Rotação'!A137="",0,IF(COUNTA('Registo da Rotação'!B137:K137)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A146="",0,IF(COUNTA('Registo da Rotação'!B146:K146)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P88" s="8">
-        <f>IF('Registo da Rotação'!A137="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C137)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A146="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C146)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q88" s="8">
-        <f>IF('Registo da Rotação'!A137="",0,IF(OR('Registo da Rotação'!F137='Registo da Rotação'!G137,'Registo da Rotação'!F137='Registo da Rotação'!H137,'Registo da Rotação'!G137='Registo da Rotação'!H137),1,0))</f>
+        <f>IF('Registo da Rotação'!A146="",0,IF(OR('Registo da Rotação'!F146='Registo da Rotação'!G146,'Registo da Rotação'!F146='Registo da Rotação'!H146,'Registo da Rotação'!G146='Registo da Rotação'!H146),1,0))</f>
         <v>0</v>
       </c>
       <c r="R88" s="8">
-        <f>IF('Registo da Rotação'!A137="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C137,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I137="Ainda não avaliado",'Registo da Rotação'!J137="Ainda não avaliado",'Registo da Rotação'!K137="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A146="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C146,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I146="Ainda não avaliado",'Registo da Rotação'!J146="Ainda não avaliado",'Registo da Rotação'!K146="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S88" s="8">
-        <f>IF('Registo da Rotação'!A137="",0,IF(AND('Registo da Rotação'!G137=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137),'Registo da Rotação'!$G$54:'Registo da Rotação'!G136),""),'Registo da Rotação'!H137=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137),'Registo da Rotação'!$H$54:'Registo da Rotação'!H136),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A146="",0,IF(AND('Registo da Rotação'!G146=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146),'Registo da Rotação'!$G$54:'Registo da Rotação'!G145),""),'Registo da Rotação'!H146=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146),'Registo da Rotação'!$H$54:'Registo da Rotação'!H145),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T88" s="8">
-        <f>IF('Registo da Rotação'!A137="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Registo da Rotação'!G137)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Registo da Rotação'!H137)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F137,'Listas de apoio'!$A$5='Registo da Rotação'!G137,'Listas de apoio'!$A$5='Registo da Rotação'!H137),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Registo da Rotação'!G137)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Registo da Rotação'!H137)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F137,'Listas de apoio'!$A$6='Registo da Rotação'!G137,'Listas de apoio'!$A$6='Registo da Rotação'!H137),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Registo da Rotação'!G137)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Registo da Rotação'!H137)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F137,'Listas de apoio'!$A$7='Registo da Rotação'!G137,'Listas de apoio'!$A$7='Registo da Rotação'!H137),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Registo da Rotação'!G137)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Registo da Rotação'!H137)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F137,'Listas de apoio'!$A$8='Registo da Rotação'!G137,'Listas de apoio'!$A$8='Registo da Rotação'!H137),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F136='Registo da Rotação'!F137)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Registo da Rotação'!G137)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Registo da Rotação'!H137)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F136)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G136='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H136='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A146="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Registo da Rotação'!G146)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Registo da Rotação'!H146)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F146,'Listas de apoio'!$A$5='Registo da Rotação'!G146,'Listas de apoio'!$A$5='Registo da Rotação'!H146),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Registo da Rotação'!G146)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Registo da Rotação'!H146)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F146,'Listas de apoio'!$A$6='Registo da Rotação'!G146,'Listas de apoio'!$A$6='Registo da Rotação'!H146),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Registo da Rotação'!G146)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Registo da Rotação'!H146)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F146,'Listas de apoio'!$A$7='Registo da Rotação'!G146,'Listas de apoio'!$A$7='Registo da Rotação'!H146),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Registo da Rotação'!G146)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Registo da Rotação'!H146)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F146,'Listas de apoio'!$A$8='Registo da Rotação'!G146,'Listas de apoio'!$A$8='Registo da Rotação'!H146),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Registo da Rotação'!G146)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Registo da Rotação'!H146)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U88" s="8">
-        <f>IF('Registo da Rotação'!A137="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A137)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C137,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D137)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A146="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A146)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C146,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D146)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V88" s="1"/>
@@ -14908,31 +15368,31 @@
       <c r="M89" s="1"/>
       <c r="N89" s="1"/>
       <c r="O89" s="8">
-        <f>IF('Registo da Rotação'!A138="",0,IF(COUNTA('Registo da Rotação'!B138:K138)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A147="",0,IF(COUNTA('Registo da Rotação'!B147:K147)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P89" s="8">
-        <f>IF('Registo da Rotação'!A138="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C138)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A147="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C147)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q89" s="8">
-        <f>IF('Registo da Rotação'!A138="",0,IF(OR('Registo da Rotação'!F138='Registo da Rotação'!G138,'Registo da Rotação'!F138='Registo da Rotação'!H138,'Registo da Rotação'!G138='Registo da Rotação'!H138),1,0))</f>
+        <f>IF('Registo da Rotação'!A147="",0,IF(OR('Registo da Rotação'!F147='Registo da Rotação'!G147,'Registo da Rotação'!F147='Registo da Rotação'!H147,'Registo da Rotação'!G147='Registo da Rotação'!H147),1,0))</f>
         <v>0</v>
       </c>
       <c r="R89" s="8">
-        <f>IF('Registo da Rotação'!A138="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C138,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I138="Ainda não avaliado",'Registo da Rotação'!J138="Ainda não avaliado",'Registo da Rotação'!K138="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A147="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C147,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I147="Ainda não avaliado",'Registo da Rotação'!J147="Ainda não avaliado",'Registo da Rotação'!K147="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S89" s="8">
-        <f>IF('Registo da Rotação'!A138="",0,IF(AND('Registo da Rotação'!G138=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138),'Registo da Rotação'!$G$54:'Registo da Rotação'!G137),""),'Registo da Rotação'!H138=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138),'Registo da Rotação'!$H$54:'Registo da Rotação'!H137),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A147="",0,IF(AND('Registo da Rotação'!G147=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147),'Registo da Rotação'!$G$54:'Registo da Rotação'!G146),""),'Registo da Rotação'!H147=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147),'Registo da Rotação'!$H$54:'Registo da Rotação'!H146),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T89" s="8">
-        <f>IF('Registo da Rotação'!A138="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Registo da Rotação'!G138)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Registo da Rotação'!H138)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F138,'Listas de apoio'!$A$5='Registo da Rotação'!G138,'Listas de apoio'!$A$5='Registo da Rotação'!H138),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Registo da Rotação'!G138)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Registo da Rotação'!H138)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F138,'Listas de apoio'!$A$6='Registo da Rotação'!G138,'Listas de apoio'!$A$6='Registo da Rotação'!H138),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Registo da Rotação'!G138)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Registo da Rotação'!H138)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F138,'Listas de apoio'!$A$7='Registo da Rotação'!G138,'Listas de apoio'!$A$7='Registo da Rotação'!H138),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Registo da Rotação'!G138)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Registo da Rotação'!H138)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F138,'Listas de apoio'!$A$8='Registo da Rotação'!G138,'Listas de apoio'!$A$8='Registo da Rotação'!H138),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F137='Registo da Rotação'!F138)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Registo da Rotação'!G138)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Registo da Rotação'!H138)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F137)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G137='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H137='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A147="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Registo da Rotação'!G147)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Registo da Rotação'!H147)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F147,'Listas de apoio'!$A$5='Registo da Rotação'!G147,'Listas de apoio'!$A$5='Registo da Rotação'!H147),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Registo da Rotação'!G147)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Registo da Rotação'!H147)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F147,'Listas de apoio'!$A$6='Registo da Rotação'!G147,'Listas de apoio'!$A$6='Registo da Rotação'!H147),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Registo da Rotação'!G147)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Registo da Rotação'!H147)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F147,'Listas de apoio'!$A$7='Registo da Rotação'!G147,'Listas de apoio'!$A$7='Registo da Rotação'!H147),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Registo da Rotação'!G147)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Registo da Rotação'!H147)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F147,'Listas de apoio'!$A$8='Registo da Rotação'!G147,'Listas de apoio'!$A$8='Registo da Rotação'!H147),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Registo da Rotação'!G147)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Registo da Rotação'!H147)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U89" s="8">
-        <f>IF('Registo da Rotação'!A138="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A138)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C138,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D138)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A147="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A147)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C147,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D147)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V89" s="1"/>
@@ -14965,31 +15425,31 @@
       <c r="M90" s="1"/>
       <c r="N90" s="1"/>
       <c r="O90" s="8">
-        <f>IF('Registo da Rotação'!A139="",0,IF(COUNTA('Registo da Rotação'!B139:K139)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A148="",0,IF(COUNTA('Registo da Rotação'!B148:K148)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P90" s="8">
-        <f>IF('Registo da Rotação'!A139="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C139)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A148="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C148)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q90" s="8">
-        <f>IF('Registo da Rotação'!A139="",0,IF(OR('Registo da Rotação'!F139='Registo da Rotação'!G139,'Registo da Rotação'!F139='Registo da Rotação'!H139,'Registo da Rotação'!G139='Registo da Rotação'!H139),1,0))</f>
+        <f>IF('Registo da Rotação'!A148="",0,IF(OR('Registo da Rotação'!F148='Registo da Rotação'!G148,'Registo da Rotação'!F148='Registo da Rotação'!H148,'Registo da Rotação'!G148='Registo da Rotação'!H148),1,0))</f>
         <v>0</v>
       </c>
       <c r="R90" s="8">
-        <f>IF('Registo da Rotação'!A139="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C139,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I139="Ainda não avaliado",'Registo da Rotação'!J139="Ainda não avaliado",'Registo da Rotação'!K139="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A148="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C148,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I148="Ainda não avaliado",'Registo da Rotação'!J148="Ainda não avaliado",'Registo da Rotação'!K148="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S90" s="8">
-        <f>IF('Registo da Rotação'!A139="",0,IF(AND('Registo da Rotação'!G139=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139),'Registo da Rotação'!$G$54:'Registo da Rotação'!G138),""),'Registo da Rotação'!H139=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139),'Registo da Rotação'!$H$54:'Registo da Rotação'!H138),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A148="",0,IF(AND('Registo da Rotação'!G148=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148),'Registo da Rotação'!$G$54:'Registo da Rotação'!G147),""),'Registo da Rotação'!H148=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148),'Registo da Rotação'!$H$54:'Registo da Rotação'!H147),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T90" s="8">
-        <f>IF('Registo da Rotação'!A139="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Registo da Rotação'!G139)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Registo da Rotação'!H139)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F139,'Listas de apoio'!$A$5='Registo da Rotação'!G139,'Listas de apoio'!$A$5='Registo da Rotação'!H139),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Registo da Rotação'!G139)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Registo da Rotação'!H139)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F139,'Listas de apoio'!$A$6='Registo da Rotação'!G139,'Listas de apoio'!$A$6='Registo da Rotação'!H139),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Registo da Rotação'!G139)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Registo da Rotação'!H139)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F139,'Listas de apoio'!$A$7='Registo da Rotação'!G139,'Listas de apoio'!$A$7='Registo da Rotação'!H139),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Registo da Rotação'!G139)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Registo da Rotação'!H139)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F139,'Listas de apoio'!$A$8='Registo da Rotação'!G139,'Listas de apoio'!$A$8='Registo da Rotação'!H139),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F138='Registo da Rotação'!F139)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Registo da Rotação'!G139)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Registo da Rotação'!H139)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F138)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G138='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H138='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A148="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Registo da Rotação'!G148)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Registo da Rotação'!H148)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F148,'Listas de apoio'!$A$5='Registo da Rotação'!G148,'Listas de apoio'!$A$5='Registo da Rotação'!H148),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Registo da Rotação'!G148)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Registo da Rotação'!H148)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F148,'Listas de apoio'!$A$6='Registo da Rotação'!G148,'Listas de apoio'!$A$6='Registo da Rotação'!H148),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Registo da Rotação'!G148)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Registo da Rotação'!H148)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F148,'Listas de apoio'!$A$7='Registo da Rotação'!G148,'Listas de apoio'!$A$7='Registo da Rotação'!H148),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Registo da Rotação'!G148)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Registo da Rotação'!H148)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F148,'Listas de apoio'!$A$8='Registo da Rotação'!G148,'Listas de apoio'!$A$8='Registo da Rotação'!H148),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Registo da Rotação'!G148)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Registo da Rotação'!H148)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U90" s="8">
-        <f>IF('Registo da Rotação'!A139="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A139)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C139,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D139)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A148="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A148)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C148,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D148)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V90" s="1"/>
@@ -15022,31 +15482,31 @@
       <c r="M91" s="1"/>
       <c r="N91" s="1"/>
       <c r="O91" s="8">
-        <f>IF('Registo da Rotação'!A140="",0,IF(COUNTA('Registo da Rotação'!B140:K140)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A149="",0,IF(COUNTA('Registo da Rotação'!B149:K149)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P91" s="8">
-        <f>IF('Registo da Rotação'!A140="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C140)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A149="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C149)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q91" s="8">
-        <f>IF('Registo da Rotação'!A140="",0,IF(OR('Registo da Rotação'!F140='Registo da Rotação'!G140,'Registo da Rotação'!F140='Registo da Rotação'!H140,'Registo da Rotação'!G140='Registo da Rotação'!H140),1,0))</f>
+        <f>IF('Registo da Rotação'!A149="",0,IF(OR('Registo da Rotação'!F149='Registo da Rotação'!G149,'Registo da Rotação'!F149='Registo da Rotação'!H149,'Registo da Rotação'!G149='Registo da Rotação'!H149),1,0))</f>
         <v>0</v>
       </c>
       <c r="R91" s="8">
-        <f>IF('Registo da Rotação'!A140="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C140,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I140="Ainda não avaliado",'Registo da Rotação'!J140="Ainda não avaliado",'Registo da Rotação'!K140="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A149="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C149,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I149="Ainda não avaliado",'Registo da Rotação'!J149="Ainda não avaliado",'Registo da Rotação'!K149="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S91" s="8">
-        <f>IF('Registo da Rotação'!A140="",0,IF(AND('Registo da Rotação'!G140=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140),'Registo da Rotação'!$G$54:'Registo da Rotação'!G139),""),'Registo da Rotação'!H140=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140),'Registo da Rotação'!$H$54:'Registo da Rotação'!H139),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A149="",0,IF(AND('Registo da Rotação'!G149=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149),'Registo da Rotação'!$G$54:'Registo da Rotação'!G148),""),'Registo da Rotação'!H149=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149),'Registo da Rotação'!$H$54:'Registo da Rotação'!H148),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T91" s="8">
-        <f>IF('Registo da Rotação'!A140="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Registo da Rotação'!G140)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Registo da Rotação'!H140)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F140,'Listas de apoio'!$A$5='Registo da Rotação'!G140,'Listas de apoio'!$A$5='Registo da Rotação'!H140),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Registo da Rotação'!G140)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Registo da Rotação'!H140)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F140,'Listas de apoio'!$A$6='Registo da Rotação'!G140,'Listas de apoio'!$A$6='Registo da Rotação'!H140),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Registo da Rotação'!G140)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Registo da Rotação'!H140)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F140,'Listas de apoio'!$A$7='Registo da Rotação'!G140,'Listas de apoio'!$A$7='Registo da Rotação'!H140),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Registo da Rotação'!G140)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Registo da Rotação'!H140)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F140,'Listas de apoio'!$A$8='Registo da Rotação'!G140,'Listas de apoio'!$A$8='Registo da Rotação'!H140),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F139='Registo da Rotação'!F140)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Registo da Rotação'!G140)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Registo da Rotação'!H140)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F139)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G139='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H139='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A149="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Registo da Rotação'!G149)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Registo da Rotação'!H149)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F149,'Listas de apoio'!$A$5='Registo da Rotação'!G149,'Listas de apoio'!$A$5='Registo da Rotação'!H149),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Registo da Rotação'!G149)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Registo da Rotação'!H149)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F149,'Listas de apoio'!$A$6='Registo da Rotação'!G149,'Listas de apoio'!$A$6='Registo da Rotação'!H149),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Registo da Rotação'!G149)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Registo da Rotação'!H149)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F149,'Listas de apoio'!$A$7='Registo da Rotação'!G149,'Listas de apoio'!$A$7='Registo da Rotação'!H149),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Registo da Rotação'!G149)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Registo da Rotação'!H149)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F149,'Listas de apoio'!$A$8='Registo da Rotação'!G149,'Listas de apoio'!$A$8='Registo da Rotação'!H149),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Registo da Rotação'!G149)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Registo da Rotação'!H149)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U91" s="8">
-        <f>IF('Registo da Rotação'!A140="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A140)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C140,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D140)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A149="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A149)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C149,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D149)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V91" s="1"/>
@@ -15079,31 +15539,31 @@
       <c r="M92" s="1"/>
       <c r="N92" s="1"/>
       <c r="O92" s="8">
-        <f>IF('Registo da Rotação'!A141="",0,IF(COUNTA('Registo da Rotação'!B141:K141)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A150="",0,IF(COUNTA('Registo da Rotação'!B150:K150)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P92" s="8">
-        <f>IF('Registo da Rotação'!A141="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C141)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A150="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C150)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q92" s="8">
-        <f>IF('Registo da Rotação'!A141="",0,IF(OR('Registo da Rotação'!F141='Registo da Rotação'!G141,'Registo da Rotação'!F141='Registo da Rotação'!H141,'Registo da Rotação'!G141='Registo da Rotação'!H141),1,0))</f>
+        <f>IF('Registo da Rotação'!A150="",0,IF(OR('Registo da Rotação'!F150='Registo da Rotação'!G150,'Registo da Rotação'!F150='Registo da Rotação'!H150,'Registo da Rotação'!G150='Registo da Rotação'!H150),1,0))</f>
         <v>0</v>
       </c>
       <c r="R92" s="8">
-        <f>IF('Registo da Rotação'!A141="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C141,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I141="Ainda não avaliado",'Registo da Rotação'!J141="Ainda não avaliado",'Registo da Rotação'!K141="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A150="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C150,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I150="Ainda não avaliado",'Registo da Rotação'!J150="Ainda não avaliado",'Registo da Rotação'!K150="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S92" s="8">
-        <f>IF('Registo da Rotação'!A141="",0,IF(AND('Registo da Rotação'!G141=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141),'Registo da Rotação'!$G$54:'Registo da Rotação'!G140),""),'Registo da Rotação'!H141=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141),'Registo da Rotação'!$H$54:'Registo da Rotação'!H140),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A150="",0,IF(AND('Registo da Rotação'!G150=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150),'Registo da Rotação'!$G$54:'Registo da Rotação'!G149),""),'Registo da Rotação'!H150=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150),'Registo da Rotação'!$H$54:'Registo da Rotação'!H149),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T92" s="8">
-        <f>IF('Registo da Rotação'!A141="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Registo da Rotação'!G141)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Registo da Rotação'!H141)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F141,'Listas de apoio'!$A$5='Registo da Rotação'!G141,'Listas de apoio'!$A$5='Registo da Rotação'!H141),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Registo da Rotação'!G141)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Registo da Rotação'!H141)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F141,'Listas de apoio'!$A$6='Registo da Rotação'!G141,'Listas de apoio'!$A$6='Registo da Rotação'!H141),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Registo da Rotação'!G141)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Registo da Rotação'!H141)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F141,'Listas de apoio'!$A$7='Registo da Rotação'!G141,'Listas de apoio'!$A$7='Registo da Rotação'!H141),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Registo da Rotação'!G141)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Registo da Rotação'!H141)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F141,'Listas de apoio'!$A$8='Registo da Rotação'!G141,'Listas de apoio'!$A$8='Registo da Rotação'!H141),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F140='Registo da Rotação'!F141)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Registo da Rotação'!G141)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Registo da Rotação'!H141)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F140)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G140='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H140='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A150="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Registo da Rotação'!G150)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Registo da Rotação'!H150)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F150,'Listas de apoio'!$A$5='Registo da Rotação'!G150,'Listas de apoio'!$A$5='Registo da Rotação'!H150),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Registo da Rotação'!G150)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Registo da Rotação'!H150)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F150,'Listas de apoio'!$A$6='Registo da Rotação'!G150,'Listas de apoio'!$A$6='Registo da Rotação'!H150),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Registo da Rotação'!G150)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Registo da Rotação'!H150)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F150,'Listas de apoio'!$A$7='Registo da Rotação'!G150,'Listas de apoio'!$A$7='Registo da Rotação'!H150),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Registo da Rotação'!G150)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Registo da Rotação'!H150)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F150,'Listas de apoio'!$A$8='Registo da Rotação'!G150,'Listas de apoio'!$A$8='Registo da Rotação'!H150),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Registo da Rotação'!G150)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Registo da Rotação'!H150)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U92" s="8">
-        <f>IF('Registo da Rotação'!A141="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A141)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C141,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D141)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A150="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A150)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C150,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D150)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V92" s="1"/>
@@ -15136,31 +15596,31 @@
       <c r="M93" s="1"/>
       <c r="N93" s="1"/>
       <c r="O93" s="8">
-        <f>IF('Registo da Rotação'!A142="",0,IF(COUNTA('Registo da Rotação'!B142:K142)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A151="",0,IF(COUNTA('Registo da Rotação'!B151:K151)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P93" s="8">
-        <f>IF('Registo da Rotação'!A142="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C142)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A151="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C151)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q93" s="8">
-        <f>IF('Registo da Rotação'!A142="",0,IF(OR('Registo da Rotação'!F142='Registo da Rotação'!G142,'Registo da Rotação'!F142='Registo da Rotação'!H142,'Registo da Rotação'!G142='Registo da Rotação'!H142),1,0))</f>
+        <f>IF('Registo da Rotação'!A151="",0,IF(OR('Registo da Rotação'!F151='Registo da Rotação'!G151,'Registo da Rotação'!F151='Registo da Rotação'!H151,'Registo da Rotação'!G151='Registo da Rotação'!H151),1,0))</f>
         <v>0</v>
       </c>
       <c r="R93" s="8">
-        <f>IF('Registo da Rotação'!A142="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C142,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I142="Ainda não avaliado",'Registo da Rotação'!J142="Ainda não avaliado",'Registo da Rotação'!K142="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A151="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C151,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I151="Ainda não avaliado",'Registo da Rotação'!J151="Ainda não avaliado",'Registo da Rotação'!K151="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S93" s="8">
-        <f>IF('Registo da Rotação'!A142="",0,IF(AND('Registo da Rotação'!G142=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142),'Registo da Rotação'!$G$54:'Registo da Rotação'!G141),""),'Registo da Rotação'!H142=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142),'Registo da Rotação'!$H$54:'Registo da Rotação'!H141),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A151="",0,IF(AND('Registo da Rotação'!G151=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151),'Registo da Rotação'!$G$54:'Registo da Rotação'!G150),""),'Registo da Rotação'!H151=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151),'Registo da Rotação'!$H$54:'Registo da Rotação'!H150),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T93" s="8">
-        <f>IF('Registo da Rotação'!A142="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Registo da Rotação'!G142)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Registo da Rotação'!H142)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F142,'Listas de apoio'!$A$5='Registo da Rotação'!G142,'Listas de apoio'!$A$5='Registo da Rotação'!H142),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Registo da Rotação'!G142)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Registo da Rotação'!H142)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F142,'Listas de apoio'!$A$6='Registo da Rotação'!G142,'Listas de apoio'!$A$6='Registo da Rotação'!H142),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Registo da Rotação'!G142)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Registo da Rotação'!H142)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F142,'Listas de apoio'!$A$7='Registo da Rotação'!G142,'Listas de apoio'!$A$7='Registo da Rotação'!H142),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Registo da Rotação'!G142)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Registo da Rotação'!H142)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F142,'Listas de apoio'!$A$8='Registo da Rotação'!G142,'Listas de apoio'!$A$8='Registo da Rotação'!H142),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F141='Registo da Rotação'!F142)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Registo da Rotação'!G142)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Registo da Rotação'!H142)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F141)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G141='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H141='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A151="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Registo da Rotação'!G151)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Registo da Rotação'!H151)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F151,'Listas de apoio'!$A$5='Registo da Rotação'!G151,'Listas de apoio'!$A$5='Registo da Rotação'!H151),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Registo da Rotação'!G151)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Registo da Rotação'!H151)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F151,'Listas de apoio'!$A$6='Registo da Rotação'!G151,'Listas de apoio'!$A$6='Registo da Rotação'!H151),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Registo da Rotação'!G151)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Registo da Rotação'!H151)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F151,'Listas de apoio'!$A$7='Registo da Rotação'!G151,'Listas de apoio'!$A$7='Registo da Rotação'!H151),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Registo da Rotação'!G151)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Registo da Rotação'!H151)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F151,'Listas de apoio'!$A$8='Registo da Rotação'!G151,'Listas de apoio'!$A$8='Registo da Rotação'!H151),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Registo da Rotação'!G151)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Registo da Rotação'!H151)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U93" s="8">
-        <f>IF('Registo da Rotação'!A142="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A142)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C142,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D142)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A151="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A151)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C151,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D151)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V93" s="1"/>
@@ -15193,31 +15653,31 @@
       <c r="M94" s="1"/>
       <c r="N94" s="1"/>
       <c r="O94" s="8">
-        <f>IF('Registo da Rotação'!A143="",0,IF(COUNTA('Registo da Rotação'!B143:K143)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A152="",0,IF(COUNTA('Registo da Rotação'!B152:K152)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P94" s="8">
-        <f>IF('Registo da Rotação'!A143="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C143)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A152="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C152)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q94" s="8">
-        <f>IF('Registo da Rotação'!A143="",0,IF(OR('Registo da Rotação'!F143='Registo da Rotação'!G143,'Registo da Rotação'!F143='Registo da Rotação'!H143,'Registo da Rotação'!G143='Registo da Rotação'!H143),1,0))</f>
+        <f>IF('Registo da Rotação'!A152="",0,IF(OR('Registo da Rotação'!F152='Registo da Rotação'!G152,'Registo da Rotação'!F152='Registo da Rotação'!H152,'Registo da Rotação'!G152='Registo da Rotação'!H152),1,0))</f>
         <v>0</v>
       </c>
       <c r="R94" s="8">
-        <f>IF('Registo da Rotação'!A143="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C143,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I143="Ainda não avaliado",'Registo da Rotação'!J143="Ainda não avaliado",'Registo da Rotação'!K143="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A152="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C152,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I152="Ainda não avaliado",'Registo da Rotação'!J152="Ainda não avaliado",'Registo da Rotação'!K152="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S94" s="8">
-        <f>IF('Registo da Rotação'!A143="",0,IF(AND('Registo da Rotação'!G143=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143),'Registo da Rotação'!$G$54:'Registo da Rotação'!G142),""),'Registo da Rotação'!H143=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143),'Registo da Rotação'!$H$54:'Registo da Rotação'!H142),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A152="",0,IF(AND('Registo da Rotação'!G152=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152),'Registo da Rotação'!$G$54:'Registo da Rotação'!G151),""),'Registo da Rotação'!H152=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152),'Registo da Rotação'!$H$54:'Registo da Rotação'!H151),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T94" s="8">
-        <f>IF('Registo da Rotação'!A143="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Registo da Rotação'!G143)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Registo da Rotação'!H143)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F143,'Listas de apoio'!$A$5='Registo da Rotação'!G143,'Listas de apoio'!$A$5='Registo da Rotação'!H143),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Registo da Rotação'!G143)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Registo da Rotação'!H143)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F143,'Listas de apoio'!$A$6='Registo da Rotação'!G143,'Listas de apoio'!$A$6='Registo da Rotação'!H143),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Registo da Rotação'!G143)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Registo da Rotação'!H143)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F143,'Listas de apoio'!$A$7='Registo da Rotação'!G143,'Listas de apoio'!$A$7='Registo da Rotação'!H143),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Registo da Rotação'!G143)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Registo da Rotação'!H143)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F143,'Listas de apoio'!$A$8='Registo da Rotação'!G143,'Listas de apoio'!$A$8='Registo da Rotação'!H143),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F142='Registo da Rotação'!F143)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Registo da Rotação'!G143)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Registo da Rotação'!H143)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F142)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G142='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H142='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A152="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Registo da Rotação'!G152)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Registo da Rotação'!H152)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F152,'Listas de apoio'!$A$5='Registo da Rotação'!G152,'Listas de apoio'!$A$5='Registo da Rotação'!H152),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Registo da Rotação'!G152)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Registo da Rotação'!H152)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F152,'Listas de apoio'!$A$6='Registo da Rotação'!G152,'Listas de apoio'!$A$6='Registo da Rotação'!H152),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Registo da Rotação'!G152)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Registo da Rotação'!H152)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F152,'Listas de apoio'!$A$7='Registo da Rotação'!G152,'Listas de apoio'!$A$7='Registo da Rotação'!H152),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Registo da Rotação'!G152)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Registo da Rotação'!H152)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F152,'Listas de apoio'!$A$8='Registo da Rotação'!G152,'Listas de apoio'!$A$8='Registo da Rotação'!H152),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Registo da Rotação'!G152)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Registo da Rotação'!H152)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U94" s="8">
-        <f>IF('Registo da Rotação'!A143="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A143)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C143,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D143)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A152="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A152)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C152,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D152)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V94" s="1"/>
@@ -15250,31 +15710,31 @@
       <c r="M95" s="1"/>
       <c r="N95" s="1"/>
       <c r="O95" s="8">
-        <f>IF('Registo da Rotação'!A144="",0,IF(COUNTA('Registo da Rotação'!B144:K144)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A153="",0,IF(COUNTA('Registo da Rotação'!B153:K153)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P95" s="8">
-        <f>IF('Registo da Rotação'!A144="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C144)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A153="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C153)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q95" s="8">
-        <f>IF('Registo da Rotação'!A144="",0,IF(OR('Registo da Rotação'!F144='Registo da Rotação'!G144,'Registo da Rotação'!F144='Registo da Rotação'!H144,'Registo da Rotação'!G144='Registo da Rotação'!H144),1,0))</f>
+        <f>IF('Registo da Rotação'!A153="",0,IF(OR('Registo da Rotação'!F153='Registo da Rotação'!G153,'Registo da Rotação'!F153='Registo da Rotação'!H153,'Registo da Rotação'!G153='Registo da Rotação'!H153),1,0))</f>
         <v>0</v>
       </c>
       <c r="R95" s="8">
-        <f>IF('Registo da Rotação'!A144="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C144,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I144="Ainda não avaliado",'Registo da Rotação'!J144="Ainda não avaliado",'Registo da Rotação'!K144="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A153="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C153,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I153="Ainda não avaliado",'Registo da Rotação'!J153="Ainda não avaliado",'Registo da Rotação'!K153="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S95" s="8">
-        <f>IF('Registo da Rotação'!A144="",0,IF(AND('Registo da Rotação'!G144=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144),'Registo da Rotação'!$G$54:'Registo da Rotação'!G143),""),'Registo da Rotação'!H144=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144),'Registo da Rotação'!$H$54:'Registo da Rotação'!H143),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A153="",0,IF(AND('Registo da Rotação'!G153=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153),'Registo da Rotação'!$G$54:'Registo da Rotação'!G152),""),'Registo da Rotação'!H153=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153),'Registo da Rotação'!$H$54:'Registo da Rotação'!H152),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T95" s="8">
-        <f>IF('Registo da Rotação'!A144="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Registo da Rotação'!G144)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Registo da Rotação'!H144)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F144,'Listas de apoio'!$A$5='Registo da Rotação'!G144,'Listas de apoio'!$A$5='Registo da Rotação'!H144),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Registo da Rotação'!G144)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Registo da Rotação'!H144)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F144,'Listas de apoio'!$A$6='Registo da Rotação'!G144,'Listas de apoio'!$A$6='Registo da Rotação'!H144),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Registo da Rotação'!G144)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Registo da Rotação'!H144)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F144,'Listas de apoio'!$A$7='Registo da Rotação'!G144,'Listas de apoio'!$A$7='Registo da Rotação'!H144),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Registo da Rotação'!G144)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Registo da Rotação'!H144)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F144,'Listas de apoio'!$A$8='Registo da Rotação'!G144,'Listas de apoio'!$A$8='Registo da Rotação'!H144),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F143='Registo da Rotação'!F144)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Registo da Rotação'!G144)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Registo da Rotação'!H144)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F143)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G143='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H143='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A153="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Registo da Rotação'!G153)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Registo da Rotação'!H153)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F153,'Listas de apoio'!$A$5='Registo da Rotação'!G153,'Listas de apoio'!$A$5='Registo da Rotação'!H153),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Registo da Rotação'!G153)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Registo da Rotação'!H153)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F153,'Listas de apoio'!$A$6='Registo da Rotação'!G153,'Listas de apoio'!$A$6='Registo da Rotação'!H153),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Registo da Rotação'!G153)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Registo da Rotação'!H153)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F153,'Listas de apoio'!$A$7='Registo da Rotação'!G153,'Listas de apoio'!$A$7='Registo da Rotação'!H153),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Registo da Rotação'!G153)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Registo da Rotação'!H153)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F153,'Listas de apoio'!$A$8='Registo da Rotação'!G153,'Listas de apoio'!$A$8='Registo da Rotação'!H153),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Registo da Rotação'!G153)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Registo da Rotação'!H153)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U95" s="8">
-        <f>IF('Registo da Rotação'!A144="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A144)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C144,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D144)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A153="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A153)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C153,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D153)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V95" s="1"/>
@@ -15307,31 +15767,31 @@
       <c r="M96" s="1"/>
       <c r="N96" s="1"/>
       <c r="O96" s="8">
-        <f>IF('Registo da Rotação'!A145="",0,IF(COUNTA('Registo da Rotação'!B145:K145)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A154="",0,IF(COUNTA('Registo da Rotação'!B154:K154)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P96" s="8">
-        <f>IF('Registo da Rotação'!A145="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C145)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A154="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C154)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q96" s="8">
-        <f>IF('Registo da Rotação'!A145="",0,IF(OR('Registo da Rotação'!F145='Registo da Rotação'!G145,'Registo da Rotação'!F145='Registo da Rotação'!H145,'Registo da Rotação'!G145='Registo da Rotação'!H145),1,0))</f>
+        <f>IF('Registo da Rotação'!A154="",0,IF(OR('Registo da Rotação'!F154='Registo da Rotação'!G154,'Registo da Rotação'!F154='Registo da Rotação'!H154,'Registo da Rotação'!G154='Registo da Rotação'!H154),1,0))</f>
         <v>0</v>
       </c>
       <c r="R96" s="8">
-        <f>IF('Registo da Rotação'!A145="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C145,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I145="Ainda não avaliado",'Registo da Rotação'!J145="Ainda não avaliado",'Registo da Rotação'!K145="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A154="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C154,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I154="Ainda não avaliado",'Registo da Rotação'!J154="Ainda não avaliado",'Registo da Rotação'!K154="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S96" s="8">
-        <f>IF('Registo da Rotação'!A145="",0,IF(AND('Registo da Rotação'!G145=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145),'Registo da Rotação'!$G$54:'Registo da Rotação'!G144),""),'Registo da Rotação'!H145=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145),'Registo da Rotação'!$H$54:'Registo da Rotação'!H144),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A154="",0,IF(AND('Registo da Rotação'!G154=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F153='Registo da Rotação'!F154),'Registo da Rotação'!$G$54:'Registo da Rotação'!G153),""),'Registo da Rotação'!H154=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F153='Registo da Rotação'!F154),'Registo da Rotação'!$H$54:'Registo da Rotação'!H153),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T96" s="8">
-        <f>IF('Registo da Rotação'!A145="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Registo da Rotação'!G145)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Registo da Rotação'!H145)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F145,'Listas de apoio'!$A$5='Registo da Rotação'!G145,'Listas de apoio'!$A$5='Registo da Rotação'!H145),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Registo da Rotação'!G145)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Registo da Rotação'!H145)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F145,'Listas de apoio'!$A$6='Registo da Rotação'!G145,'Listas de apoio'!$A$6='Registo da Rotação'!H145),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Registo da Rotação'!G145)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Registo da Rotação'!H145)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F145,'Listas de apoio'!$A$7='Registo da Rotação'!G145,'Listas de apoio'!$A$7='Registo da Rotação'!H145),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Registo da Rotação'!G145)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Registo da Rotação'!H145)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F145,'Listas de apoio'!$A$8='Registo da Rotação'!G145,'Listas de apoio'!$A$8='Registo da Rotação'!H145),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F144='Registo da Rotação'!F145)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Registo da Rotação'!G145)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Registo da Rotação'!H145)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F144)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G144='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H144='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A154="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F153='Registo da Rotação'!F154)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G153='Registo da Rotação'!G154)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H153='Registo da Rotação'!H154)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F153)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F154,'Listas de apoio'!$A$5='Registo da Rotação'!G154,'Listas de apoio'!$A$5='Registo da Rotação'!H154),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F153='Registo da Rotação'!F154),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F153)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F153='Registo da Rotação'!F154)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G153='Registo da Rotação'!G154)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H153='Registo da Rotação'!H154)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F153)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G153='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H153='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F154,'Listas de apoio'!$A$6='Registo da Rotação'!G154,'Listas de apoio'!$A$6='Registo da Rotação'!H154),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F153='Registo da Rotação'!F154),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F153)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F153='Registo da Rotação'!F154)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G153='Registo da Rotação'!G154)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H153='Registo da Rotação'!H154)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F153)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G153='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H153='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F154,'Listas de apoio'!$A$7='Registo da Rotação'!G154,'Listas de apoio'!$A$7='Registo da Rotação'!H154),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F153='Registo da Rotação'!F154),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F153)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F153='Registo da Rotação'!F154)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G153='Registo da Rotação'!G154)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H153='Registo da Rotação'!H154)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F153)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G153='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H153='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F154,'Listas de apoio'!$A$8='Registo da Rotação'!G154,'Listas de apoio'!$A$8='Registo da Rotação'!H154),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F153='Registo da Rotação'!F154),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F153)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F153='Registo da Rotação'!F154)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G153='Registo da Rotação'!G154)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H153='Registo da Rotação'!H154)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F153)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G153='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H153='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U96" s="8">
-        <f>IF('Registo da Rotação'!A145="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A145)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C145,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D145)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A154="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A154)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C154,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D154)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V96" s="1"/>
@@ -15364,31 +15824,31 @@
       <c r="M97" s="1"/>
       <c r="N97" s="1"/>
       <c r="O97" s="8">
-        <f>IF('Registo da Rotação'!A146="",0,IF(COUNTA('Registo da Rotação'!B146:K146)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A155="",0,IF(COUNTA('Registo da Rotação'!B155:K155)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P97" s="8">
-        <f>IF('Registo da Rotação'!A146="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C146)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A155="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C155)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q97" s="8">
-        <f>IF('Registo da Rotação'!A146="",0,IF(OR('Registo da Rotação'!F146='Registo da Rotação'!G146,'Registo da Rotação'!F146='Registo da Rotação'!H146,'Registo da Rotação'!G146='Registo da Rotação'!H146),1,0))</f>
+        <f>IF('Registo da Rotação'!A155="",0,IF(OR('Registo da Rotação'!F155='Registo da Rotação'!G155,'Registo da Rotação'!F155='Registo da Rotação'!H155,'Registo da Rotação'!G155='Registo da Rotação'!H155),1,0))</f>
         <v>0</v>
       </c>
       <c r="R97" s="8">
-        <f>IF('Registo da Rotação'!A146="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C146,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I146="Ainda não avaliado",'Registo da Rotação'!J146="Ainda não avaliado",'Registo da Rotação'!K146="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A155="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C155,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I155="Ainda não avaliado",'Registo da Rotação'!J155="Ainda não avaliado",'Registo da Rotação'!K155="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S97" s="8">
-        <f>IF('Registo da Rotação'!A146="",0,IF(AND('Registo da Rotação'!G146=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146),'Registo da Rotação'!$G$54:'Registo da Rotação'!G145),""),'Registo da Rotação'!H146=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146),'Registo da Rotação'!$H$54:'Registo da Rotação'!H145),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A155="",0,IF(AND('Registo da Rotação'!G155=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F154='Registo da Rotação'!F155),'Registo da Rotação'!$G$54:'Registo da Rotação'!G154),""),'Registo da Rotação'!H155=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F154='Registo da Rotação'!F155),'Registo da Rotação'!$H$54:'Registo da Rotação'!H154),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T97" s="8">
-        <f>IF('Registo da Rotação'!A146="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Registo da Rotação'!G146)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Registo da Rotação'!H146)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F146,'Listas de apoio'!$A$5='Registo da Rotação'!G146,'Listas de apoio'!$A$5='Registo da Rotação'!H146),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Registo da Rotação'!G146)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Registo da Rotação'!H146)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F146,'Listas de apoio'!$A$6='Registo da Rotação'!G146,'Listas de apoio'!$A$6='Registo da Rotação'!H146),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Registo da Rotação'!G146)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Registo da Rotação'!H146)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F146,'Listas de apoio'!$A$7='Registo da Rotação'!G146,'Listas de apoio'!$A$7='Registo da Rotação'!H146),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Registo da Rotação'!G146)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Registo da Rotação'!H146)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F146,'Listas de apoio'!$A$8='Registo da Rotação'!G146,'Listas de apoio'!$A$8='Registo da Rotação'!H146),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F145='Registo da Rotação'!F146)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Registo da Rotação'!G146)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Registo da Rotação'!H146)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F145)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G145='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H145='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A155="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F154='Registo da Rotação'!F155)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G154='Registo da Rotação'!G155)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H154='Registo da Rotação'!H155)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F154)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F155,'Listas de apoio'!$A$5='Registo da Rotação'!G155,'Listas de apoio'!$A$5='Registo da Rotação'!H155),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F154='Registo da Rotação'!F155),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F154)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F154='Registo da Rotação'!F155)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G154='Registo da Rotação'!G155)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H154='Registo da Rotação'!H155)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F154)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G154='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H154='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F155,'Listas de apoio'!$A$6='Registo da Rotação'!G155,'Listas de apoio'!$A$6='Registo da Rotação'!H155),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F154='Registo da Rotação'!F155),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F154)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F154='Registo da Rotação'!F155)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G154='Registo da Rotação'!G155)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H154='Registo da Rotação'!H155)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F154)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G154='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H154='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F155,'Listas de apoio'!$A$7='Registo da Rotação'!G155,'Listas de apoio'!$A$7='Registo da Rotação'!H155),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F154='Registo da Rotação'!F155),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F154)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F154='Registo da Rotação'!F155)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G154='Registo da Rotação'!G155)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H154='Registo da Rotação'!H155)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F154)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G154='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H154='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F155,'Listas de apoio'!$A$8='Registo da Rotação'!G155,'Listas de apoio'!$A$8='Registo da Rotação'!H155),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F154='Registo da Rotação'!F155),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F154)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F154='Registo da Rotação'!F155)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G154='Registo da Rotação'!G155)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H154='Registo da Rotação'!H155)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F154)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G154='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H154='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U97" s="8">
-        <f>IF('Registo da Rotação'!A146="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A146)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C146,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D146)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A155="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A155)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C155,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D155)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V97" s="1"/>
@@ -15421,31 +15881,31 @@
       <c r="M98" s="1"/>
       <c r="N98" s="1"/>
       <c r="O98" s="8">
-        <f>IF('Registo da Rotação'!A147="",0,IF(COUNTA('Registo da Rotação'!B147:K147)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A156="",0,IF(COUNTA('Registo da Rotação'!B156:K156)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P98" s="8">
-        <f>IF('Registo da Rotação'!A147="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C147)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A156="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C156)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q98" s="8">
-        <f>IF('Registo da Rotação'!A147="",0,IF(OR('Registo da Rotação'!F147='Registo da Rotação'!G147,'Registo da Rotação'!F147='Registo da Rotação'!H147,'Registo da Rotação'!G147='Registo da Rotação'!H147),1,0))</f>
+        <f>IF('Registo da Rotação'!A156="",0,IF(OR('Registo da Rotação'!F156='Registo da Rotação'!G156,'Registo da Rotação'!F156='Registo da Rotação'!H156,'Registo da Rotação'!G156='Registo da Rotação'!H156),1,0))</f>
         <v>0</v>
       </c>
       <c r="R98" s="8">
-        <f>IF('Registo da Rotação'!A147="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C147,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I147="Ainda não avaliado",'Registo da Rotação'!J147="Ainda não avaliado",'Registo da Rotação'!K147="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A156="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C156,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I156="Ainda não avaliado",'Registo da Rotação'!J156="Ainda não avaliado",'Registo da Rotação'!K156="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S98" s="8">
-        <f>IF('Registo da Rotação'!A147="",0,IF(AND('Registo da Rotação'!G147=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147),'Registo da Rotação'!$G$54:'Registo da Rotação'!G146),""),'Registo da Rotação'!H147=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147),'Registo da Rotação'!$H$54:'Registo da Rotação'!H146),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A156="",0,IF(AND('Registo da Rotação'!G156=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F155='Registo da Rotação'!F156),'Registo da Rotação'!$G$54:'Registo da Rotação'!G155),""),'Registo da Rotação'!H156=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F155='Registo da Rotação'!F156),'Registo da Rotação'!$H$54:'Registo da Rotação'!H155),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T98" s="8">
-        <f>IF('Registo da Rotação'!A147="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Registo da Rotação'!G147)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Registo da Rotação'!H147)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F147,'Listas de apoio'!$A$5='Registo da Rotação'!G147,'Listas de apoio'!$A$5='Registo da Rotação'!H147),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Registo da Rotação'!G147)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Registo da Rotação'!H147)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F147,'Listas de apoio'!$A$6='Registo da Rotação'!G147,'Listas de apoio'!$A$6='Registo da Rotação'!H147),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Registo da Rotação'!G147)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Registo da Rotação'!H147)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F147,'Listas de apoio'!$A$7='Registo da Rotação'!G147,'Listas de apoio'!$A$7='Registo da Rotação'!H147),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Registo da Rotação'!G147)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Registo da Rotação'!H147)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F147,'Listas de apoio'!$A$8='Registo da Rotação'!G147,'Listas de apoio'!$A$8='Registo da Rotação'!H147),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F146='Registo da Rotação'!F147)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Registo da Rotação'!G147)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Registo da Rotação'!H147)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F146)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G146='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H146='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A156="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F155='Registo da Rotação'!F156)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G155='Registo da Rotação'!G156)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H155='Registo da Rotação'!H156)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F155)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F156,'Listas de apoio'!$A$5='Registo da Rotação'!G156,'Listas de apoio'!$A$5='Registo da Rotação'!H156),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F155='Registo da Rotação'!F156),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F155)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F155='Registo da Rotação'!F156)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G155='Registo da Rotação'!G156)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H155='Registo da Rotação'!H156)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F155)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G155='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H155='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F156,'Listas de apoio'!$A$6='Registo da Rotação'!G156,'Listas de apoio'!$A$6='Registo da Rotação'!H156),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F155='Registo da Rotação'!F156),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F155)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F155='Registo da Rotação'!F156)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G155='Registo da Rotação'!G156)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H155='Registo da Rotação'!H156)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F155)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G155='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H155='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F156,'Listas de apoio'!$A$7='Registo da Rotação'!G156,'Listas de apoio'!$A$7='Registo da Rotação'!H156),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F155='Registo da Rotação'!F156),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F155)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F155='Registo da Rotação'!F156)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G155='Registo da Rotação'!G156)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H155='Registo da Rotação'!H156)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F155)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G155='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H155='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F156,'Listas de apoio'!$A$8='Registo da Rotação'!G156,'Listas de apoio'!$A$8='Registo da Rotação'!H156),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F155='Registo da Rotação'!F156),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F155)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F155='Registo da Rotação'!F156)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G155='Registo da Rotação'!G156)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H155='Registo da Rotação'!H156)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F155)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G155='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H155='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U98" s="8">
-        <f>IF('Registo da Rotação'!A147="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A147)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C147,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D147)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A156="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A156)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C156,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D156)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V98" s="1"/>
@@ -15478,31 +15938,31 @@
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
       <c r="O99" s="8">
-        <f>IF('Registo da Rotação'!A148="",0,IF(COUNTA('Registo da Rotação'!B148:K148)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A157="",0,IF(COUNTA('Registo da Rotação'!B157:K157)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P99" s="8">
-        <f>IF('Registo da Rotação'!A148="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C148)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A157="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C157)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q99" s="8">
-        <f>IF('Registo da Rotação'!A148="",0,IF(OR('Registo da Rotação'!F148='Registo da Rotação'!G148,'Registo da Rotação'!F148='Registo da Rotação'!H148,'Registo da Rotação'!G148='Registo da Rotação'!H148),1,0))</f>
+        <f>IF('Registo da Rotação'!A157="",0,IF(OR('Registo da Rotação'!F157='Registo da Rotação'!G157,'Registo da Rotação'!F157='Registo da Rotação'!H157,'Registo da Rotação'!G157='Registo da Rotação'!H157),1,0))</f>
         <v>0</v>
       </c>
       <c r="R99" s="8">
-        <f>IF('Registo da Rotação'!A148="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C148,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I148="Ainda não avaliado",'Registo da Rotação'!J148="Ainda não avaliado",'Registo da Rotação'!K148="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A157="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C157,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I157="Ainda não avaliado",'Registo da Rotação'!J157="Ainda não avaliado",'Registo da Rotação'!K157="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S99" s="8">
-        <f>IF('Registo da Rotação'!A148="",0,IF(AND('Registo da Rotação'!G148=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148),'Registo da Rotação'!$G$54:'Registo da Rotação'!G147),""),'Registo da Rotação'!H148=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148),'Registo da Rotação'!$H$54:'Registo da Rotação'!H147),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A157="",0,IF(AND('Registo da Rotação'!G157=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F156='Registo da Rotação'!F157),'Registo da Rotação'!$G$54:'Registo da Rotação'!G156),""),'Registo da Rotação'!H157=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F156='Registo da Rotação'!F157),'Registo da Rotação'!$H$54:'Registo da Rotação'!H156),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T99" s="8">
-        <f>IF('Registo da Rotação'!A148="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Registo da Rotação'!G148)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Registo da Rotação'!H148)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F148,'Listas de apoio'!$A$5='Registo da Rotação'!G148,'Listas de apoio'!$A$5='Registo da Rotação'!H148),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Registo da Rotação'!G148)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Registo da Rotação'!H148)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F148,'Listas de apoio'!$A$6='Registo da Rotação'!G148,'Listas de apoio'!$A$6='Registo da Rotação'!H148),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Registo da Rotação'!G148)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Registo da Rotação'!H148)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F148,'Listas de apoio'!$A$7='Registo da Rotação'!G148,'Listas de apoio'!$A$7='Registo da Rotação'!H148),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Registo da Rotação'!G148)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Registo da Rotação'!H148)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F148,'Listas de apoio'!$A$8='Registo da Rotação'!G148,'Listas de apoio'!$A$8='Registo da Rotação'!H148),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F147='Registo da Rotação'!F148)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Registo da Rotação'!G148)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Registo da Rotação'!H148)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F147)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G147='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H147='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A157="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F156='Registo da Rotação'!F157)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G156='Registo da Rotação'!G157)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H156='Registo da Rotação'!H157)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F156)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F157,'Listas de apoio'!$A$5='Registo da Rotação'!G157,'Listas de apoio'!$A$5='Registo da Rotação'!H157),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F156='Registo da Rotação'!F157),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F156)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F156='Registo da Rotação'!F157)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G156='Registo da Rotação'!G157)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H156='Registo da Rotação'!H157)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F156)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G156='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H156='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F157,'Listas de apoio'!$A$6='Registo da Rotação'!G157,'Listas de apoio'!$A$6='Registo da Rotação'!H157),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F156='Registo da Rotação'!F157),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F156)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F156='Registo da Rotação'!F157)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G156='Registo da Rotação'!G157)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H156='Registo da Rotação'!H157)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F156)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G156='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H156='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F157,'Listas de apoio'!$A$7='Registo da Rotação'!G157,'Listas de apoio'!$A$7='Registo da Rotação'!H157),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F156='Registo da Rotação'!F157),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F156)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F156='Registo da Rotação'!F157)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G156='Registo da Rotação'!G157)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H156='Registo da Rotação'!H157)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F156)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G156='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H156='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F157,'Listas de apoio'!$A$8='Registo da Rotação'!G157,'Listas de apoio'!$A$8='Registo da Rotação'!H157),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F156='Registo da Rotação'!F157),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F156)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F156='Registo da Rotação'!F157)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G156='Registo da Rotação'!G157)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H156='Registo da Rotação'!H157)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F156)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G156='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H156='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U99" s="8">
-        <f>IF('Registo da Rotação'!A148="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A148)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C148,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D148)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A157="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A157)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C157,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D157)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V99" s="1"/>
@@ -15535,31 +15995,31 @@
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
       <c r="O100" s="8">
-        <f>IF('Registo da Rotação'!A149="",0,IF(COUNTA('Registo da Rotação'!B149:K149)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A158="",0,IF(COUNTA('Registo da Rotação'!B158:K158)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P100" s="8">
-        <f>IF('Registo da Rotação'!A149="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C149)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A158="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C158)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q100" s="8">
-        <f>IF('Registo da Rotação'!A149="",0,IF(OR('Registo da Rotação'!F149='Registo da Rotação'!G149,'Registo da Rotação'!F149='Registo da Rotação'!H149,'Registo da Rotação'!G149='Registo da Rotação'!H149),1,0))</f>
+        <f>IF('Registo da Rotação'!A158="",0,IF(OR('Registo da Rotação'!F158='Registo da Rotação'!G158,'Registo da Rotação'!F158='Registo da Rotação'!H158,'Registo da Rotação'!G158='Registo da Rotação'!H158),1,0))</f>
         <v>0</v>
       </c>
       <c r="R100" s="8">
-        <f>IF('Registo da Rotação'!A149="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C149,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I149="Ainda não avaliado",'Registo da Rotação'!J149="Ainda não avaliado",'Registo da Rotação'!K149="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A158="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C158,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I158="Ainda não avaliado",'Registo da Rotação'!J158="Ainda não avaliado",'Registo da Rotação'!K158="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S100" s="8">
-        <f>IF('Registo da Rotação'!A149="",0,IF(AND('Registo da Rotação'!G149=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149),'Registo da Rotação'!$G$54:'Registo da Rotação'!G148),""),'Registo da Rotação'!H149=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149),'Registo da Rotação'!$H$54:'Registo da Rotação'!H148),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A158="",0,IF(AND('Registo da Rotação'!G158=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F157='Registo da Rotação'!F158),'Registo da Rotação'!$G$54:'Registo da Rotação'!G157),""),'Registo da Rotação'!H158=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F157='Registo da Rotação'!F158),'Registo da Rotação'!$H$54:'Registo da Rotação'!H157),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T100" s="8">
-        <f>IF('Registo da Rotação'!A149="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Registo da Rotação'!G149)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Registo da Rotação'!H149)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F149,'Listas de apoio'!$A$5='Registo da Rotação'!G149,'Listas de apoio'!$A$5='Registo da Rotação'!H149),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Registo da Rotação'!G149)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Registo da Rotação'!H149)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F149,'Listas de apoio'!$A$6='Registo da Rotação'!G149,'Listas de apoio'!$A$6='Registo da Rotação'!H149),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Registo da Rotação'!G149)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Registo da Rotação'!H149)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F149,'Listas de apoio'!$A$7='Registo da Rotação'!G149,'Listas de apoio'!$A$7='Registo da Rotação'!H149),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Registo da Rotação'!G149)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Registo da Rotação'!H149)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F149,'Listas de apoio'!$A$8='Registo da Rotação'!G149,'Listas de apoio'!$A$8='Registo da Rotação'!H149),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F148='Registo da Rotação'!F149)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Registo da Rotação'!G149)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Registo da Rotação'!H149)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F148)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G148='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H148='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A158="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F157='Registo da Rotação'!F158)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G157='Registo da Rotação'!G158)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H157='Registo da Rotação'!H158)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F157)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F158,'Listas de apoio'!$A$5='Registo da Rotação'!G158,'Listas de apoio'!$A$5='Registo da Rotação'!H158),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F157='Registo da Rotação'!F158),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F157)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F157='Registo da Rotação'!F158)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G157='Registo da Rotação'!G158)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H157='Registo da Rotação'!H158)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F157)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G157='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H157='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F158,'Listas de apoio'!$A$6='Registo da Rotação'!G158,'Listas de apoio'!$A$6='Registo da Rotação'!H158),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F157='Registo da Rotação'!F158),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F157)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F157='Registo da Rotação'!F158)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G157='Registo da Rotação'!G158)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H157='Registo da Rotação'!H158)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F157)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G157='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H157='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F158,'Listas de apoio'!$A$7='Registo da Rotação'!G158,'Listas de apoio'!$A$7='Registo da Rotação'!H158),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F157='Registo da Rotação'!F158),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F157)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F157='Registo da Rotação'!F158)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G157='Registo da Rotação'!G158)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H157='Registo da Rotação'!H158)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F157)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G157='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H157='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F158,'Listas de apoio'!$A$8='Registo da Rotação'!G158,'Listas de apoio'!$A$8='Registo da Rotação'!H158),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F157='Registo da Rotação'!F158),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F157)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F157='Registo da Rotação'!F158)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G157='Registo da Rotação'!G158)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H157='Registo da Rotação'!H158)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F157)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G157='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H157='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U100" s="8">
-        <f>IF('Registo da Rotação'!A149="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A149)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C149,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D149)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A158="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A158)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C158,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D158)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V100" s="1"/>
@@ -15592,31 +16052,31 @@
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
       <c r="O101" s="8">
-        <f>IF('Registo da Rotação'!A150="",0,IF(COUNTA('Registo da Rotação'!B150:K150)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A159="",0,IF(COUNTA('Registo da Rotação'!B159:K159)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P101" s="8">
-        <f>IF('Registo da Rotação'!A150="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C150)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A159="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C159)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q101" s="8">
-        <f>IF('Registo da Rotação'!A150="",0,IF(OR('Registo da Rotação'!F150='Registo da Rotação'!G150,'Registo da Rotação'!F150='Registo da Rotação'!H150,'Registo da Rotação'!G150='Registo da Rotação'!H150),1,0))</f>
+        <f>IF('Registo da Rotação'!A159="",0,IF(OR('Registo da Rotação'!F159='Registo da Rotação'!G159,'Registo da Rotação'!F159='Registo da Rotação'!H159,'Registo da Rotação'!G159='Registo da Rotação'!H159),1,0))</f>
         <v>0</v>
       </c>
       <c r="R101" s="8">
-        <f>IF('Registo da Rotação'!A150="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C150,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I150="Ainda não avaliado",'Registo da Rotação'!J150="Ainda não avaliado",'Registo da Rotação'!K150="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A159="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C159,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I159="Ainda não avaliado",'Registo da Rotação'!J159="Ainda não avaliado",'Registo da Rotação'!K159="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S101" s="8">
-        <f>IF('Registo da Rotação'!A150="",0,IF(AND('Registo da Rotação'!G150=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150),'Registo da Rotação'!$G$54:'Registo da Rotação'!G149),""),'Registo da Rotação'!H150=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150),'Registo da Rotação'!$H$54:'Registo da Rotação'!H149),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A159="",0,IF(AND('Registo da Rotação'!G159=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F158='Registo da Rotação'!F159),'Registo da Rotação'!$G$54:'Registo da Rotação'!G158),""),'Registo da Rotação'!H159=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F158='Registo da Rotação'!F159),'Registo da Rotação'!$H$54:'Registo da Rotação'!H158),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T101" s="8">
-        <f>IF('Registo da Rotação'!A150="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Registo da Rotação'!G150)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Registo da Rotação'!H150)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F150,'Listas de apoio'!$A$5='Registo da Rotação'!G150,'Listas de apoio'!$A$5='Registo da Rotação'!H150),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Registo da Rotação'!G150)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Registo da Rotação'!H150)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F150,'Listas de apoio'!$A$6='Registo da Rotação'!G150,'Listas de apoio'!$A$6='Registo da Rotação'!H150),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Registo da Rotação'!G150)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Registo da Rotação'!H150)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F150,'Listas de apoio'!$A$7='Registo da Rotação'!G150,'Listas de apoio'!$A$7='Registo da Rotação'!H150),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Registo da Rotação'!G150)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Registo da Rotação'!H150)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F150,'Listas de apoio'!$A$8='Registo da Rotação'!G150,'Listas de apoio'!$A$8='Registo da Rotação'!H150),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F149='Registo da Rotação'!F150)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Registo da Rotação'!G150)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Registo da Rotação'!H150)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F149)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G149='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H149='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A159="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F158='Registo da Rotação'!F159)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G158='Registo da Rotação'!G159)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H158='Registo da Rotação'!H159)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F158)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F159,'Listas de apoio'!$A$5='Registo da Rotação'!G159,'Listas de apoio'!$A$5='Registo da Rotação'!H159),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F158='Registo da Rotação'!F159),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F158)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F158='Registo da Rotação'!F159)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G158='Registo da Rotação'!G159)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H158='Registo da Rotação'!H159)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F158)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G158='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H158='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F159,'Listas de apoio'!$A$6='Registo da Rotação'!G159,'Listas de apoio'!$A$6='Registo da Rotação'!H159),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F158='Registo da Rotação'!F159),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F158)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F158='Registo da Rotação'!F159)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G158='Registo da Rotação'!G159)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H158='Registo da Rotação'!H159)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F158)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G158='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H158='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F159,'Listas de apoio'!$A$7='Registo da Rotação'!G159,'Listas de apoio'!$A$7='Registo da Rotação'!H159),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F158='Registo da Rotação'!F159),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F158)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F158='Registo da Rotação'!F159)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G158='Registo da Rotação'!G159)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H158='Registo da Rotação'!H159)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F158)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G158='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H158='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F159,'Listas de apoio'!$A$8='Registo da Rotação'!G159,'Listas de apoio'!$A$8='Registo da Rotação'!H159),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F158='Registo da Rotação'!F159),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F158)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F158='Registo da Rotação'!F159)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G158='Registo da Rotação'!G159)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H158='Registo da Rotação'!H159)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F158)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G158='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H158='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U101" s="8">
-        <f>IF('Registo da Rotação'!A150="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A150)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C150,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D150)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A159="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A159)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C159,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D159)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V101" s="1"/>
@@ -15649,31 +16109,31 @@
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
       <c r="O102" s="8">
-        <f>IF('Registo da Rotação'!A151="",0,IF(COUNTA('Registo da Rotação'!B151:K151)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A160="",0,IF(COUNTA('Registo da Rotação'!B160:K160)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P102" s="8">
-        <f>IF('Registo da Rotação'!A151="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C151)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A160="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C160)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q102" s="8">
-        <f>IF('Registo da Rotação'!A151="",0,IF(OR('Registo da Rotação'!F151='Registo da Rotação'!G151,'Registo da Rotação'!F151='Registo da Rotação'!H151,'Registo da Rotação'!G151='Registo da Rotação'!H151),1,0))</f>
+        <f>IF('Registo da Rotação'!A160="",0,IF(OR('Registo da Rotação'!F160='Registo da Rotação'!G160,'Registo da Rotação'!F160='Registo da Rotação'!H160,'Registo da Rotação'!G160='Registo da Rotação'!H160),1,0))</f>
         <v>0</v>
       </c>
       <c r="R102" s="8">
-        <f>IF('Registo da Rotação'!A151="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C151,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I151="Ainda não avaliado",'Registo da Rotação'!J151="Ainda não avaliado",'Registo da Rotação'!K151="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A160="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C160,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I160="Ainda não avaliado",'Registo da Rotação'!J160="Ainda não avaliado",'Registo da Rotação'!K160="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S102" s="8">
-        <f>IF('Registo da Rotação'!A151="",0,IF(AND('Registo da Rotação'!G151=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151),'Registo da Rotação'!$G$54:'Registo da Rotação'!G150),""),'Registo da Rotação'!H151=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151),'Registo da Rotação'!$H$54:'Registo da Rotação'!H150),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A160="",0,IF(AND('Registo da Rotação'!G160=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F159='Registo da Rotação'!F160),'Registo da Rotação'!$G$54:'Registo da Rotação'!G159),""),'Registo da Rotação'!H160=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F159='Registo da Rotação'!F160),'Registo da Rotação'!$H$54:'Registo da Rotação'!H159),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T102" s="8">
-        <f>IF('Registo da Rotação'!A151="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Registo da Rotação'!G151)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Registo da Rotação'!H151)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F151,'Listas de apoio'!$A$5='Registo da Rotação'!G151,'Listas de apoio'!$A$5='Registo da Rotação'!H151),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Registo da Rotação'!G151)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Registo da Rotação'!H151)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F151,'Listas de apoio'!$A$6='Registo da Rotação'!G151,'Listas de apoio'!$A$6='Registo da Rotação'!H151),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Registo da Rotação'!G151)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Registo da Rotação'!H151)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F151,'Listas de apoio'!$A$7='Registo da Rotação'!G151,'Listas de apoio'!$A$7='Registo da Rotação'!H151),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Registo da Rotação'!G151)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Registo da Rotação'!H151)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F151,'Listas de apoio'!$A$8='Registo da Rotação'!G151,'Listas de apoio'!$A$8='Registo da Rotação'!H151),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F150='Registo da Rotação'!F151)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Registo da Rotação'!G151)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Registo da Rotação'!H151)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F150)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G150='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H150='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A160="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F159='Registo da Rotação'!F160)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G159='Registo da Rotação'!G160)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H159='Registo da Rotação'!H160)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F159)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F160,'Listas de apoio'!$A$5='Registo da Rotação'!G160,'Listas de apoio'!$A$5='Registo da Rotação'!H160),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F159='Registo da Rotação'!F160),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F159)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F159='Registo da Rotação'!F160)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G159='Registo da Rotação'!G160)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H159='Registo da Rotação'!H160)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F159)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G159='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H159='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F160,'Listas de apoio'!$A$6='Registo da Rotação'!G160,'Listas de apoio'!$A$6='Registo da Rotação'!H160),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F159='Registo da Rotação'!F160),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F159)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F159='Registo da Rotação'!F160)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G159='Registo da Rotação'!G160)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H159='Registo da Rotação'!H160)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F159)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G159='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H159='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F160,'Listas de apoio'!$A$7='Registo da Rotação'!G160,'Listas de apoio'!$A$7='Registo da Rotação'!H160),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F159='Registo da Rotação'!F160),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F159)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F159='Registo da Rotação'!F160)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G159='Registo da Rotação'!G160)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H159='Registo da Rotação'!H160)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F159)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G159='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H159='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F160,'Listas de apoio'!$A$8='Registo da Rotação'!G160,'Listas de apoio'!$A$8='Registo da Rotação'!H160),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F159='Registo da Rotação'!F160),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F159)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F159='Registo da Rotação'!F160)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G159='Registo da Rotação'!G160)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H159='Registo da Rotação'!H160)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F159)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G159='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H159='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U102" s="8">
-        <f>IF('Registo da Rotação'!A151="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A151)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C151,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D151)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A160="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A160)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C160,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D160)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V102" s="1"/>
@@ -15706,31 +16166,31 @@
       <c r="M103" s="1"/>
       <c r="N103" s="1"/>
       <c r="O103" s="8">
-        <f>IF('Registo da Rotação'!A152="",0,IF(COUNTA('Registo da Rotação'!B152:K152)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A161="",0,IF(COUNTA('Registo da Rotação'!B161:K161)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P103" s="8">
-        <f>IF('Registo da Rotação'!A152="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C152)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A161="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C161)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q103" s="8">
-        <f>IF('Registo da Rotação'!A152="",0,IF(OR('Registo da Rotação'!F152='Registo da Rotação'!G152,'Registo da Rotação'!F152='Registo da Rotação'!H152,'Registo da Rotação'!G152='Registo da Rotação'!H152),1,0))</f>
+        <f>IF('Registo da Rotação'!A161="",0,IF(OR('Registo da Rotação'!F161='Registo da Rotação'!G161,'Registo da Rotação'!F161='Registo da Rotação'!H161,'Registo da Rotação'!G161='Registo da Rotação'!H161),1,0))</f>
         <v>0</v>
       </c>
       <c r="R103" s="8">
-        <f>IF('Registo da Rotação'!A152="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C152,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I152="Ainda não avaliado",'Registo da Rotação'!J152="Ainda não avaliado",'Registo da Rotação'!K152="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A161="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C161,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I161="Ainda não avaliado",'Registo da Rotação'!J161="Ainda não avaliado",'Registo da Rotação'!K161="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S103" s="8">
-        <f>IF('Registo da Rotação'!A152="",0,IF(AND('Registo da Rotação'!G152=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152),'Registo da Rotação'!$G$54:'Registo da Rotação'!G151),""),'Registo da Rotação'!H152=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152),'Registo da Rotação'!$H$54:'Registo da Rotação'!H151),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A161="",0,IF(AND('Registo da Rotação'!G161=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F160='Registo da Rotação'!F161),'Registo da Rotação'!$G$54:'Registo da Rotação'!G160),""),'Registo da Rotação'!H161=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F160='Registo da Rotação'!F161),'Registo da Rotação'!$H$54:'Registo da Rotação'!H160),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T103" s="8">
-        <f>IF('Registo da Rotação'!A152="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Registo da Rotação'!G152)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Registo da Rotação'!H152)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F152,'Listas de apoio'!$A$5='Registo da Rotação'!G152,'Listas de apoio'!$A$5='Registo da Rotação'!H152),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Registo da Rotação'!G152)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Registo da Rotação'!H152)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F152,'Listas de apoio'!$A$6='Registo da Rotação'!G152,'Listas de apoio'!$A$6='Registo da Rotação'!H152),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Registo da Rotação'!G152)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Registo da Rotação'!H152)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F152,'Listas de apoio'!$A$7='Registo da Rotação'!G152,'Listas de apoio'!$A$7='Registo da Rotação'!H152),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Registo da Rotação'!G152)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Registo da Rotação'!H152)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F152,'Listas de apoio'!$A$8='Registo da Rotação'!G152,'Listas de apoio'!$A$8='Registo da Rotação'!H152),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F151='Registo da Rotação'!F152)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Registo da Rotação'!G152)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Registo da Rotação'!H152)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F151)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G151='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H151='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A161="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F160='Registo da Rotação'!F161)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G160='Registo da Rotação'!G161)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H160='Registo da Rotação'!H161)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F160)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F161,'Listas de apoio'!$A$5='Registo da Rotação'!G161,'Listas de apoio'!$A$5='Registo da Rotação'!H161),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F160='Registo da Rotação'!F161),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F160)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F160='Registo da Rotação'!F161)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G160='Registo da Rotação'!G161)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H160='Registo da Rotação'!H161)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F160)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G160='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H160='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F161,'Listas de apoio'!$A$6='Registo da Rotação'!G161,'Listas de apoio'!$A$6='Registo da Rotação'!H161),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F160='Registo da Rotação'!F161),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F160)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F160='Registo da Rotação'!F161)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G160='Registo da Rotação'!G161)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H160='Registo da Rotação'!H161)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F160)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G160='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H160='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F161,'Listas de apoio'!$A$7='Registo da Rotação'!G161,'Listas de apoio'!$A$7='Registo da Rotação'!H161),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F160='Registo da Rotação'!F161),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F160)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F160='Registo da Rotação'!F161)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G160='Registo da Rotação'!G161)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H160='Registo da Rotação'!H161)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F160)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G160='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H160='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F161,'Listas de apoio'!$A$8='Registo da Rotação'!G161,'Listas de apoio'!$A$8='Registo da Rotação'!H161),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F160='Registo da Rotação'!F161),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F160)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F160='Registo da Rotação'!F161)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G160='Registo da Rotação'!G161)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H160='Registo da Rotação'!H161)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F160)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G160='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H160='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U103" s="8">
-        <f>IF('Registo da Rotação'!A152="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A152)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C152,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D152)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A161="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A161)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C161,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D161)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V103" s="1"/>
@@ -15763,31 +16223,31 @@
       <c r="M104" s="1"/>
       <c r="N104" s="1"/>
       <c r="O104" s="8">
-        <f>IF('Registo da Rotação'!A153="",0,IF(COUNTA('Registo da Rotação'!B153:K153)&lt;10,1,0))</f>
+        <f>IF('Registo da Rotação'!A162="",0,IF(COUNTA('Registo da Rotação'!B162:K162)&lt;10,1,0))</f>
         <v>0</v>
       </c>
       <c r="P104" s="8">
-        <f>IF('Registo da Rotação'!A153="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C153)=0,1,0))</f>
+        <f>IF('Registo da Rotação'!A162="",0,IF(COUNTIF('Registo da Rotação'!$C$6:$C$25,'Registo da Rotação'!C162)=0,1,0))</f>
         <v>0</v>
       </c>
       <c r="Q104" s="8">
-        <f>IF('Registo da Rotação'!A153="",0,IF(OR('Registo da Rotação'!F153='Registo da Rotação'!G153,'Registo da Rotação'!F153='Registo da Rotação'!H153,'Registo da Rotação'!G153='Registo da Rotação'!H153),1,0))</f>
+        <f>IF('Registo da Rotação'!A162="",0,IF(OR('Registo da Rotação'!F162='Registo da Rotação'!G162,'Registo da Rotação'!F162='Registo da Rotação'!H162,'Registo da Rotação'!G162='Registo da Rotação'!H162),1,0))</f>
         <v>0</v>
       </c>
       <c r="R104" s="8">
-        <f>IF('Registo da Rotação'!A153="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C153,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I153="Ainda não avaliado",'Registo da Rotação'!J153="Ainda não avaliado",'Registo da Rotação'!K153="Ainda não avaliado")),1,0))</f>
+        <f>IF('Registo da Rotação'!A162="",0,IF(AND(IFERROR(VLOOKUP('Registo da Rotação'!C162,'Registo da Rotação'!$C$6:$D$25,2,FALSE),"")="Concluído",OR('Registo da Rotação'!I162="Ainda não avaliado",'Registo da Rotação'!J162="Ainda não avaliado",'Registo da Rotação'!K162="Ainda não avaliado")),1,0))</f>
         <v>0</v>
       </c>
       <c r="S104" s="8">
-        <f>IF('Registo da Rotação'!A153="",0,IF(AND('Registo da Rotação'!G153=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153),'Registo da Rotação'!$G$54:'Registo da Rotação'!G152),""),'Registo da Rotação'!H153=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153),'Registo da Rotação'!$H$54:'Registo da Rotação'!H152),"")),1,0))</f>
+        <f>IF('Registo da Rotação'!A162="",0,IF(AND('Registo da Rotação'!G162=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F161='Registo da Rotação'!F162),'Registo da Rotação'!$G$54:'Registo da Rotação'!G161),""),'Registo da Rotação'!H162=IFERROR(LOOKUP(2,1/('Registo da Rotação'!$F$54:'Registo da Rotação'!F161='Registo da Rotação'!F162),'Registo da Rotação'!$H$54:'Registo da Rotação'!H161),"")),1,0))</f>
         <v>0</v>
       </c>
       <c r="T104" s="8">
-        <f>IF('Registo da Rotação'!A153="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Registo da Rotação'!G153)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Registo da Rotação'!H153)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F153,'Listas de apoio'!$A$5='Registo da Rotação'!G153,'Listas de apoio'!$A$5='Registo da Rotação'!H153),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Registo da Rotação'!G153)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Registo da Rotação'!H153)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F153,'Listas de apoio'!$A$6='Registo da Rotação'!G153,'Listas de apoio'!$A$6='Registo da Rotação'!H153),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Registo da Rotação'!G153)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Registo da Rotação'!H153)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F153,'Listas de apoio'!$A$7='Registo da Rotação'!G153,'Listas de apoio'!$A$7='Registo da Rotação'!H153),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Registo da Rotação'!G153)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Registo da Rotação'!H153)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F153,'Listas de apoio'!$A$8='Registo da Rotação'!G153,'Listas de apoio'!$A$8='Registo da Rotação'!H153),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F152='Registo da Rotação'!F153)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Registo da Rotação'!G153)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Registo da Rotação'!H153)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F152)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G152='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H152='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
+        <f>IF('Registo da Rotação'!A162="",0,IF(IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F161='Registo da Rotação'!F162)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G161='Registo da Rotação'!G162)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H161='Registo da Rotação'!H162)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F161)),0)=0,0,IF(OR('Listas de apoio'!$A$5="",'Listas de apoio'!$A$5='Registo da Rotação'!F162,'Listas de apoio'!$A$5='Registo da Rotação'!G162,'Listas de apoio'!$A$5='Registo da Rotação'!H162),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F161='Registo da Rotação'!F162),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F161)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F161='Registo da Rotação'!F162)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G161='Registo da Rotação'!G162)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H161='Registo da Rotação'!H162)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F161)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G161='Listas de apoio'!$A$5)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H161='Listas de apoio'!$A$5))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$6="",'Listas de apoio'!$A$6='Registo da Rotação'!F162,'Listas de apoio'!$A$6='Registo da Rotação'!G162,'Listas de apoio'!$A$6='Registo da Rotação'!H162),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F161='Registo da Rotação'!F162),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F161)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F161='Registo da Rotação'!F162)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G161='Registo da Rotação'!G162)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H161='Registo da Rotação'!H162)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F161)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G161='Listas de apoio'!$A$6)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H161='Listas de apoio'!$A$6))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$7="",'Listas de apoio'!$A$7='Registo da Rotação'!F162,'Listas de apoio'!$A$7='Registo da Rotação'!G162,'Listas de apoio'!$A$7='Registo da Rotação'!H162),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F161='Registo da Rotação'!F162),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F161)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F161='Registo da Rotação'!F162)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G161='Registo da Rotação'!G162)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H161='Registo da Rotação'!H162)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F161)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G161='Listas de apoio'!$A$7)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H161='Listas de apoio'!$A$7))&gt;0))&gt;0,0,1))+IF(OR('Listas de apoio'!$A$8="",'Listas de apoio'!$A$8='Registo da Rotação'!F162,'Listas de apoio'!$A$8='Registo da Rotação'!G162,'Listas de apoio'!$A$8='Registo da Rotação'!H162),0,IF(SUMPRODUCT(--('Registo da Rotação'!$F$54:'Registo da Rotação'!F161='Registo da Rotação'!F162),--(ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F161)&gt;IFERROR(LOOKUP(2,1/(('Registo da Rotação'!$F$54:'Registo da Rotação'!F161='Registo da Rotação'!F162)*('Registo da Rotação'!$G$54:'Registo da Rotação'!G161='Registo da Rotação'!G162)*('Registo da Rotação'!$H$54:'Registo da Rotação'!H161='Registo da Rotação'!H162)),ROW('Registo da Rotação'!$F$54:'Registo da Rotação'!F161)),0)),--((('Registo da Rotação'!$G$54:'Registo da Rotação'!G161='Listas de apoio'!$A$8)+('Registo da Rotação'!$H$54:'Registo da Rotação'!H161='Listas de apoio'!$A$8))&gt;0))&gt;0,0,1))))</f>
         <v>0</v>
       </c>
       <c r="U104" s="8">
-        <f>IF('Registo da Rotação'!A153="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$153,'Registo da Rotação'!A153)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$153,'Registo da Rotação'!C153,'Registo da Rotação'!$D$54:$D$153,'Registo da Rotação'!D153)&gt;1),1,0))</f>
+        <f>IF('Registo da Rotação'!A162="",0,IF(OR(COUNTIF('Registo da Rotação'!$A$54:$A$162,'Registo da Rotação'!A162)&gt;1,COUNTIFS('Registo da Rotação'!$C$54:$C$162,'Registo da Rotação'!C162,'Registo da Rotação'!$D$54:$D$162,'Registo da Rotação'!D162)&gt;1),1,0))</f>
         <v>0</v>
       </c>
       <c r="V104" s="1"/>
